--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFE3B84-36E0-4899-8D05-D95A00FB59FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E007CA9D-0DAC-4F89-93D0-A0D1C6A6975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="248">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Gleicy Ferreira Gomes</t>
   </si>
   <si>
-    <t>PENDÊNCIA DOC</t>
-  </si>
-  <si>
     <t>Jamily de Lima Alves dos Santos</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>Carla Cristina de Lima Kauffmann</t>
   </si>
   <si>
-    <t>Lavinia Guimaraes Bueno</t>
-  </si>
-  <si>
     <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
   </si>
   <si>
@@ -149,12 +143,6 @@
     <t>DS FOOD &amp; BEVARAGE LTDA</t>
   </si>
   <si>
-    <t>33708448000113</t>
-  </si>
-  <si>
-    <t>ASSOCIACAO DESPORTIVA ATHLETIC MERITI</t>
-  </si>
-  <si>
     <t>30174204000100</t>
   </si>
   <si>
@@ -200,9 +188,6 @@
     <t>CENTRO RECREATIVO ESP UNIAO AMIGOS DE VILA PROSPERIDADE</t>
   </si>
   <si>
-    <t>Procuracao da empresa . Identificamos que a representacao da sua empresa e realizada em conjunto com o tesoureiro  nomeado na clausula de administracao do contrato social e, por esse motivo, e necessario que os demais representantes tambem assinem a procuracao.&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
-  </si>
-  <si>
     <t>47294711000180</t>
   </si>
   <si>
@@ -753,6 +738,51 @@
   </si>
   <si>
     <t>42.906.995 JULIANE CRISTINA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Ainda nao iniciou a abertura de conta</t>
+  </si>
+  <si>
+    <t>CARIMBADA</t>
+  </si>
+  <si>
+    <t>57779508000157</t>
+  </si>
+  <si>
+    <t>P V DE LIMA PEREIRA  LTDA</t>
+  </si>
+  <si>
+    <t>46974898000108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GISELE SERAFIM </t>
+  </si>
+  <si>
+    <t>21669892000198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAYANA DABADIA GOMES </t>
+  </si>
+  <si>
+    <t>65984009000120</t>
+  </si>
+  <si>
+    <t>BB GESTAO E ASSESSORIA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>BACKOFFICE</t>
+  </si>
+  <si>
+    <t>63993426000103</t>
+  </si>
+  <si>
+    <t>MANAH ALIMENTACAO E CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>18669738000101</t>
+  </si>
+  <si>
+    <t>RO AMARO DECORACOES LTDA</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1153,7 +1183,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1170,25 +1200,25 @@
         <v>46113</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1196,22 +1226,22 @@
         <v>46113</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1222,19 +1252,19 @@
         <v>46113</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1248,19 +1278,19 @@
         <v>46113</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -1274,19 +1304,19 @@
         <v>46113</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
@@ -1300,16 +1330,16 @@
         <v>46113</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1326,25 +1356,25 @@
         <v>46113</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="H8">
-        <v>0</v>
+      <c r="H8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1352,25 +1382,25 @@
         <v>46113</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1378,25 +1408,25 @@
         <v>46113</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1404,16 +1434,16 @@
         <v>46113</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -1430,16 +1460,16 @@
         <v>46113</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -1456,16 +1486,16 @@
         <v>46113</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -1482,19 +1512,19 @@
         <v>46113</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
@@ -1508,19 +1538,19 @@
         <v>46113</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -1534,19 +1564,19 @@
         <v>46113</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
@@ -1560,16 +1590,16 @@
         <v>46113</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -1586,22 +1616,22 @@
         <v>46113</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1612,22 +1642,22 @@
         <v>46113</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1638,22 +1668,22 @@
         <v>46113</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1664,22 +1694,22 @@
         <v>46113</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1690,22 +1720,22 @@
         <v>46113</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1716,22 +1746,22 @@
         <v>46113</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1742,22 +1772,22 @@
         <v>46113</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1768,16 +1798,16 @@
         <v>46113</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -1794,16 +1824,16 @@
         <v>46113</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -1820,16 +1850,16 @@
         <v>46113</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -1846,22 +1876,22 @@
         <v>46113</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1872,22 +1902,22 @@
         <v>46113</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1898,16 +1928,16 @@
         <v>46113</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -1924,22 +1954,22 @@
         <v>46113</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
         <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1950,22 +1980,22 @@
         <v>46113</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1976,19 +2006,19 @@
         <v>46113</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
@@ -2002,19 +2032,19 @@
         <v>46113</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
         <v>18</v>
@@ -2028,16 +2058,16 @@
         <v>46113</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -2054,22 +2084,22 @@
         <v>46113</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2080,22 +2110,22 @@
         <v>46113</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2106,22 +2136,22 @@
         <v>46113</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2129,22 +2159,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -2158,19 +2188,19 @@
         <v>46114</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G40" t="s">
         <v>18</v>
@@ -2184,19 +2214,19 @@
         <v>46114</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
         <v>18</v>
@@ -2210,22 +2240,25 @@
         <v>46114</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2233,22 +2266,25 @@
         <v>46114</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -2256,22 +2292,25 @@
         <v>46114</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2279,22 +2318,25 @@
         <v>46114</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2302,22 +2344,25 @@
         <v>46114</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F46" t="s">
         <v>8</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -2325,22 +2370,25 @@
         <v>46114</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -2348,16 +2396,16 @@
         <v>46114</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
@@ -2365,1178 +2413,1443 @@
       <c r="G48" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46114</v>
       </c>
       <c r="B49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" t="s">
+        <v>233</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
         <v>141</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>37</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B51" t="s">
         <v>142</v>
       </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="C51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" t="s">
+        <v>233</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" t="s">
         <v>41</v>
       </c>
-      <c r="F49" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B50" t="s">
-        <v>143</v>
-      </c>
-      <c r="C50" t="s">
-        <v>144</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="E55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B56" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" t="s">
+        <v>154</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" t="s">
+        <v>156</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
         <v>33</v>
-      </c>
-      <c r="E50" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" t="s">
-        <v>8</v>
-      </c>
-      <c r="G50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B51" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51" t="s">
-        <v>146</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" t="s">
-        <v>8</v>
-      </c>
-      <c r="G51" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B52" t="s">
-        <v>147</v>
-      </c>
-      <c r="C52" t="s">
-        <v>148</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s">
-        <v>41</v>
-      </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B53" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B54" t="s">
-        <v>149</v>
-      </c>
-      <c r="C54" t="s">
-        <v>150</v>
-      </c>
-      <c r="D54" t="s">
-        <v>16</v>
-      </c>
-      <c r="E54" t="s">
-        <v>41</v>
-      </c>
-      <c r="F54" t="s">
-        <v>8</v>
-      </c>
-      <c r="G54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B55" t="s">
-        <v>151</v>
-      </c>
-      <c r="C55" t="s">
-        <v>152</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s">
-        <v>41</v>
-      </c>
-      <c r="F55" t="s">
-        <v>8</v>
-      </c>
-      <c r="G55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B56" t="s">
-        <v>153</v>
-      </c>
-      <c r="C56" t="s">
-        <v>154</v>
-      </c>
-      <c r="D56" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" t="s">
-        <v>43</v>
-      </c>
-      <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B57" t="s">
-        <v>155</v>
-      </c>
-      <c r="C57" t="s">
-        <v>156</v>
-      </c>
-      <c r="D57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F57" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B58" t="s">
-        <v>157</v>
-      </c>
-      <c r="C58" t="s">
-        <v>158</v>
-      </c>
-      <c r="D58" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" t="s">
-        <v>159</v>
-      </c>
-      <c r="D59" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59" t="s">
-        <v>43</v>
-      </c>
-      <c r="F59" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B60" t="s">
-        <v>160</v>
-      </c>
-      <c r="C60" t="s">
-        <v>161</v>
-      </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F60" t="s">
-        <v>8</v>
-      </c>
-      <c r="G60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B61" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" t="s">
-        <v>163</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s">
-        <v>41</v>
-      </c>
-      <c r="F61" t="s">
-        <v>8</v>
-      </c>
-      <c r="G61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B62" t="s">
-        <v>164</v>
-      </c>
-      <c r="C62" t="s">
-        <v>165</v>
       </c>
       <c r="D62" t="s">
         <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
         <v>8</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46114</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="D63" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" t="s">
+        <v>39</v>
+      </c>
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>233</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B64" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" t="s">
         <v>23</v>
       </c>
-      <c r="E63" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" t="s">
-        <v>8</v>
-      </c>
-      <c r="G63" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="E64" t="s">
+        <v>37</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B65" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" t="s">
         <v>166</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B66" t="s">
         <v>167</v>
       </c>
-      <c r="D64" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" t="s">
-        <v>43</v>
-      </c>
-      <c r="F64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="C66" t="s">
         <v>168</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D66" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" t="s">
+        <v>37</v>
+      </c>
+      <c r="F66" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B67" t="s">
         <v>169</v>
       </c>
-      <c r="D65" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" t="s">
-        <v>41</v>
-      </c>
-      <c r="F65" t="s">
-        <v>8</v>
-      </c>
-      <c r="G65" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="C67" t="s">
         <v>170</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>39</v>
+      </c>
+      <c r="F67" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B68" t="s">
         <v>171</v>
       </c>
-      <c r="D66" t="s">
-        <v>16</v>
-      </c>
-      <c r="E66" t="s">
-        <v>41</v>
-      </c>
-      <c r="F66" t="s">
-        <v>8</v>
-      </c>
-      <c r="G66" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="C68" t="s">
         <v>172</v>
-      </c>
-      <c r="C67" t="s">
-        <v>173</v>
-      </c>
-      <c r="D67" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" t="s">
-        <v>8</v>
-      </c>
-      <c r="G67" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B68" t="s">
-        <v>174</v>
-      </c>
-      <c r="C68" t="s">
-        <v>175</v>
       </c>
       <c r="D68" t="s">
         <v>22</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46114</v>
       </c>
       <c r="B69" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F69" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" t="s">
         <v>176</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>39</v>
+      </c>
+      <c r="F70" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B71" t="s">
         <v>177</v>
       </c>
-      <c r="D69" t="s">
-        <v>22</v>
-      </c>
-      <c r="E69" t="s">
-        <v>43</v>
-      </c>
-      <c r="F69" t="s">
-        <v>8</v>
-      </c>
-      <c r="G69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="C71" t="s">
         <v>178</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B72" t="s">
         <v>179</v>
       </c>
-      <c r="D70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E70" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="C72" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" t="s">
+        <v>40</v>
+      </c>
+      <c r="E72" t="s">
+        <v>39</v>
+      </c>
+      <c r="F72" t="s">
         <v>7</v>
-      </c>
-      <c r="G70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B71" t="s">
-        <v>180</v>
-      </c>
-      <c r="C71" t="s">
-        <v>181</v>
-      </c>
-      <c r="D71" t="s">
-        <v>33</v>
-      </c>
-      <c r="E71" t="s">
-        <v>43</v>
-      </c>
-      <c r="F71" t="s">
-        <v>8</v>
-      </c>
-      <c r="G71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B72" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" t="s">
-        <v>183</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s">
-        <v>41</v>
-      </c>
-      <c r="F72" t="s">
-        <v>8</v>
       </c>
       <c r="G72" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46114</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
       </c>
       <c r="G73" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46114</v>
       </c>
       <c r="B74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" t="s">
         <v>186</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s">
+        <v>37</v>
+      </c>
+      <c r="F75" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B76" t="s">
         <v>187</v>
       </c>
-      <c r="D74" t="s">
-        <v>45</v>
-      </c>
-      <c r="E74" t="s">
-        <v>43</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="C76" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B77" t="s">
+        <v>189</v>
+      </c>
+      <c r="C77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>37</v>
+      </c>
+      <c r="F77" t="s">
+        <v>8</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B78" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B79" t="s">
+        <v>193</v>
+      </c>
+      <c r="C79" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" t="s">
+        <v>8</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B80" t="s">
+        <v>195</v>
+      </c>
+      <c r="C80" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" t="s">
+        <v>8</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B81" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" t="s">
         <v>7</v>
       </c>
-      <c r="G74" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B75" t="s">
-        <v>188</v>
-      </c>
-      <c r="C75" t="s">
-        <v>189</v>
-      </c>
-      <c r="D75" t="s">
-        <v>33</v>
-      </c>
-      <c r="E75" t="s">
-        <v>43</v>
-      </c>
-      <c r="F75" t="s">
-        <v>8</v>
-      </c>
-      <c r="G75" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B76" t="s">
-        <v>190</v>
-      </c>
-      <c r="C76" t="s">
-        <v>191</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="G81" t="s">
+        <v>233</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B82" t="s">
+        <v>199</v>
+      </c>
+      <c r="C82" t="s">
+        <v>200</v>
+      </c>
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" t="s">
+        <v>8</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B83" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" t="s">
+        <v>204</v>
+      </c>
+      <c r="D84" t="s">
         <v>14</v>
       </c>
-      <c r="E76" t="s">
-        <v>41</v>
-      </c>
-      <c r="F76" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B77" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" t="s">
-        <v>193</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="E84" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B85" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" t="s">
+        <v>37</v>
+      </c>
+      <c r="F85" t="s">
+        <v>8</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B86" t="s">
+        <v>207</v>
+      </c>
+      <c r="C86" t="s">
+        <v>208</v>
+      </c>
+      <c r="D86" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86" t="s">
+        <v>37</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B87" t="s">
+        <v>209</v>
+      </c>
+      <c r="C87" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" t="s">
         <v>15</v>
       </c>
-      <c r="E77" t="s">
-        <v>41</v>
-      </c>
-      <c r="F77" t="s">
-        <v>8</v>
-      </c>
-      <c r="G77" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B78" t="s">
-        <v>194</v>
-      </c>
-      <c r="C78" t="s">
-        <v>195</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="E87" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87" t="s">
+        <v>233</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B88" t="s">
+        <v>211</v>
+      </c>
+      <c r="C88" t="s">
+        <v>212</v>
+      </c>
+      <c r="D88" t="s">
         <v>11</v>
       </c>
-      <c r="E78" t="s">
-        <v>41</v>
-      </c>
-      <c r="F78" t="s">
-        <v>8</v>
-      </c>
-      <c r="G78" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B79" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79" t="s">
-        <v>197</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="E88" t="s">
+        <v>37</v>
+      </c>
+      <c r="F88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B89" t="s">
+        <v>213</v>
+      </c>
+      <c r="C89" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" t="s">
+        <v>233</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B90" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" t="s">
+        <v>216</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B91" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" t="s">
+        <v>39</v>
+      </c>
+      <c r="F91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B92" t="s">
+        <v>219</v>
+      </c>
+      <c r="C92" t="s">
+        <v>220</v>
+      </c>
+      <c r="D92" t="s">
         <v>14</v>
       </c>
-      <c r="E79" t="s">
-        <v>41</v>
-      </c>
-      <c r="F79" t="s">
-        <v>8</v>
-      </c>
-      <c r="G79" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B80" t="s">
-        <v>198</v>
-      </c>
-      <c r="C80" t="s">
-        <v>199</v>
-      </c>
-      <c r="D80" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" t="s">
-        <v>41</v>
-      </c>
-      <c r="F80" t="s">
-        <v>8</v>
-      </c>
-      <c r="G80" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B81" t="s">
-        <v>200</v>
-      </c>
-      <c r="C81" t="s">
-        <v>201</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E92" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" t="s">
+        <v>8</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B93" t="s">
+        <v>221</v>
+      </c>
+      <c r="C93" t="s">
+        <v>222</v>
+      </c>
+      <c r="D93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>39</v>
+      </c>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B94" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B95" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" t="s">
+        <v>226</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B96" t="s">
+        <v>227</v>
+      </c>
+      <c r="C96" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B97" t="s">
+        <v>229</v>
+      </c>
+      <c r="C97" t="s">
+        <v>230</v>
+      </c>
+      <c r="D97" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" t="s">
+        <v>39</v>
+      </c>
+      <c r="F97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G97" t="s">
+        <v>18</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B98" t="s">
+        <v>231</v>
+      </c>
+      <c r="C98" t="s">
+        <v>232</v>
+      </c>
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>37</v>
+      </c>
+      <c r="F98" t="s">
+        <v>8</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B99" t="s">
+        <v>235</v>
+      </c>
+      <c r="C99" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B100" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B101" t="s">
+        <v>239</v>
+      </c>
+      <c r="C101" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" t="s">
         <v>6</v>
       </c>
-      <c r="E81" t="s">
-        <v>41</v>
-      </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B82" t="s">
-        <v>202</v>
-      </c>
-      <c r="C82" t="s">
-        <v>203</v>
-      </c>
-      <c r="D82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" t="s">
-        <v>7</v>
-      </c>
-      <c r="G82" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B83" t="s">
-        <v>204</v>
-      </c>
-      <c r="C83" t="s">
-        <v>205</v>
-      </c>
-      <c r="D83" t="s">
-        <v>29</v>
-      </c>
-      <c r="E83" t="s">
-        <v>41</v>
-      </c>
-      <c r="F83" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B84" t="s">
-        <v>206</v>
-      </c>
-      <c r="C84" t="s">
-        <v>207</v>
-      </c>
-      <c r="D84" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" t="s">
-        <v>41</v>
-      </c>
-      <c r="F84" t="s">
-        <v>8</v>
-      </c>
-      <c r="G84" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B85" t="s">
-        <v>208</v>
-      </c>
-      <c r="C85" t="s">
-        <v>209</v>
-      </c>
-      <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s">
-        <v>41</v>
-      </c>
-      <c r="F85" t="s">
-        <v>8</v>
-      </c>
-      <c r="G85" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B86" t="s">
-        <v>210</v>
-      </c>
-      <c r="C86" t="s">
-        <v>211</v>
-      </c>
-      <c r="D86" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" t="s">
-        <v>41</v>
-      </c>
-      <c r="F86" t="s">
-        <v>8</v>
-      </c>
-      <c r="G86" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B87" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" t="s">
-        <v>213</v>
-      </c>
-      <c r="D87" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" t="s">
-        <v>41</v>
-      </c>
-      <c r="F87" t="s">
-        <v>8</v>
-      </c>
-      <c r="G87" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B88" t="s">
-        <v>214</v>
-      </c>
-      <c r="C88" t="s">
-        <v>215</v>
-      </c>
-      <c r="D88" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" t="s">
-        <v>41</v>
-      </c>
-      <c r="F88" t="s">
-        <v>8</v>
-      </c>
-      <c r="G88" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B89" t="s">
-        <v>216</v>
-      </c>
-      <c r="C89" t="s">
-        <v>217</v>
-      </c>
-      <c r="D89" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" t="s">
-        <v>41</v>
-      </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B90" t="s">
-        <v>218</v>
-      </c>
-      <c r="C90" t="s">
-        <v>219</v>
-      </c>
-      <c r="D90" t="s">
-        <v>16</v>
-      </c>
-      <c r="E90" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" t="s">
-        <v>8</v>
-      </c>
-      <c r="G90" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C91" t="s">
-        <v>221</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91" t="s">
-        <v>43</v>
-      </c>
-      <c r="F91" t="s">
-        <v>7</v>
-      </c>
-      <c r="G91" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B92" t="s">
-        <v>222</v>
-      </c>
-      <c r="C92" t="s">
-        <v>223</v>
-      </c>
-      <c r="D92" t="s">
-        <v>22</v>
-      </c>
-      <c r="E92" t="s">
-        <v>43</v>
-      </c>
-      <c r="F92" t="s">
-        <v>8</v>
-      </c>
-      <c r="G92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B93" t="s">
-        <v>224</v>
-      </c>
-      <c r="C93" t="s">
-        <v>225</v>
-      </c>
-      <c r="D93" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s">
-        <v>41</v>
-      </c>
-      <c r="F93" t="s">
-        <v>8</v>
-      </c>
-      <c r="G93" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B94" t="s">
-        <v>226</v>
-      </c>
-      <c r="C94" t="s">
-        <v>227</v>
-      </c>
-      <c r="D94" t="s">
-        <v>26</v>
-      </c>
-      <c r="E94" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B95" t="s">
-        <v>228</v>
-      </c>
-      <c r="C95" t="s">
-        <v>229</v>
-      </c>
-      <c r="D95" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" t="s">
-        <v>41</v>
-      </c>
-      <c r="F95" t="s">
-        <v>8</v>
-      </c>
-      <c r="G95" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B96" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" t="s">
-        <v>231</v>
-      </c>
-      <c r="D96" t="s">
-        <v>16</v>
-      </c>
-      <c r="E96" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B97" t="s">
-        <v>232</v>
-      </c>
-      <c r="C97" t="s">
-        <v>233</v>
-      </c>
-      <c r="D97" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G97" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B98" t="s">
-        <v>234</v>
-      </c>
-      <c r="C98" t="s">
-        <v>235</v>
-      </c>
-      <c r="D98" t="s">
-        <v>26</v>
-      </c>
-      <c r="E98" t="s">
-        <v>43</v>
-      </c>
-      <c r="F98" t="s">
-        <v>8</v>
-      </c>
-      <c r="G98" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B99" t="s">
-        <v>236</v>
-      </c>
-      <c r="C99" t="s">
-        <v>237</v>
-      </c>
-      <c r="D99" t="s">
-        <v>16</v>
-      </c>
-      <c r="E99" t="s">
-        <v>41</v>
-      </c>
-      <c r="F99" t="s">
-        <v>8</v>
-      </c>
-      <c r="G99" t="s">
-        <v>20</v>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B102" t="s">
+        <v>241</v>
+      </c>
+      <c r="C102" t="s">
+        <v>242</v>
+      </c>
+      <c r="D102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" t="s">
+        <v>243</v>
+      </c>
+      <c r="G102" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B103" t="s">
+        <v>244</v>
+      </c>
+      <c r="C103" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B104" t="s">
+        <v>246</v>
+      </c>
+      <c r="C104" t="s">
+        <v>247</v>
+      </c>
+      <c r="D104" t="s">
+        <v>6</v>
+      </c>
+      <c r="F104" t="s">
+        <v>8</v>
+      </c>
+      <c r="G104" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E007CA9D-0DAC-4F89-93D0-A0D1C6A6975C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B3935-63A7-43F2-A66A-0FAFDECA49C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="411">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -783,6 +783,495 @@
   </si>
   <si>
     <t>RO AMARO DECORACOES LTDA</t>
+  </si>
+  <si>
+    <t>35448429000120</t>
+  </si>
+  <si>
+    <t>A P DE OLIVEIRA DRINKS</t>
+  </si>
+  <si>
+    <t>61243990000183</t>
+  </si>
+  <si>
+    <t>23805136000174</t>
+  </si>
+  <si>
+    <t>47021542000104</t>
+  </si>
+  <si>
+    <t>47.021.542 MARCELO SEBASTIAO DA SILVA</t>
+  </si>
+  <si>
+    <t>VISAO ATACADO 2025 LTDA</t>
+  </si>
+  <si>
+    <t>53169061000143</t>
+  </si>
+  <si>
+    <t>HAMILTON FERREIRA SANTOS</t>
+  </si>
+  <si>
+    <t>62911781000123</t>
+  </si>
+  <si>
+    <t>LUCAS ALEXANDRE DA SILVA</t>
+  </si>
+  <si>
+    <t>45813756000198</t>
+  </si>
+  <si>
+    <t>GISLAINE DOS SANTOS OLIVEIRA ENXOVAIS</t>
+  </si>
+  <si>
+    <t>36692888000118</t>
+  </si>
+  <si>
+    <t>DALVA TOLOTO DA SILVA</t>
+  </si>
+  <si>
+    <t>52836638000160</t>
+  </si>
+  <si>
+    <t>JONATHAN LIMA COSTA</t>
+  </si>
+  <si>
+    <t>60393286000144</t>
+  </si>
+  <si>
+    <t>ELIVELTON LINHARES CAMPOS</t>
+  </si>
+  <si>
+    <t>Sophia Bagagi Pigente</t>
+  </si>
+  <si>
+    <t>43353024000137</t>
+  </si>
+  <si>
+    <t>DUDU MED LTDA</t>
+  </si>
+  <si>
+    <t>42124483000186</t>
+  </si>
+  <si>
+    <t>DANIEL SOSO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>62380827000125</t>
+  </si>
+  <si>
+    <t>JOAO AUGUSTO GUSMIN</t>
+  </si>
+  <si>
+    <t>Mensageria</t>
+  </si>
+  <si>
+    <t>63516613000104</t>
+  </si>
+  <si>
+    <t>MIGUEL DE OLIVEIRA HELIODORO</t>
+  </si>
+  <si>
+    <t>42278873000100</t>
+  </si>
+  <si>
+    <t>PEMASA ACIONAMENTOS EM VENDAS LTDA</t>
+  </si>
+  <si>
+    <t>38209501000155</t>
+  </si>
+  <si>
+    <t>RAYLENA ANGELI FERREIRA SOUSA LTDA</t>
+  </si>
+  <si>
+    <t>45673721000109</t>
+  </si>
+  <si>
+    <t>JANAINA PETRY DIAS ARAUJO</t>
+  </si>
+  <si>
+    <t>44855510000116</t>
+  </si>
+  <si>
+    <t>FABRICIO DA SILVA BORGES</t>
+  </si>
+  <si>
+    <t>42082269000104</t>
+  </si>
+  <si>
+    <t>CARDOSO REFORMAS E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>35627147000190</t>
+  </si>
+  <si>
+    <t>KAIO DIAS BRAGA</t>
+  </si>
+  <si>
+    <t>62918441000124</t>
+  </si>
+  <si>
+    <t>DELLICATO MOVEIS RUSTICOS LTDA</t>
+  </si>
+  <si>
+    <t>21792653000120</t>
+  </si>
+  <si>
+    <t>AGNALDO LOPES DE OLIVEIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>29691416000185</t>
+  </si>
+  <si>
+    <t>VILMA C DOS SANTOS</t>
+  </si>
+  <si>
+    <t>60662949000189</t>
+  </si>
+  <si>
+    <t>FABRICIO RODRIGUES FERREIRA LTDA</t>
+  </si>
+  <si>
+    <t>24904741000165</t>
+  </si>
+  <si>
+    <t>FABIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>44174304000140</t>
+  </si>
+  <si>
+    <t>L. W. INTERMEDIACOES E PARANA REPASSES DE VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>35348212000149</t>
+  </si>
+  <si>
+    <t>BARBEARIA ROBSON RODRIGUES LTDA</t>
+  </si>
+  <si>
+    <t>40729151000108</t>
+  </si>
+  <si>
+    <t>VERA MARIA ALVES</t>
+  </si>
+  <si>
+    <t>51918690000101</t>
+  </si>
+  <si>
+    <t>GD ADMINISTRACAO DE IMOVEIS LTDA</t>
+  </si>
+  <si>
+    <t>63196651000119</t>
+  </si>
+  <si>
+    <t>ERICK VINICIUS PEREIRA</t>
+  </si>
+  <si>
+    <t>48972361000126</t>
+  </si>
+  <si>
+    <t>48.972.361 MARCOS JUNIOR LEMOS QUADROS</t>
+  </si>
+  <si>
+    <t>MARCO AURELIO FERNANDESQUADROS</t>
+  </si>
+  <si>
+    <t>53945967000102</t>
+  </si>
+  <si>
+    <t>53.945.967 JOHN WARLLEY PERES DA CUNHA</t>
+  </si>
+  <si>
+    <t>35909090000112</t>
+  </si>
+  <si>
+    <t>TOME P PEIXOTO CONSULTORIA E ASSESSORIA EM GESTAO PUBLICA E PRIVADA</t>
+  </si>
+  <si>
+    <t>26055903000163</t>
+  </si>
+  <si>
+    <t>CLAUDIA KELLY DE PAULA CARONI</t>
+  </si>
+  <si>
+    <t>40795819000107</t>
+  </si>
+  <si>
+    <t>40.795.819 JOAO VITOR FERREIRA</t>
+  </si>
+  <si>
+    <t>64736462000154</t>
+  </si>
+  <si>
+    <t>HUB SERV LTDA</t>
+  </si>
+  <si>
+    <t>43080997000140</t>
+  </si>
+  <si>
+    <t>GEORGE ALBERTO SILVA</t>
+  </si>
+  <si>
+    <t>58450219000172</t>
+  </si>
+  <si>
+    <t>FILIPE SOUZA WISNIEWSKI</t>
+  </si>
+  <si>
+    <t>54700991000144</t>
+  </si>
+  <si>
+    <t>L H R M TEIXEIRA REPRESENTACOES</t>
+  </si>
+  <si>
+    <t>25316150000130</t>
+  </si>
+  <si>
+    <t>MANOEL TRANSPORTE E TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>34594623000151</t>
+  </si>
+  <si>
+    <t>34.594.623 MARIA TAIS ALVES FERREIRA</t>
+  </si>
+  <si>
+    <t>55487148000194</t>
+  </si>
+  <si>
+    <t>BRAVENICA CLINIC LTDA</t>
+  </si>
+  <si>
+    <t>43424148000166</t>
+  </si>
+  <si>
+    <t>GALO PINTURAS LTDA</t>
+  </si>
+  <si>
+    <t>33775001000167</t>
+  </si>
+  <si>
+    <t>ALUIZIO DA FRANCA SAMPAIO NETO LTDA</t>
+  </si>
+  <si>
+    <t>35480368000189</t>
+  </si>
+  <si>
+    <t>35.480.368 JOSE MARCIO DE OLIVEIRA FELIPE</t>
+  </si>
+  <si>
+    <t>58746440000172</t>
+  </si>
+  <si>
+    <t>58.746.440 FERNANDA MOURA DA COSTA</t>
+  </si>
+  <si>
+    <t>62829235000148</t>
+  </si>
+  <si>
+    <t>RENOVE TEXTURA E GRAFIATOS LTDA</t>
+  </si>
+  <si>
+    <t>43350059000112</t>
+  </si>
+  <si>
+    <t>M SALES DA COSTA</t>
+  </si>
+  <si>
+    <t>60398871000137</t>
+  </si>
+  <si>
+    <t>FREE-LANCER APOIO E CONSULTORIA EM LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>26365461000151</t>
+  </si>
+  <si>
+    <t>AA ESTILO LTDA</t>
+  </si>
+  <si>
+    <t>33936185000108</t>
+  </si>
+  <si>
+    <t>DANILO ENIO FERREIRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>15640609000100</t>
+  </si>
+  <si>
+    <t>15.640.609 DIOGO JOSE PIRES FERREIRA E SILVA</t>
+  </si>
+  <si>
+    <t>58612131000100</t>
+  </si>
+  <si>
+    <t>58.612.131 EVANDRO SANTOS NUNES</t>
+  </si>
+  <si>
+    <t>46351752000106</t>
+  </si>
+  <si>
+    <t>MARILANE V. DA SILVA TRANSPORTES</t>
+  </si>
+  <si>
+    <t>62931198000184</t>
+  </si>
+  <si>
+    <t>62.931.198 PYETTRO PEREIRA SANTOS</t>
+  </si>
+  <si>
+    <t>57379665000175</t>
+  </si>
+  <si>
+    <t>RONALDO DE SOUSA BARBOSA</t>
+  </si>
+  <si>
+    <t>07587995000188</t>
+  </si>
+  <si>
+    <t>ELIO PEREIRA NEVES</t>
+  </si>
+  <si>
+    <t>42636556000119</t>
+  </si>
+  <si>
+    <t>42.636.556 ADRIANA FELIZARDO DA SILVA ANDRADE</t>
+  </si>
+  <si>
+    <t>53275325000143</t>
+  </si>
+  <si>
+    <t>ADRIANA BARBOSA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>54644628000159</t>
+  </si>
+  <si>
+    <t>VALDIR FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>41408783000124</t>
+  </si>
+  <si>
+    <t>JOSE MARIEL GOIS DA SILVA</t>
+  </si>
+  <si>
+    <t>21808221000160</t>
+  </si>
+  <si>
+    <t>JACKSON DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>48436958000156</t>
+  </si>
+  <si>
+    <t>DOUGLAS P. DA SILVA MANUTENCAO E REPARACAO LTDA</t>
+  </si>
+  <si>
+    <t>04950823000139</t>
+  </si>
+  <si>
+    <t>LUCIANO GUERRA</t>
+  </si>
+  <si>
+    <t>29680418000179</t>
+  </si>
+  <si>
+    <t>FLAVIO MAIA DOS REIS</t>
+  </si>
+  <si>
+    <t>59397317000156</t>
+  </si>
+  <si>
+    <t>59.397.317 CIRENIO ALVES DE SOUSA</t>
+  </si>
+  <si>
+    <t>23791623000125</t>
+  </si>
+  <si>
+    <t>ROJAKE GUSTAVO GUIMARAES DA SILVA</t>
+  </si>
+  <si>
+    <t>24596809000196</t>
+  </si>
+  <si>
+    <t>24.596.809 GRAZIELLE FERNANDA RIBEIRO</t>
+  </si>
+  <si>
+    <t>27299033000130</t>
+  </si>
+  <si>
+    <t>RAFAELA LISANDRA DE OLIVEIRA FREITAS</t>
+  </si>
+  <si>
+    <t>46802938000126</t>
+  </si>
+  <si>
+    <t>SAVIO BARBOSA SANTOS</t>
+  </si>
+  <si>
+    <t>66094998000149</t>
+  </si>
+  <si>
+    <t>JULIA MAIA LIPPI SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>LEAD MANUAL</t>
+  </si>
+  <si>
+    <t>23551126000150</t>
+  </si>
+  <si>
+    <t>JULIANA ARAUJO SALES PILATES</t>
+  </si>
+  <si>
+    <t>47814690000186</t>
+  </si>
+  <si>
+    <t>CARLOS IZUILO MEIRELES GOMES</t>
+  </si>
+  <si>
+    <t>41861083000190</t>
+  </si>
+  <si>
+    <t>MARCELO SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>58382829000186</t>
+  </si>
+  <si>
+    <t>GOLDEN COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>43802995000117</t>
+  </si>
+  <si>
+    <t>CEREALISTA ARVORE DA VIDA MEDICINA NATURAL LTDA</t>
+  </si>
+  <si>
+    <t>28075940000169</t>
+  </si>
+  <si>
+    <t>PAULO CESAR MACHADO</t>
+  </si>
+  <si>
+    <t>52542837000166</t>
+  </si>
+  <si>
+    <t>THAYNA CRISTHYNA DA SILVA MORAIS</t>
+  </si>
+  <si>
+    <t>40385373000142</t>
+  </si>
+  <si>
+    <t>GABRIEL HENRIQUE DE SOUSA</t>
+  </si>
+  <si>
+    <t>58325459000145</t>
+  </si>
+  <si>
+    <t>58.325.459 GENAILDO DE SOUZA SANTOS</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -3727,6 +4216,9 @@
       <c r="D99" t="s">
         <v>24</v>
       </c>
+      <c r="E99" t="s">
+        <v>39</v>
+      </c>
       <c r="F99" t="s">
         <v>7</v>
       </c>
@@ -3750,6 +4242,9 @@
       <c r="D100" t="s">
         <v>19</v>
       </c>
+      <c r="E100" t="s">
+        <v>37</v>
+      </c>
       <c r="F100" t="s">
         <v>8</v>
       </c>
@@ -3773,6 +4268,9 @@
       <c r="D101" t="s">
         <v>6</v>
       </c>
+      <c r="E101" t="s">
+        <v>37</v>
+      </c>
       <c r="F101" t="s">
         <v>8</v>
       </c>
@@ -3796,6 +4294,9 @@
       <c r="D102" t="s">
         <v>27</v>
       </c>
+      <c r="E102" t="s">
+        <v>38</v>
+      </c>
       <c r="F102" t="s">
         <v>243</v>
       </c>
@@ -3819,6 +4320,9 @@
       <c r="D103" t="s">
         <v>27</v>
       </c>
+      <c r="E103" t="s">
+        <v>38</v>
+      </c>
       <c r="F103" t="s">
         <v>8</v>
       </c>
@@ -3842,6 +4346,9 @@
       <c r="D104" t="s">
         <v>6</v>
       </c>
+      <c r="E104" t="s">
+        <v>37</v>
+      </c>
       <c r="F104" t="s">
         <v>8</v>
       </c>
@@ -3850,6 +4357,1846 @@
       </c>
       <c r="H104">
         <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B105" t="s">
+        <v>252</v>
+      </c>
+      <c r="C105" t="s">
+        <v>253</v>
+      </c>
+      <c r="D105" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" t="s">
+        <v>37</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+      <c r="G105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B106" t="s">
+        <v>248</v>
+      </c>
+      <c r="C106" t="s">
+        <v>249</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>39</v>
+      </c>
+      <c r="F106" t="s">
+        <v>8</v>
+      </c>
+      <c r="G106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B107" t="s">
+        <v>250</v>
+      </c>
+      <c r="C107" t="s">
+        <v>254</v>
+      </c>
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>39</v>
+      </c>
+      <c r="F107" t="s">
+        <v>8</v>
+      </c>
+      <c r="G107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B108" t="s">
+        <v>255</v>
+      </c>
+      <c r="C108" t="s">
+        <v>256</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B109" t="s">
+        <v>257</v>
+      </c>
+      <c r="C109" t="s">
+        <v>258</v>
+      </c>
+      <c r="D109" t="s">
+        <v>6</v>
+      </c>
+      <c r="E109" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B110" t="s">
+        <v>259</v>
+      </c>
+      <c r="C110" t="s">
+        <v>260</v>
+      </c>
+      <c r="D110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" t="s">
+        <v>37</v>
+      </c>
+      <c r="F110" t="s">
+        <v>8</v>
+      </c>
+      <c r="G110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B111" t="s">
+        <v>261</v>
+      </c>
+      <c r="C111" t="s">
+        <v>262</v>
+      </c>
+      <c r="D111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F111" t="s">
+        <v>8</v>
+      </c>
+      <c r="G111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>263</v>
+      </c>
+      <c r="C112" t="s">
+        <v>264</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" t="s">
+        <v>8</v>
+      </c>
+      <c r="G112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" t="s">
+        <v>266</v>
+      </c>
+      <c r="D113" t="s">
+        <v>267</v>
+      </c>
+      <c r="E113" t="s">
+        <v>37</v>
+      </c>
+      <c r="F113" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B114" t="s">
+        <v>268</v>
+      </c>
+      <c r="C114" t="s">
+        <v>269</v>
+      </c>
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
+        <v>39</v>
+      </c>
+      <c r="F114" t="s">
+        <v>7</v>
+      </c>
+      <c r="G114" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B115" t="s">
+        <v>270</v>
+      </c>
+      <c r="C115" t="s">
+        <v>271</v>
+      </c>
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" t="s">
+        <v>8</v>
+      </c>
+      <c r="G115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" t="s">
+        <v>273</v>
+      </c>
+      <c r="D116" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" t="s">
+        <v>274</v>
+      </c>
+      <c r="G116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B117" t="s">
+        <v>275</v>
+      </c>
+      <c r="C117" t="s">
+        <v>276</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" t="s">
+        <v>8</v>
+      </c>
+      <c r="G117" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>277</v>
+      </c>
+      <c r="C118" t="s">
+        <v>278</v>
+      </c>
+      <c r="D118" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" t="s">
+        <v>8</v>
+      </c>
+      <c r="G118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>279</v>
+      </c>
+      <c r="C119" t="s">
+        <v>280</v>
+      </c>
+      <c r="D119" t="s">
+        <v>267</v>
+      </c>
+      <c r="E119" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" t="s">
+        <v>8</v>
+      </c>
+      <c r="G119" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>281</v>
+      </c>
+      <c r="C120" t="s">
+        <v>282</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="s">
+        <v>39</v>
+      </c>
+      <c r="F120" t="s">
+        <v>7</v>
+      </c>
+      <c r="G120" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B121" t="s">
+        <v>283</v>
+      </c>
+      <c r="C121" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" t="s">
+        <v>267</v>
+      </c>
+      <c r="E121" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" t="s">
+        <v>8</v>
+      </c>
+      <c r="G121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="s">
+        <v>285</v>
+      </c>
+      <c r="C122" t="s">
+        <v>286</v>
+      </c>
+      <c r="D122" t="s">
+        <v>15</v>
+      </c>
+      <c r="E122" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" t="s">
+        <v>8</v>
+      </c>
+      <c r="G122" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B123" t="s">
+        <v>287</v>
+      </c>
+      <c r="C123" t="s">
+        <v>288</v>
+      </c>
+      <c r="D123" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" t="s">
+        <v>8</v>
+      </c>
+      <c r="G123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B124" t="s">
+        <v>289</v>
+      </c>
+      <c r="C124" t="s">
+        <v>290</v>
+      </c>
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" t="s">
+        <v>8</v>
+      </c>
+      <c r="G124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B125" t="s">
+        <v>291</v>
+      </c>
+      <c r="C125" t="s">
+        <v>292</v>
+      </c>
+      <c r="D125" t="s">
+        <v>28</v>
+      </c>
+      <c r="E125" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" t="s">
+        <v>8</v>
+      </c>
+      <c r="G125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B126" t="s">
+        <v>293</v>
+      </c>
+      <c r="C126" t="s">
+        <v>294</v>
+      </c>
+      <c r="D126" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" t="s">
+        <v>37</v>
+      </c>
+      <c r="F126" t="s">
+        <v>8</v>
+      </c>
+      <c r="G126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B127" t="s">
+        <v>295</v>
+      </c>
+      <c r="C127" t="s">
+        <v>296</v>
+      </c>
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" t="s">
+        <v>8</v>
+      </c>
+      <c r="G127" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B128" t="s">
+        <v>297</v>
+      </c>
+      <c r="C128" t="s">
+        <v>298</v>
+      </c>
+      <c r="D128" t="s">
+        <v>28</v>
+      </c>
+      <c r="E128" t="s">
+        <v>37</v>
+      </c>
+      <c r="F128" t="s">
+        <v>8</v>
+      </c>
+      <c r="G128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B129" t="s">
+        <v>299</v>
+      </c>
+      <c r="C129" t="s">
+        <v>300</v>
+      </c>
+      <c r="D129" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" t="s">
+        <v>37</v>
+      </c>
+      <c r="F129" t="s">
+        <v>8</v>
+      </c>
+      <c r="G129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B130" t="s">
+        <v>301</v>
+      </c>
+      <c r="C130" t="s">
+        <v>302</v>
+      </c>
+      <c r="D130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" t="s">
+        <v>39</v>
+      </c>
+      <c r="F130" t="s">
+        <v>7</v>
+      </c>
+      <c r="G130" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B131" t="s">
+        <v>303</v>
+      </c>
+      <c r="C131" t="s">
+        <v>304</v>
+      </c>
+      <c r="D131" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131" t="s">
+        <v>39</v>
+      </c>
+      <c r="F131" t="s">
+        <v>7</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B132" t="s">
+        <v>305</v>
+      </c>
+      <c r="C132" t="s">
+        <v>306</v>
+      </c>
+      <c r="D132" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" t="s">
+        <v>37</v>
+      </c>
+      <c r="F132" t="s">
+        <v>8</v>
+      </c>
+      <c r="G132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B133" t="s">
+        <v>307</v>
+      </c>
+      <c r="C133" t="s">
+        <v>308</v>
+      </c>
+      <c r="D133" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133" t="s">
+        <v>39</v>
+      </c>
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+      <c r="G133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B134" t="s">
+        <v>309</v>
+      </c>
+      <c r="C134" t="s">
+        <v>310</v>
+      </c>
+      <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" t="s">
+        <v>37</v>
+      </c>
+      <c r="F134" t="s">
+        <v>8</v>
+      </c>
+      <c r="G134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B135" t="s">
+        <v>251</v>
+      </c>
+      <c r="C135" t="s">
+        <v>311</v>
+      </c>
+      <c r="D135" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" t="s">
+        <v>39</v>
+      </c>
+      <c r="F135" t="s">
+        <v>8</v>
+      </c>
+      <c r="G135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B136" t="s">
+        <v>312</v>
+      </c>
+      <c r="C136" t="s">
+        <v>313</v>
+      </c>
+      <c r="D136" t="s">
+        <v>28</v>
+      </c>
+      <c r="E136" t="s">
+        <v>37</v>
+      </c>
+      <c r="F136" t="s">
+        <v>8</v>
+      </c>
+      <c r="G136" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B137" t="s">
+        <v>314</v>
+      </c>
+      <c r="C137" t="s">
+        <v>315</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" t="s">
+        <v>37</v>
+      </c>
+      <c r="F137" t="s">
+        <v>8</v>
+      </c>
+      <c r="G137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B138" t="s">
+        <v>316</v>
+      </c>
+      <c r="C138" t="s">
+        <v>317</v>
+      </c>
+      <c r="D138" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" t="s">
+        <v>37</v>
+      </c>
+      <c r="F138" t="s">
+        <v>8</v>
+      </c>
+      <c r="G138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B139" t="s">
+        <v>318</v>
+      </c>
+      <c r="C139" t="s">
+        <v>319</v>
+      </c>
+      <c r="D139" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" t="s">
+        <v>37</v>
+      </c>
+      <c r="F139" t="s">
+        <v>8</v>
+      </c>
+      <c r="G139" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B140" t="s">
+        <v>320</v>
+      </c>
+      <c r="C140" t="s">
+        <v>321</v>
+      </c>
+      <c r="D140" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" t="s">
+        <v>37</v>
+      </c>
+      <c r="F140" t="s">
+        <v>8</v>
+      </c>
+      <c r="G140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B141" t="s">
+        <v>322</v>
+      </c>
+      <c r="C141" t="s">
+        <v>323</v>
+      </c>
+      <c r="D141" t="s">
+        <v>6</v>
+      </c>
+      <c r="E141" t="s">
+        <v>37</v>
+      </c>
+      <c r="F141" t="s">
+        <v>8</v>
+      </c>
+      <c r="G141" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B142" t="s">
+        <v>324</v>
+      </c>
+      <c r="C142" t="s">
+        <v>325</v>
+      </c>
+      <c r="D142" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" t="s">
+        <v>37</v>
+      </c>
+      <c r="F142" t="s">
+        <v>8</v>
+      </c>
+      <c r="G142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B143" t="s">
+        <v>326</v>
+      </c>
+      <c r="C143" t="s">
+        <v>327</v>
+      </c>
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" t="s">
+        <v>39</v>
+      </c>
+      <c r="F143" t="s">
+        <v>7</v>
+      </c>
+      <c r="G143" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B144" t="s">
+        <v>328</v>
+      </c>
+      <c r="C144" t="s">
+        <v>329</v>
+      </c>
+      <c r="D144" t="s">
+        <v>31</v>
+      </c>
+      <c r="E144" t="s">
+        <v>39</v>
+      </c>
+      <c r="F144" t="s">
+        <v>8</v>
+      </c>
+      <c r="G144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B145" t="s">
+        <v>330</v>
+      </c>
+      <c r="C145" t="s">
+        <v>331</v>
+      </c>
+      <c r="D145" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" t="s">
+        <v>37</v>
+      </c>
+      <c r="F145" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B146" t="s">
+        <v>332</v>
+      </c>
+      <c r="C146" t="s">
+        <v>333</v>
+      </c>
+      <c r="D146" t="s">
+        <v>15</v>
+      </c>
+      <c r="E146" t="s">
+        <v>37</v>
+      </c>
+      <c r="F146" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="s">
+        <v>334</v>
+      </c>
+      <c r="C147" t="s">
+        <v>335</v>
+      </c>
+      <c r="D147" t="s">
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>39</v>
+      </c>
+      <c r="F147" t="s">
+        <v>8</v>
+      </c>
+      <c r="G147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B148" t="s">
+        <v>336</v>
+      </c>
+      <c r="C148" t="s">
+        <v>337</v>
+      </c>
+      <c r="D148" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" t="s">
+        <v>37</v>
+      </c>
+      <c r="F148" t="s">
+        <v>8</v>
+      </c>
+      <c r="G148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B149" t="s">
+        <v>338</v>
+      </c>
+      <c r="C149" t="s">
+        <v>339</v>
+      </c>
+      <c r="D149" t="s">
+        <v>15</v>
+      </c>
+      <c r="E149" t="s">
+        <v>37</v>
+      </c>
+      <c r="F149" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B150" t="s">
+        <v>340</v>
+      </c>
+      <c r="C150" t="s">
+        <v>341</v>
+      </c>
+      <c r="D150" t="s">
+        <v>16</v>
+      </c>
+      <c r="E150" t="s">
+        <v>37</v>
+      </c>
+      <c r="F150" t="s">
+        <v>8</v>
+      </c>
+      <c r="G150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B151" t="s">
+        <v>342</v>
+      </c>
+      <c r="C151" t="s">
+        <v>343</v>
+      </c>
+      <c r="D151" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" t="s">
+        <v>37</v>
+      </c>
+      <c r="F151" t="s">
+        <v>8</v>
+      </c>
+      <c r="G151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B152" t="s">
+        <v>344</v>
+      </c>
+      <c r="C152" t="s">
+        <v>345</v>
+      </c>
+      <c r="D152" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" t="s">
+        <v>37</v>
+      </c>
+      <c r="F152" t="s">
+        <v>8</v>
+      </c>
+      <c r="G152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B153" t="s">
+        <v>346</v>
+      </c>
+      <c r="C153" t="s">
+        <v>347</v>
+      </c>
+      <c r="D153" t="s">
+        <v>31</v>
+      </c>
+      <c r="E153" t="s">
+        <v>39</v>
+      </c>
+      <c r="F153" t="s">
+        <v>8</v>
+      </c>
+      <c r="G153" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B154" t="s">
+        <v>348</v>
+      </c>
+      <c r="C154" t="s">
+        <v>349</v>
+      </c>
+      <c r="D154" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" t="s">
+        <v>37</v>
+      </c>
+      <c r="F154" t="s">
+        <v>8</v>
+      </c>
+      <c r="G154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B155" t="s">
+        <v>350</v>
+      </c>
+      <c r="C155" t="s">
+        <v>351</v>
+      </c>
+      <c r="D155" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" t="s">
+        <v>37</v>
+      </c>
+      <c r="F155" t="s">
+        <v>8</v>
+      </c>
+      <c r="G155" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B156" t="s">
+        <v>352</v>
+      </c>
+      <c r="C156" t="s">
+        <v>353</v>
+      </c>
+      <c r="D156" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" t="s">
+        <v>37</v>
+      </c>
+      <c r="F156" t="s">
+        <v>8</v>
+      </c>
+      <c r="G156" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B157" t="s">
+        <v>354</v>
+      </c>
+      <c r="C157" t="s">
+        <v>355</v>
+      </c>
+      <c r="D157" t="s">
+        <v>31</v>
+      </c>
+      <c r="E157" t="s">
+        <v>39</v>
+      </c>
+      <c r="F157" t="s">
+        <v>8</v>
+      </c>
+      <c r="G157" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B158" t="s">
+        <v>356</v>
+      </c>
+      <c r="C158" t="s">
+        <v>357</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>37</v>
+      </c>
+      <c r="F158" t="s">
+        <v>8</v>
+      </c>
+      <c r="G158" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B159" t="s">
+        <v>358</v>
+      </c>
+      <c r="C159" t="s">
+        <v>359</v>
+      </c>
+      <c r="D159" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" t="s">
+        <v>39</v>
+      </c>
+      <c r="F159" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B160" t="s">
+        <v>360</v>
+      </c>
+      <c r="C160" t="s">
+        <v>361</v>
+      </c>
+      <c r="D160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B161" t="s">
+        <v>362</v>
+      </c>
+      <c r="C161" t="s">
+        <v>363</v>
+      </c>
+      <c r="D161" t="s">
+        <v>6</v>
+      </c>
+      <c r="E161" t="s">
+        <v>37</v>
+      </c>
+      <c r="F161" t="s">
+        <v>8</v>
+      </c>
+      <c r="G161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B162" t="s">
+        <v>364</v>
+      </c>
+      <c r="C162" t="s">
+        <v>365</v>
+      </c>
+      <c r="D162" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" t="s">
+        <v>37</v>
+      </c>
+      <c r="F162" t="s">
+        <v>8</v>
+      </c>
+      <c r="G162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B163" t="s">
+        <v>366</v>
+      </c>
+      <c r="C163" t="s">
+        <v>367</v>
+      </c>
+      <c r="D163" t="s">
+        <v>40</v>
+      </c>
+      <c r="E163" t="s">
+        <v>39</v>
+      </c>
+      <c r="F163" t="s">
+        <v>7</v>
+      </c>
+      <c r="G163" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B164" t="s">
+        <v>368</v>
+      </c>
+      <c r="C164" t="s">
+        <v>369</v>
+      </c>
+      <c r="D164" t="s">
+        <v>25</v>
+      </c>
+      <c r="E164" t="s">
+        <v>39</v>
+      </c>
+      <c r="F164" t="s">
+        <v>7</v>
+      </c>
+      <c r="G164" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B165" t="s">
+        <v>370</v>
+      </c>
+      <c r="C165" t="s">
+        <v>371</v>
+      </c>
+      <c r="D165" t="s">
+        <v>14</v>
+      </c>
+      <c r="E165" t="s">
+        <v>37</v>
+      </c>
+      <c r="F165" t="s">
+        <v>8</v>
+      </c>
+      <c r="G165" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B166" t="s">
+        <v>372</v>
+      </c>
+      <c r="C166" t="s">
+        <v>373</v>
+      </c>
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="s">
+        <v>37</v>
+      </c>
+      <c r="F166" t="s">
+        <v>8</v>
+      </c>
+      <c r="G166" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B167" t="s">
+        <v>374</v>
+      </c>
+      <c r="C167" t="s">
+        <v>375</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" t="s">
+        <v>8</v>
+      </c>
+      <c r="G167" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B168" t="s">
+        <v>376</v>
+      </c>
+      <c r="C168" t="s">
+        <v>377</v>
+      </c>
+      <c r="D168" t="s">
+        <v>24</v>
+      </c>
+      <c r="E168" t="s">
+        <v>39</v>
+      </c>
+      <c r="F168" t="s">
+        <v>8</v>
+      </c>
+      <c r="G168" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B169" t="s">
+        <v>378</v>
+      </c>
+      <c r="C169" t="s">
+        <v>379</v>
+      </c>
+      <c r="D169" t="s">
+        <v>40</v>
+      </c>
+      <c r="E169" t="s">
+        <v>39</v>
+      </c>
+      <c r="F169" t="s">
+        <v>7</v>
+      </c>
+      <c r="G169" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B170" t="s">
+        <v>380</v>
+      </c>
+      <c r="C170" t="s">
+        <v>381</v>
+      </c>
+      <c r="D170" t="s">
+        <v>15</v>
+      </c>
+      <c r="E170" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170" t="s">
+        <v>8</v>
+      </c>
+      <c r="G170" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B171" t="s">
+        <v>382</v>
+      </c>
+      <c r="C171" t="s">
+        <v>383</v>
+      </c>
+      <c r="D171" t="s">
+        <v>15</v>
+      </c>
+      <c r="E171" t="s">
+        <v>37</v>
+      </c>
+      <c r="F171" t="s">
+        <v>8</v>
+      </c>
+      <c r="G171" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B172" t="s">
+        <v>384</v>
+      </c>
+      <c r="C172" t="s">
+        <v>385</v>
+      </c>
+      <c r="D172" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" t="s">
+        <v>39</v>
+      </c>
+      <c r="F172" t="s">
+        <v>8</v>
+      </c>
+      <c r="G172" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B173" t="s">
+        <v>386</v>
+      </c>
+      <c r="C173" t="s">
+        <v>387</v>
+      </c>
+      <c r="D173" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173" t="s">
+        <v>8</v>
+      </c>
+      <c r="G173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B174" t="s">
+        <v>388</v>
+      </c>
+      <c r="C174" t="s">
+        <v>389</v>
+      </c>
+      <c r="D174" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" t="s">
+        <v>37</v>
+      </c>
+      <c r="F174" t="s">
+        <v>8</v>
+      </c>
+      <c r="G174" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B175" t="s">
+        <v>390</v>
+      </c>
+      <c r="C175" t="s">
+        <v>391</v>
+      </c>
+      <c r="D175" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" t="s">
+        <v>37</v>
+      </c>
+      <c r="F175" t="s">
+        <v>392</v>
+      </c>
+      <c r="G175" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B176" t="s">
+        <v>393</v>
+      </c>
+      <c r="C176" t="s">
+        <v>394</v>
+      </c>
+      <c r="D176" t="s">
+        <v>23</v>
+      </c>
+      <c r="E176" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176" t="s">
+        <v>8</v>
+      </c>
+      <c r="G176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B177" t="s">
+        <v>395</v>
+      </c>
+      <c r="C177" t="s">
+        <v>396</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" t="s">
+        <v>37</v>
+      </c>
+      <c r="F177" t="s">
+        <v>8</v>
+      </c>
+      <c r="G177" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B178" t="s">
+        <v>397</v>
+      </c>
+      <c r="C178" t="s">
+        <v>398</v>
+      </c>
+      <c r="D178" t="s">
+        <v>28</v>
+      </c>
+      <c r="E178" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178" t="s">
+        <v>8</v>
+      </c>
+      <c r="G178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B179" t="s">
+        <v>399</v>
+      </c>
+      <c r="C179" t="s">
+        <v>400</v>
+      </c>
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="s">
+        <v>37</v>
+      </c>
+      <c r="F179" t="s">
+        <v>392</v>
+      </c>
+      <c r="G179" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B180" t="s">
+        <v>401</v>
+      </c>
+      <c r="C180" t="s">
+        <v>402</v>
+      </c>
+      <c r="D180" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" t="s">
+        <v>37</v>
+      </c>
+      <c r="F180" t="s">
+        <v>8</v>
+      </c>
+      <c r="G180" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B181" t="s">
+        <v>403</v>
+      </c>
+      <c r="C181" t="s">
+        <v>404</v>
+      </c>
+      <c r="D181" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" t="s">
+        <v>8</v>
+      </c>
+      <c r="G181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B182" t="s">
+        <v>405</v>
+      </c>
+      <c r="C182" t="s">
+        <v>406</v>
+      </c>
+      <c r="D182" t="s">
+        <v>24</v>
+      </c>
+      <c r="E182" t="s">
+        <v>39</v>
+      </c>
+      <c r="F182" t="s">
+        <v>7</v>
+      </c>
+      <c r="G182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B183" t="s">
+        <v>407</v>
+      </c>
+      <c r="C183" t="s">
+        <v>408</v>
+      </c>
+      <c r="D183" t="s">
+        <v>6</v>
+      </c>
+      <c r="E183" t="s">
+        <v>37</v>
+      </c>
+      <c r="F183" t="s">
+        <v>8</v>
+      </c>
+      <c r="G183" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B184" t="s">
+        <v>409</v>
+      </c>
+      <c r="C184" t="s">
+        <v>410</v>
+      </c>
+      <c r="D184" t="s">
+        <v>25</v>
+      </c>
+      <c r="E184" t="s">
+        <v>39</v>
+      </c>
+      <c r="F184" t="s">
+        <v>7</v>
+      </c>
+      <c r="G184" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B3935-63A7-43F2-A66A-0FAFDECA49C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A041E685-8238-4CDC-93D1-2440A91FF980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="519">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -785,27 +785,12 @@
     <t>RO AMARO DECORACOES LTDA</t>
   </si>
   <si>
-    <t>35448429000120</t>
-  </si>
-  <si>
-    <t>A P DE OLIVEIRA DRINKS</t>
-  </si>
-  <si>
-    <t>61243990000183</t>
-  </si>
-  <si>
-    <t>23805136000174</t>
-  </si>
-  <si>
     <t>47021542000104</t>
   </si>
   <si>
     <t>47.021.542 MARCELO SEBASTIAO DA SILVA</t>
   </si>
   <si>
-    <t>VISAO ATACADO 2025 LTDA</t>
-  </si>
-  <si>
     <t>53169061000143</t>
   </si>
   <si>
@@ -863,9 +848,6 @@
     <t>JOAO AUGUSTO GUSMIN</t>
   </si>
   <si>
-    <t>Mensageria</t>
-  </si>
-  <si>
     <t>63516613000104</t>
   </si>
   <si>
@@ -974,9 +956,6 @@
     <t>48.972.361 MARCOS JUNIOR LEMOS QUADROS</t>
   </si>
   <si>
-    <t>MARCO AURELIO FERNANDESQUADROS</t>
-  </si>
-  <si>
     <t>53945967000102</t>
   </si>
   <si>
@@ -1272,6 +1251,351 @@
   </si>
   <si>
     <t>58.325.459 GENAILDO DE SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>INVÁLIDA</t>
+  </si>
+  <si>
+    <t>MENSAGERIA</t>
+  </si>
+  <si>
+    <t>46479453000143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIVAL GOMES DA SILVA </t>
+  </si>
+  <si>
+    <t>51258944000102</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WALLAS DE CARVALHO SOUSA</t>
+  </si>
+  <si>
+    <t>35298474000146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAELA DE JESUS OLIVEIRA </t>
+  </si>
+  <si>
+    <t>49846268000138</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GEOVANNE ELLER REDER</t>
+  </si>
+  <si>
+    <t>64202721000167</t>
+  </si>
+  <si>
+    <t>KAIQUE MORAES SILVA</t>
+  </si>
+  <si>
+    <t>62581381000105</t>
+  </si>
+  <si>
+    <t>ELVANIO KRAMER DOS SANTOS JUNIOR</t>
+  </si>
+  <si>
+    <t>25212344000195</t>
+  </si>
+  <si>
+    <t>TECNOBIKE COMERCIO DE BICICLETAS LTDA</t>
+  </si>
+  <si>
+    <t>31450741000106</t>
+  </si>
+  <si>
+    <t>GABRIEL DA SILVA</t>
+  </si>
+  <si>
+    <t>39500666000144</t>
+  </si>
+  <si>
+    <t>COMERCIAL CARNEIRO LTDA</t>
+  </si>
+  <si>
+    <t>44321202000100</t>
+  </si>
+  <si>
+    <t>ANDRE DA SILVA MARQUES</t>
+  </si>
+  <si>
+    <t>58484027000187</t>
+  </si>
+  <si>
+    <t>V CANDIDO DE COUTO</t>
+  </si>
+  <si>
+    <t>63439209000176</t>
+  </si>
+  <si>
+    <t>ACF TRANSPORTADORA URUPES LTDA</t>
+  </si>
+  <si>
+    <t>60786656000103</t>
+  </si>
+  <si>
+    <t>60.786.656 LUIZ HENRIQUE MONTALVAO SANTOS</t>
+  </si>
+  <si>
+    <t>10143643000229</t>
+  </si>
+  <si>
+    <t>LAIS SANTANA BARBOSA</t>
+  </si>
+  <si>
+    <t>80284276000188</t>
+  </si>
+  <si>
+    <t>AMARILDO PETRY LTDA</t>
+  </si>
+  <si>
+    <t>14011364000181</t>
+  </si>
+  <si>
+    <t>C T MARTINS SEPEDA</t>
+  </si>
+  <si>
+    <t>35577130000176</t>
+  </si>
+  <si>
+    <t>MLC PUBLICIDADE LTDA</t>
+  </si>
+  <si>
+    <t>39589883000152</t>
+  </si>
+  <si>
+    <t>MIRIAN PIRES APOIO E GESTAO DA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>63879986000131</t>
+  </si>
+  <si>
+    <t>FARMARCIA BEM ESTAR LTDA</t>
+  </si>
+  <si>
+    <t>66082839000124</t>
+  </si>
+  <si>
+    <t>CORREIRA E LUSTOSA LTDA</t>
+  </si>
+  <si>
+    <t>33014070000158</t>
+  </si>
+  <si>
+    <t>M. M DOS ANJOS SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>43732109000126</t>
+  </si>
+  <si>
+    <t>LOTEAMENTO CHACARAS PORTAL DE VERTENTES LTDA</t>
+  </si>
+  <si>
+    <t>55569973000138</t>
+  </si>
+  <si>
+    <t>ERREJOTA PETISCO BURGUER LTDA</t>
+  </si>
+  <si>
+    <t>13805274000108</t>
+  </si>
+  <si>
+    <t>BOMFIM ASSESSORIA E SERVICOS ADMINISTRATIVOS LTDA</t>
+  </si>
+  <si>
+    <t>10143643000148</t>
+  </si>
+  <si>
+    <t>15199705000157</t>
+  </si>
+  <si>
+    <t>ELETRO MASPI LTDA</t>
+  </si>
+  <si>
+    <t>05098154000181</t>
+  </si>
+  <si>
+    <t>EMPREITEIRA DE OBRAS A M FE LTDA</t>
+  </si>
+  <si>
+    <t>58709343000100</t>
+  </si>
+  <si>
+    <t>N P DOS SANTOS</t>
+  </si>
+  <si>
+    <t>56906839000148</t>
+  </si>
+  <si>
+    <t>56.906.839 NAJARA NASCIMENTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>10973804000120</t>
+  </si>
+  <si>
+    <t>M.D.R. AUTOMACAO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>63298527000164</t>
+  </si>
+  <si>
+    <t>63.298.527 BRENO HENRIQUE ALVES DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>61528372000180</t>
+  </si>
+  <si>
+    <t>JL PALLETS E TRANSPORTE LTDA</t>
+  </si>
+  <si>
+    <t>54661682000102</t>
+  </si>
+  <si>
+    <t>54.661.682 SEVERINA ALEXANDRINA HOLANDA NETA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>17160132000183</t>
+  </si>
+  <si>
+    <t>COMERCIAL ASSUNCAO LTDA</t>
+  </si>
+  <si>
+    <t>37145793000147</t>
+  </si>
+  <si>
+    <t>MJS USINAGEM E TORNEARIA LTDA</t>
+  </si>
+  <si>
+    <t>49238526000101</t>
+  </si>
+  <si>
+    <t>DOIS A TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>58022498000173</t>
+  </si>
+  <si>
+    <t>58.022.498 VAGNER DA SILVA NONATO</t>
+  </si>
+  <si>
+    <t>34810659000125</t>
+  </si>
+  <si>
+    <t>CARLINDA CORDEIRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>39328139000102</t>
+  </si>
+  <si>
+    <t>R FABIANO VAZ NEPOMUCENO CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>31679708000144</t>
+  </si>
+  <si>
+    <t>FAMILIA NUNES PROMOCAO DE VENDAS E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>32901525000194</t>
+  </si>
+  <si>
+    <t>L. RODRIGUES GOMES JUNIOR</t>
+  </si>
+  <si>
+    <t>55991389000176</t>
+  </si>
+  <si>
+    <t>55.991.389 LUCAS PIRES SANTARIOSI</t>
+  </si>
+  <si>
+    <t>41422796000158</t>
+  </si>
+  <si>
+    <t>41.422.796 SILVANA SILVA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>63998951000111</t>
+  </si>
+  <si>
+    <t>L. A. BORTOLANZA</t>
+  </si>
+  <si>
+    <t>14349731000151</t>
+  </si>
+  <si>
+    <t>VANESSA A. F. GOMES BRINQUEDOS</t>
+  </si>
+  <si>
+    <t>33907836000123</t>
+  </si>
+  <si>
+    <t>AUGUSTO CEZAR SANTOS FREITAS</t>
+  </si>
+  <si>
+    <t>10393175000160</t>
+  </si>
+  <si>
+    <t>PIATA APLICACAO DE REVESTIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>51870072000120</t>
+  </si>
+  <si>
+    <t>ANTONIO F SOARES REFORMAS &amp; CONST EM GERAIS LTDA</t>
+  </si>
+  <si>
+    <t>21301911000129</t>
+  </si>
+  <si>
+    <t>RCBN PLANEJAMENTO E APOIO ADMINISTRATIVO LTDA</t>
+  </si>
+  <si>
+    <t>61302563000129</t>
+  </si>
+  <si>
+    <t>ATELIER CASA DE CARNE LTDA</t>
+  </si>
+  <si>
+    <t>57737319000111</t>
+  </si>
+  <si>
+    <t>R. DA S. JORGE</t>
+  </si>
+  <si>
+    <t>43016670000109</t>
+  </si>
+  <si>
+    <t>LOBAO BEERS LTDA</t>
+  </si>
+  <si>
+    <t>59292654000189</t>
+  </si>
+  <si>
+    <t>VANESSA V DE CASTRO</t>
+  </si>
+  <si>
+    <t>34704614000176</t>
+  </si>
+  <si>
+    <t>CR ESPORTES &amp; MARKETING AGENCIAMENTO ESPORTIVO LTDA</t>
+  </si>
+  <si>
+    <t>15367532000139</t>
+  </si>
+  <si>
+    <t>GLAGAU &amp; AGUILHER LTDA</t>
+  </si>
+  <si>
+    <t>39296716000113</t>
+  </si>
+  <si>
+    <t>39.296.716 EDENA CORDEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>31743612000106</t>
+  </si>
+  <si>
+    <t>VALERIO BELISARIO CRUZ LTDA</t>
   </si>
 </sst>
 </file>
@@ -1644,12 +1968,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
@@ -1756,7 +2080,7 @@
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2183,22 +2507,22 @@
         <v>46113</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2209,10 +2533,10 @@
         <v>46113</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -2235,22 +2559,22 @@
         <v>46113</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2261,16 +2585,16 @@
         <v>46113</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -2287,16 +2611,16 @@
         <v>46113</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -2313,22 +2637,22 @@
         <v>46113</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
         <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2339,16 +2663,16 @@
         <v>46113</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -2365,22 +2689,22 @@
         <v>46113</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2391,13 +2715,13 @@
         <v>46113</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E29" t="s">
         <v>37</v>
@@ -2406,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2417,13 +2741,13 @@
         <v>46113</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E30" t="s">
         <v>37</v>
@@ -2443,22 +2767,22 @@
         <v>46113</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2469,13 +2793,13 @@
         <v>46113</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
         <v>37</v>
@@ -2495,19 +2819,19 @@
         <v>46113</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
@@ -2521,22 +2845,22 @@
         <v>46113</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2547,16 +2871,16 @@
         <v>46113</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -2573,22 +2897,22 @@
         <v>46113</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2596,22 +2920,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s">
         <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
@@ -2622,19 +2946,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
         <v>8</v>
@@ -2651,19 +2975,19 @@
         <v>46114</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -2677,16 +3001,16 @@
         <v>46114</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
         <v>8</v>
@@ -2703,22 +3027,22 @@
         <v>46114</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2729,19 +3053,19 @@
         <v>46114</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" t="s">
         <v>18</v>
@@ -2755,22 +3079,22 @@
         <v>46114</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2781,19 +3105,19 @@
         <v>46114</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
@@ -2807,22 +3131,22 @@
         <v>46114</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
         <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2833,13 +3157,13 @@
         <v>46114</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
         <v>37</v>
@@ -2848,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="G46" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2859,13 +3183,13 @@
         <v>46114</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E47" t="s">
         <v>39</v>
@@ -2874,7 +3198,7 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2885,10 +3209,10 @@
         <v>46114</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -2911,22 +3235,22 @@
         <v>46114</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F49" t="s">
         <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2937,22 +3261,22 @@
         <v>46114</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2963,13 +3287,13 @@
         <v>46114</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
         <v>37</v>
@@ -2989,22 +3313,22 @@
         <v>46114</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -3015,19 +3339,19 @@
         <v>46114</v>
       </c>
       <c r="B53" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" t="s">
         <v>18</v>
@@ -3041,16 +3365,16 @@
         <v>46114</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -3067,13 +3391,13 @@
         <v>46114</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
         <v>39</v>
@@ -3093,13 +3417,13 @@
         <v>46114</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E56" t="s">
         <v>39</v>
@@ -3119,19 +3443,19 @@
         <v>46114</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
@@ -3145,16 +3469,16 @@
         <v>46114</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F58" t="s">
         <v>8</v>
@@ -3171,13 +3495,13 @@
         <v>46114</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
         <v>37</v>
@@ -3197,13 +3521,13 @@
         <v>46114</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
         <v>37</v>
@@ -3223,22 +3547,22 @@
         <v>46114</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3249,10 +3573,10 @@
         <v>46114</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="D62" t="s">
         <v>23</v>
@@ -3275,22 +3599,22 @@
         <v>46114</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D63" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3301,13 +3625,13 @@
         <v>46114</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E64" t="s">
         <v>37</v>
@@ -3327,16 +3651,16 @@
         <v>46114</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F65" t="s">
         <v>8</v>
@@ -3353,16 +3677,16 @@
         <v>46114</v>
       </c>
       <c r="B66" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D66" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F66" t="s">
         <v>8</v>
@@ -3379,19 +3703,19 @@
         <v>46114</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E67" t="s">
         <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G67" t="s">
         <v>18</v>
@@ -3405,13 +3729,13 @@
         <v>46114</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E68" t="s">
         <v>39</v>
@@ -3420,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3431,19 +3755,19 @@
         <v>46114</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G69" t="s">
         <v>18</v>
@@ -3457,25 +3781,25 @@
         <v>46114</v>
       </c>
       <c r="B70" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C70" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E70" t="s">
         <v>39</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="H70" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -3483,19 +3807,19 @@
         <v>46114</v>
       </c>
       <c r="B71" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C71" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E71" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -3509,25 +3833,22 @@
         <v>46114</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C72" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D72" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E72" t="s">
         <v>39</v>
       </c>
       <c r="F72" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G72" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" t="s">
-        <v>30</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -3535,19 +3856,19 @@
         <v>46114</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G73" t="s">
         <v>18</v>
@@ -3561,22 +3882,25 @@
         <v>46114</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C74" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D74" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F74" t="s">
         <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>234</v>
+        <v>18</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -3584,13 +3908,13 @@
         <v>46114</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C75" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E75" t="s">
         <v>37</v>
@@ -3610,13 +3934,13 @@
         <v>46114</v>
       </c>
       <c r="B76" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C76" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s">
         <v>37</v>
@@ -3636,10 +3960,10 @@
         <v>46114</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -3662,13 +3986,13 @@
         <v>46114</v>
       </c>
       <c r="B78" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
         <v>37</v>
@@ -3688,22 +4012,22 @@
         <v>46114</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3714,13 +4038,13 @@
         <v>46114</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D80" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
         <v>37</v>
@@ -3740,22 +4064,22 @@
         <v>46114</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C81" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F81" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G81" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3766,13 +4090,13 @@
         <v>46114</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C82" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E82" t="s">
         <v>37</v>
@@ -3792,13 +4116,13 @@
         <v>46114</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C83" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E83" t="s">
         <v>37</v>
@@ -3818,13 +4142,13 @@
         <v>46114</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C84" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E84" t="s">
         <v>37</v>
@@ -3844,13 +4168,13 @@
         <v>46114</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C85" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D85" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
         <v>37</v>
@@ -3859,7 +4183,7 @@
         <v>8</v>
       </c>
       <c r="G85" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3870,13 +4194,13 @@
         <v>46114</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C86" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E86" t="s">
         <v>37</v>
@@ -3896,13 +4220,13 @@
         <v>46114</v>
       </c>
       <c r="B87" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E87" t="s">
         <v>37</v>
@@ -3922,19 +4246,19 @@
         <v>46114</v>
       </c>
       <c r="B88" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D88" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G88" t="s">
         <v>18</v>
@@ -3948,22 +4272,22 @@
         <v>46114</v>
       </c>
       <c r="B89" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C89" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F89" t="s">
         <v>8</v>
       </c>
       <c r="G89" t="s">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3974,19 +4298,19 @@
         <v>46114</v>
       </c>
       <c r="B90" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D90" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F90" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
@@ -4000,22 +4324,22 @@
         <v>46114</v>
       </c>
       <c r="B91" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C91" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
         <v>39</v>
       </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -4026,10 +4350,10 @@
         <v>46114</v>
       </c>
       <c r="B92" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
@@ -4052,19 +4376,19 @@
         <v>46114</v>
       </c>
       <c r="B93" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C93" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D93" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G93" t="s">
         <v>18</v>
@@ -4078,13 +4402,13 @@
         <v>46114</v>
       </c>
       <c r="B94" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C94" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E94" t="s">
         <v>37</v>
@@ -4104,16 +4428,16 @@
         <v>46114</v>
       </c>
       <c r="B95" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C95" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E95" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F95" t="s">
         <v>8</v>
@@ -4130,13 +4454,13 @@
         <v>46114</v>
       </c>
       <c r="B96" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C96" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D96" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
         <v>37</v>
@@ -4153,22 +4477,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C97" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
         <v>39</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G97" t="s">
         <v>18</v>
@@ -4179,16 +4503,16 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B98" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C98" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
         <v>37</v>
@@ -4208,19 +4532,19 @@
         <v>46118</v>
       </c>
       <c r="B99" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F99" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G99" t="s">
         <v>18</v>
@@ -4234,19 +4558,19 @@
         <v>46118</v>
       </c>
       <c r="B100" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C100" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D100" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>243</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
@@ -4260,16 +4584,16 @@
         <v>46118</v>
       </c>
       <c r="B101" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D101" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
         <v>8</v>
@@ -4286,19 +4610,19 @@
         <v>46118</v>
       </c>
       <c r="B102" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D102" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>243</v>
+        <v>8</v>
       </c>
       <c r="G102" t="s">
         <v>18</v>
@@ -4312,16 +4636,16 @@
         <v>46118</v>
       </c>
       <c r="B103" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C103" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
@@ -4338,13 +4662,13 @@
         <v>46118</v>
       </c>
       <c r="B104" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C104" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D104" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E104" t="s">
         <v>37</v>
@@ -4370,7 +4694,7 @@
         <v>253</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E105" t="s">
         <v>37</v>
@@ -4380,6 +4704,9 @@
       </c>
       <c r="G105" t="s">
         <v>18</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -4387,22 +4714,25 @@
         <v>46118</v>
       </c>
       <c r="B106" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C106" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F106" t="s">
         <v>8</v>
       </c>
       <c r="G106" t="s">
         <v>18</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -4410,22 +4740,25 @@
         <v>46118</v>
       </c>
       <c r="B107" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C107" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E107" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F107" t="s">
         <v>8</v>
       </c>
       <c r="G107" t="s">
         <v>18</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -4433,13 +4766,13 @@
         <v>46118</v>
       </c>
       <c r="B108" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C108" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
         <v>37</v>
@@ -4449,6 +4782,9 @@
       </c>
       <c r="G108" t="s">
         <v>18</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -4456,22 +4792,25 @@
         <v>46118</v>
       </c>
       <c r="B109" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C109" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D109" t="s">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="E109" t="s">
         <v>37</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -4479,22 +4818,25 @@
         <v>46118</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C110" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>404</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -4502,13 +4844,13 @@
         <v>46118</v>
       </c>
       <c r="B111" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E111" t="s">
         <v>37</v>
@@ -4518,6 +4860,9 @@
       </c>
       <c r="G111" t="s">
         <v>18</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -4525,516 +4870,582 @@
         <v>46118</v>
       </c>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C112" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" t="s">
+        <v>405</v>
+      </c>
+      <c r="G112" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>269</v>
+      </c>
+      <c r="C113" t="s">
+        <v>270</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" t="s">
+        <v>37</v>
+      </c>
+      <c r="F113" t="s">
+        <v>8</v>
+      </c>
+      <c r="G113" t="s">
+        <v>21</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B114" t="s">
+        <v>271</v>
+      </c>
+      <c r="C114" t="s">
+        <v>272</v>
+      </c>
+      <c r="D114" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" t="s">
+        <v>8</v>
+      </c>
+      <c r="G114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B115" t="s">
+        <v>273</v>
+      </c>
+      <c r="C115" t="s">
+        <v>274</v>
+      </c>
+      <c r="D115" t="s">
+        <v>262</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" t="s">
+        <v>8</v>
+      </c>
+      <c r="G115" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B116" t="s">
+        <v>275</v>
+      </c>
+      <c r="C116" t="s">
+        <v>276</v>
+      </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" t="s">
+        <v>7</v>
+      </c>
+      <c r="G116" t="s">
+        <v>21</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B117" t="s">
+        <v>277</v>
+      </c>
+      <c r="C117" t="s">
+        <v>278</v>
+      </c>
+      <c r="D117" t="s">
+        <v>262</v>
+      </c>
+      <c r="E117" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" t="s">
+        <v>8</v>
+      </c>
+      <c r="G117" t="s">
+        <v>18</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>279</v>
+      </c>
+      <c r="C118" t="s">
+        <v>280</v>
+      </c>
+      <c r="D118" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" t="s">
+        <v>8</v>
+      </c>
+      <c r="G118" t="s">
+        <v>21</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>281</v>
+      </c>
+      <c r="C119" t="s">
+        <v>282</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" t="s">
+        <v>8</v>
+      </c>
+      <c r="G119" t="s">
+        <v>18</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>283</v>
+      </c>
+      <c r="C120" t="s">
+        <v>284</v>
+      </c>
+      <c r="D120" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120" t="s">
+        <v>8</v>
+      </c>
+      <c r="G120" t="s">
+        <v>18</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B121" t="s">
+        <v>285</v>
+      </c>
+      <c r="C121" t="s">
+        <v>286</v>
+      </c>
+      <c r="D121" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" t="s">
+        <v>8</v>
+      </c>
+      <c r="G121" t="s">
+        <v>18</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B122" t="s">
+        <v>287</v>
+      </c>
+      <c r="C122" t="s">
+        <v>288</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" t="s">
+        <v>8</v>
+      </c>
+      <c r="G122" t="s">
+        <v>18</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B123" t="s">
+        <v>289</v>
+      </c>
+      <c r="C123" t="s">
+        <v>290</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" t="s">
+        <v>8</v>
+      </c>
+      <c r="G123" t="s">
+        <v>21</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B124" t="s">
+        <v>291</v>
+      </c>
+      <c r="C124" t="s">
+        <v>292</v>
+      </c>
+      <c r="D124" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" t="s">
+        <v>8</v>
+      </c>
+      <c r="G124" t="s">
+        <v>18</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B125" t="s">
+        <v>293</v>
+      </c>
+      <c r="C125" t="s">
+        <v>294</v>
+      </c>
+      <c r="D125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" t="s">
+        <v>8</v>
+      </c>
+      <c r="G125" t="s">
+        <v>18</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B126" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" t="s">
+        <v>296</v>
+      </c>
+      <c r="D126" t="s">
+        <v>22</v>
+      </c>
+      <c r="E126" t="s">
+        <v>39</v>
+      </c>
+      <c r="F126" t="s">
+        <v>7</v>
+      </c>
+      <c r="G126" t="s">
+        <v>18</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B127" t="s">
+        <v>297</v>
+      </c>
+      <c r="C127" t="s">
+        <v>298</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" t="s">
+        <v>39</v>
+      </c>
+      <c r="F127" t="s">
+        <v>7</v>
+      </c>
+      <c r="G127" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B128" t="s">
+        <v>299</v>
+      </c>
+      <c r="C128" t="s">
+        <v>300</v>
+      </c>
+      <c r="D128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" t="s">
+        <v>37</v>
+      </c>
+      <c r="F128" t="s">
+        <v>8</v>
+      </c>
+      <c r="G128" t="s">
+        <v>18</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B129" t="s">
+        <v>301</v>
+      </c>
+      <c r="C129" t="s">
+        <v>302</v>
+      </c>
+      <c r="D129" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129" t="s">
+        <v>39</v>
+      </c>
+      <c r="F129" t="s">
+        <v>7</v>
+      </c>
+      <c r="G129" t="s">
+        <v>18</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B130" t="s">
+        <v>303</v>
+      </c>
+      <c r="C130" t="s">
+        <v>304</v>
+      </c>
+      <c r="D130" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" t="s">
+        <v>37</v>
+      </c>
+      <c r="F130" t="s">
+        <v>8</v>
+      </c>
+      <c r="G130" t="s">
+        <v>18</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B131" t="s">
+        <v>305</v>
+      </c>
+      <c r="C131" t="s">
+        <v>306</v>
+      </c>
+      <c r="D131" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" t="s">
+        <v>37</v>
+      </c>
+      <c r="F131" t="s">
+        <v>8</v>
+      </c>
+      <c r="G131" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B132" t="s">
+        <v>307</v>
+      </c>
+      <c r="C132" t="s">
+        <v>308</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" t="s">
+        <v>37</v>
+      </c>
+      <c r="F132" t="s">
+        <v>8</v>
+      </c>
+      <c r="G132" t="s">
+        <v>18</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B133" t="s">
+        <v>309</v>
+      </c>
+      <c r="C133" t="s">
+        <v>310</v>
+      </c>
+      <c r="D133" t="s">
         <v>12</v>
       </c>
-      <c r="E112" t="s">
-        <v>37</v>
-      </c>
-      <c r="F112" t="s">
-        <v>8</v>
-      </c>
-      <c r="G112" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B113" t="s">
-        <v>265</v>
-      </c>
-      <c r="C113" t="s">
-        <v>266</v>
-      </c>
-      <c r="D113" t="s">
-        <v>267</v>
-      </c>
-      <c r="E113" t="s">
-        <v>37</v>
-      </c>
-      <c r="F113" t="s">
-        <v>7</v>
-      </c>
-      <c r="G113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B114" t="s">
-        <v>268</v>
-      </c>
-      <c r="C114" t="s">
-        <v>269</v>
-      </c>
-      <c r="D114" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" t="s">
-        <v>39</v>
-      </c>
-      <c r="F114" t="s">
-        <v>7</v>
-      </c>
-      <c r="G114" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B115" t="s">
-        <v>270</v>
-      </c>
-      <c r="C115" t="s">
-        <v>271</v>
-      </c>
-      <c r="D115" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" t="s">
-        <v>37</v>
-      </c>
-      <c r="F115" t="s">
-        <v>8</v>
-      </c>
-      <c r="G115" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B116" t="s">
-        <v>272</v>
-      </c>
-      <c r="C116" t="s">
-        <v>273</v>
-      </c>
-      <c r="D116" t="s">
-        <v>14</v>
-      </c>
-      <c r="E116" t="s">
-        <v>37</v>
-      </c>
-      <c r="F116" t="s">
-        <v>274</v>
-      </c>
-      <c r="G116" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B117" t="s">
-        <v>275</v>
-      </c>
-      <c r="C117" t="s">
-        <v>276</v>
-      </c>
-      <c r="D117" t="s">
-        <v>23</v>
-      </c>
-      <c r="E117" t="s">
-        <v>37</v>
-      </c>
-      <c r="F117" t="s">
-        <v>8</v>
-      </c>
-      <c r="G117" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B118" t="s">
-        <v>277</v>
-      </c>
-      <c r="C118" t="s">
-        <v>278</v>
-      </c>
-      <c r="D118" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" t="s">
-        <v>37</v>
-      </c>
-      <c r="F118" t="s">
-        <v>8</v>
-      </c>
-      <c r="G118" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B119" t="s">
-        <v>279</v>
-      </c>
-      <c r="C119" t="s">
-        <v>280</v>
-      </c>
-      <c r="D119" t="s">
-        <v>267</v>
-      </c>
-      <c r="E119" t="s">
-        <v>37</v>
-      </c>
-      <c r="F119" t="s">
-        <v>8</v>
-      </c>
-      <c r="G119" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B120" t="s">
-        <v>281</v>
-      </c>
-      <c r="C120" t="s">
-        <v>282</v>
-      </c>
-      <c r="D120" t="s">
-        <v>24</v>
-      </c>
-      <c r="E120" t="s">
-        <v>39</v>
-      </c>
-      <c r="F120" t="s">
-        <v>7</v>
-      </c>
-      <c r="G120" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B121" t="s">
-        <v>283</v>
-      </c>
-      <c r="C121" t="s">
-        <v>284</v>
-      </c>
-      <c r="D121" t="s">
-        <v>267</v>
-      </c>
-      <c r="E121" t="s">
-        <v>37</v>
-      </c>
-      <c r="F121" t="s">
-        <v>8</v>
-      </c>
-      <c r="G121" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B122" t="s">
-        <v>285</v>
-      </c>
-      <c r="C122" t="s">
-        <v>286</v>
-      </c>
-      <c r="D122" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" t="s">
-        <v>37</v>
-      </c>
-      <c r="F122" t="s">
-        <v>8</v>
-      </c>
-      <c r="G122" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B123" t="s">
-        <v>287</v>
-      </c>
-      <c r="C123" t="s">
-        <v>288</v>
-      </c>
-      <c r="D123" t="s">
-        <v>16</v>
-      </c>
-      <c r="E123" t="s">
-        <v>37</v>
-      </c>
-      <c r="F123" t="s">
-        <v>8</v>
-      </c>
-      <c r="G123" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B124" t="s">
-        <v>289</v>
-      </c>
-      <c r="C124" t="s">
-        <v>290</v>
-      </c>
-      <c r="D124" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" t="s">
-        <v>37</v>
-      </c>
-      <c r="F124" t="s">
-        <v>8</v>
-      </c>
-      <c r="G124" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B125" t="s">
-        <v>291</v>
-      </c>
-      <c r="C125" t="s">
-        <v>292</v>
-      </c>
-      <c r="D125" t="s">
-        <v>28</v>
-      </c>
-      <c r="E125" t="s">
-        <v>37</v>
-      </c>
-      <c r="F125" t="s">
-        <v>8</v>
-      </c>
-      <c r="G125" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B126" t="s">
-        <v>293</v>
-      </c>
-      <c r="C126" t="s">
-        <v>294</v>
-      </c>
-      <c r="D126" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" t="s">
-        <v>37</v>
-      </c>
-      <c r="F126" t="s">
-        <v>8</v>
-      </c>
-      <c r="G126" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B127" t="s">
-        <v>295</v>
-      </c>
-      <c r="C127" t="s">
-        <v>296</v>
-      </c>
-      <c r="D127" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" t="s">
-        <v>37</v>
-      </c>
-      <c r="F127" t="s">
-        <v>8</v>
-      </c>
-      <c r="G127" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B128" t="s">
-        <v>297</v>
-      </c>
-      <c r="C128" t="s">
-        <v>298</v>
-      </c>
-      <c r="D128" t="s">
-        <v>28</v>
-      </c>
-      <c r="E128" t="s">
-        <v>37</v>
-      </c>
-      <c r="F128" t="s">
-        <v>8</v>
-      </c>
-      <c r="G128" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B129" t="s">
-        <v>299</v>
-      </c>
-      <c r="C129" t="s">
-        <v>300</v>
-      </c>
-      <c r="D129" t="s">
-        <v>16</v>
-      </c>
-      <c r="E129" t="s">
-        <v>37</v>
-      </c>
-      <c r="F129" t="s">
-        <v>8</v>
-      </c>
-      <c r="G129" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B130" t="s">
-        <v>301</v>
-      </c>
-      <c r="C130" t="s">
-        <v>302</v>
-      </c>
-      <c r="D130" t="s">
-        <v>22</v>
-      </c>
-      <c r="E130" t="s">
-        <v>39</v>
-      </c>
-      <c r="F130" t="s">
-        <v>7</v>
-      </c>
-      <c r="G130" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B131" t="s">
-        <v>303</v>
-      </c>
-      <c r="C131" t="s">
-        <v>304</v>
-      </c>
-      <c r="D131" t="s">
-        <v>24</v>
-      </c>
-      <c r="E131" t="s">
-        <v>39</v>
-      </c>
-      <c r="F131" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B132" t="s">
-        <v>305</v>
-      </c>
-      <c r="C132" t="s">
-        <v>306</v>
-      </c>
-      <c r="D132" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" t="s">
-        <v>37</v>
-      </c>
-      <c r="F132" t="s">
-        <v>8</v>
-      </c>
-      <c r="G132" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B133" t="s">
-        <v>307</v>
-      </c>
-      <c r="C133" t="s">
-        <v>308</v>
-      </c>
-      <c r="D133" t="s">
-        <v>24</v>
-      </c>
       <c r="E133" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F133" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G133" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46118</v>
       </c>
       <c r="B134" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C134" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
@@ -5046,136 +5457,154 @@
         <v>8</v>
       </c>
       <c r="G134" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46118</v>
       </c>
       <c r="B135" t="s">
-        <v>251</v>
+        <v>313</v>
       </c>
       <c r="C135" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D135" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" t="s">
+        <v>37</v>
+      </c>
+      <c r="F135" t="s">
+        <v>8</v>
+      </c>
+      <c r="G135" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B136" t="s">
+        <v>315</v>
+      </c>
+      <c r="C136" t="s">
+        <v>316</v>
+      </c>
+      <c r="D136" t="s">
+        <v>6</v>
+      </c>
+      <c r="E136" t="s">
+        <v>37</v>
+      </c>
+      <c r="F136" t="s">
+        <v>8</v>
+      </c>
+      <c r="G136" t="s">
+        <v>21</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B137" t="s">
+        <v>317</v>
+      </c>
+      <c r="C137" t="s">
+        <v>318</v>
+      </c>
+      <c r="D137" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" t="s">
+        <v>37</v>
+      </c>
+      <c r="F137" t="s">
+        <v>8</v>
+      </c>
+      <c r="G137" t="s">
+        <v>18</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B138" t="s">
+        <v>319</v>
+      </c>
+      <c r="C138" t="s">
+        <v>320</v>
+      </c>
+      <c r="D138" t="s">
         <v>9</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E138" t="s">
         <v>39</v>
       </c>
-      <c r="F135" t="s">
-        <v>8</v>
-      </c>
-      <c r="G135" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B136" t="s">
-        <v>312</v>
-      </c>
-      <c r="C136" t="s">
-        <v>313</v>
-      </c>
-      <c r="D136" t="s">
-        <v>28</v>
-      </c>
-      <c r="E136" t="s">
-        <v>37</v>
-      </c>
-      <c r="F136" t="s">
-        <v>8</v>
-      </c>
-      <c r="G136" t="s">
+      <c r="F138" t="s">
+        <v>7</v>
+      </c>
+      <c r="G138" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B137" t="s">
-        <v>314</v>
-      </c>
-      <c r="C137" t="s">
-        <v>315</v>
-      </c>
-      <c r="D137" t="s">
-        <v>23</v>
-      </c>
-      <c r="E137" t="s">
-        <v>37</v>
-      </c>
-      <c r="F137" t="s">
-        <v>8</v>
-      </c>
-      <c r="G137" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B138" t="s">
-        <v>316</v>
-      </c>
-      <c r="C138" t="s">
-        <v>317</v>
-      </c>
-      <c r="D138" t="s">
-        <v>12</v>
-      </c>
-      <c r="E138" t="s">
-        <v>37</v>
-      </c>
-      <c r="F138" t="s">
-        <v>8</v>
-      </c>
-      <c r="G138" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46118</v>
       </c>
       <c r="B139" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C139" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E139" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F139" t="s">
         <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46118</v>
       </c>
       <c r="B140" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C140" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D140" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
         <v>37</v>
@@ -5186,19 +5615,22 @@
       <c r="G140" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46118</v>
       </c>
       <c r="B141" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C141" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D141" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E141" t="s">
         <v>37</v>
@@ -5207,24 +5639,27 @@
         <v>8</v>
       </c>
       <c r="G141" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46118</v>
       </c>
       <c r="B142" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C142" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D142" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -5232,502 +5667,565 @@
       <c r="G142" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46118</v>
       </c>
       <c r="B143" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C143" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G143" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46118</v>
       </c>
       <c r="B144" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C144" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D144" t="s">
+        <v>15</v>
+      </c>
+      <c r="E144" t="s">
+        <v>37</v>
+      </c>
+      <c r="F144" t="s">
+        <v>8</v>
+      </c>
+      <c r="G144" t="s">
+        <v>18</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B145" t="s">
+        <v>333</v>
+      </c>
+      <c r="C145" t="s">
+        <v>334</v>
+      </c>
+      <c r="D145" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" t="s">
+        <v>37</v>
+      </c>
+      <c r="F145" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B146" t="s">
+        <v>335</v>
+      </c>
+      <c r="C146" t="s">
+        <v>336</v>
+      </c>
+      <c r="D146" t="s">
+        <v>28</v>
+      </c>
+      <c r="E146" t="s">
+        <v>37</v>
+      </c>
+      <c r="F146" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" t="s">
+        <v>18</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="s">
+        <v>337</v>
+      </c>
+      <c r="C147" t="s">
+        <v>338</v>
+      </c>
+      <c r="D147" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" t="s">
+        <v>37</v>
+      </c>
+      <c r="F147" t="s">
+        <v>8</v>
+      </c>
+      <c r="G147" t="s">
+        <v>18</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B148" t="s">
+        <v>339</v>
+      </c>
+      <c r="C148" t="s">
+        <v>340</v>
+      </c>
+      <c r="D148" t="s">
         <v>31</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E148" t="s">
         <v>39</v>
       </c>
-      <c r="F144" t="s">
-        <v>8</v>
-      </c>
-      <c r="G144" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B145" t="s">
-        <v>330</v>
-      </c>
-      <c r="C145" t="s">
-        <v>331</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="F148" t="s">
+        <v>8</v>
+      </c>
+      <c r="G148" t="s">
+        <v>21</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B149" t="s">
+        <v>341</v>
+      </c>
+      <c r="C149" t="s">
+        <v>342</v>
+      </c>
+      <c r="D149" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" t="s">
+        <v>37</v>
+      </c>
+      <c r="F149" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B150" t="s">
+        <v>343</v>
+      </c>
+      <c r="C150" t="s">
+        <v>344</v>
+      </c>
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" t="s">
+        <v>37</v>
+      </c>
+      <c r="F150" t="s">
+        <v>8</v>
+      </c>
+      <c r="G150" t="s">
+        <v>18</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B151" t="s">
+        <v>345</v>
+      </c>
+      <c r="C151" t="s">
+        <v>346</v>
+      </c>
+      <c r="D151" t="s">
         <v>14</v>
       </c>
-      <c r="E145" t="s">
-        <v>37</v>
-      </c>
-      <c r="F145" t="s">
-        <v>8</v>
-      </c>
-      <c r="G145" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B146" t="s">
-        <v>332</v>
-      </c>
-      <c r="C146" t="s">
-        <v>333</v>
-      </c>
-      <c r="D146" t="s">
-        <v>15</v>
-      </c>
-      <c r="E146" t="s">
-        <v>37</v>
-      </c>
-      <c r="F146" t="s">
-        <v>8</v>
-      </c>
-      <c r="G146" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B147" t="s">
-        <v>334</v>
-      </c>
-      <c r="C147" t="s">
-        <v>335</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="E151" t="s">
+        <v>37</v>
+      </c>
+      <c r="F151" t="s">
+        <v>8</v>
+      </c>
+      <c r="G151" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B152" t="s">
+        <v>347</v>
+      </c>
+      <c r="C152" t="s">
+        <v>348</v>
+      </c>
+      <c r="D152" t="s">
         <v>31</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E152" t="s">
         <v>39</v>
       </c>
-      <c r="F147" t="s">
-        <v>8</v>
-      </c>
-      <c r="G147" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B148" t="s">
-        <v>336</v>
-      </c>
-      <c r="C148" t="s">
-        <v>337</v>
-      </c>
-      <c r="D148" t="s">
+      <c r="F152" t="s">
+        <v>8</v>
+      </c>
+      <c r="G152" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B153" t="s">
+        <v>349</v>
+      </c>
+      <c r="C153" t="s">
+        <v>350</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>37</v>
+      </c>
+      <c r="F153" t="s">
+        <v>8</v>
+      </c>
+      <c r="G153" t="s">
+        <v>20</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B154" t="s">
+        <v>351</v>
+      </c>
+      <c r="C154" t="s">
+        <v>352</v>
+      </c>
+      <c r="D154" t="s">
+        <v>22</v>
+      </c>
+      <c r="E154" t="s">
+        <v>39</v>
+      </c>
+      <c r="F154" t="s">
+        <v>8</v>
+      </c>
+      <c r="G154" t="s">
+        <v>20</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B155" t="s">
+        <v>353</v>
+      </c>
+      <c r="C155" t="s">
+        <v>354</v>
+      </c>
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" t="s">
+        <v>39</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" t="s">
+        <v>18</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B156" t="s">
+        <v>355</v>
+      </c>
+      <c r="C156" t="s">
+        <v>356</v>
+      </c>
+      <c r="D156" t="s">
+        <v>6</v>
+      </c>
+      <c r="E156" t="s">
+        <v>37</v>
+      </c>
+      <c r="F156" t="s">
+        <v>8</v>
+      </c>
+      <c r="G156" t="s">
+        <v>18</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B157" t="s">
+        <v>357</v>
+      </c>
+      <c r="C157" t="s">
+        <v>358</v>
+      </c>
+      <c r="D157" t="s">
         <v>14</v>
       </c>
-      <c r="E148" t="s">
-        <v>37</v>
-      </c>
-      <c r="F148" t="s">
-        <v>8</v>
-      </c>
-      <c r="G148" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B149" t="s">
-        <v>338</v>
-      </c>
-      <c r="C149" t="s">
-        <v>339</v>
-      </c>
-      <c r="D149" t="s">
-        <v>15</v>
-      </c>
-      <c r="E149" t="s">
-        <v>37</v>
-      </c>
-      <c r="F149" t="s">
-        <v>8</v>
-      </c>
-      <c r="G149" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B150" t="s">
-        <v>340</v>
-      </c>
-      <c r="C150" t="s">
-        <v>341</v>
-      </c>
-      <c r="D150" t="s">
-        <v>16</v>
-      </c>
-      <c r="E150" t="s">
-        <v>37</v>
-      </c>
-      <c r="F150" t="s">
-        <v>8</v>
-      </c>
-      <c r="G150" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B151" t="s">
-        <v>342</v>
-      </c>
-      <c r="C151" t="s">
-        <v>343</v>
-      </c>
-      <c r="D151" t="s">
-        <v>28</v>
-      </c>
-      <c r="E151" t="s">
-        <v>37</v>
-      </c>
-      <c r="F151" t="s">
-        <v>8</v>
-      </c>
-      <c r="G151" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B152" t="s">
-        <v>344</v>
-      </c>
-      <c r="C152" t="s">
-        <v>345</v>
-      </c>
-      <c r="D152" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152" t="s">
-        <v>37</v>
-      </c>
-      <c r="F152" t="s">
-        <v>8</v>
-      </c>
-      <c r="G152" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B153" t="s">
-        <v>346</v>
-      </c>
-      <c r="C153" t="s">
-        <v>347</v>
-      </c>
-      <c r="D153" t="s">
-        <v>31</v>
-      </c>
-      <c r="E153" t="s">
+      <c r="E157" t="s">
+        <v>37</v>
+      </c>
+      <c r="F157" t="s">
+        <v>8</v>
+      </c>
+      <c r="G157" t="s">
+        <v>18</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B158" t="s">
+        <v>359</v>
+      </c>
+      <c r="C158" t="s">
+        <v>360</v>
+      </c>
+      <c r="D158" t="s">
+        <v>40</v>
+      </c>
+      <c r="E158" t="s">
         <v>39</v>
       </c>
-      <c r="F153" t="s">
-        <v>8</v>
-      </c>
-      <c r="G153" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B154" t="s">
-        <v>348</v>
-      </c>
-      <c r="C154" t="s">
-        <v>349</v>
-      </c>
-      <c r="D154" t="s">
-        <v>16</v>
-      </c>
-      <c r="E154" t="s">
-        <v>37</v>
-      </c>
-      <c r="F154" t="s">
-        <v>8</v>
-      </c>
-      <c r="G154" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B155" t="s">
-        <v>350</v>
-      </c>
-      <c r="C155" t="s">
-        <v>351</v>
-      </c>
-      <c r="D155" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" t="s">
-        <v>37</v>
-      </c>
-      <c r="F155" t="s">
-        <v>8</v>
-      </c>
-      <c r="G155" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B156" t="s">
-        <v>352</v>
-      </c>
-      <c r="C156" t="s">
-        <v>353</v>
-      </c>
-      <c r="D156" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156" t="s">
-        <v>37</v>
-      </c>
-      <c r="F156" t="s">
-        <v>8</v>
-      </c>
-      <c r="G156" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B157" t="s">
-        <v>354</v>
-      </c>
-      <c r="C157" t="s">
-        <v>355</v>
-      </c>
-      <c r="D157" t="s">
-        <v>31</v>
-      </c>
-      <c r="E157" t="s">
-        <v>39</v>
-      </c>
-      <c r="F157" t="s">
-        <v>8</v>
-      </c>
-      <c r="G157" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B158" t="s">
-        <v>356</v>
-      </c>
-      <c r="C158" t="s">
-        <v>357</v>
-      </c>
-      <c r="D158" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" t="s">
-        <v>37</v>
-      </c>
       <c r="F158" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G158" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46118</v>
       </c>
       <c r="B159" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C159" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D159" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E159" t="s">
         <v>39</v>
       </c>
       <c r="F159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G159" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46118</v>
       </c>
       <c r="B160" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C160" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s">
+        <v>37</v>
+      </c>
+      <c r="F160" t="s">
+        <v>8</v>
+      </c>
+      <c r="G160" t="s">
+        <v>18</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B161" t="s">
+        <v>365</v>
+      </c>
+      <c r="C161" t="s">
+        <v>366</v>
+      </c>
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="s">
+        <v>37</v>
+      </c>
+      <c r="F161" t="s">
+        <v>8</v>
+      </c>
+      <c r="G161" t="s">
+        <v>18</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B162" t="s">
+        <v>367</v>
+      </c>
+      <c r="C162" t="s">
+        <v>368</v>
+      </c>
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" t="s">
+        <v>37</v>
+      </c>
+      <c r="F162" t="s">
+        <v>8</v>
+      </c>
+      <c r="G162" t="s">
+        <v>404</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B163" t="s">
+        <v>369</v>
+      </c>
+      <c r="C163" t="s">
+        <v>370</v>
+      </c>
+      <c r="D163" t="s">
         <v>24</v>
-      </c>
-      <c r="E160" t="s">
-        <v>39</v>
-      </c>
-      <c r="F160" t="s">
-        <v>7</v>
-      </c>
-      <c r="G160" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B161" t="s">
-        <v>362</v>
-      </c>
-      <c r="C161" t="s">
-        <v>363</v>
-      </c>
-      <c r="D161" t="s">
-        <v>6</v>
-      </c>
-      <c r="E161" t="s">
-        <v>37</v>
-      </c>
-      <c r="F161" t="s">
-        <v>8</v>
-      </c>
-      <c r="G161" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B162" t="s">
-        <v>364</v>
-      </c>
-      <c r="C162" t="s">
-        <v>365</v>
-      </c>
-      <c r="D162" t="s">
-        <v>14</v>
-      </c>
-      <c r="E162" t="s">
-        <v>37</v>
-      </c>
-      <c r="F162" t="s">
-        <v>8</v>
-      </c>
-      <c r="G162" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B163" t="s">
-        <v>366</v>
-      </c>
-      <c r="C163" t="s">
-        <v>367</v>
-      </c>
-      <c r="D163" t="s">
-        <v>40</v>
       </c>
       <c r="E163" t="s">
         <v>39</v>
       </c>
       <c r="F163" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46118</v>
       </c>
       <c r="B164" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C164" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D164" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E164" t="s">
         <v>39</v>
@@ -5736,467 +6234,1754 @@
         <v>7</v>
       </c>
       <c r="G164" t="s">
+        <v>18</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B165" t="s">
+        <v>373</v>
+      </c>
+      <c r="C165" t="s">
+        <v>374</v>
+      </c>
+      <c r="D165" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" t="s">
+        <v>37</v>
+      </c>
+      <c r="F165" t="s">
+        <v>8</v>
+      </c>
+      <c r="G165" t="s">
+        <v>18</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B166" t="s">
+        <v>375</v>
+      </c>
+      <c r="C166" t="s">
+        <v>376</v>
+      </c>
+      <c r="D166" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" t="s">
+        <v>37</v>
+      </c>
+      <c r="F166" t="s">
+        <v>8</v>
+      </c>
+      <c r="G166" t="s">
+        <v>21</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B167" t="s">
+        <v>377</v>
+      </c>
+      <c r="C167" t="s">
+        <v>378</v>
+      </c>
+      <c r="D167" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" t="s">
+        <v>39</v>
+      </c>
+      <c r="F167" t="s">
+        <v>8</v>
+      </c>
+      <c r="G167" t="s">
+        <v>18</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B168" t="s">
+        <v>379</v>
+      </c>
+      <c r="C168" t="s">
+        <v>380</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>37</v>
+      </c>
+      <c r="F168" t="s">
+        <v>8</v>
+      </c>
+      <c r="G168" t="s">
+        <v>18</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B169" t="s">
+        <v>381</v>
+      </c>
+      <c r="C169" t="s">
+        <v>382</v>
+      </c>
+      <c r="D169" t="s">
+        <v>12</v>
+      </c>
+      <c r="E169" t="s">
+        <v>37</v>
+      </c>
+      <c r="F169" t="s">
+        <v>8</v>
+      </c>
+      <c r="G169" t="s">
+        <v>21</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B170" t="s">
+        <v>383</v>
+      </c>
+      <c r="C170" t="s">
+        <v>384</v>
+      </c>
+      <c r="D170" t="s">
+        <v>12</v>
+      </c>
+      <c r="E170" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170" t="s">
+        <v>385</v>
+      </c>
+      <c r="G170" t="s">
+        <v>18</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B171" t="s">
+        <v>386</v>
+      </c>
+      <c r="C171" t="s">
+        <v>387</v>
+      </c>
+      <c r="D171" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" t="s">
+        <v>37</v>
+      </c>
+      <c r="F171" t="s">
+        <v>8</v>
+      </c>
+      <c r="G171" t="s">
+        <v>18</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B172" t="s">
+        <v>388</v>
+      </c>
+      <c r="C172" t="s">
+        <v>389</v>
+      </c>
+      <c r="D172" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" t="s">
+        <v>37</v>
+      </c>
+      <c r="F172" t="s">
+        <v>8</v>
+      </c>
+      <c r="G172" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B173" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" t="s">
+        <v>391</v>
+      </c>
+      <c r="D173" t="s">
+        <v>28</v>
+      </c>
+      <c r="E173" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173" t="s">
+        <v>8</v>
+      </c>
+      <c r="G173" t="s">
+        <v>18</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B174" t="s">
+        <v>392</v>
+      </c>
+      <c r="C174" t="s">
+        <v>393</v>
+      </c>
+      <c r="D174" t="s">
+        <v>19</v>
+      </c>
+      <c r="E174" t="s">
+        <v>37</v>
+      </c>
+      <c r="F174" t="s">
+        <v>385</v>
+      </c>
+      <c r="G174" t="s">
+        <v>18</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B175" t="s">
+        <v>394</v>
+      </c>
+      <c r="C175" t="s">
+        <v>395</v>
+      </c>
+      <c r="D175" t="s">
+        <v>15</v>
+      </c>
+      <c r="E175" t="s">
+        <v>37</v>
+      </c>
+      <c r="F175" t="s">
+        <v>8</v>
+      </c>
+      <c r="G175" t="s">
+        <v>18</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B176" t="s">
+        <v>396</v>
+      </c>
+      <c r="C176" t="s">
+        <v>397</v>
+      </c>
+      <c r="D176" t="s">
+        <v>15</v>
+      </c>
+      <c r="E176" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176" t="s">
+        <v>8</v>
+      </c>
+      <c r="G176" t="s">
+        <v>18</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B177" t="s">
+        <v>398</v>
+      </c>
+      <c r="C177" t="s">
+        <v>399</v>
+      </c>
+      <c r="D177" t="s">
+        <v>24</v>
+      </c>
+      <c r="E177" t="s">
+        <v>39</v>
+      </c>
+      <c r="F177" t="s">
+        <v>7</v>
+      </c>
+      <c r="G177" t="s">
+        <v>18</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B178" t="s">
+        <v>400</v>
+      </c>
+      <c r="C178" t="s">
+        <v>401</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+      <c r="E178" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178" t="s">
+        <v>8</v>
+      </c>
+      <c r="G178" t="s">
+        <v>18</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B179" t="s">
+        <v>402</v>
+      </c>
+      <c r="C179" t="s">
+        <v>403</v>
+      </c>
+      <c r="D179" t="s">
+        <v>25</v>
+      </c>
+      <c r="E179" t="s">
+        <v>39</v>
+      </c>
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+      <c r="G179" t="s">
+        <v>18</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B180" t="s">
+        <v>406</v>
+      </c>
+      <c r="C180" t="s">
+        <v>407</v>
+      </c>
+      <c r="D180" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" t="s">
+        <v>37</v>
+      </c>
+      <c r="F180" t="s">
+        <v>8</v>
+      </c>
+      <c r="G180" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B181" t="s">
+        <v>408</v>
+      </c>
+      <c r="C181" t="s">
+        <v>409</v>
+      </c>
+      <c r="D181" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" t="s">
+        <v>37</v>
+      </c>
+      <c r="F181" t="s">
+        <v>8</v>
+      </c>
+      <c r="G181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B182" t="s">
+        <v>410</v>
+      </c>
+      <c r="C182" t="s">
+        <v>411</v>
+      </c>
+      <c r="D182" t="s">
+        <v>6</v>
+      </c>
+      <c r="E182" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182" t="s">
+        <v>8</v>
+      </c>
+      <c r="G182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B183" t="s">
+        <v>412</v>
+      </c>
+      <c r="C183" t="s">
+        <v>413</v>
+      </c>
+      <c r="D183" t="s">
+        <v>27</v>
+      </c>
+      <c r="E183" t="s">
+        <v>38</v>
+      </c>
+      <c r="F183" t="s">
+        <v>8</v>
+      </c>
+      <c r="G183" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B184" t="s">
+        <v>414</v>
+      </c>
+      <c r="C184" t="s">
+        <v>415</v>
+      </c>
+      <c r="D184" t="s">
+        <v>27</v>
+      </c>
+      <c r="E184" t="s">
+        <v>38</v>
+      </c>
+      <c r="F184" t="s">
+        <v>243</v>
+      </c>
+      <c r="G184" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B185" t="s">
+        <v>416</v>
+      </c>
+      <c r="C185" t="s">
+        <v>417</v>
+      </c>
+      <c r="D185" t="s">
+        <v>27</v>
+      </c>
+      <c r="E185" t="s">
+        <v>38</v>
+      </c>
+      <c r="F185" t="s">
+        <v>243</v>
+      </c>
+      <c r="G185" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B186" t="s">
+        <v>418</v>
+      </c>
+      <c r="C186" t="s">
+        <v>419</v>
+      </c>
+      <c r="D186" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" t="s">
+        <v>37</v>
+      </c>
+      <c r="F186" t="s">
+        <v>8</v>
+      </c>
+      <c r="G186" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B187" t="s">
+        <v>420</v>
+      </c>
+      <c r="C187" t="s">
+        <v>421</v>
+      </c>
+      <c r="D187" t="s">
+        <v>31</v>
+      </c>
+      <c r="E187" t="s">
+        <v>39</v>
+      </c>
+      <c r="F187" t="s">
+        <v>7</v>
+      </c>
+      <c r="G187" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B188" t="s">
+        <v>422</v>
+      </c>
+      <c r="C188" t="s">
+        <v>423</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
+        <v>39</v>
+      </c>
+      <c r="F188" t="s">
+        <v>7</v>
+      </c>
+      <c r="G188" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B165" t="s">
-        <v>370</v>
-      </c>
-      <c r="C165" t="s">
-        <v>371</v>
-      </c>
-      <c r="D165" t="s">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B189" t="s">
+        <v>424</v>
+      </c>
+      <c r="C189" t="s">
+        <v>425</v>
+      </c>
+      <c r="D189" t="s">
+        <v>24</v>
+      </c>
+      <c r="E189" t="s">
+        <v>39</v>
+      </c>
+      <c r="F189" t="s">
+        <v>7</v>
+      </c>
+      <c r="G189" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B190" t="s">
+        <v>426</v>
+      </c>
+      <c r="C190" t="s">
+        <v>427</v>
+      </c>
+      <c r="D190" t="s">
+        <v>28</v>
+      </c>
+      <c r="E190" t="s">
+        <v>37</v>
+      </c>
+      <c r="F190" t="s">
+        <v>8</v>
+      </c>
+      <c r="G190" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B191" t="s">
+        <v>428</v>
+      </c>
+      <c r="C191" t="s">
+        <v>429</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" t="s">
+        <v>39</v>
+      </c>
+      <c r="F191" t="s">
+        <v>7</v>
+      </c>
+      <c r="G191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B192" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" t="s">
+        <v>431</v>
+      </c>
+      <c r="D192" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" t="s">
+        <v>37</v>
+      </c>
+      <c r="F192" t="s">
+        <v>8</v>
+      </c>
+      <c r="G192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B193" t="s">
+        <v>432</v>
+      </c>
+      <c r="C193" t="s">
+        <v>433</v>
+      </c>
+      <c r="D193" t="s">
         <v>14</v>
       </c>
-      <c r="E165" t="s">
-        <v>37</v>
-      </c>
-      <c r="F165" t="s">
-        <v>8</v>
-      </c>
-      <c r="G165" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B166" t="s">
-        <v>372</v>
-      </c>
-      <c r="C166" t="s">
-        <v>373</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="E193" t="s">
+        <v>37</v>
+      </c>
+      <c r="F193" t="s">
+        <v>8</v>
+      </c>
+      <c r="G193" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B194" t="s">
+        <v>434</v>
+      </c>
+      <c r="C194" t="s">
+        <v>435</v>
+      </c>
+      <c r="D194" t="s">
+        <v>22</v>
+      </c>
+      <c r="E194" t="s">
+        <v>39</v>
+      </c>
+      <c r="F194" t="s">
+        <v>7</v>
+      </c>
+      <c r="G194" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B195" t="s">
+        <v>436</v>
+      </c>
+      <c r="C195" t="s">
+        <v>437</v>
+      </c>
+      <c r="D195" t="s">
+        <v>14</v>
+      </c>
+      <c r="E195" t="s">
+        <v>37</v>
+      </c>
+      <c r="F195" t="s">
+        <v>8</v>
+      </c>
+      <c r="G195" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B196" t="s">
+        <v>438</v>
+      </c>
+      <c r="C196" t="s">
+        <v>439</v>
+      </c>
+      <c r="D196" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" t="s">
+        <v>37</v>
+      </c>
+      <c r="F196" t="s">
+        <v>8</v>
+      </c>
+      <c r="G196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B197" t="s">
+        <v>440</v>
+      </c>
+      <c r="C197" t="s">
+        <v>441</v>
+      </c>
+      <c r="D197" t="s">
+        <v>22</v>
+      </c>
+      <c r="E197" t="s">
+        <v>39</v>
+      </c>
+      <c r="F197" t="s">
+        <v>8</v>
+      </c>
+      <c r="G197" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B198" t="s">
+        <v>442</v>
+      </c>
+      <c r="C198" t="s">
+        <v>443</v>
+      </c>
+      <c r="D198" t="s">
         <v>19</v>
       </c>
-      <c r="E166" t="s">
-        <v>37</v>
-      </c>
-      <c r="F166" t="s">
-        <v>8</v>
-      </c>
-      <c r="G166" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B167" t="s">
-        <v>374</v>
-      </c>
-      <c r="C167" t="s">
-        <v>375</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="E198" t="s">
+        <v>37</v>
+      </c>
+      <c r="F198" t="s">
+        <v>8</v>
+      </c>
+      <c r="G198" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B199" t="s">
+        <v>444</v>
+      </c>
+      <c r="C199" t="s">
+        <v>445</v>
+      </c>
+      <c r="D199" t="s">
+        <v>31</v>
+      </c>
+      <c r="E199" t="s">
+        <v>39</v>
+      </c>
+      <c r="F199" t="s">
+        <v>405</v>
+      </c>
+      <c r="G199" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B200" t="s">
+        <v>446</v>
+      </c>
+      <c r="C200" t="s">
+        <v>447</v>
+      </c>
+      <c r="D200" t="s">
+        <v>14</v>
+      </c>
+      <c r="E200" t="s">
+        <v>37</v>
+      </c>
+      <c r="F200" t="s">
+        <v>8</v>
+      </c>
+      <c r="G200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B201" t="s">
+        <v>448</v>
+      </c>
+      <c r="C201" t="s">
+        <v>449</v>
+      </c>
+      <c r="D201" t="s">
+        <v>22</v>
+      </c>
+      <c r="E201" t="s">
+        <v>39</v>
+      </c>
+      <c r="F201" t="s">
+        <v>8</v>
+      </c>
+      <c r="G201" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B202" t="s">
+        <v>450</v>
+      </c>
+      <c r="C202" t="s">
+        <v>451</v>
+      </c>
+      <c r="D202" t="s">
+        <v>31</v>
+      </c>
+      <c r="E202" t="s">
+        <v>39</v>
+      </c>
+      <c r="F202" t="s">
+        <v>7</v>
+      </c>
+      <c r="G202" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B203" t="s">
+        <v>452</v>
+      </c>
+      <c r="C203" t="s">
+        <v>453</v>
+      </c>
+      <c r="D203" t="s">
         <v>11</v>
       </c>
-      <c r="E167" t="s">
-        <v>37</v>
-      </c>
-      <c r="F167" t="s">
-        <v>8</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="E203" t="s">
+        <v>37</v>
+      </c>
+      <c r="F203" t="s">
+        <v>8</v>
+      </c>
+      <c r="G203" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B204" t="s">
+        <v>454</v>
+      </c>
+      <c r="C204" t="s">
+        <v>433</v>
+      </c>
+      <c r="D204" t="s">
+        <v>14</v>
+      </c>
+      <c r="E204" t="s">
+        <v>37</v>
+      </c>
+      <c r="F204" t="s">
+        <v>8</v>
+      </c>
+      <c r="G204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B205" t="s">
+        <v>455</v>
+      </c>
+      <c r="C205" t="s">
+        <v>456</v>
+      </c>
+      <c r="D205" t="s">
+        <v>28</v>
+      </c>
+      <c r="E205" t="s">
+        <v>37</v>
+      </c>
+      <c r="F205" t="s">
+        <v>8</v>
+      </c>
+      <c r="G205" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B206" t="s">
+        <v>457</v>
+      </c>
+      <c r="C206" t="s">
+        <v>458</v>
+      </c>
+      <c r="D206" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206" t="s">
+        <v>39</v>
+      </c>
+      <c r="F206" t="s">
+        <v>7</v>
+      </c>
+      <c r="G206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B207" t="s">
+        <v>459</v>
+      </c>
+      <c r="C207" t="s">
+        <v>460</v>
+      </c>
+      <c r="D207" t="s">
+        <v>23</v>
+      </c>
+      <c r="E207" t="s">
+        <v>37</v>
+      </c>
+      <c r="F207" t="s">
+        <v>8</v>
+      </c>
+      <c r="G207" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B208" t="s">
+        <v>461</v>
+      </c>
+      <c r="C208" t="s">
+        <v>462</v>
+      </c>
+      <c r="D208" t="s">
+        <v>19</v>
+      </c>
+      <c r="E208" t="s">
+        <v>37</v>
+      </c>
+      <c r="F208" t="s">
+        <v>8</v>
+      </c>
+      <c r="G208" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B168" t="s">
-        <v>376</v>
-      </c>
-      <c r="C168" t="s">
-        <v>377</v>
-      </c>
-      <c r="D168" t="s">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B209" t="s">
+        <v>463</v>
+      </c>
+      <c r="C209" t="s">
+        <v>464</v>
+      </c>
+      <c r="D209" t="s">
+        <v>262</v>
+      </c>
+      <c r="E209" t="s">
+        <v>37</v>
+      </c>
+      <c r="F209" t="s">
+        <v>7</v>
+      </c>
+      <c r="G209" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B210" t="s">
+        <v>465</v>
+      </c>
+      <c r="C210" t="s">
+        <v>466</v>
+      </c>
+      <c r="D210" t="s">
+        <v>28</v>
+      </c>
+      <c r="E210" t="s">
+        <v>37</v>
+      </c>
+      <c r="F210" t="s">
+        <v>8</v>
+      </c>
+      <c r="G210" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B211" t="s">
+        <v>467</v>
+      </c>
+      <c r="C211" t="s">
+        <v>468</v>
+      </c>
+      <c r="D211" t="s">
+        <v>22</v>
+      </c>
+      <c r="E211" t="s">
+        <v>39</v>
+      </c>
+      <c r="F211" t="s">
+        <v>7</v>
+      </c>
+      <c r="G211" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B212" t="s">
+        <v>469</v>
+      </c>
+      <c r="C212" t="s">
+        <v>470</v>
+      </c>
+      <c r="D212" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" t="s">
+        <v>37</v>
+      </c>
+      <c r="F212" t="s">
+        <v>8</v>
+      </c>
+      <c r="G212" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B213" t="s">
+        <v>471</v>
+      </c>
+      <c r="C213" t="s">
+        <v>472</v>
+      </c>
+      <c r="D213" t="s">
+        <v>31</v>
+      </c>
+      <c r="E213" t="s">
+        <v>39</v>
+      </c>
+      <c r="F213" t="s">
+        <v>7</v>
+      </c>
+      <c r="G213" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B214" t="s">
+        <v>473</v>
+      </c>
+      <c r="C214" t="s">
+        <v>474</v>
+      </c>
+      <c r="D214" t="s">
+        <v>6</v>
+      </c>
+      <c r="E214" t="s">
+        <v>37</v>
+      </c>
+      <c r="F214" t="s">
+        <v>8</v>
+      </c>
+      <c r="G214" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B215" t="s">
+        <v>475</v>
+      </c>
+      <c r="C215" t="s">
+        <v>476</v>
+      </c>
+      <c r="D215" t="s">
+        <v>12</v>
+      </c>
+      <c r="E215" t="s">
+        <v>37</v>
+      </c>
+      <c r="F215" t="s">
+        <v>8</v>
+      </c>
+      <c r="G215" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B216" t="s">
+        <v>477</v>
+      </c>
+      <c r="C216" t="s">
+        <v>478</v>
+      </c>
+      <c r="D216" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216" t="s">
+        <v>37</v>
+      </c>
+      <c r="F216" t="s">
+        <v>8</v>
+      </c>
+      <c r="G216" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B217" t="s">
+        <v>479</v>
+      </c>
+      <c r="C217" t="s">
+        <v>480</v>
+      </c>
+      <c r="D217" t="s">
+        <v>31</v>
+      </c>
+      <c r="E217" t="s">
+        <v>39</v>
+      </c>
+      <c r="F217" t="s">
+        <v>405</v>
+      </c>
+      <c r="G217" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B218" t="s">
+        <v>481</v>
+      </c>
+      <c r="C218" t="s">
+        <v>482</v>
+      </c>
+      <c r="D218" t="s">
+        <v>16</v>
+      </c>
+      <c r="E218" t="s">
+        <v>37</v>
+      </c>
+      <c r="F218" t="s">
+        <v>8</v>
+      </c>
+      <c r="G218" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B219" t="s">
+        <v>483</v>
+      </c>
+      <c r="C219" t="s">
+        <v>484</v>
+      </c>
+      <c r="D219" t="s">
+        <v>19</v>
+      </c>
+      <c r="E219" t="s">
+        <v>37</v>
+      </c>
+      <c r="F219" t="s">
+        <v>8</v>
+      </c>
+      <c r="G219" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B220" t="s">
+        <v>485</v>
+      </c>
+      <c r="C220" t="s">
+        <v>486</v>
+      </c>
+      <c r="D220" t="s">
+        <v>31</v>
+      </c>
+      <c r="E220" t="s">
+        <v>39</v>
+      </c>
+      <c r="F220" t="s">
+        <v>7</v>
+      </c>
+      <c r="G220" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B221" t="s">
+        <v>487</v>
+      </c>
+      <c r="C221" t="s">
+        <v>488</v>
+      </c>
+      <c r="D221" t="s">
+        <v>16</v>
+      </c>
+      <c r="E221" t="s">
+        <v>37</v>
+      </c>
+      <c r="F221" t="s">
+        <v>8</v>
+      </c>
+      <c r="G221" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B222" t="s">
+        <v>489</v>
+      </c>
+      <c r="C222" t="s">
+        <v>490</v>
+      </c>
+      <c r="D222" t="s">
+        <v>31</v>
+      </c>
+      <c r="E222" t="s">
+        <v>39</v>
+      </c>
+      <c r="F222" t="s">
+        <v>7</v>
+      </c>
+      <c r="G222" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B223" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" t="s">
+        <v>492</v>
+      </c>
+      <c r="D223" t="s">
+        <v>14</v>
+      </c>
+      <c r="E223" t="s">
+        <v>37</v>
+      </c>
+      <c r="F223" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B224" t="s">
+        <v>493</v>
+      </c>
+      <c r="C224" t="s">
+        <v>494</v>
+      </c>
+      <c r="D224" t="s">
+        <v>14</v>
+      </c>
+      <c r="E224" t="s">
+        <v>37</v>
+      </c>
+      <c r="F224" t="s">
+        <v>8</v>
+      </c>
+      <c r="G224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B225" t="s">
+        <v>82</v>
+      </c>
+      <c r="C225" t="s">
+        <v>83</v>
+      </c>
+      <c r="D225" t="s">
+        <v>262</v>
+      </c>
+      <c r="E225" t="s">
+        <v>37</v>
+      </c>
+      <c r="F225" t="s">
+        <v>7</v>
+      </c>
+      <c r="G225" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B226" t="s">
+        <v>495</v>
+      </c>
+      <c r="C226" t="s">
+        <v>496</v>
+      </c>
+      <c r="D226" t="s">
+        <v>262</v>
+      </c>
+      <c r="E226" t="s">
+        <v>37</v>
+      </c>
+      <c r="F226" t="s">
+        <v>7</v>
+      </c>
+      <c r="G226" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B227" t="s">
+        <v>497</v>
+      </c>
+      <c r="C227" t="s">
+        <v>498</v>
+      </c>
+      <c r="D227" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227" t="s">
+        <v>37</v>
+      </c>
+      <c r="F227" t="s">
+        <v>405</v>
+      </c>
+      <c r="G227" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B228" t="s">
+        <v>499</v>
+      </c>
+      <c r="C228" t="s">
+        <v>500</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" t="s">
+        <v>39</v>
+      </c>
+      <c r="F228" t="s">
+        <v>7</v>
+      </c>
+      <c r="G228" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B229" t="s">
+        <v>501</v>
+      </c>
+      <c r="C229" t="s">
+        <v>502</v>
+      </c>
+      <c r="D229" t="s">
+        <v>262</v>
+      </c>
+      <c r="E229" t="s">
+        <v>37</v>
+      </c>
+      <c r="F229" t="s">
+        <v>7</v>
+      </c>
+      <c r="G229" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B230" t="s">
+        <v>503</v>
+      </c>
+      <c r="C230" t="s">
+        <v>504</v>
+      </c>
+      <c r="D230" t="s">
         <v>24</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E230" t="s">
         <v>39</v>
       </c>
-      <c r="F168" t="s">
-        <v>8</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="F230" t="s">
+        <v>8</v>
+      </c>
+      <c r="G230" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B169" t="s">
-        <v>378</v>
-      </c>
-      <c r="C169" t="s">
-        <v>379</v>
-      </c>
-      <c r="D169" t="s">
-        <v>40</v>
-      </c>
-      <c r="E169" t="s">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B231" t="s">
+        <v>505</v>
+      </c>
+      <c r="C231" t="s">
+        <v>506</v>
+      </c>
+      <c r="D231" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" t="s">
+        <v>37</v>
+      </c>
+      <c r="F231" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B232" t="s">
+        <v>507</v>
+      </c>
+      <c r="C232" t="s">
+        <v>508</v>
+      </c>
+      <c r="D232" t="s">
+        <v>24</v>
+      </c>
+      <c r="E232" t="s">
         <v>39</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F232" t="s">
         <v>7</v>
       </c>
-      <c r="G169" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B170" t="s">
-        <v>380</v>
-      </c>
-      <c r="C170" t="s">
-        <v>381</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="G232" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B233" t="s">
+        <v>509</v>
+      </c>
+      <c r="C233" t="s">
+        <v>510</v>
+      </c>
+      <c r="D233" t="s">
         <v>15</v>
       </c>
-      <c r="E170" t="s">
-        <v>37</v>
-      </c>
-      <c r="F170" t="s">
-        <v>8</v>
-      </c>
-      <c r="G170" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B171" t="s">
-        <v>382</v>
-      </c>
-      <c r="C171" t="s">
-        <v>383</v>
-      </c>
-      <c r="D171" t="s">
-        <v>15</v>
-      </c>
-      <c r="E171" t="s">
-        <v>37</v>
-      </c>
-      <c r="F171" t="s">
-        <v>8</v>
-      </c>
-      <c r="G171" t="s">
+      <c r="E233" t="s">
+        <v>37</v>
+      </c>
+      <c r="F233" t="s">
+        <v>8</v>
+      </c>
+      <c r="G233" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B234" t="s">
+        <v>511</v>
+      </c>
+      <c r="C234" t="s">
+        <v>512</v>
+      </c>
+      <c r="D234" t="s">
+        <v>14</v>
+      </c>
+      <c r="E234" t="s">
+        <v>37</v>
+      </c>
+      <c r="F234" t="s">
+        <v>8</v>
+      </c>
+      <c r="G234" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B235" t="s">
+        <v>513</v>
+      </c>
+      <c r="C235" t="s">
+        <v>514</v>
+      </c>
+      <c r="D235" t="s">
+        <v>28</v>
+      </c>
+      <c r="E235" t="s">
+        <v>37</v>
+      </c>
+      <c r="F235" t="s">
+        <v>8</v>
+      </c>
+      <c r="G235" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B236" t="s">
+        <v>515</v>
+      </c>
+      <c r="C236" t="s">
+        <v>516</v>
+      </c>
+      <c r="D236" t="s">
+        <v>25</v>
+      </c>
+      <c r="E236" t="s">
+        <v>39</v>
+      </c>
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+      <c r="G236" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B172" t="s">
-        <v>384</v>
-      </c>
-      <c r="C172" t="s">
-        <v>385</v>
-      </c>
-      <c r="D172" t="s">
-        <v>22</v>
-      </c>
-      <c r="E172" t="s">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B237" t="s">
+        <v>517</v>
+      </c>
+      <c r="C237" t="s">
+        <v>518</v>
+      </c>
+      <c r="D237" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" t="s">
+        <v>37</v>
+      </c>
+      <c r="F237" t="s">
+        <v>8</v>
+      </c>
+      <c r="G237" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B238" t="s">
+        <v>86</v>
+      </c>
+      <c r="C238" t="s">
+        <v>87</v>
+      </c>
+      <c r="D238" t="s">
+        <v>24</v>
+      </c>
+      <c r="E238" t="s">
         <v>39</v>
       </c>
-      <c r="F172" t="s">
-        <v>8</v>
-      </c>
-      <c r="G172" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B173" t="s">
-        <v>386</v>
-      </c>
-      <c r="C173" t="s">
-        <v>387</v>
-      </c>
-      <c r="D173" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" t="s">
-        <v>37</v>
-      </c>
-      <c r="F173" t="s">
-        <v>8</v>
-      </c>
-      <c r="G173" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B174" t="s">
-        <v>388</v>
-      </c>
-      <c r="C174" t="s">
-        <v>389</v>
-      </c>
-      <c r="D174" t="s">
-        <v>12</v>
-      </c>
-      <c r="E174" t="s">
-        <v>37</v>
-      </c>
-      <c r="F174" t="s">
-        <v>8</v>
-      </c>
-      <c r="G174" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B175" t="s">
-        <v>390</v>
-      </c>
-      <c r="C175" t="s">
-        <v>391</v>
-      </c>
-      <c r="D175" t="s">
-        <v>12</v>
-      </c>
-      <c r="E175" t="s">
-        <v>37</v>
-      </c>
-      <c r="F175" t="s">
-        <v>392</v>
-      </c>
-      <c r="G175" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B176" t="s">
-        <v>393</v>
-      </c>
-      <c r="C176" t="s">
-        <v>394</v>
-      </c>
-      <c r="D176" t="s">
-        <v>23</v>
-      </c>
-      <c r="E176" t="s">
-        <v>37</v>
-      </c>
-      <c r="F176" t="s">
-        <v>8</v>
-      </c>
-      <c r="G176" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B177" t="s">
-        <v>395</v>
-      </c>
-      <c r="C177" t="s">
-        <v>396</v>
-      </c>
-      <c r="D177" t="s">
-        <v>14</v>
-      </c>
-      <c r="E177" t="s">
-        <v>37</v>
-      </c>
-      <c r="F177" t="s">
-        <v>8</v>
-      </c>
-      <c r="G177" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B178" t="s">
-        <v>397</v>
-      </c>
-      <c r="C178" t="s">
-        <v>398</v>
-      </c>
-      <c r="D178" t="s">
-        <v>28</v>
-      </c>
-      <c r="E178" t="s">
-        <v>37</v>
-      </c>
-      <c r="F178" t="s">
-        <v>8</v>
-      </c>
-      <c r="G178" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B179" t="s">
-        <v>399</v>
-      </c>
-      <c r="C179" t="s">
-        <v>400</v>
-      </c>
-      <c r="D179" t="s">
-        <v>19</v>
-      </c>
-      <c r="E179" t="s">
-        <v>37</v>
-      </c>
-      <c r="F179" t="s">
-        <v>392</v>
-      </c>
-      <c r="G179" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B180" t="s">
-        <v>401</v>
-      </c>
-      <c r="C180" t="s">
-        <v>402</v>
-      </c>
-      <c r="D180" t="s">
-        <v>15</v>
-      </c>
-      <c r="E180" t="s">
-        <v>37</v>
-      </c>
-      <c r="F180" t="s">
-        <v>8</v>
-      </c>
-      <c r="G180" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B181" t="s">
-        <v>403</v>
-      </c>
-      <c r="C181" t="s">
-        <v>404</v>
-      </c>
-      <c r="D181" t="s">
-        <v>15</v>
-      </c>
-      <c r="E181" t="s">
-        <v>37</v>
-      </c>
-      <c r="F181" t="s">
-        <v>8</v>
-      </c>
-      <c r="G181" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B182" t="s">
-        <v>405</v>
-      </c>
-      <c r="C182" t="s">
-        <v>406</v>
-      </c>
-      <c r="D182" t="s">
-        <v>24</v>
-      </c>
-      <c r="E182" t="s">
-        <v>39</v>
-      </c>
-      <c r="F182" t="s">
+      <c r="F238" t="s">
         <v>7</v>
       </c>
-      <c r="G182" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B183" t="s">
-        <v>407</v>
-      </c>
-      <c r="C183" t="s">
-        <v>408</v>
-      </c>
-      <c r="D183" t="s">
-        <v>6</v>
-      </c>
-      <c r="E183" t="s">
-        <v>37</v>
-      </c>
-      <c r="F183" t="s">
-        <v>8</v>
-      </c>
-      <c r="G183" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B184" t="s">
-        <v>409</v>
-      </c>
-      <c r="C184" t="s">
-        <v>410</v>
-      </c>
-      <c r="D184" t="s">
-        <v>25</v>
-      </c>
-      <c r="E184" t="s">
-        <v>39</v>
-      </c>
-      <c r="F184" t="s">
-        <v>7</v>
-      </c>
-      <c r="G184" t="s">
-        <v>20</v>
+      <c r="G238" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A041E685-8238-4CDC-93D1-2440A91FF980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFA352B-6409-4D08-A7F1-C669F9A2B4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="696">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Carla Cristina de Lima Kauffmann</t>
   </si>
   <si>
-    <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
-  </si>
-  <si>
     <t>Pablo Ricardo Camilo Lopes</t>
   </si>
   <si>
@@ -1596,6 +1593,540 @@
   </si>
   <si>
     <t>VALERIO BELISARIO CRUZ LTDA</t>
+  </si>
+  <si>
+    <t>PENDÊNCIA DOC</t>
+  </si>
+  <si>
+    <t>54222968000191</t>
+  </si>
+  <si>
+    <t>PAZ E BEM CONFECCAO LTDA</t>
+  </si>
+  <si>
+    <t>63885190000191</t>
+  </si>
+  <si>
+    <t>REVEST AFD LIMITADA</t>
+  </si>
+  <si>
+    <t>45458730000179</t>
+  </si>
+  <si>
+    <t>CROSS NUTRITION BOX SARZEDO LTDA</t>
+  </si>
+  <si>
+    <t>58790963000116</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JOSE ADILSON DA SILVA</t>
+  </si>
+  <si>
+    <t>42589468000103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDENISE ROSARIO DE JESUS </t>
+  </si>
+  <si>
+    <t>Bruna Tobias dos Santos</t>
+  </si>
+  <si>
+    <t>LOBO</t>
+  </si>
+  <si>
+    <t>45482217000113</t>
+  </si>
+  <si>
+    <t>TA MALHAS MODA FEMININA LTDA</t>
+  </si>
+  <si>
+    <t>50582843000111</t>
+  </si>
+  <si>
+    <t>JOCELI V MARDEGAN</t>
+  </si>
+  <si>
+    <t>58.790.963 JOSE ADILSON DA SILVA</t>
+  </si>
+  <si>
+    <t>33497465000159</t>
+  </si>
+  <si>
+    <t>GILBERTO HOM - FRUTAS</t>
+  </si>
+  <si>
+    <t>23755872000165</t>
+  </si>
+  <si>
+    <t>23.755.872 SARA REGINA CERBI SAETTINE</t>
+  </si>
+  <si>
+    <t>50405338000100</t>
+  </si>
+  <si>
+    <t>50.405.338 JOAO PEDRO CAMARA GOMES</t>
+  </si>
+  <si>
+    <t>49597551000173</t>
+  </si>
+  <si>
+    <t>ABCOM SERVICOS DE TELECOMUNICACAO LTDA</t>
+  </si>
+  <si>
+    <t>66114553000183</t>
+  </si>
+  <si>
+    <t>LUCIANA SANTOS SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>30022547000159</t>
+  </si>
+  <si>
+    <t>JEFERSON LOPES BARBOSA</t>
+  </si>
+  <si>
+    <t>32225085000100</t>
+  </si>
+  <si>
+    <t>SUPERGAS COMERCIO DE GASES LTDA</t>
+  </si>
+  <si>
+    <t>57783230000191</t>
+  </si>
+  <si>
+    <t>JAO &amp; BATATA COMERCIO DE PRODUTOS ALIMENTICIOS LTDA</t>
+  </si>
+  <si>
+    <t>46714941000198</t>
+  </si>
+  <si>
+    <t>46.714.941 JERONIMO DA CONCEICAO PLACIDO</t>
+  </si>
+  <si>
+    <t>53897643000146</t>
+  </si>
+  <si>
+    <t>S FERRAZ DE SOUZA</t>
+  </si>
+  <si>
+    <t>45153001000104</t>
+  </si>
+  <si>
+    <t>FRANCISCO DE ASSIS SILVA ALVES</t>
+  </si>
+  <si>
+    <t>52648901000198</t>
+  </si>
+  <si>
+    <t>52.648.901 LAISSA PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>34349232000171</t>
+  </si>
+  <si>
+    <t>34.349.232 LUCIANO OLIVEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>19514239000108</t>
+  </si>
+  <si>
+    <t>OZEIAS DA SILVA VERA</t>
+  </si>
+  <si>
+    <t>61487853000194</t>
+  </si>
+  <si>
+    <t>MARCO POLO PISCINAS LTDA</t>
+  </si>
+  <si>
+    <t>31217175000189</t>
+  </si>
+  <si>
+    <t>DEBORA REGINA LOPRETE</t>
+  </si>
+  <si>
+    <t>43489946000176</t>
+  </si>
+  <si>
+    <t>PAULO RODRIGUES MENDES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>35541076000109</t>
+  </si>
+  <si>
+    <t>ALEF VALBUSA MOURA</t>
+  </si>
+  <si>
+    <t>24353909000191</t>
+  </si>
+  <si>
+    <t>GILMAR ROBERTO SOUZA OLIVEIRA MANUTENCAO</t>
+  </si>
+  <si>
+    <t>30521010000133</t>
+  </si>
+  <si>
+    <t>30.521.010 GILSON RODRIGUES MEDEIROS ALVES GOMES</t>
+  </si>
+  <si>
+    <t>30098876000183</t>
+  </si>
+  <si>
+    <t>BENHUR GORGES VOOS</t>
+  </si>
+  <si>
+    <t>64987633000118</t>
+  </si>
+  <si>
+    <t>RECREIO PINTURAS LTDA</t>
+  </si>
+  <si>
+    <t>52982524000129</t>
+  </si>
+  <si>
+    <t>MARLA GABRIELA BISPO TEIXEIRA</t>
+  </si>
+  <si>
+    <t>83868448000159</t>
+  </si>
+  <si>
+    <t>CLUBE RECREATIVO ESPORTIVO OLARIA</t>
+  </si>
+  <si>
+    <t>61249333000143</t>
+  </si>
+  <si>
+    <t>RICARDO WETTERLEIN GALVAO</t>
+  </si>
+  <si>
+    <t>51220009000149</t>
+  </si>
+  <si>
+    <t>51.220.009 ADENIR DE OLIVEIRA XAVIER</t>
+  </si>
+  <si>
+    <t>57805410000127</t>
+  </si>
+  <si>
+    <t>DEYSE LUCI SILVA LODI - SERVICOS DE FONOAUDIOLOGIA</t>
+  </si>
+  <si>
+    <t>29105518000171</t>
+  </si>
+  <si>
+    <t>29.105.518 ALAN MADEIRA NUNES</t>
+  </si>
+  <si>
+    <t>24515711000167</t>
+  </si>
+  <si>
+    <t>GABRIEL NORONHA DE MORAES</t>
+  </si>
+  <si>
+    <t>46857482000100</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO DE ABREU MARTINS</t>
+  </si>
+  <si>
+    <t>11802596000160</t>
+  </si>
+  <si>
+    <t>ESTER MARLI DA SILVA</t>
+  </si>
+  <si>
+    <t>16530629000183</t>
+  </si>
+  <si>
+    <t>METALVES METAIS LTDA</t>
+  </si>
+  <si>
+    <t>45899915000119</t>
+  </si>
+  <si>
+    <t>MARCELO AUGUSTO BARBOSA BARCELLOS</t>
+  </si>
+  <si>
+    <t>51233648000149</t>
+  </si>
+  <si>
+    <t>A A ACIOLI SERVICOS AUTOMOTIVOS</t>
+  </si>
+  <si>
+    <t>24773302000160</t>
+  </si>
+  <si>
+    <t>LIAMARA HOFF</t>
+  </si>
+  <si>
+    <t>40318355000148</t>
+  </si>
+  <si>
+    <t>L M TUPINAMBA</t>
+  </si>
+  <si>
+    <t>44343419000111</t>
+  </si>
+  <si>
+    <t>THAIARA ROCHA ARGOLO LTDA</t>
+  </si>
+  <si>
+    <t>71629828000151</t>
+  </si>
+  <si>
+    <t>MONI ATELIER FANTASIAS LTDA</t>
+  </si>
+  <si>
+    <t>37918545000191</t>
+  </si>
+  <si>
+    <t>SAULO DE ALMEIDA ALFONSO</t>
+  </si>
+  <si>
+    <t>51900953000147</t>
+  </si>
+  <si>
+    <t>DENIS CHARLES DA ROCHA ARNAUD</t>
+  </si>
+  <si>
+    <t>35209106000184</t>
+  </si>
+  <si>
+    <t>ELIEZEL FRANCA DA SILVA</t>
+  </si>
+  <si>
+    <t>50530470000135</t>
+  </si>
+  <si>
+    <t>50.530.470 GUSTAVO APARECIDO BARBOSA</t>
+  </si>
+  <si>
+    <t>60908905000196</t>
+  </si>
+  <si>
+    <t>FAZENDA SITIO QUATRO VENTOS LTDA</t>
+  </si>
+  <si>
+    <t>51970927000195</t>
+  </si>
+  <si>
+    <t>MARCOS LEANDRO PINEYRO DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>32662138000142</t>
+  </si>
+  <si>
+    <t>MARIO FERREIRA LIMA</t>
+  </si>
+  <si>
+    <t>45340340000108</t>
+  </si>
+  <si>
+    <t>VITORIA APARECIDA DE OLIVEIRA CARASSA</t>
+  </si>
+  <si>
+    <t>19739421000167</t>
+  </si>
+  <si>
+    <t>SERRALHERIA ARTISTICA MARTINS LAZARO LTDA.</t>
+  </si>
+  <si>
+    <t>28351137000100</t>
+  </si>
+  <si>
+    <t>BRUNA APARECIDA DE CASTRO BEVACQUA</t>
+  </si>
+  <si>
+    <t>61304279000191</t>
+  </si>
+  <si>
+    <t>61.304.279 VALTER JOAO DA SILVA</t>
+  </si>
+  <si>
+    <t>22007230000115</t>
+  </si>
+  <si>
+    <t>22.007.230 EURICLES ALVES DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>49616511000121</t>
+  </si>
+  <si>
+    <t>49.616.511 MARIA ROSANGELA DOS SANTOS RIBEIRO</t>
+  </si>
+  <si>
+    <t>36883204000165</t>
+  </si>
+  <si>
+    <t>LS BARBOSA DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>52168542000171</t>
+  </si>
+  <si>
+    <t>52.168.542 JULYANNA CAMPOS SEVERO</t>
+  </si>
+  <si>
+    <t>32288829000128</t>
+  </si>
+  <si>
+    <t>LA COSTA LTDA</t>
+  </si>
+  <si>
+    <t>27397200000186</t>
+  </si>
+  <si>
+    <t>JULIO CESAR EVANGELISTA TRANSPORTE</t>
+  </si>
+  <si>
+    <t>32380184000159</t>
+  </si>
+  <si>
+    <t>ANTONIO CARLOS SILVA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>44072847000157</t>
+  </si>
+  <si>
+    <t>JOSE ELINALDO DA SILVA</t>
+  </si>
+  <si>
+    <t>42203641000193</t>
+  </si>
+  <si>
+    <t>STELLA ALBUQUERQUE DE MELO</t>
+  </si>
+  <si>
+    <t>57608244000179</t>
+  </si>
+  <si>
+    <t>W. LUIZ PEREIRA REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>14079090000162</t>
+  </si>
+  <si>
+    <t>DERNIVALDO RIBEIRO SANTOS</t>
+  </si>
+  <si>
+    <t>44706239000157</t>
+  </si>
+  <si>
+    <t>VITOR LUIS BATISTA BRAGA</t>
+  </si>
+  <si>
+    <t>46238288000138</t>
+  </si>
+  <si>
+    <t>G D V VENTURA LTDA</t>
+  </si>
+  <si>
+    <t>64460917000151</t>
+  </si>
+  <si>
+    <t>P. RICARDO CUNHA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>37208475000188</t>
+  </si>
+  <si>
+    <t>MARCIO DUTRA GEREVINI</t>
+  </si>
+  <si>
+    <t>21884794000173</t>
+  </si>
+  <si>
+    <t>CLEBER MARQUES NOGUEIRA</t>
+  </si>
+  <si>
+    <t>07624171000130</t>
+  </si>
+  <si>
+    <t>LUCIA PEREIRA DE MELO</t>
+  </si>
+  <si>
+    <t>45430666000118</t>
+  </si>
+  <si>
+    <t>STANLEY EDUARDO DE CAMARGO</t>
+  </si>
+  <si>
+    <t>03378454000199</t>
+  </si>
+  <si>
+    <t>JM PEREIRA MINIMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>33427950000156</t>
+  </si>
+  <si>
+    <t>33.427.950 RAFAEL DOS SANTOS RIBEIRO</t>
+  </si>
+  <si>
+    <t>63967777000140</t>
+  </si>
+  <si>
+    <t>JONATHAS ROCHA DO AMARAL LTDA</t>
+  </si>
+  <si>
+    <t>07277716000180</t>
+  </si>
+  <si>
+    <t>BIGU CORRETORA DE SEGUROS LTDA</t>
+  </si>
+  <si>
+    <t>62557364000124</t>
+  </si>
+  <si>
+    <t>ANDREZA SANTOS PSICOLOGIA E BEM ESTAR LTDA</t>
+  </si>
+  <si>
+    <t>41722946000149</t>
+  </si>
+  <si>
+    <t>J.C NUNES DA SILVA</t>
+  </si>
+  <si>
+    <t>11246481000136</t>
+  </si>
+  <si>
+    <t>JOAO PAULO DE OLIVEIRA SILVEIRA</t>
+  </si>
+  <si>
+    <t>23741219000147</t>
+  </si>
+  <si>
+    <t>23.741.219 DANIELE DA SILVA JULIO</t>
+  </si>
+  <si>
+    <t>50567495000103</t>
+  </si>
+  <si>
+    <t>GR PESCADOS LTDA</t>
+  </si>
+  <si>
+    <t>44920746000199</t>
+  </si>
+  <si>
+    <t>LINA TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>44078208000107</t>
+  </si>
+  <si>
+    <t>LGO SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>Envie uma procuracao com o prazo vigente, pois a enviada foi emitida a mais de tres anos.</t>
+  </si>
+  <si>
+    <t>Ata de eleicao da empresa CENTRO RECREATIVO ESP UNIAO AMIGOS DE VILA PROSPERIDADE, atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade.&lt;br&gt;&lt;br&gt;Estatuto social da empresa CENTRO RECREATIVO ESP UNIAO AMIGOS DE VILA PROSPERIDADE, atualizado e registrado no orgao competente. Esse documento estabelece as regras de funcionamento da empresa, descrevendo sua finalidade, estrutura administrativa, orgaos de gestao e forma de representacao legal, comprovando sua existencia e regularidade.</t>
+  </si>
+  <si>
+    <t>Estatuto social da empresa, atualizado e registrado no orgao competente. Esse documento estabelece as regras de funcionamento da empresa, descrevendo sua finalidade, estrutura administrativa, orgaos de gestao e forma de representacao legal, comprovando sua existencia e regularidade.&lt;br&gt;&lt;br&gt;Ata de eleicao da empresa, registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade.</t>
+  </si>
+  <si>
+    <t>Procuracao com poderes de abrir e movimentar conta corrente junto a instituicoes financeiras com mandato vigente e devidamente assinada&lt;br&gt;&lt;br&gt;Contrato Social atualizado e registrado no orgao competente</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1996,7 +2527,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -2013,16 +2544,16 @@
         <v>46113</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -2039,22 +2570,22 @@
         <v>46113</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2065,16 +2596,16 @@
         <v>46113</v>
       </c>
       <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
         <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -2091,16 +2622,16 @@
         <v>46113</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -2108,8 +2639,8 @@
       <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="H5" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2117,22 +2648,22 @@
         <v>46113</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
         <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>58</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2143,22 +2674,22 @@
         <v>46113</v>
       </c>
       <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
         <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2169,25 +2700,25 @@
         <v>46113</v>
       </c>
       <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2195,16 +2726,16 @@
         <v>46113</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
@@ -2221,16 +2752,16 @@
         <v>46113</v>
       </c>
       <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
@@ -2247,16 +2778,16 @@
         <v>46113</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
@@ -2273,16 +2804,16 @@
         <v>46113</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>8</v>
@@ -2299,16 +2830,16 @@
         <v>46113</v>
       </c>
       <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -2325,16 +2856,16 @@
         <v>46113</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -2351,19 +2882,19 @@
         <v>46113</v>
       </c>
       <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
         <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -2377,16 +2908,16 @@
         <v>46113</v>
       </c>
       <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
         <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
         <v>8</v>
@@ -2403,16 +2934,16 @@
         <v>46113</v>
       </c>
       <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
         <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -2429,16 +2960,16 @@
         <v>46113</v>
       </c>
       <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
         <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
         <v>8</v>
@@ -2455,16 +2986,16 @@
         <v>46113</v>
       </c>
       <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
         <v>78</v>
       </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -2481,22 +3012,22 @@
         <v>46113</v>
       </c>
       <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
         <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2507,16 +3038,16 @@
         <v>46113</v>
       </c>
       <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
         <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -2533,16 +3064,16 @@
         <v>46113</v>
       </c>
       <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
         <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -2559,16 +3090,16 @@
         <v>46113</v>
       </c>
       <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -2585,16 +3116,16 @@
         <v>46113</v>
       </c>
       <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
         <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -2611,16 +3142,16 @@
         <v>46113</v>
       </c>
       <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
         <v>94</v>
       </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -2637,22 +3168,22 @@
         <v>46113</v>
       </c>
       <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
         <v>96</v>
       </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
       </c>
       <c r="G26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2663,16 +3194,16 @@
         <v>46113</v>
       </c>
       <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
         <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -2689,16 +3220,16 @@
         <v>46113</v>
       </c>
       <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
         <v>100</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
@@ -2715,16 +3246,16 @@
         <v>46113</v>
       </c>
       <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
         <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
         <v>8</v>
@@ -2741,16 +3272,16 @@
         <v>46113</v>
       </c>
       <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
         <v>104</v>
-      </c>
-      <c r="C30" t="s">
-        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -2767,16 +3298,16 @@
         <v>46113</v>
       </c>
       <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -2793,16 +3324,16 @@
         <v>46113</v>
       </c>
       <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
         <v>108</v>
-      </c>
-      <c r="C32" t="s">
-        <v>109</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
@@ -2819,16 +3350,16 @@
         <v>46113</v>
       </c>
       <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
         <v>110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F33" t="s">
         <v>8</v>
@@ -2845,22 +3376,22 @@
         <v>46113</v>
       </c>
       <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="s">
         <v>112</v>
       </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2871,16 +3402,16 @@
         <v>46113</v>
       </c>
       <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
         <v>114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>115</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -2897,16 +3428,16 @@
         <v>46113</v>
       </c>
       <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
         <v>116</v>
-      </c>
-      <c r="C36" t="s">
-        <v>117</v>
       </c>
       <c r="D36" t="s">
         <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -2923,16 +3454,16 @@
         <v>46114</v>
       </c>
       <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
         <v>118</v>
       </c>
-      <c r="C37" t="s">
-        <v>119</v>
-      </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -2949,16 +3480,16 @@
         <v>46114</v>
       </c>
       <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" t="s">
         <v>120</v>
-      </c>
-      <c r="C38" t="s">
-        <v>121</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>8</v>
@@ -2975,16 +3506,16 @@
         <v>46114</v>
       </c>
       <c r="B39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" t="s">
         <v>122</v>
-      </c>
-      <c r="C39" t="s">
-        <v>123</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
@@ -3001,16 +3532,16 @@
         <v>46114</v>
       </c>
       <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
         <v>124</v>
-      </c>
-      <c r="C40" t="s">
-        <v>125</v>
       </c>
       <c r="D40" t="s">
         <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
         <v>8</v>
@@ -3027,16 +3558,16 @@
         <v>46114</v>
       </c>
       <c r="B41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s">
         <v>126</v>
       </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
         <v>8</v>
@@ -3053,16 +3584,16 @@
         <v>46114</v>
       </c>
       <c r="B42" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" t="s">
         <v>128</v>
       </c>
-      <c r="C42" t="s">
-        <v>129</v>
-      </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -3079,16 +3610,16 @@
         <v>46114</v>
       </c>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
         <v>130</v>
-      </c>
-      <c r="C43" t="s">
-        <v>131</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -3105,16 +3636,16 @@
         <v>46114</v>
       </c>
       <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" t="s">
         <v>132</v>
-      </c>
-      <c r="C44" t="s">
-        <v>133</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s">
         <v>8</v>
@@ -3131,16 +3662,16 @@
         <v>46114</v>
       </c>
       <c r="B45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" t="s">
         <v>134</v>
-      </c>
-      <c r="C45" t="s">
-        <v>135</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
         <v>8</v>
@@ -3157,16 +3688,16 @@
         <v>46114</v>
       </c>
       <c r="B46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" t="s">
         <v>136</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
         <v>8</v>
@@ -3183,22 +3714,22 @@
         <v>46114</v>
       </c>
       <c r="B47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" t="s">
         <v>138</v>
       </c>
-      <c r="C47" t="s">
-        <v>139</v>
-      </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -3209,16 +3740,16 @@
         <v>46114</v>
       </c>
       <c r="B48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" t="s">
         <v>140</v>
-      </c>
-      <c r="C48" t="s">
-        <v>141</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
@@ -3235,16 +3766,16 @@
         <v>46114</v>
       </c>
       <c r="B49" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" t="s">
         <v>142</v>
-      </c>
-      <c r="C49" t="s">
-        <v>143</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
         <v>8</v>
@@ -3261,22 +3792,22 @@
         <v>46114</v>
       </c>
       <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" t="s">
         <v>34</v>
-      </c>
-      <c r="C50" t="s">
-        <v>35</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
       </c>
       <c r="G50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -3287,16 +3818,16 @@
         <v>46114</v>
       </c>
       <c r="B51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
         <v>144</v>
-      </c>
-      <c r="C51" t="s">
-        <v>145</v>
       </c>
       <c r="D51" t="s">
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F51" t="s">
         <v>8</v>
@@ -3313,16 +3844,16 @@
         <v>46114</v>
       </c>
       <c r="B52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" t="s">
         <v>146</v>
-      </c>
-      <c r="C52" t="s">
-        <v>147</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F52" t="s">
         <v>8</v>
@@ -3339,16 +3870,16 @@
         <v>46114</v>
       </c>
       <c r="B53" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" t="s">
         <v>148</v>
       </c>
-      <c r="C53" t="s">
-        <v>149</v>
-      </c>
       <c r="D53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -3365,16 +3896,16 @@
         <v>46114</v>
       </c>
       <c r="B54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" t="s">
         <v>150</v>
       </c>
-      <c r="C54" t="s">
-        <v>151</v>
-      </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -3391,16 +3922,16 @@
         <v>46114</v>
       </c>
       <c r="B55" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" t="s">
         <v>152</v>
       </c>
-      <c r="C55" t="s">
-        <v>153</v>
-      </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -3417,16 +3948,16 @@
         <v>46114</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
         <v>22</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -3443,16 +3974,16 @@
         <v>46114</v>
       </c>
       <c r="B57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" t="s">
         <v>155</v>
-      </c>
-      <c r="C57" t="s">
-        <v>156</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" t="s">
         <v>8</v>
@@ -3469,16 +4000,16 @@
         <v>46114</v>
       </c>
       <c r="B58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" t="s">
         <v>157</v>
-      </c>
-      <c r="C58" t="s">
-        <v>158</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
         <v>8</v>
@@ -3495,16 +4026,16 @@
         <v>46114</v>
       </c>
       <c r="B59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" t="s">
         <v>159</v>
-      </c>
-      <c r="C59" t="s">
-        <v>160</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F59" t="s">
         <v>8</v>
@@ -3521,16 +4052,16 @@
         <v>46114</v>
       </c>
       <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" t="s">
         <v>32</v>
-      </c>
-      <c r="C60" t="s">
-        <v>33</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
         <v>8</v>
@@ -3547,22 +4078,22 @@
         <v>46114</v>
       </c>
       <c r="B61" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" t="s">
         <v>161</v>
       </c>
-      <c r="C61" t="s">
-        <v>162</v>
-      </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3573,16 +4104,16 @@
         <v>46114</v>
       </c>
       <c r="B62" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" t="s">
         <v>163</v>
-      </c>
-      <c r="C62" t="s">
-        <v>164</v>
       </c>
       <c r="D62" t="s">
         <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
         <v>8</v>
@@ -3599,16 +4130,16 @@
         <v>46114</v>
       </c>
       <c r="B63" t="s">
+        <v>164</v>
+      </c>
+      <c r="C63" t="s">
         <v>165</v>
-      </c>
-      <c r="C63" t="s">
-        <v>166</v>
       </c>
       <c r="D63" t="s">
         <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F63" t="s">
         <v>8</v>
@@ -3625,16 +4156,16 @@
         <v>46114</v>
       </c>
       <c r="B64" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" t="s">
         <v>167</v>
-      </c>
-      <c r="C64" t="s">
-        <v>168</v>
       </c>
       <c r="D64" t="s">
         <v>6</v>
       </c>
       <c r="E64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
         <v>8</v>
@@ -3651,16 +4182,16 @@
         <v>46114</v>
       </c>
       <c r="B65" t="s">
+        <v>168</v>
+      </c>
+      <c r="C65" t="s">
         <v>169</v>
-      </c>
-      <c r="C65" t="s">
-        <v>170</v>
       </c>
       <c r="D65" t="s">
         <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
         <v>8</v>
@@ -3677,16 +4208,16 @@
         <v>46114</v>
       </c>
       <c r="B66" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" t="s">
         <v>171</v>
-      </c>
-      <c r="C66" t="s">
-        <v>172</v>
       </c>
       <c r="D66" t="s">
         <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
         <v>8</v>
@@ -3703,16 +4234,16 @@
         <v>46114</v>
       </c>
       <c r="B67" t="s">
+        <v>172</v>
+      </c>
+      <c r="C67" t="s">
         <v>173</v>
       </c>
-      <c r="C67" t="s">
-        <v>174</v>
-      </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
@@ -3729,16 +4260,16 @@
         <v>46114</v>
       </c>
       <c r="B68" t="s">
+        <v>174</v>
+      </c>
+      <c r="C68" t="s">
         <v>175</v>
       </c>
-      <c r="C68" t="s">
-        <v>176</v>
-      </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
@@ -3755,16 +4286,16 @@
         <v>46114</v>
       </c>
       <c r="B69" t="s">
+        <v>176</v>
+      </c>
+      <c r="C69" t="s">
         <v>177</v>
-      </c>
-      <c r="C69" t="s">
-        <v>178</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -3781,25 +4312,25 @@
         <v>46114</v>
       </c>
       <c r="B70" t="s">
+        <v>178</v>
+      </c>
+      <c r="C70" t="s">
         <v>179</v>
       </c>
-      <c r="C70" t="s">
-        <v>180</v>
-      </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>694</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -3807,16 +4338,16 @@
         <v>46114</v>
       </c>
       <c r="B71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" t="s">
         <v>181</v>
       </c>
-      <c r="C71" t="s">
-        <v>182</v>
-      </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -3833,22 +4364,22 @@
         <v>46114</v>
       </c>
       <c r="B72" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" t="s">
         <v>183</v>
       </c>
-      <c r="C72" t="s">
-        <v>184</v>
-      </c>
       <c r="D72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
         <v>8</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -3856,16 +4387,16 @@
         <v>46114</v>
       </c>
       <c r="B73" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" t="s">
         <v>185</v>
-      </c>
-      <c r="C73" t="s">
-        <v>186</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F73" t="s">
         <v>8</v>
@@ -3882,16 +4413,16 @@
         <v>46114</v>
       </c>
       <c r="B74" t="s">
+        <v>186</v>
+      </c>
+      <c r="C74" t="s">
         <v>187</v>
-      </c>
-      <c r="C74" t="s">
-        <v>188</v>
       </c>
       <c r="D74" t="s">
         <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
         <v>8</v>
@@ -3908,16 +4439,16 @@
         <v>46114</v>
       </c>
       <c r="B75" t="s">
+        <v>188</v>
+      </c>
+      <c r="C75" t="s">
         <v>189</v>
-      </c>
-      <c r="C75" t="s">
-        <v>190</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F75" t="s">
         <v>8</v>
@@ -3934,16 +4465,16 @@
         <v>46114</v>
       </c>
       <c r="B76" t="s">
+        <v>190</v>
+      </c>
+      <c r="C76" t="s">
         <v>191</v>
-      </c>
-      <c r="C76" t="s">
-        <v>192</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F76" t="s">
         <v>8</v>
@@ -3960,16 +4491,16 @@
         <v>46114</v>
       </c>
       <c r="B77" t="s">
+        <v>192</v>
+      </c>
+      <c r="C77" t="s">
         <v>193</v>
-      </c>
-      <c r="C77" t="s">
-        <v>194</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F77" t="s">
         <v>8</v>
@@ -3986,16 +4517,16 @@
         <v>46114</v>
       </c>
       <c r="B78" t="s">
+        <v>194</v>
+      </c>
+      <c r="C78" t="s">
         <v>195</v>
-      </c>
-      <c r="C78" t="s">
-        <v>196</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" t="s">
         <v>8</v>
@@ -4012,22 +4543,22 @@
         <v>46114</v>
       </c>
       <c r="B79" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79" t="s">
         <v>197</v>
-      </c>
-      <c r="C79" t="s">
-        <v>198</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -4038,16 +4569,16 @@
         <v>46114</v>
       </c>
       <c r="B80" t="s">
+        <v>198</v>
+      </c>
+      <c r="C80" t="s">
         <v>199</v>
-      </c>
-      <c r="C80" t="s">
-        <v>200</v>
       </c>
       <c r="D80" t="s">
         <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
         <v>8</v>
@@ -4064,16 +4595,16 @@
         <v>46114</v>
       </c>
       <c r="B81" t="s">
+        <v>200</v>
+      </c>
+      <c r="C81" t="s">
         <v>201</v>
-      </c>
-      <c r="C81" t="s">
-        <v>202</v>
       </c>
       <c r="D81" t="s">
         <v>15</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F81" t="s">
         <v>8</v>
@@ -4090,16 +4621,16 @@
         <v>46114</v>
       </c>
       <c r="B82" t="s">
+        <v>202</v>
+      </c>
+      <c r="C82" t="s">
         <v>203</v>
-      </c>
-      <c r="C82" t="s">
-        <v>204</v>
       </c>
       <c r="D82" t="s">
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F82" t="s">
         <v>8</v>
@@ -4116,16 +4647,16 @@
         <v>46114</v>
       </c>
       <c r="B83" t="s">
+        <v>204</v>
+      </c>
+      <c r="C83" t="s">
         <v>205</v>
-      </c>
-      <c r="C83" t="s">
-        <v>206</v>
       </c>
       <c r="D83" t="s">
         <v>19</v>
       </c>
       <c r="E83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -4142,16 +4673,16 @@
         <v>46114</v>
       </c>
       <c r="B84" t="s">
+        <v>206</v>
+      </c>
+      <c r="C84" t="s">
         <v>207</v>
-      </c>
-      <c r="C84" t="s">
-        <v>208</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
@@ -4168,22 +4699,22 @@
         <v>46114</v>
       </c>
       <c r="B85" t="s">
+        <v>208</v>
+      </c>
+      <c r="C85" t="s">
         <v>209</v>
-      </c>
-      <c r="C85" t="s">
-        <v>210</v>
       </c>
       <c r="D85" t="s">
         <v>15</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F85" t="s">
         <v>8</v>
       </c>
       <c r="G85" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -4194,16 +4725,16 @@
         <v>46114</v>
       </c>
       <c r="B86" t="s">
+        <v>210</v>
+      </c>
+      <c r="C86" t="s">
         <v>211</v>
-      </c>
-      <c r="C86" t="s">
-        <v>212</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F86" t="s">
         <v>8</v>
@@ -4220,22 +4751,22 @@
         <v>46114</v>
       </c>
       <c r="B87" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" t="s">
         <v>213</v>
-      </c>
-      <c r="C87" t="s">
-        <v>214</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" t="s">
         <v>8</v>
       </c>
       <c r="G87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -4246,16 +4777,16 @@
         <v>46114</v>
       </c>
       <c r="B88" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" t="s">
         <v>215</v>
-      </c>
-      <c r="C88" t="s">
-        <v>216</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F88" t="s">
         <v>7</v>
@@ -4272,16 +4803,16 @@
         <v>46114</v>
       </c>
       <c r="B89" t="s">
+        <v>216</v>
+      </c>
+      <c r="C89" t="s">
         <v>217</v>
-      </c>
-      <c r="C89" t="s">
-        <v>218</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F89" t="s">
         <v>8</v>
@@ -4298,16 +4829,16 @@
         <v>46114</v>
       </c>
       <c r="B90" t="s">
+        <v>218</v>
+      </c>
+      <c r="C90" t="s">
         <v>219</v>
-      </c>
-      <c r="C90" t="s">
-        <v>220</v>
       </c>
       <c r="D90" t="s">
         <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F90" t="s">
         <v>8</v>
@@ -4324,16 +4855,16 @@
         <v>46114</v>
       </c>
       <c r="B91" t="s">
+        <v>220</v>
+      </c>
+      <c r="C91" t="s">
         <v>221</v>
-      </c>
-      <c r="C91" t="s">
-        <v>222</v>
       </c>
       <c r="D91" t="s">
         <v>25</v>
       </c>
       <c r="E91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F91" t="s">
         <v>10</v>
@@ -4350,16 +4881,16 @@
         <v>46114</v>
       </c>
       <c r="B92" t="s">
+        <v>222</v>
+      </c>
+      <c r="C92" t="s">
         <v>223</v>
-      </c>
-      <c r="C92" t="s">
-        <v>224</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
         <v>8</v>
@@ -4376,16 +4907,16 @@
         <v>46114</v>
       </c>
       <c r="B93" t="s">
+        <v>224</v>
+      </c>
+      <c r="C93" t="s">
         <v>225</v>
-      </c>
-      <c r="C93" t="s">
-        <v>226</v>
       </c>
       <c r="D93" t="s">
         <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F93" t="s">
         <v>8</v>
@@ -4402,16 +4933,16 @@
         <v>46114</v>
       </c>
       <c r="B94" t="s">
+        <v>226</v>
+      </c>
+      <c r="C94" t="s">
         <v>227</v>
-      </c>
-      <c r="C94" t="s">
-        <v>228</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
         <v>8</v>
@@ -4428,16 +4959,16 @@
         <v>46114</v>
       </c>
       <c r="B95" t="s">
+        <v>228</v>
+      </c>
+      <c r="C95" t="s">
         <v>229</v>
-      </c>
-      <c r="C95" t="s">
-        <v>230</v>
       </c>
       <c r="D95" t="s">
         <v>25</v>
       </c>
       <c r="E95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F95" t="s">
         <v>8</v>
@@ -4454,16 +4985,16 @@
         <v>46114</v>
       </c>
       <c r="B96" t="s">
+        <v>230</v>
+      </c>
+      <c r="C96" t="s">
         <v>231</v>
-      </c>
-      <c r="C96" t="s">
-        <v>232</v>
       </c>
       <c r="D96" t="s">
         <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F96" t="s">
         <v>8</v>
@@ -4480,16 +5011,16 @@
         <v>46118</v>
       </c>
       <c r="B97" t="s">
+        <v>234</v>
+      </c>
+      <c r="C97" t="s">
         <v>235</v>
-      </c>
-      <c r="C97" t="s">
-        <v>236</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F97" t="s">
         <v>7</v>
@@ -4506,16 +5037,16 @@
         <v>46118</v>
       </c>
       <c r="B98" t="s">
+        <v>236</v>
+      </c>
+      <c r="C98" t="s">
         <v>237</v>
-      </c>
-      <c r="C98" t="s">
-        <v>238</v>
       </c>
       <c r="D98" t="s">
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
         <v>8</v>
@@ -4532,16 +5063,16 @@
         <v>46118</v>
       </c>
       <c r="B99" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" t="s">
         <v>239</v>
-      </c>
-      <c r="C99" t="s">
-        <v>240</v>
       </c>
       <c r="D99" t="s">
         <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
@@ -4558,19 +5089,19 @@
         <v>46118</v>
       </c>
       <c r="B100" t="s">
+        <v>240</v>
+      </c>
+      <c r="C100" t="s">
         <v>241</v>
-      </c>
-      <c r="C100" t="s">
-        <v>242</v>
       </c>
       <c r="D100" t="s">
         <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
@@ -4584,16 +5115,16 @@
         <v>46118</v>
       </c>
       <c r="B101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C101" t="s">
         <v>244</v>
-      </c>
-      <c r="C101" t="s">
-        <v>245</v>
       </c>
       <c r="D101" t="s">
         <v>27</v>
       </c>
       <c r="E101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
         <v>8</v>
@@ -4610,16 +5141,16 @@
         <v>46118</v>
       </c>
       <c r="B102" t="s">
+        <v>245</v>
+      </c>
+      <c r="C102" t="s">
         <v>246</v>
-      </c>
-      <c r="C102" t="s">
-        <v>247</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
       </c>
       <c r="E102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
@@ -4636,16 +5167,16 @@
         <v>46118</v>
       </c>
       <c r="B103" t="s">
+        <v>247</v>
+      </c>
+      <c r="C103" t="s">
         <v>248</v>
-      </c>
-      <c r="C103" t="s">
-        <v>249</v>
       </c>
       <c r="D103" t="s">
         <v>28</v>
       </c>
       <c r="E103" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
@@ -4662,16 +5193,16 @@
         <v>46118</v>
       </c>
       <c r="B104" t="s">
+        <v>249</v>
+      </c>
+      <c r="C104" t="s">
         <v>250</v>
-      </c>
-      <c r="C104" t="s">
-        <v>251</v>
       </c>
       <c r="D104" t="s">
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F104" t="s">
         <v>8</v>
@@ -4688,16 +5219,16 @@
         <v>46118</v>
       </c>
       <c r="B105" t="s">
+        <v>251</v>
+      </c>
+      <c r="C105" t="s">
         <v>252</v>
-      </c>
-      <c r="C105" t="s">
-        <v>253</v>
       </c>
       <c r="D105" t="s">
         <v>6</v>
       </c>
       <c r="E105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F105" t="s">
         <v>8</v>
@@ -4714,16 +5245,16 @@
         <v>46118</v>
       </c>
       <c r="B106" t="s">
+        <v>253</v>
+      </c>
+      <c r="C106" t="s">
         <v>254</v>
-      </c>
-      <c r="C106" t="s">
-        <v>255</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F106" t="s">
         <v>8</v>
@@ -4740,16 +5271,16 @@
         <v>46118</v>
       </c>
       <c r="B107" t="s">
+        <v>255</v>
+      </c>
+      <c r="C107" t="s">
         <v>256</v>
-      </c>
-      <c r="C107" t="s">
-        <v>257</v>
       </c>
       <c r="D107" t="s">
         <v>16</v>
       </c>
       <c r="E107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F107" t="s">
         <v>8</v>
@@ -4766,16 +5297,16 @@
         <v>46118</v>
       </c>
       <c r="B108" t="s">
+        <v>257</v>
+      </c>
+      <c r="C108" t="s">
         <v>258</v>
-      </c>
-      <c r="C108" t="s">
-        <v>259</v>
       </c>
       <c r="D108" t="s">
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F108" t="s">
         <v>8</v>
@@ -4792,16 +5323,16 @@
         <v>46118</v>
       </c>
       <c r="B109" t="s">
+        <v>259</v>
+      </c>
+      <c r="C109" t="s">
         <v>260</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>261</v>
       </c>
-      <c r="D109" t="s">
-        <v>262</v>
-      </c>
       <c r="E109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F109" t="s">
         <v>7</v>
@@ -4818,22 +5349,22 @@
         <v>46118</v>
       </c>
       <c r="B110" t="s">
+        <v>262</v>
+      </c>
+      <c r="C110" t="s">
         <v>263</v>
-      </c>
-      <c r="C110" t="s">
-        <v>264</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F110" t="s">
         <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -4844,16 +5375,16 @@
         <v>46118</v>
       </c>
       <c r="B111" t="s">
+        <v>264</v>
+      </c>
+      <c r="C111" t="s">
         <v>265</v>
-      </c>
-      <c r="C111" t="s">
-        <v>266</v>
       </c>
       <c r="D111" t="s">
         <v>6</v>
       </c>
       <c r="E111" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F111" t="s">
         <v>8</v>
@@ -4870,19 +5401,19 @@
         <v>46118</v>
       </c>
       <c r="B112" t="s">
+        <v>266</v>
+      </c>
+      <c r="C112" t="s">
         <v>267</v>
-      </c>
-      <c r="C112" t="s">
-        <v>268</v>
       </c>
       <c r="D112" t="s">
         <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F112" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G112" t="s">
         <v>18</v>
@@ -4896,16 +5427,16 @@
         <v>46118</v>
       </c>
       <c r="B113" t="s">
+        <v>268</v>
+      </c>
+      <c r="C113" t="s">
         <v>269</v>
-      </c>
-      <c r="C113" t="s">
-        <v>270</v>
       </c>
       <c r="D113" t="s">
         <v>23</v>
       </c>
       <c r="E113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F113" t="s">
         <v>8</v>
@@ -4922,16 +5453,16 @@
         <v>46118</v>
       </c>
       <c r="B114" t="s">
+        <v>270</v>
+      </c>
+      <c r="C114" t="s">
         <v>271</v>
-      </c>
-      <c r="C114" t="s">
-        <v>272</v>
       </c>
       <c r="D114" t="s">
         <v>6</v>
       </c>
       <c r="E114" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F114" t="s">
         <v>8</v>
@@ -4948,22 +5479,22 @@
         <v>46118</v>
       </c>
       <c r="B115" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" t="s">
         <v>273</v>
       </c>
-      <c r="C115" t="s">
-        <v>274</v>
-      </c>
       <c r="D115" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F115" t="s">
         <v>8</v>
       </c>
       <c r="G115" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -4974,16 +5505,16 @@
         <v>46118</v>
       </c>
       <c r="B116" t="s">
+        <v>274</v>
+      </c>
+      <c r="C116" t="s">
         <v>275</v>
-      </c>
-      <c r="C116" t="s">
-        <v>276</v>
       </c>
       <c r="D116" t="s">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F116" t="s">
         <v>7</v>
@@ -5000,16 +5531,16 @@
         <v>46118</v>
       </c>
       <c r="B117" t="s">
+        <v>276</v>
+      </c>
+      <c r="C117" t="s">
         <v>277</v>
       </c>
-      <c r="C117" t="s">
-        <v>278</v>
-      </c>
       <c r="D117" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F117" t="s">
         <v>8</v>
@@ -5026,16 +5557,16 @@
         <v>46118</v>
       </c>
       <c r="B118" t="s">
+        <v>278</v>
+      </c>
+      <c r="C118" t="s">
         <v>279</v>
-      </c>
-      <c r="C118" t="s">
-        <v>280</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
       </c>
       <c r="E118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F118" t="s">
         <v>8</v>
@@ -5052,16 +5583,16 @@
         <v>46118</v>
       </c>
       <c r="B119" t="s">
+        <v>280</v>
+      </c>
+      <c r="C119" t="s">
         <v>281</v>
-      </c>
-      <c r="C119" t="s">
-        <v>282</v>
       </c>
       <c r="D119" t="s">
         <v>16</v>
       </c>
       <c r="E119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F119" t="s">
         <v>8</v>
@@ -5078,16 +5609,16 @@
         <v>46118</v>
       </c>
       <c r="B120" t="s">
+        <v>282</v>
+      </c>
+      <c r="C120" t="s">
         <v>283</v>
-      </c>
-      <c r="C120" t="s">
-        <v>284</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F120" t="s">
         <v>8</v>
@@ -5104,16 +5635,16 @@
         <v>46118</v>
       </c>
       <c r="B121" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" t="s">
         <v>285</v>
-      </c>
-      <c r="C121" t="s">
-        <v>286</v>
       </c>
       <c r="D121" t="s">
         <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F121" t="s">
         <v>8</v>
@@ -5130,16 +5661,16 @@
         <v>46118</v>
       </c>
       <c r="B122" t="s">
+        <v>286</v>
+      </c>
+      <c r="C122" t="s">
         <v>287</v>
-      </c>
-      <c r="C122" t="s">
-        <v>288</v>
       </c>
       <c r="D122" t="s">
         <v>23</v>
       </c>
       <c r="E122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F122" t="s">
         <v>8</v>
@@ -5156,16 +5687,16 @@
         <v>46118</v>
       </c>
       <c r="B123" t="s">
+        <v>288</v>
+      </c>
+      <c r="C123" t="s">
         <v>289</v>
-      </c>
-      <c r="C123" t="s">
-        <v>290</v>
       </c>
       <c r="D123" t="s">
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F123" t="s">
         <v>8</v>
@@ -5182,16 +5713,16 @@
         <v>46118</v>
       </c>
       <c r="B124" t="s">
+        <v>290</v>
+      </c>
+      <c r="C124" t="s">
         <v>291</v>
-      </c>
-      <c r="C124" t="s">
-        <v>292</v>
       </c>
       <c r="D124" t="s">
         <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F124" t="s">
         <v>8</v>
@@ -5208,16 +5739,16 @@
         <v>46118</v>
       </c>
       <c r="B125" t="s">
+        <v>292</v>
+      </c>
+      <c r="C125" t="s">
         <v>293</v>
-      </c>
-      <c r="C125" t="s">
-        <v>294</v>
       </c>
       <c r="D125" t="s">
         <v>16</v>
       </c>
       <c r="E125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F125" t="s">
         <v>8</v>
@@ -5234,16 +5765,16 @@
         <v>46118</v>
       </c>
       <c r="B126" t="s">
+        <v>294</v>
+      </c>
+      <c r="C126" t="s">
         <v>295</v>
-      </c>
-      <c r="C126" t="s">
-        <v>296</v>
       </c>
       <c r="D126" t="s">
         <v>22</v>
       </c>
       <c r="E126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F126" t="s">
         <v>7</v>
@@ -5260,16 +5791,16 @@
         <v>46118</v>
       </c>
       <c r="B127" t="s">
+        <v>296</v>
+      </c>
+      <c r="C127" t="s">
         <v>297</v>
-      </c>
-      <c r="C127" t="s">
-        <v>298</v>
       </c>
       <c r="D127" t="s">
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
         <v>7</v>
@@ -5286,16 +5817,16 @@
         <v>46118</v>
       </c>
       <c r="B128" t="s">
+        <v>298</v>
+      </c>
+      <c r="C128" t="s">
         <v>299</v>
-      </c>
-      <c r="C128" t="s">
-        <v>300</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F128" t="s">
         <v>8</v>
@@ -5312,16 +5843,16 @@
         <v>46118</v>
       </c>
       <c r="B129" t="s">
+        <v>300</v>
+      </c>
+      <c r="C129" t="s">
         <v>301</v>
-      </c>
-      <c r="C129" t="s">
-        <v>302</v>
       </c>
       <c r="D129" t="s">
         <v>24</v>
       </c>
       <c r="E129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s">
         <v>7</v>
@@ -5338,16 +5869,16 @@
         <v>46118</v>
       </c>
       <c r="B130" t="s">
+        <v>302</v>
+      </c>
+      <c r="C130" t="s">
         <v>303</v>
-      </c>
-      <c r="C130" t="s">
-        <v>304</v>
       </c>
       <c r="D130" t="s">
         <v>16</v>
       </c>
       <c r="E130" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F130" t="s">
         <v>8</v>
@@ -5364,16 +5895,16 @@
         <v>46118</v>
       </c>
       <c r="B131" t="s">
+        <v>304</v>
+      </c>
+      <c r="C131" t="s">
         <v>305</v>
-      </c>
-      <c r="C131" t="s">
-        <v>306</v>
       </c>
       <c r="D131" t="s">
         <v>28</v>
       </c>
       <c r="E131" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F131" t="s">
         <v>8</v>
@@ -5390,16 +5921,16 @@
         <v>46118</v>
       </c>
       <c r="B132" t="s">
+        <v>306</v>
+      </c>
+      <c r="C132" t="s">
         <v>307</v>
-      </c>
-      <c r="C132" t="s">
-        <v>308</v>
       </c>
       <c r="D132" t="s">
         <v>23</v>
       </c>
       <c r="E132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F132" t="s">
         <v>8</v>
@@ -5416,16 +5947,16 @@
         <v>46118</v>
       </c>
       <c r="B133" t="s">
+        <v>308</v>
+      </c>
+      <c r="C133" t="s">
         <v>309</v>
-      </c>
-      <c r="C133" t="s">
-        <v>310</v>
       </c>
       <c r="D133" t="s">
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F133" t="s">
         <v>8</v>
@@ -5442,16 +5973,16 @@
         <v>46118</v>
       </c>
       <c r="B134" t="s">
+        <v>310</v>
+      </c>
+      <c r="C134" t="s">
         <v>311</v>
-      </c>
-      <c r="C134" t="s">
-        <v>312</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
       </c>
       <c r="E134" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F134" t="s">
         <v>8</v>
@@ -5468,16 +5999,16 @@
         <v>46118</v>
       </c>
       <c r="B135" t="s">
+        <v>312</v>
+      </c>
+      <c r="C135" t="s">
         <v>313</v>
-      </c>
-      <c r="C135" t="s">
-        <v>314</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
       </c>
       <c r="E135" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F135" t="s">
         <v>8</v>
@@ -5494,16 +6025,16 @@
         <v>46118</v>
       </c>
       <c r="B136" t="s">
+        <v>314</v>
+      </c>
+      <c r="C136" t="s">
         <v>315</v>
-      </c>
-      <c r="C136" t="s">
-        <v>316</v>
       </c>
       <c r="D136" t="s">
         <v>6</v>
       </c>
       <c r="E136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F136" t="s">
         <v>8</v>
@@ -5520,16 +6051,16 @@
         <v>46118</v>
       </c>
       <c r="B137" t="s">
+        <v>316</v>
+      </c>
+      <c r="C137" t="s">
         <v>317</v>
-      </c>
-      <c r="C137" t="s">
-        <v>318</v>
       </c>
       <c r="D137" t="s">
         <v>12</v>
       </c>
       <c r="E137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F137" t="s">
         <v>8</v>
@@ -5546,22 +6077,22 @@
         <v>46118</v>
       </c>
       <c r="B138" t="s">
+        <v>318</v>
+      </c>
+      <c r="C138" t="s">
         <v>319</v>
-      </c>
-      <c r="C138" t="s">
-        <v>320</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F138" t="s">
         <v>7</v>
       </c>
       <c r="G138" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -5572,16 +6103,16 @@
         <v>46118</v>
       </c>
       <c r="B139" t="s">
+        <v>320</v>
+      </c>
+      <c r="C139" t="s">
         <v>321</v>
       </c>
-      <c r="C139" t="s">
-        <v>322</v>
-      </c>
       <c r="D139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s">
         <v>8</v>
@@ -5598,16 +6129,16 @@
         <v>46118</v>
       </c>
       <c r="B140" t="s">
+        <v>322</v>
+      </c>
+      <c r="C140" t="s">
         <v>323</v>
-      </c>
-      <c r="C140" t="s">
-        <v>324</v>
       </c>
       <c r="D140" t="s">
         <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F140" t="s">
         <v>8</v>
@@ -5624,16 +6155,16 @@
         <v>46118</v>
       </c>
       <c r="B141" t="s">
+        <v>324</v>
+      </c>
+      <c r="C141" t="s">
         <v>325</v>
-      </c>
-      <c r="C141" t="s">
-        <v>326</v>
       </c>
       <c r="D141" t="s">
         <v>15</v>
       </c>
       <c r="E141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F141" t="s">
         <v>8</v>
@@ -5650,16 +6181,16 @@
         <v>46118</v>
       </c>
       <c r="B142" t="s">
+        <v>326</v>
+      </c>
+      <c r="C142" t="s">
         <v>327</v>
       </c>
-      <c r="C142" t="s">
-        <v>328</v>
-      </c>
       <c r="D142" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F142" t="s">
         <v>8</v>
@@ -5676,22 +6207,22 @@
         <v>46118</v>
       </c>
       <c r="B143" t="s">
+        <v>328</v>
+      </c>
+      <c r="C143" t="s">
         <v>329</v>
-      </c>
-      <c r="C143" t="s">
-        <v>330</v>
       </c>
       <c r="D143" t="s">
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F143" t="s">
         <v>8</v>
       </c>
       <c r="G143" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -5702,16 +6233,16 @@
         <v>46118</v>
       </c>
       <c r="B144" t="s">
+        <v>330</v>
+      </c>
+      <c r="C144" t="s">
         <v>331</v>
-      </c>
-      <c r="C144" t="s">
-        <v>332</v>
       </c>
       <c r="D144" t="s">
         <v>15</v>
       </c>
       <c r="E144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F144" t="s">
         <v>8</v>
@@ -5728,16 +6259,16 @@
         <v>46118</v>
       </c>
       <c r="B145" t="s">
+        <v>332</v>
+      </c>
+      <c r="C145" t="s">
         <v>333</v>
-      </c>
-      <c r="C145" t="s">
-        <v>334</v>
       </c>
       <c r="D145" t="s">
         <v>16</v>
       </c>
       <c r="E145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F145" t="s">
         <v>8</v>
@@ -5754,16 +6285,16 @@
         <v>46118</v>
       </c>
       <c r="B146" t="s">
+        <v>334</v>
+      </c>
+      <c r="C146" t="s">
         <v>335</v>
-      </c>
-      <c r="C146" t="s">
-        <v>336</v>
       </c>
       <c r="D146" t="s">
         <v>28</v>
       </c>
       <c r="E146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F146" t="s">
         <v>8</v>
@@ -5780,16 +6311,16 @@
         <v>46118</v>
       </c>
       <c r="B147" t="s">
+        <v>336</v>
+      </c>
+      <c r="C147" t="s">
         <v>337</v>
-      </c>
-      <c r="C147" t="s">
-        <v>338</v>
       </c>
       <c r="D147" t="s">
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F147" t="s">
         <v>8</v>
@@ -5806,16 +6337,16 @@
         <v>46118</v>
       </c>
       <c r="B148" t="s">
+        <v>338</v>
+      </c>
+      <c r="C148" t="s">
         <v>339</v>
       </c>
-      <c r="C148" t="s">
-        <v>340</v>
-      </c>
       <c r="D148" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E148" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F148" t="s">
         <v>8</v>
@@ -5832,16 +6363,16 @@
         <v>46118</v>
       </c>
       <c r="B149" t="s">
+        <v>340</v>
+      </c>
+      <c r="C149" t="s">
         <v>341</v>
-      </c>
-      <c r="C149" t="s">
-        <v>342</v>
       </c>
       <c r="D149" t="s">
         <v>16</v>
       </c>
       <c r="E149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F149" t="s">
         <v>8</v>
@@ -5858,16 +6389,16 @@
         <v>46118</v>
       </c>
       <c r="B150" t="s">
+        <v>342</v>
+      </c>
+      <c r="C150" t="s">
         <v>343</v>
-      </c>
-      <c r="C150" t="s">
-        <v>344</v>
       </c>
       <c r="D150" t="s">
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F150" t="s">
         <v>8</v>
@@ -5884,22 +6415,22 @@
         <v>46118</v>
       </c>
       <c r="B151" t="s">
+        <v>344</v>
+      </c>
+      <c r="C151" t="s">
         <v>345</v>
-      </c>
-      <c r="C151" t="s">
-        <v>346</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F151" t="s">
         <v>8</v>
       </c>
       <c r="G151" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -5910,22 +6441,22 @@
         <v>46118</v>
       </c>
       <c r="B152" t="s">
+        <v>346</v>
+      </c>
+      <c r="C152" t="s">
         <v>347</v>
       </c>
-      <c r="C152" t="s">
-        <v>348</v>
-      </c>
       <c r="D152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F152" t="s">
         <v>8</v>
       </c>
       <c r="G152" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -5936,22 +6467,22 @@
         <v>46118</v>
       </c>
       <c r="B153" t="s">
+        <v>348</v>
+      </c>
+      <c r="C153" t="s">
         <v>349</v>
-      </c>
-      <c r="C153" t="s">
-        <v>350</v>
       </c>
       <c r="D153" t="s">
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F153" t="s">
         <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -5962,22 +6493,22 @@
         <v>46118</v>
       </c>
       <c r="B154" t="s">
+        <v>350</v>
+      </c>
+      <c r="C154" t="s">
         <v>351</v>
-      </c>
-      <c r="C154" t="s">
-        <v>352</v>
       </c>
       <c r="D154" t="s">
         <v>22</v>
       </c>
       <c r="E154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F154" t="s">
         <v>8</v>
       </c>
       <c r="G154" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -5988,16 +6519,16 @@
         <v>46118</v>
       </c>
       <c r="B155" t="s">
+        <v>352</v>
+      </c>
+      <c r="C155" t="s">
         <v>353</v>
-      </c>
-      <c r="C155" t="s">
-        <v>354</v>
       </c>
       <c r="D155" t="s">
         <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F155" t="s">
         <v>7</v>
@@ -6014,16 +6545,16 @@
         <v>46118</v>
       </c>
       <c r="B156" t="s">
+        <v>354</v>
+      </c>
+      <c r="C156" t="s">
         <v>355</v>
-      </c>
-      <c r="C156" t="s">
-        <v>356</v>
       </c>
       <c r="D156" t="s">
         <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F156" t="s">
         <v>8</v>
@@ -6040,16 +6571,16 @@
         <v>46118</v>
       </c>
       <c r="B157" t="s">
+        <v>356</v>
+      </c>
+      <c r="C157" t="s">
         <v>357</v>
-      </c>
-      <c r="C157" t="s">
-        <v>358</v>
       </c>
       <c r="D157" t="s">
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F157" t="s">
         <v>8</v>
@@ -6066,16 +6597,16 @@
         <v>46118</v>
       </c>
       <c r="B158" t="s">
+        <v>358</v>
+      </c>
+      <c r="C158" t="s">
         <v>359</v>
       </c>
-      <c r="C158" t="s">
-        <v>360</v>
-      </c>
       <c r="D158" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F158" t="s">
         <v>7</v>
@@ -6092,22 +6623,22 @@
         <v>46118</v>
       </c>
       <c r="B159" t="s">
+        <v>360</v>
+      </c>
+      <c r="C159" t="s">
         <v>361</v>
-      </c>
-      <c r="C159" t="s">
-        <v>362</v>
       </c>
       <c r="D159" t="s">
         <v>25</v>
       </c>
       <c r="E159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F159" t="s">
         <v>7</v>
       </c>
       <c r="G159" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -6118,16 +6649,16 @@
         <v>46118</v>
       </c>
       <c r="B160" t="s">
+        <v>362</v>
+      </c>
+      <c r="C160" t="s">
         <v>363</v>
-      </c>
-      <c r="C160" t="s">
-        <v>364</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F160" t="s">
         <v>8</v>
@@ -6144,16 +6675,16 @@
         <v>46118</v>
       </c>
       <c r="B161" t="s">
+        <v>364</v>
+      </c>
+      <c r="C161" t="s">
         <v>365</v>
-      </c>
-      <c r="C161" t="s">
-        <v>366</v>
       </c>
       <c r="D161" t="s">
         <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F161" t="s">
         <v>8</v>
@@ -6170,25 +6701,22 @@
         <v>46118</v>
       </c>
       <c r="B162" t="s">
+        <v>366</v>
+      </c>
+      <c r="C162" t="s">
         <v>367</v>
-      </c>
-      <c r="C162" t="s">
-        <v>368</v>
       </c>
       <c r="D162" t="s">
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>404</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -6196,22 +6724,22 @@
         <v>46118</v>
       </c>
       <c r="B163" t="s">
+        <v>368</v>
+      </c>
+      <c r="C163" t="s">
         <v>369</v>
-      </c>
-      <c r="C163" t="s">
-        <v>370</v>
       </c>
       <c r="D163" t="s">
         <v>24</v>
       </c>
       <c r="E163" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F163" t="s">
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -6219,16 +6747,16 @@
         <v>46118</v>
       </c>
       <c r="B164" t="s">
+        <v>370</v>
+      </c>
+      <c r="C164" t="s">
         <v>371</v>
       </c>
-      <c r="C164" t="s">
-        <v>372</v>
-      </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E164" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F164" t="s">
         <v>7</v>
@@ -6245,16 +6773,16 @@
         <v>46118</v>
       </c>
       <c r="B165" t="s">
+        <v>372</v>
+      </c>
+      <c r="C165" t="s">
         <v>373</v>
-      </c>
-      <c r="C165" t="s">
-        <v>374</v>
       </c>
       <c r="D165" t="s">
         <v>15</v>
       </c>
       <c r="E165" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F165" t="s">
         <v>8</v>
@@ -6271,16 +6799,16 @@
         <v>46118</v>
       </c>
       <c r="B166" t="s">
+        <v>374</v>
+      </c>
+      <c r="C166" t="s">
         <v>375</v>
-      </c>
-      <c r="C166" t="s">
-        <v>376</v>
       </c>
       <c r="D166" t="s">
         <v>15</v>
       </c>
       <c r="E166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F166" t="s">
         <v>8</v>
@@ -6297,16 +6825,16 @@
         <v>46118</v>
       </c>
       <c r="B167" t="s">
+        <v>376</v>
+      </c>
+      <c r="C167" t="s">
         <v>377</v>
-      </c>
-      <c r="C167" t="s">
-        <v>378</v>
       </c>
       <c r="D167" t="s">
         <v>22</v>
       </c>
       <c r="E167" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F167" t="s">
         <v>8</v>
@@ -6323,16 +6851,16 @@
         <v>46118</v>
       </c>
       <c r="B168" t="s">
+        <v>378</v>
+      </c>
+      <c r="C168" t="s">
         <v>379</v>
-      </c>
-      <c r="C168" t="s">
-        <v>380</v>
       </c>
       <c r="D168" t="s">
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F168" t="s">
         <v>8</v>
@@ -6349,16 +6877,16 @@
         <v>46118</v>
       </c>
       <c r="B169" t="s">
+        <v>380</v>
+      </c>
+      <c r="C169" t="s">
         <v>381</v>
-      </c>
-      <c r="C169" t="s">
-        <v>382</v>
       </c>
       <c r="D169" t="s">
         <v>12</v>
       </c>
       <c r="E169" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F169" t="s">
         <v>8</v>
@@ -6375,19 +6903,19 @@
         <v>46118</v>
       </c>
       <c r="B170" t="s">
+        <v>382</v>
+      </c>
+      <c r="C170" t="s">
         <v>383</v>
-      </c>
-      <c r="C170" t="s">
-        <v>384</v>
       </c>
       <c r="D170" t="s">
         <v>12</v>
       </c>
       <c r="E170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F170" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G170" t="s">
         <v>18</v>
@@ -6401,16 +6929,16 @@
         <v>46118</v>
       </c>
       <c r="B171" t="s">
+        <v>385</v>
+      </c>
+      <c r="C171" t="s">
         <v>386</v>
-      </c>
-      <c r="C171" t="s">
-        <v>387</v>
       </c>
       <c r="D171" t="s">
         <v>23</v>
       </c>
       <c r="E171" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F171" t="s">
         <v>8</v>
@@ -6427,16 +6955,16 @@
         <v>46118</v>
       </c>
       <c r="B172" t="s">
+        <v>387</v>
+      </c>
+      <c r="C172" t="s">
         <v>388</v>
-      </c>
-      <c r="C172" t="s">
-        <v>389</v>
       </c>
       <c r="D172" t="s">
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F172" t="s">
         <v>8</v>
@@ -6450,16 +6978,16 @@
         <v>46118</v>
       </c>
       <c r="B173" t="s">
+        <v>389</v>
+      </c>
+      <c r="C173" t="s">
         <v>390</v>
-      </c>
-      <c r="C173" t="s">
-        <v>391</v>
       </c>
       <c r="D173" t="s">
         <v>28</v>
       </c>
       <c r="E173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F173" t="s">
         <v>8</v>
@@ -6476,19 +7004,19 @@
         <v>46118</v>
       </c>
       <c r="B174" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" t="s">
         <v>392</v>
-      </c>
-      <c r="C174" t="s">
-        <v>393</v>
       </c>
       <c r="D174" t="s">
         <v>19</v>
       </c>
       <c r="E174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F174" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G174" t="s">
         <v>18</v>
@@ -6502,16 +7030,16 @@
         <v>46118</v>
       </c>
       <c r="B175" t="s">
+        <v>393</v>
+      </c>
+      <c r="C175" t="s">
         <v>394</v>
-      </c>
-      <c r="C175" t="s">
-        <v>395</v>
       </c>
       <c r="D175" t="s">
         <v>15</v>
       </c>
       <c r="E175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F175" t="s">
         <v>8</v>
@@ -6528,16 +7056,16 @@
         <v>46118</v>
       </c>
       <c r="B176" t="s">
+        <v>395</v>
+      </c>
+      <c r="C176" t="s">
         <v>396</v>
-      </c>
-      <c r="C176" t="s">
-        <v>397</v>
       </c>
       <c r="D176" t="s">
         <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F176" t="s">
         <v>8</v>
@@ -6554,16 +7082,16 @@
         <v>46118</v>
       </c>
       <c r="B177" t="s">
+        <v>397</v>
+      </c>
+      <c r="C177" t="s">
         <v>398</v>
-      </c>
-      <c r="C177" t="s">
-        <v>399</v>
       </c>
       <c r="D177" t="s">
         <v>24</v>
       </c>
       <c r="E177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F177" t="s">
         <v>7</v>
@@ -6580,16 +7108,16 @@
         <v>46118</v>
       </c>
       <c r="B178" t="s">
+        <v>399</v>
+      </c>
+      <c r="C178" t="s">
         <v>400</v>
-      </c>
-      <c r="C178" t="s">
-        <v>401</v>
       </c>
       <c r="D178" t="s">
         <v>6</v>
       </c>
       <c r="E178" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F178" t="s">
         <v>8</v>
@@ -6606,16 +7134,16 @@
         <v>46118</v>
       </c>
       <c r="B179" t="s">
+        <v>401</v>
+      </c>
+      <c r="C179" t="s">
         <v>402</v>
-      </c>
-      <c r="C179" t="s">
-        <v>403</v>
       </c>
       <c r="D179" t="s">
         <v>25</v>
       </c>
       <c r="E179" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F179" t="s">
         <v>7</v>
@@ -6632,22 +7160,25 @@
         <v>46119</v>
       </c>
       <c r="B180" t="s">
+        <v>405</v>
+      </c>
+      <c r="C180" t="s">
         <v>406</v>
-      </c>
-      <c r="C180" t="s">
-        <v>407</v>
       </c>
       <c r="D180" t="s">
         <v>16</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F180" t="s">
         <v>8</v>
       </c>
       <c r="G180" t="s">
         <v>18</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -6655,22 +7186,25 @@
         <v>46119</v>
       </c>
       <c r="B181" t="s">
+        <v>407</v>
+      </c>
+      <c r="C181" t="s">
         <v>408</v>
-      </c>
-      <c r="C181" t="s">
-        <v>409</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F181" t="s">
         <v>8</v>
       </c>
       <c r="G181" t="s">
         <v>18</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -6678,22 +7212,25 @@
         <v>46119</v>
       </c>
       <c r="B182" t="s">
+        <v>409</v>
+      </c>
+      <c r="C182" t="s">
         <v>410</v>
-      </c>
-      <c r="C182" t="s">
-        <v>411</v>
       </c>
       <c r="D182" t="s">
         <v>6</v>
       </c>
       <c r="E182" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F182" t="s">
         <v>8</v>
       </c>
       <c r="G182" t="s">
         <v>18</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -6701,22 +7238,25 @@
         <v>46119</v>
       </c>
       <c r="B183" t="s">
+        <v>411</v>
+      </c>
+      <c r="C183" t="s">
         <v>412</v>
-      </c>
-      <c r="C183" t="s">
-        <v>413</v>
       </c>
       <c r="D183" t="s">
         <v>27</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F183" t="s">
         <v>8</v>
       </c>
       <c r="G183" t="s">
         <v>18</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -6724,22 +7264,25 @@
         <v>46119</v>
       </c>
       <c r="B184" t="s">
+        <v>413</v>
+      </c>
+      <c r="C184" t="s">
         <v>414</v>
-      </c>
-      <c r="C184" t="s">
-        <v>415</v>
       </c>
       <c r="D184" t="s">
         <v>27</v>
       </c>
       <c r="E184" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G184" t="s">
         <v>18</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -6747,22 +7290,25 @@
         <v>46119</v>
       </c>
       <c r="B185" t="s">
+        <v>415</v>
+      </c>
+      <c r="C185" t="s">
         <v>416</v>
-      </c>
-      <c r="C185" t="s">
-        <v>417</v>
       </c>
       <c r="D185" t="s">
         <v>27</v>
       </c>
       <c r="E185" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G185" t="s">
         <v>18</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -6770,22 +7316,25 @@
         <v>46119</v>
       </c>
       <c r="B186" t="s">
+        <v>417</v>
+      </c>
+      <c r="C186" t="s">
         <v>418</v>
-      </c>
-      <c r="C186" t="s">
-        <v>419</v>
       </c>
       <c r="D186" t="s">
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F186" t="s">
         <v>8</v>
       </c>
       <c r="G186" t="s">
         <v>18</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -6793,22 +7342,25 @@
         <v>46119</v>
       </c>
       <c r="B187" t="s">
+        <v>419</v>
+      </c>
+      <c r="C187" t="s">
         <v>420</v>
       </c>
-      <c r="C187" t="s">
-        <v>421</v>
-      </c>
       <c r="D187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E187" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F187" t="s">
         <v>7</v>
       </c>
       <c r="G187" t="s">
         <v>18</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -6816,22 +7368,25 @@
         <v>46119</v>
       </c>
       <c r="B188" t="s">
+        <v>421</v>
+      </c>
+      <c r="C188" t="s">
         <v>422</v>
-      </c>
-      <c r="C188" t="s">
-        <v>423</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F188" t="s">
         <v>7</v>
       </c>
       <c r="G188" t="s">
-        <v>20</v>
+        <v>518</v>
+      </c>
+      <c r="H188" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -6839,22 +7394,25 @@
         <v>46119</v>
       </c>
       <c r="B189" t="s">
+        <v>423</v>
+      </c>
+      <c r="C189" t="s">
         <v>424</v>
-      </c>
-      <c r="C189" t="s">
-        <v>425</v>
       </c>
       <c r="D189" t="s">
         <v>24</v>
       </c>
       <c r="E189" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F189" t="s">
         <v>7</v>
       </c>
       <c r="G189" t="s">
         <v>18</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -6862,22 +7420,25 @@
         <v>46119</v>
       </c>
       <c r="B190" t="s">
+        <v>425</v>
+      </c>
+      <c r="C190" t="s">
         <v>426</v>
-      </c>
-      <c r="C190" t="s">
-        <v>427</v>
       </c>
       <c r="D190" t="s">
         <v>28</v>
       </c>
       <c r="E190" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F190" t="s">
         <v>8</v>
       </c>
       <c r="G190" t="s">
         <v>21</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -6885,22 +7446,25 @@
         <v>46119</v>
       </c>
       <c r="B191" t="s">
+        <v>427</v>
+      </c>
+      <c r="C191" t="s">
         <v>428</v>
-      </c>
-      <c r="C191" t="s">
-        <v>429</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F191" t="s">
         <v>7</v>
       </c>
       <c r="G191" t="s">
         <v>18</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -6908,16 +7472,16 @@
         <v>46119</v>
       </c>
       <c r="B192" t="s">
+        <v>429</v>
+      </c>
+      <c r="C192" t="s">
         <v>430</v>
-      </c>
-      <c r="C192" t="s">
-        <v>431</v>
       </c>
       <c r="D192" t="s">
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F192" t="s">
         <v>8</v>
@@ -6925,22 +7489,25 @@
       <c r="G192" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>46119</v>
       </c>
       <c r="B193" t="s">
+        <v>431</v>
+      </c>
+      <c r="C193" t="s">
         <v>432</v>
-      </c>
-      <c r="C193" t="s">
-        <v>433</v>
       </c>
       <c r="D193" t="s">
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F193" t="s">
         <v>8</v>
@@ -6948,22 +7515,25 @@
       <c r="G193" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>46119</v>
       </c>
       <c r="B194" t="s">
+        <v>433</v>
+      </c>
+      <c r="C194" t="s">
         <v>434</v>
-      </c>
-      <c r="C194" t="s">
-        <v>435</v>
       </c>
       <c r="D194" t="s">
         <v>22</v>
       </c>
       <c r="E194" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F194" t="s">
         <v>7</v>
@@ -6971,22 +7541,25 @@
       <c r="G194" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>46119</v>
       </c>
       <c r="B195" t="s">
+        <v>435</v>
+      </c>
+      <c r="C195" t="s">
         <v>436</v>
-      </c>
-      <c r="C195" t="s">
-        <v>437</v>
       </c>
       <c r="D195" t="s">
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F195" t="s">
         <v>8</v>
@@ -6994,22 +7567,25 @@
       <c r="G195" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>46119</v>
       </c>
       <c r="B196" t="s">
+        <v>437</v>
+      </c>
+      <c r="C196" t="s">
         <v>438</v>
-      </c>
-      <c r="C196" t="s">
-        <v>439</v>
       </c>
       <c r="D196" t="s">
         <v>23</v>
       </c>
       <c r="E196" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F196" t="s">
         <v>8</v>
@@ -7017,22 +7593,25 @@
       <c r="G196" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>46119</v>
       </c>
       <c r="B197" t="s">
+        <v>439</v>
+      </c>
+      <c r="C197" t="s">
         <v>440</v>
-      </c>
-      <c r="C197" t="s">
-        <v>441</v>
       </c>
       <c r="D197" t="s">
         <v>22</v>
       </c>
       <c r="E197" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F197" t="s">
         <v>8</v>
@@ -7040,22 +7619,25 @@
       <c r="G197" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>46119</v>
       </c>
       <c r="B198" t="s">
+        <v>441</v>
+      </c>
+      <c r="C198" t="s">
         <v>442</v>
-      </c>
-      <c r="C198" t="s">
-        <v>443</v>
       </c>
       <c r="D198" t="s">
         <v>19</v>
       </c>
       <c r="E198" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F198" t="s">
         <v>8</v>
@@ -7063,45 +7645,48 @@
       <c r="G198" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>46119</v>
       </c>
       <c r="B199" t="s">
+        <v>443</v>
+      </c>
+      <c r="C199" t="s">
         <v>444</v>
       </c>
-      <c r="C199" t="s">
-        <v>445</v>
-      </c>
       <c r="D199" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E199" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F199" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G199" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>46119</v>
       </c>
       <c r="B200" t="s">
+        <v>445</v>
+      </c>
+      <c r="C200" t="s">
         <v>446</v>
-      </c>
-      <c r="C200" t="s">
-        <v>447</v>
       </c>
       <c r="D200" t="s">
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F200" t="s">
         <v>8</v>
@@ -7109,22 +7694,25 @@
       <c r="G200" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>46119</v>
       </c>
       <c r="B201" t="s">
+        <v>447</v>
+      </c>
+      <c r="C201" t="s">
         <v>448</v>
-      </c>
-      <c r="C201" t="s">
-        <v>449</v>
       </c>
       <c r="D201" t="s">
         <v>22</v>
       </c>
       <c r="E201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F201" t="s">
         <v>8</v>
@@ -7132,22 +7720,25 @@
       <c r="G201" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>46119</v>
       </c>
       <c r="B202" t="s">
+        <v>449</v>
+      </c>
+      <c r="C202" t="s">
         <v>450</v>
       </c>
-      <c r="C202" t="s">
-        <v>451</v>
-      </c>
       <c r="D202" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E202" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F202" t="s">
         <v>7</v>
@@ -7155,22 +7746,25 @@
       <c r="G202" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>46119</v>
       </c>
       <c r="B203" t="s">
+        <v>451</v>
+      </c>
+      <c r="C203" t="s">
         <v>452</v>
-      </c>
-      <c r="C203" t="s">
-        <v>453</v>
       </c>
       <c r="D203" t="s">
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F203" t="s">
         <v>8</v>
@@ -7178,22 +7772,25 @@
       <c r="G203" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>46119</v>
       </c>
       <c r="B204" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D204" t="s">
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F204" t="s">
         <v>8</v>
@@ -7201,22 +7798,25 @@
       <c r="G204" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>46119</v>
       </c>
       <c r="B205" t="s">
+        <v>454</v>
+      </c>
+      <c r="C205" t="s">
         <v>455</v>
-      </c>
-      <c r="C205" t="s">
-        <v>456</v>
       </c>
       <c r="D205" t="s">
         <v>28</v>
       </c>
       <c r="E205" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F205" t="s">
         <v>8</v>
@@ -7224,45 +7824,51 @@
       <c r="G205" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>46119</v>
       </c>
       <c r="B206" t="s">
+        <v>456</v>
+      </c>
+      <c r="C206" t="s">
         <v>457</v>
       </c>
-      <c r="C206" t="s">
-        <v>458</v>
-      </c>
       <c r="D206" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E206" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F206" t="s">
         <v>7</v>
       </c>
       <c r="G206" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>46119</v>
       </c>
       <c r="B207" t="s">
+        <v>458</v>
+      </c>
+      <c r="C207" t="s">
         <v>459</v>
-      </c>
-      <c r="C207" t="s">
-        <v>460</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
       </c>
       <c r="E207" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F207" t="s">
         <v>8</v>
@@ -7270,45 +7876,51 @@
       <c r="G207" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>46119</v>
       </c>
       <c r="B208" t="s">
+        <v>460</v>
+      </c>
+      <c r="C208" t="s">
         <v>461</v>
-      </c>
-      <c r="C208" t="s">
-        <v>462</v>
       </c>
       <c r="D208" t="s">
         <v>19</v>
       </c>
       <c r="E208" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F208" t="s">
         <v>8</v>
       </c>
       <c r="G208" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>46119</v>
       </c>
       <c r="B209" t="s">
+        <v>462</v>
+      </c>
+      <c r="C209" t="s">
         <v>463</v>
       </c>
-      <c r="C209" t="s">
-        <v>464</v>
-      </c>
       <c r="D209" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E209" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F209" t="s">
         <v>7</v>
@@ -7316,22 +7928,25 @@
       <c r="G209" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>46119</v>
       </c>
       <c r="B210" t="s">
+        <v>464</v>
+      </c>
+      <c r="C210" t="s">
         <v>465</v>
-      </c>
-      <c r="C210" t="s">
-        <v>466</v>
       </c>
       <c r="D210" t="s">
         <v>28</v>
       </c>
       <c r="E210" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F210" t="s">
         <v>8</v>
@@ -7339,45 +7954,51 @@
       <c r="G210" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>46119</v>
       </c>
       <c r="B211" t="s">
+        <v>466</v>
+      </c>
+      <c r="C211" t="s">
         <v>467</v>
-      </c>
-      <c r="C211" t="s">
-        <v>468</v>
       </c>
       <c r="D211" t="s">
         <v>22</v>
       </c>
       <c r="E211" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F211" t="s">
         <v>7</v>
       </c>
       <c r="G211" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>46119</v>
       </c>
       <c r="B212" t="s">
+        <v>468</v>
+      </c>
+      <c r="C212" t="s">
         <v>469</v>
-      </c>
-      <c r="C212" t="s">
-        <v>470</v>
       </c>
       <c r="D212" t="s">
         <v>23</v>
       </c>
       <c r="E212" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F212" t="s">
         <v>8</v>
@@ -7385,22 +8006,25 @@
       <c r="G212" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>46119</v>
       </c>
       <c r="B213" t="s">
+        <v>470</v>
+      </c>
+      <c r="C213" t="s">
         <v>471</v>
       </c>
-      <c r="C213" t="s">
-        <v>472</v>
-      </c>
       <c r="D213" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E213" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
@@ -7408,22 +8032,25 @@
       <c r="G213" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>46119</v>
       </c>
       <c r="B214" t="s">
+        <v>472</v>
+      </c>
+      <c r="C214" t="s">
         <v>473</v>
-      </c>
-      <c r="C214" t="s">
-        <v>474</v>
       </c>
       <c r="D214" t="s">
         <v>6</v>
       </c>
       <c r="E214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F214" t="s">
         <v>8</v>
@@ -7431,22 +8058,25 @@
       <c r="G214" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>46119</v>
       </c>
       <c r="B215" t="s">
+        <v>474</v>
+      </c>
+      <c r="C215" t="s">
         <v>475</v>
-      </c>
-      <c r="C215" t="s">
-        <v>476</v>
       </c>
       <c r="D215" t="s">
         <v>12</v>
       </c>
       <c r="E215" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F215" t="s">
         <v>8</v>
@@ -7454,22 +8084,25 @@
       <c r="G215" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>46119</v>
       </c>
       <c r="B216" t="s">
+        <v>476</v>
+      </c>
+      <c r="C216" t="s">
         <v>477</v>
-      </c>
-      <c r="C216" t="s">
-        <v>478</v>
       </c>
       <c r="D216" t="s">
         <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F216" t="s">
         <v>8</v>
@@ -7477,45 +8110,51 @@
       <c r="G216" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>46119</v>
       </c>
       <c r="B217" t="s">
+        <v>478</v>
+      </c>
+      <c r="C217" t="s">
         <v>479</v>
       </c>
-      <c r="C217" t="s">
-        <v>480</v>
-      </c>
       <c r="D217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E217" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F217" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G217" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>46119</v>
       </c>
       <c r="B218" t="s">
+        <v>480</v>
+      </c>
+      <c r="C218" t="s">
         <v>481</v>
-      </c>
-      <c r="C218" t="s">
-        <v>482</v>
       </c>
       <c r="D218" t="s">
         <v>16</v>
       </c>
       <c r="E218" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F218" t="s">
         <v>8</v>
@@ -7523,68 +8162,77 @@
       <c r="G218" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>46119</v>
       </c>
       <c r="B219" t="s">
+        <v>482</v>
+      </c>
+      <c r="C219" t="s">
         <v>483</v>
-      </c>
-      <c r="C219" t="s">
-        <v>484</v>
       </c>
       <c r="D219" t="s">
         <v>19</v>
       </c>
       <c r="E219" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F219" t="s">
         <v>8</v>
       </c>
       <c r="G219" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>46119</v>
       </c>
       <c r="B220" t="s">
+        <v>484</v>
+      </c>
+      <c r="C220" t="s">
         <v>485</v>
       </c>
-      <c r="C220" t="s">
-        <v>486</v>
-      </c>
       <c r="D220" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E220" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>46119</v>
       </c>
       <c r="B221" t="s">
+        <v>486</v>
+      </c>
+      <c r="C221" t="s">
         <v>487</v>
-      </c>
-      <c r="C221" t="s">
-        <v>488</v>
       </c>
       <c r="D221" t="s">
         <v>16</v>
       </c>
       <c r="E221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F221" t="s">
         <v>8</v>
@@ -7592,22 +8240,25 @@
       <c r="G221" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>46119</v>
       </c>
       <c r="B222" t="s">
+        <v>488</v>
+      </c>
+      <c r="C222" t="s">
         <v>489</v>
       </c>
-      <c r="C222" t="s">
-        <v>490</v>
-      </c>
       <c r="D222" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E222" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F222" t="s">
         <v>7</v>
@@ -7615,22 +8266,25 @@
       <c r="G222" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>46119</v>
       </c>
       <c r="B223" t="s">
+        <v>490</v>
+      </c>
+      <c r="C223" t="s">
         <v>491</v>
-      </c>
-      <c r="C223" t="s">
-        <v>492</v>
       </c>
       <c r="D223" t="s">
         <v>14</v>
       </c>
       <c r="E223" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F223" t="s">
         <v>8</v>
@@ -7638,22 +8292,25 @@
       <c r="G223" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>46119</v>
       </c>
       <c r="B224" t="s">
+        <v>492</v>
+      </c>
+      <c r="C224" t="s">
         <v>493</v>
-      </c>
-      <c r="C224" t="s">
-        <v>494</v>
       </c>
       <c r="D224" t="s">
         <v>14</v>
       </c>
       <c r="E224" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F224" t="s">
         <v>8</v>
@@ -7661,22 +8318,25 @@
       <c r="G224" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>46119</v>
       </c>
       <c r="B225" t="s">
+        <v>81</v>
+      </c>
+      <c r="C225" t="s">
         <v>82</v>
       </c>
-      <c r="C225" t="s">
-        <v>83</v>
-      </c>
       <c r="D225" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E225" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F225" t="s">
         <v>7</v>
@@ -7684,22 +8344,25 @@
       <c r="G225" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>46119</v>
       </c>
       <c r="B226" t="s">
+        <v>494</v>
+      </c>
+      <c r="C226" t="s">
         <v>495</v>
       </c>
-      <c r="C226" t="s">
-        <v>496</v>
-      </c>
       <c r="D226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F226" t="s">
         <v>7</v>
@@ -7707,45 +8370,51 @@
       <c r="G226" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>46119</v>
       </c>
       <c r="B227" t="s">
+        <v>496</v>
+      </c>
+      <c r="C227" t="s">
         <v>497</v>
-      </c>
-      <c r="C227" t="s">
-        <v>498</v>
       </c>
       <c r="D227" t="s">
         <v>19</v>
       </c>
       <c r="E227" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F227" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G227" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>46119</v>
       </c>
       <c r="B228" t="s">
+        <v>498</v>
+      </c>
+      <c r="C228" t="s">
         <v>499</v>
-      </c>
-      <c r="C228" t="s">
-        <v>500</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
       </c>
       <c r="E228" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F228" t="s">
         <v>7</v>
@@ -7753,22 +8422,25 @@
       <c r="G228" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>46119</v>
       </c>
       <c r="B229" t="s">
+        <v>500</v>
+      </c>
+      <c r="C229" t="s">
         <v>501</v>
       </c>
-      <c r="C229" t="s">
-        <v>502</v>
-      </c>
       <c r="D229" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E229" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F229" t="s">
         <v>7</v>
@@ -7776,45 +8448,51 @@
       <c r="G229" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>46119</v>
       </c>
       <c r="B230" t="s">
+        <v>502</v>
+      </c>
+      <c r="C230" t="s">
         <v>503</v>
-      </c>
-      <c r="C230" t="s">
-        <v>504</v>
       </c>
       <c r="D230" t="s">
         <v>24</v>
       </c>
       <c r="E230" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F230" t="s">
         <v>8</v>
       </c>
       <c r="G230" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>46119</v>
       </c>
       <c r="B231" t="s">
+        <v>504</v>
+      </c>
+      <c r="C231" t="s">
         <v>505</v>
-      </c>
-      <c r="C231" t="s">
-        <v>506</v>
       </c>
       <c r="D231" t="s">
         <v>11</v>
       </c>
       <c r="E231" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F231" t="s">
         <v>8</v>
@@ -7822,22 +8500,25 @@
       <c r="G231" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>46119</v>
       </c>
       <c r="B232" t="s">
+        <v>506</v>
+      </c>
+      <c r="C232" t="s">
         <v>507</v>
-      </c>
-      <c r="C232" t="s">
-        <v>508</v>
       </c>
       <c r="D232" t="s">
         <v>24</v>
       </c>
       <c r="E232" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F232" t="s">
         <v>7</v>
@@ -7845,22 +8526,25 @@
       <c r="G232" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>46119</v>
       </c>
       <c r="B233" t="s">
+        <v>508</v>
+      </c>
+      <c r="C233" t="s">
         <v>509</v>
-      </c>
-      <c r="C233" t="s">
-        <v>510</v>
       </c>
       <c r="D233" t="s">
         <v>15</v>
       </c>
       <c r="E233" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F233" t="s">
         <v>8</v>
@@ -7868,22 +8552,25 @@
       <c r="G233" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>46119</v>
       </c>
       <c r="B234" t="s">
+        <v>510</v>
+      </c>
+      <c r="C234" t="s">
         <v>511</v>
-      </c>
-      <c r="C234" t="s">
-        <v>512</v>
       </c>
       <c r="D234" t="s">
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F234" t="s">
         <v>8</v>
@@ -7891,22 +8578,25 @@
       <c r="G234" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>46119</v>
       </c>
       <c r="B235" t="s">
+        <v>512</v>
+      </c>
+      <c r="C235" t="s">
         <v>513</v>
-      </c>
-      <c r="C235" t="s">
-        <v>514</v>
       </c>
       <c r="D235" t="s">
         <v>28</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F235" t="s">
         <v>8</v>
@@ -7914,22 +8604,25 @@
       <c r="G235" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>46119</v>
       </c>
       <c r="B236" t="s">
+        <v>514</v>
+      </c>
+      <c r="C236" t="s">
         <v>515</v>
-      </c>
-      <c r="C236" t="s">
-        <v>516</v>
       </c>
       <c r="D236" t="s">
         <v>25</v>
       </c>
       <c r="E236" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F236" t="s">
         <v>7</v>
@@ -7937,51 +8630,2053 @@
       <c r="G236" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>46119</v>
       </c>
       <c r="B237" t="s">
+        <v>516</v>
+      </c>
+      <c r="C237" t="s">
         <v>517</v>
-      </c>
-      <c r="C237" t="s">
-        <v>518</v>
       </c>
       <c r="D237" t="s">
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F237" t="s">
         <v>8</v>
       </c>
       <c r="G237" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>46119</v>
       </c>
       <c r="B238" t="s">
+        <v>85</v>
+      </c>
+      <c r="C238" t="s">
         <v>86</v>
-      </c>
-      <c r="C238" t="s">
-        <v>87</v>
       </c>
       <c r="D238" t="s">
         <v>24</v>
       </c>
       <c r="E238" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F238" t="s">
         <v>7</v>
       </c>
       <c r="G238" t="s">
         <v>18</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B239" t="s">
+        <v>519</v>
+      </c>
+      <c r="C239" t="s">
+        <v>520</v>
+      </c>
+      <c r="D239" t="s">
+        <v>24</v>
+      </c>
+      <c r="E239" t="s">
+        <v>38</v>
+      </c>
+      <c r="F239" t="s">
+        <v>7</v>
+      </c>
+      <c r="G239" t="s">
+        <v>18</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B240" t="s">
+        <v>521</v>
+      </c>
+      <c r="C240" t="s">
+        <v>522</v>
+      </c>
+      <c r="D240" t="s">
+        <v>24</v>
+      </c>
+      <c r="E240" t="s">
+        <v>38</v>
+      </c>
+      <c r="F240" t="s">
+        <v>7</v>
+      </c>
+      <c r="G240" t="s">
+        <v>18</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B241" t="s">
+        <v>523</v>
+      </c>
+      <c r="C241" t="s">
+        <v>524</v>
+      </c>
+      <c r="D241" t="s">
+        <v>24</v>
+      </c>
+      <c r="E241" t="s">
+        <v>38</v>
+      </c>
+      <c r="F241" t="s">
+        <v>7</v>
+      </c>
+      <c r="G241" t="s">
+        <v>18</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B242" t="s">
+        <v>525</v>
+      </c>
+      <c r="C242" t="s">
+        <v>526</v>
+      </c>
+      <c r="D242" t="s">
+        <v>23</v>
+      </c>
+      <c r="E242" t="s">
+        <v>36</v>
+      </c>
+      <c r="F242" t="s">
+        <v>8</v>
+      </c>
+      <c r="G242" t="s">
+        <v>18</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B243" t="s">
+        <v>527</v>
+      </c>
+      <c r="C243" t="s">
+        <v>528</v>
+      </c>
+      <c r="D243" t="s">
+        <v>529</v>
+      </c>
+      <c r="E243" t="s">
+        <v>530</v>
+      </c>
+      <c r="F243" t="s">
+        <v>242</v>
+      </c>
+      <c r="G243" t="s">
+        <v>18</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B244" t="s">
+        <v>531</v>
+      </c>
+      <c r="C244" t="s">
+        <v>532</v>
+      </c>
+      <c r="D244" t="s">
+        <v>27</v>
+      </c>
+      <c r="E244" t="s">
+        <v>37</v>
+      </c>
+      <c r="F244" t="s">
+        <v>242</v>
+      </c>
+      <c r="G244" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B245" t="s">
+        <v>533</v>
+      </c>
+      <c r="C245" t="s">
+        <v>534</v>
+      </c>
+      <c r="D245" t="s">
+        <v>27</v>
+      </c>
+      <c r="E245" t="s">
+        <v>37</v>
+      </c>
+      <c r="F245" t="s">
+        <v>242</v>
+      </c>
+      <c r="G245" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B246" t="s">
+        <v>525</v>
+      </c>
+      <c r="C246" t="s">
+        <v>535</v>
+      </c>
+      <c r="D246" t="s">
+        <v>23</v>
+      </c>
+      <c r="E246" t="s">
+        <v>36</v>
+      </c>
+      <c r="F246" t="s">
+        <v>8</v>
+      </c>
+      <c r="G246" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B247" t="s">
+        <v>536</v>
+      </c>
+      <c r="C247" t="s">
+        <v>537</v>
+      </c>
+      <c r="D247" t="s">
+        <v>28</v>
+      </c>
+      <c r="E247" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" t="s">
+        <v>384</v>
+      </c>
+      <c r="G247" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B248" t="s">
+        <v>538</v>
+      </c>
+      <c r="C248" t="s">
+        <v>539</v>
+      </c>
+      <c r="D248" t="s">
+        <v>19</v>
+      </c>
+      <c r="E248" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" t="s">
+        <v>8</v>
+      </c>
+      <c r="G248" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B249" t="s">
+        <v>540</v>
+      </c>
+      <c r="C249" t="s">
+        <v>541</v>
+      </c>
+      <c r="D249" t="s">
+        <v>11</v>
+      </c>
+      <c r="E249" t="s">
+        <v>36</v>
+      </c>
+      <c r="F249" t="s">
+        <v>8</v>
+      </c>
+      <c r="G249" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B250" t="s">
+        <v>542</v>
+      </c>
+      <c r="C250" t="s">
+        <v>543</v>
+      </c>
+      <c r="D250" t="s">
+        <v>19</v>
+      </c>
+      <c r="E250" t="s">
+        <v>36</v>
+      </c>
+      <c r="F250" t="s">
+        <v>384</v>
+      </c>
+      <c r="G250" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B251" t="s">
+        <v>544</v>
+      </c>
+      <c r="C251" t="s">
+        <v>545</v>
+      </c>
+      <c r="D251" t="s">
+        <v>12</v>
+      </c>
+      <c r="E251" t="s">
+        <v>36</v>
+      </c>
+      <c r="F251" t="s">
+        <v>384</v>
+      </c>
+      <c r="G251" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B252" t="s">
+        <v>546</v>
+      </c>
+      <c r="C252" t="s">
+        <v>547</v>
+      </c>
+      <c r="D252" t="s">
+        <v>22</v>
+      </c>
+      <c r="E252" t="s">
+        <v>38</v>
+      </c>
+      <c r="F252" t="s">
+        <v>7</v>
+      </c>
+      <c r="G252" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B253" t="s">
+        <v>548</v>
+      </c>
+      <c r="C253" t="s">
+        <v>549</v>
+      </c>
+      <c r="D253" t="s">
+        <v>28</v>
+      </c>
+      <c r="E253" t="s">
+        <v>36</v>
+      </c>
+      <c r="F253" t="s">
+        <v>8</v>
+      </c>
+      <c r="G253" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B254" t="s">
+        <v>550</v>
+      </c>
+      <c r="C254" t="s">
+        <v>551</v>
+      </c>
+      <c r="D254" t="s">
+        <v>14</v>
+      </c>
+      <c r="E254" t="s">
+        <v>36</v>
+      </c>
+      <c r="F254" t="s">
+        <v>8</v>
+      </c>
+      <c r="G254" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B255" t="s">
+        <v>552</v>
+      </c>
+      <c r="C255" t="s">
+        <v>553</v>
+      </c>
+      <c r="D255" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" t="s">
+        <v>36</v>
+      </c>
+      <c r="F255" t="s">
+        <v>8</v>
+      </c>
+      <c r="G255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B256" t="s">
+        <v>554</v>
+      </c>
+      <c r="C256" t="s">
+        <v>555</v>
+      </c>
+      <c r="D256" t="s">
+        <v>24</v>
+      </c>
+      <c r="E256" t="s">
+        <v>38</v>
+      </c>
+      <c r="F256" t="s">
+        <v>7</v>
+      </c>
+      <c r="G256" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B257" t="s">
+        <v>556</v>
+      </c>
+      <c r="C257" t="s">
+        <v>557</v>
+      </c>
+      <c r="D257" t="s">
+        <v>14</v>
+      </c>
+      <c r="E257" t="s">
+        <v>36</v>
+      </c>
+      <c r="F257" t="s">
+        <v>8</v>
+      </c>
+      <c r="G257" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B258" t="s">
+        <v>558</v>
+      </c>
+      <c r="C258" t="s">
+        <v>559</v>
+      </c>
+      <c r="D258" t="s">
+        <v>23</v>
+      </c>
+      <c r="E258" t="s">
+        <v>36</v>
+      </c>
+      <c r="F258" t="s">
+        <v>8</v>
+      </c>
+      <c r="G258" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B259" t="s">
+        <v>560</v>
+      </c>
+      <c r="C259" t="s">
+        <v>561</v>
+      </c>
+      <c r="D259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
+        <v>36</v>
+      </c>
+      <c r="F259" t="s">
+        <v>8</v>
+      </c>
+      <c r="G259" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B260" t="s">
+        <v>562</v>
+      </c>
+      <c r="C260" t="s">
+        <v>563</v>
+      </c>
+      <c r="D260" t="s">
+        <v>40</v>
+      </c>
+      <c r="E260" t="s">
+        <v>38</v>
+      </c>
+      <c r="F260" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B261" t="s">
+        <v>564</v>
+      </c>
+      <c r="C261" t="s">
+        <v>565</v>
+      </c>
+      <c r="D261" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" t="s">
+        <v>38</v>
+      </c>
+      <c r="F261" t="s">
+        <v>7</v>
+      </c>
+      <c r="G261" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B262" t="s">
+        <v>566</v>
+      </c>
+      <c r="C262" t="s">
+        <v>567</v>
+      </c>
+      <c r="D262" t="s">
+        <v>39</v>
+      </c>
+      <c r="E262" t="s">
+        <v>38</v>
+      </c>
+      <c r="F262" t="s">
+        <v>10</v>
+      </c>
+      <c r="G262" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B263" t="s">
+        <v>568</v>
+      </c>
+      <c r="C263" t="s">
+        <v>569</v>
+      </c>
+      <c r="D263" t="s">
+        <v>12</v>
+      </c>
+      <c r="E263" t="s">
+        <v>36</v>
+      </c>
+      <c r="F263" t="s">
+        <v>8</v>
+      </c>
+      <c r="G263" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B264" t="s">
+        <v>570</v>
+      </c>
+      <c r="C264" t="s">
+        <v>571</v>
+      </c>
+      <c r="D264" t="s">
+        <v>28</v>
+      </c>
+      <c r="E264" t="s">
+        <v>36</v>
+      </c>
+      <c r="F264" t="s">
+        <v>8</v>
+      </c>
+      <c r="G264" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B265" t="s">
+        <v>572</v>
+      </c>
+      <c r="C265" t="s">
+        <v>573</v>
+      </c>
+      <c r="D265" t="s">
+        <v>16</v>
+      </c>
+      <c r="E265" t="s">
+        <v>36</v>
+      </c>
+      <c r="F265" t="s">
+        <v>13</v>
+      </c>
+      <c r="G265" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B266" t="s">
+        <v>574</v>
+      </c>
+      <c r="C266" t="s">
+        <v>575</v>
+      </c>
+      <c r="D266" t="s">
+        <v>261</v>
+      </c>
+      <c r="E266" t="s">
+        <v>36</v>
+      </c>
+      <c r="F266" t="s">
+        <v>8</v>
+      </c>
+      <c r="G266" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B267" t="s">
+        <v>576</v>
+      </c>
+      <c r="C267" t="s">
+        <v>577</v>
+      </c>
+      <c r="D267" t="s">
+        <v>11</v>
+      </c>
+      <c r="E267" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" t="s">
+        <v>8</v>
+      </c>
+      <c r="G267" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B268" t="s">
+        <v>578</v>
+      </c>
+      <c r="C268" t="s">
+        <v>579</v>
+      </c>
+      <c r="D268" t="s">
+        <v>261</v>
+      </c>
+      <c r="E268" t="s">
+        <v>36</v>
+      </c>
+      <c r="F268" t="s">
+        <v>7</v>
+      </c>
+      <c r="G268" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B269" t="s">
+        <v>580</v>
+      </c>
+      <c r="C269" t="s">
+        <v>581</v>
+      </c>
+      <c r="D269" t="s">
+        <v>39</v>
+      </c>
+      <c r="E269" t="s">
+        <v>38</v>
+      </c>
+      <c r="F269" t="s">
+        <v>8</v>
+      </c>
+      <c r="G269" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B270" t="s">
+        <v>582</v>
+      </c>
+      <c r="C270" t="s">
+        <v>583</v>
+      </c>
+      <c r="D270" t="s">
+        <v>28</v>
+      </c>
+      <c r="E270" t="s">
+        <v>36</v>
+      </c>
+      <c r="F270" t="s">
+        <v>8</v>
+      </c>
+      <c r="G270" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B271" t="s">
+        <v>584</v>
+      </c>
+      <c r="C271" t="s">
+        <v>585</v>
+      </c>
+      <c r="D271" t="s">
+        <v>11</v>
+      </c>
+      <c r="E271" t="s">
+        <v>36</v>
+      </c>
+      <c r="F271" t="s">
+        <v>8</v>
+      </c>
+      <c r="G271" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B272" t="s">
+        <v>586</v>
+      </c>
+      <c r="C272" t="s">
+        <v>587</v>
+      </c>
+      <c r="D272" t="s">
+        <v>14</v>
+      </c>
+      <c r="E272" t="s">
+        <v>36</v>
+      </c>
+      <c r="F272" t="s">
+        <v>8</v>
+      </c>
+      <c r="G272" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B273" t="s">
+        <v>588</v>
+      </c>
+      <c r="C273" t="s">
+        <v>589</v>
+      </c>
+      <c r="D273" t="s">
+        <v>261</v>
+      </c>
+      <c r="E273" t="s">
+        <v>36</v>
+      </c>
+      <c r="F273" t="s">
+        <v>8</v>
+      </c>
+      <c r="G273" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B274" t="s">
+        <v>590</v>
+      </c>
+      <c r="C274" t="s">
+        <v>591</v>
+      </c>
+      <c r="D274" t="s">
+        <v>9</v>
+      </c>
+      <c r="E274" t="s">
+        <v>38</v>
+      </c>
+      <c r="F274" t="s">
+        <v>7</v>
+      </c>
+      <c r="G274" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B275" t="s">
+        <v>592</v>
+      </c>
+      <c r="C275" t="s">
+        <v>593</v>
+      </c>
+      <c r="D275" t="s">
+        <v>28</v>
+      </c>
+      <c r="E275" t="s">
+        <v>36</v>
+      </c>
+      <c r="F275" t="s">
+        <v>8</v>
+      </c>
+      <c r="G275" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B276" t="s">
+        <v>594</v>
+      </c>
+      <c r="C276" t="s">
+        <v>595</v>
+      </c>
+      <c r="D276" t="s">
+        <v>11</v>
+      </c>
+      <c r="E276" t="s">
+        <v>36</v>
+      </c>
+      <c r="F276" t="s">
+        <v>8</v>
+      </c>
+      <c r="G276" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B277" t="s">
+        <v>596</v>
+      </c>
+      <c r="C277" t="s">
+        <v>597</v>
+      </c>
+      <c r="D277" t="s">
+        <v>14</v>
+      </c>
+      <c r="E277" t="s">
+        <v>36</v>
+      </c>
+      <c r="F277" t="s">
+        <v>8</v>
+      </c>
+      <c r="G277" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B278" t="s">
+        <v>598</v>
+      </c>
+      <c r="C278" t="s">
+        <v>599</v>
+      </c>
+      <c r="D278" t="s">
+        <v>23</v>
+      </c>
+      <c r="E278" t="s">
+        <v>36</v>
+      </c>
+      <c r="F278" t="s">
+        <v>8</v>
+      </c>
+      <c r="G278" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B279" t="s">
+        <v>600</v>
+      </c>
+      <c r="C279" t="s">
+        <v>601</v>
+      </c>
+      <c r="D279" t="s">
+        <v>12</v>
+      </c>
+      <c r="E279" t="s">
+        <v>36</v>
+      </c>
+      <c r="F279" t="s">
+        <v>8</v>
+      </c>
+      <c r="G279" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B280" t="s">
+        <v>602</v>
+      </c>
+      <c r="C280" t="s">
+        <v>603</v>
+      </c>
+      <c r="D280" t="s">
+        <v>12</v>
+      </c>
+      <c r="E280" t="s">
+        <v>36</v>
+      </c>
+      <c r="F280" t="s">
+        <v>8</v>
+      </c>
+      <c r="G280" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B281" t="s">
+        <v>604</v>
+      </c>
+      <c r="C281" t="s">
+        <v>605</v>
+      </c>
+      <c r="D281" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" t="s">
+        <v>38</v>
+      </c>
+      <c r="F281" t="s">
+        <v>8</v>
+      </c>
+      <c r="G281" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B282" t="s">
+        <v>606</v>
+      </c>
+      <c r="C282" t="s">
+        <v>607</v>
+      </c>
+      <c r="D282" t="s">
+        <v>24</v>
+      </c>
+      <c r="E282" t="s">
+        <v>38</v>
+      </c>
+      <c r="F282" t="s">
+        <v>8</v>
+      </c>
+      <c r="G282" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B283" t="s">
+        <v>608</v>
+      </c>
+      <c r="C283" t="s">
+        <v>609</v>
+      </c>
+      <c r="D283" t="s">
+        <v>12</v>
+      </c>
+      <c r="E283" t="s">
+        <v>36</v>
+      </c>
+      <c r="F283" t="s">
+        <v>8</v>
+      </c>
+      <c r="G283" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B284" t="s">
+        <v>610</v>
+      </c>
+      <c r="C284" t="s">
+        <v>611</v>
+      </c>
+      <c r="D284" t="s">
+        <v>6</v>
+      </c>
+      <c r="E284" t="s">
+        <v>36</v>
+      </c>
+      <c r="F284" t="s">
+        <v>8</v>
+      </c>
+      <c r="G284" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B285" t="s">
+        <v>612</v>
+      </c>
+      <c r="C285" t="s">
+        <v>613</v>
+      </c>
+      <c r="D285" t="s">
+        <v>19</v>
+      </c>
+      <c r="E285" t="s">
+        <v>36</v>
+      </c>
+      <c r="F285" t="s">
+        <v>8</v>
+      </c>
+      <c r="G285" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B286" t="s">
+        <v>614</v>
+      </c>
+      <c r="C286" t="s">
+        <v>615</v>
+      </c>
+      <c r="D286" t="s">
+        <v>24</v>
+      </c>
+      <c r="E286" t="s">
+        <v>38</v>
+      </c>
+      <c r="F286" t="s">
+        <v>8</v>
+      </c>
+      <c r="G286" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B287" t="s">
+        <v>616</v>
+      </c>
+      <c r="C287" t="s">
+        <v>617</v>
+      </c>
+      <c r="D287" t="s">
+        <v>14</v>
+      </c>
+      <c r="E287" t="s">
+        <v>36</v>
+      </c>
+      <c r="F287" t="s">
+        <v>8</v>
+      </c>
+      <c r="G287" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B288" t="s">
+        <v>618</v>
+      </c>
+      <c r="C288" t="s">
+        <v>619</v>
+      </c>
+      <c r="D288" t="s">
+        <v>15</v>
+      </c>
+      <c r="E288" t="s">
+        <v>36</v>
+      </c>
+      <c r="F288" t="s">
+        <v>8</v>
+      </c>
+      <c r="G288" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B289" t="s">
+        <v>620</v>
+      </c>
+      <c r="C289" t="s">
+        <v>621</v>
+      </c>
+      <c r="D289" t="s">
+        <v>24</v>
+      </c>
+      <c r="E289" t="s">
+        <v>38</v>
+      </c>
+      <c r="F289" t="s">
+        <v>8</v>
+      </c>
+      <c r="G289" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B290" t="s">
+        <v>622</v>
+      </c>
+      <c r="C290" t="s">
+        <v>623</v>
+      </c>
+      <c r="D290" t="s">
+        <v>15</v>
+      </c>
+      <c r="E290" t="s">
+        <v>36</v>
+      </c>
+      <c r="F290" t="s">
+        <v>8</v>
+      </c>
+      <c r="G290" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B291" t="s">
+        <v>624</v>
+      </c>
+      <c r="C291" t="s">
+        <v>625</v>
+      </c>
+      <c r="D291" t="s">
+        <v>16</v>
+      </c>
+      <c r="E291" t="s">
+        <v>36</v>
+      </c>
+      <c r="F291" t="s">
+        <v>8</v>
+      </c>
+      <c r="G291" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B292" t="s">
+        <v>626</v>
+      </c>
+      <c r="C292" t="s">
+        <v>627</v>
+      </c>
+      <c r="D292" t="s">
+        <v>14</v>
+      </c>
+      <c r="E292" t="s">
+        <v>36</v>
+      </c>
+      <c r="F292" t="s">
+        <v>8</v>
+      </c>
+      <c r="G292" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B293" t="s">
+        <v>628</v>
+      </c>
+      <c r="C293" t="s">
+        <v>629</v>
+      </c>
+      <c r="D293" t="s">
+        <v>11</v>
+      </c>
+      <c r="E293" t="s">
+        <v>36</v>
+      </c>
+      <c r="F293" t="s">
+        <v>8</v>
+      </c>
+      <c r="G293" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B294" t="s">
+        <v>630</v>
+      </c>
+      <c r="C294" t="s">
+        <v>631</v>
+      </c>
+      <c r="D294" t="s">
+        <v>22</v>
+      </c>
+      <c r="E294" t="s">
+        <v>38</v>
+      </c>
+      <c r="F294" t="s">
+        <v>8</v>
+      </c>
+      <c r="G294" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B295" t="s">
+        <v>632</v>
+      </c>
+      <c r="C295" t="s">
+        <v>633</v>
+      </c>
+      <c r="D295" t="s">
+        <v>15</v>
+      </c>
+      <c r="E295" t="s">
+        <v>36</v>
+      </c>
+      <c r="F295" t="s">
+        <v>8</v>
+      </c>
+      <c r="G295" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B296" t="s">
+        <v>634</v>
+      </c>
+      <c r="C296" t="s">
+        <v>635</v>
+      </c>
+      <c r="D296" t="s">
+        <v>15</v>
+      </c>
+      <c r="E296" t="s">
+        <v>36</v>
+      </c>
+      <c r="F296" t="s">
+        <v>8</v>
+      </c>
+      <c r="G296" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B297" t="s">
+        <v>636</v>
+      </c>
+      <c r="C297" t="s">
+        <v>637</v>
+      </c>
+      <c r="D297" t="s">
+        <v>28</v>
+      </c>
+      <c r="E297" t="s">
+        <v>36</v>
+      </c>
+      <c r="F297" t="s">
+        <v>8</v>
+      </c>
+      <c r="G297" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B298" t="s">
+        <v>638</v>
+      </c>
+      <c r="C298" t="s">
+        <v>639</v>
+      </c>
+      <c r="D298" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" t="s">
+        <v>36</v>
+      </c>
+      <c r="F298" t="s">
+        <v>8</v>
+      </c>
+      <c r="G298" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B299" t="s">
+        <v>640</v>
+      </c>
+      <c r="C299" t="s">
+        <v>641</v>
+      </c>
+      <c r="D299" t="s">
+        <v>16</v>
+      </c>
+      <c r="E299" t="s">
+        <v>36</v>
+      </c>
+      <c r="F299" t="s">
+        <v>8</v>
+      </c>
+      <c r="G299" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B300" t="s">
+        <v>642</v>
+      </c>
+      <c r="C300" t="s">
+        <v>643</v>
+      </c>
+      <c r="D300" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>36</v>
+      </c>
+      <c r="F300" t="s">
+        <v>8</v>
+      </c>
+      <c r="G300" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B301" t="s">
+        <v>644</v>
+      </c>
+      <c r="C301" t="s">
+        <v>645</v>
+      </c>
+      <c r="D301" t="s">
+        <v>14</v>
+      </c>
+      <c r="E301" t="s">
+        <v>36</v>
+      </c>
+      <c r="F301" t="s">
+        <v>8</v>
+      </c>
+      <c r="G301" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B302" t="s">
+        <v>646</v>
+      </c>
+      <c r="C302" t="s">
+        <v>647</v>
+      </c>
+      <c r="D302" t="s">
+        <v>6</v>
+      </c>
+      <c r="E302" t="s">
+        <v>36</v>
+      </c>
+      <c r="F302" t="s">
+        <v>8</v>
+      </c>
+      <c r="G302" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B303" t="s">
+        <v>648</v>
+      </c>
+      <c r="C303" t="s">
+        <v>649</v>
+      </c>
+      <c r="D303" t="s">
+        <v>28</v>
+      </c>
+      <c r="E303" t="s">
+        <v>36</v>
+      </c>
+      <c r="F303" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B304" t="s">
+        <v>650</v>
+      </c>
+      <c r="C304" t="s">
+        <v>651</v>
+      </c>
+      <c r="D304" t="s">
+        <v>28</v>
+      </c>
+      <c r="E304" t="s">
+        <v>36</v>
+      </c>
+      <c r="F304" t="s">
+        <v>8</v>
+      </c>
+      <c r="G304" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B305" t="s">
+        <v>652</v>
+      </c>
+      <c r="C305" t="s">
+        <v>653</v>
+      </c>
+      <c r="D305" t="s">
+        <v>261</v>
+      </c>
+      <c r="E305" t="s">
+        <v>36</v>
+      </c>
+      <c r="F305" t="s">
+        <v>8</v>
+      </c>
+      <c r="G305" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B306" t="s">
+        <v>654</v>
+      </c>
+      <c r="C306" t="s">
+        <v>655</v>
+      </c>
+      <c r="D306" t="s">
+        <v>19</v>
+      </c>
+      <c r="E306" t="s">
+        <v>36</v>
+      </c>
+      <c r="F306" t="s">
+        <v>404</v>
+      </c>
+      <c r="G306" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B307" t="s">
+        <v>656</v>
+      </c>
+      <c r="C307" t="s">
+        <v>657</v>
+      </c>
+      <c r="D307" t="s">
+        <v>19</v>
+      </c>
+      <c r="E307" t="s">
+        <v>36</v>
+      </c>
+      <c r="F307" t="s">
+        <v>8</v>
+      </c>
+      <c r="G307" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B308" t="s">
+        <v>658</v>
+      </c>
+      <c r="C308" t="s">
+        <v>659</v>
+      </c>
+      <c r="D308" t="s">
+        <v>40</v>
+      </c>
+      <c r="E308" t="s">
+        <v>38</v>
+      </c>
+      <c r="F308" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B309" t="s">
+        <v>660</v>
+      </c>
+      <c r="C309" t="s">
+        <v>661</v>
+      </c>
+      <c r="D309" t="s">
+        <v>28</v>
+      </c>
+      <c r="E309" t="s">
+        <v>36</v>
+      </c>
+      <c r="F309" t="s">
+        <v>8</v>
+      </c>
+      <c r="G309" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B310" t="s">
+        <v>662</v>
+      </c>
+      <c r="C310" t="s">
+        <v>663</v>
+      </c>
+      <c r="D310" t="s">
+        <v>16</v>
+      </c>
+      <c r="E310" t="s">
+        <v>36</v>
+      </c>
+      <c r="F310" t="s">
+        <v>8</v>
+      </c>
+      <c r="G310" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B311" t="s">
+        <v>664</v>
+      </c>
+      <c r="C311" t="s">
+        <v>665</v>
+      </c>
+      <c r="D311" t="s">
+        <v>28</v>
+      </c>
+      <c r="E311" t="s">
+        <v>36</v>
+      </c>
+      <c r="F311" t="s">
+        <v>8</v>
+      </c>
+      <c r="G311" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B312" t="s">
+        <v>666</v>
+      </c>
+      <c r="C312" t="s">
+        <v>667</v>
+      </c>
+      <c r="D312" t="s">
+        <v>14</v>
+      </c>
+      <c r="E312" t="s">
+        <v>36</v>
+      </c>
+      <c r="F312" t="s">
+        <v>8</v>
+      </c>
+      <c r="G312" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B313" t="s">
+        <v>668</v>
+      </c>
+      <c r="C313" t="s">
+        <v>669</v>
+      </c>
+      <c r="D313" t="s">
+        <v>15</v>
+      </c>
+      <c r="E313" t="s">
+        <v>36</v>
+      </c>
+      <c r="F313" t="s">
+        <v>8</v>
+      </c>
+      <c r="G313" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B314" t="s">
+        <v>670</v>
+      </c>
+      <c r="C314" t="s">
+        <v>671</v>
+      </c>
+      <c r="D314" t="s">
+        <v>19</v>
+      </c>
+      <c r="E314" t="s">
+        <v>36</v>
+      </c>
+      <c r="F314" t="s">
+        <v>8</v>
+      </c>
+      <c r="G314" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B315" t="s">
+        <v>672</v>
+      </c>
+      <c r="C315" t="s">
+        <v>673</v>
+      </c>
+      <c r="D315" t="s">
+        <v>16</v>
+      </c>
+      <c r="E315" t="s">
+        <v>36</v>
+      </c>
+      <c r="F315" t="s">
+        <v>8</v>
+      </c>
+      <c r="G315" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B316" t="s">
+        <v>674</v>
+      </c>
+      <c r="C316" t="s">
+        <v>675</v>
+      </c>
+      <c r="D316" t="s">
+        <v>22</v>
+      </c>
+      <c r="E316" t="s">
+        <v>38</v>
+      </c>
+      <c r="F316" t="s">
+        <v>8</v>
+      </c>
+      <c r="G316" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B317" t="s">
+        <v>676</v>
+      </c>
+      <c r="C317" t="s">
+        <v>677</v>
+      </c>
+      <c r="D317" t="s">
+        <v>23</v>
+      </c>
+      <c r="E317" t="s">
+        <v>36</v>
+      </c>
+      <c r="F317" t="s">
+        <v>8</v>
+      </c>
+      <c r="G317" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B318" t="s">
+        <v>678</v>
+      </c>
+      <c r="C318" t="s">
+        <v>679</v>
+      </c>
+      <c r="D318" t="s">
+        <v>22</v>
+      </c>
+      <c r="E318" t="s">
+        <v>38</v>
+      </c>
+      <c r="F318" t="s">
+        <v>8</v>
+      </c>
+      <c r="G318" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B319" t="s">
+        <v>680</v>
+      </c>
+      <c r="C319" t="s">
+        <v>681</v>
+      </c>
+      <c r="D319" t="s">
+        <v>16</v>
+      </c>
+      <c r="E319" t="s">
+        <v>36</v>
+      </c>
+      <c r="F319" t="s">
+        <v>8</v>
+      </c>
+      <c r="G319" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B320" t="s">
+        <v>682</v>
+      </c>
+      <c r="C320" t="s">
+        <v>683</v>
+      </c>
+      <c r="D320" t="s">
+        <v>15</v>
+      </c>
+      <c r="E320" t="s">
+        <v>36</v>
+      </c>
+      <c r="F320" t="s">
+        <v>8</v>
+      </c>
+      <c r="G320" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B321" t="s">
+        <v>684</v>
+      </c>
+      <c r="C321" t="s">
+        <v>685</v>
+      </c>
+      <c r="D321" t="s">
+        <v>19</v>
+      </c>
+      <c r="E321" t="s">
+        <v>36</v>
+      </c>
+      <c r="F321" t="s">
+        <v>8</v>
+      </c>
+      <c r="G321" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B322" t="s">
+        <v>686</v>
+      </c>
+      <c r="C322" t="s">
+        <v>687</v>
+      </c>
+      <c r="D322" t="s">
+        <v>16</v>
+      </c>
+      <c r="E322" t="s">
+        <v>36</v>
+      </c>
+      <c r="F322" t="s">
+        <v>8</v>
+      </c>
+      <c r="G322" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B323" t="s">
+        <v>688</v>
+      </c>
+      <c r="C323" t="s">
+        <v>689</v>
+      </c>
+      <c r="D323" t="s">
+        <v>6</v>
+      </c>
+      <c r="E323" t="s">
+        <v>36</v>
+      </c>
+      <c r="F323" t="s">
+        <v>8</v>
+      </c>
+      <c r="G323" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B324" t="s">
+        <v>690</v>
+      </c>
+      <c r="C324" t="s">
+        <v>691</v>
+      </c>
+      <c r="D324" t="s">
+        <v>25</v>
+      </c>
+      <c r="E324" t="s">
+        <v>38</v>
+      </c>
+      <c r="F324" t="s">
+        <v>8</v>
+      </c>
+      <c r="G324" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFA352B-6409-4D08-A7F1-C669F9A2B4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8F060-660E-46A1-807D-14851B6658A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="824">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -2127,6 +2127,390 @@
   </si>
   <si>
     <t>Procuracao com poderes de abrir e movimentar conta corrente junto a instituicoes financeiras com mandato vigente e devidamente assinada&lt;br&gt;&lt;br&gt;Contrato Social atualizado e registrado no orgao competente</t>
+  </si>
+  <si>
+    <t>66119726000156</t>
+  </si>
+  <si>
+    <t>SAMUEL CHRISTO SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>52201313000101</t>
+  </si>
+  <si>
+    <t>GIAN CARLOS</t>
+  </si>
+  <si>
+    <t>35329411000100</t>
+  </si>
+  <si>
+    <t>ATUAL SOLUCOES EMPRESARIAIS LTDA</t>
+  </si>
+  <si>
+    <t>41338993000193</t>
+  </si>
+  <si>
+    <t>AR INTERMEDIACOES E REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>36411708000182</t>
+  </si>
+  <si>
+    <t>MARIA DA LUZ TRINDADE DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>62575959000102</t>
+  </si>
+  <si>
+    <t>TAYLOR KLEIN NUNES REPRESENTACOES</t>
+  </si>
+  <si>
+    <t>44961037000151</t>
+  </si>
+  <si>
+    <t>LEILA LIMA DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>39147133000120</t>
+  </si>
+  <si>
+    <t>JANETE DA APARECIDA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>33157239000129</t>
+  </si>
+  <si>
+    <t>FABRICIO BERNARDINO DA SILVA</t>
+  </si>
+  <si>
+    <t>40410461000157</t>
+  </si>
+  <si>
+    <t>40.410.461 FRANCISCO DAS CHAGAS RODRIGUES</t>
+  </si>
+  <si>
+    <t>50813026000127</t>
+  </si>
+  <si>
+    <t>KAUAN MILHOMEM LIMA</t>
+  </si>
+  <si>
+    <t>65128920000135</t>
+  </si>
+  <si>
+    <t>M WEALTH E WELFARE ID LTDA</t>
+  </si>
+  <si>
+    <t>32018926000109</t>
+  </si>
+  <si>
+    <t>FLAVIO ALEXANDRE GIOIA CELESTE</t>
+  </si>
+  <si>
+    <t>44270036000160</t>
+  </si>
+  <si>
+    <t>PRISCILA MARIA LEALDINI</t>
+  </si>
+  <si>
+    <t>27642521000107</t>
+  </si>
+  <si>
+    <t>JOSE ROBERTO MEDEIROS BATISTA</t>
+  </si>
+  <si>
+    <t>54948362000138</t>
+  </si>
+  <si>
+    <t>FABIANA SINNES LTDA</t>
+  </si>
+  <si>
+    <t>60912849000163</t>
+  </si>
+  <si>
+    <t>V RODRIGUES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>63645708000110</t>
+  </si>
+  <si>
+    <t>63.645.708 MOISES LAZARO DA ROCHA</t>
+  </si>
+  <si>
+    <t>61113487000103</t>
+  </si>
+  <si>
+    <t>F M DO VALE COMERCIO E SERVICOS</t>
+  </si>
+  <si>
+    <t>33721165000101</t>
+  </si>
+  <si>
+    <t>KATIA BARGIERI DE CARVALHO ROCHA GESTAO EMPRESARIAL</t>
+  </si>
+  <si>
+    <t>44068144000155</t>
+  </si>
+  <si>
+    <t>ALCIONE TORRES SENA ANDRADE</t>
+  </si>
+  <si>
+    <t>44127933000110</t>
+  </si>
+  <si>
+    <t>DAIANA LOPES TAVARES</t>
+  </si>
+  <si>
+    <t>18844706000103</t>
+  </si>
+  <si>
+    <t>CLAYTON NOEL DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>45796541000106</t>
+  </si>
+  <si>
+    <t>FRANCISCO JOSE FERNANDES ANDRE</t>
+  </si>
+  <si>
+    <t>34371846000150</t>
+  </si>
+  <si>
+    <t>IRINEU FRANCISCO DE LACERDA</t>
+  </si>
+  <si>
+    <t>35256355000120</t>
+  </si>
+  <si>
+    <t>ALDINETE RIBEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>19843526000161</t>
+  </si>
+  <si>
+    <t>PRECISA SOLUCOES EM MOVEIS PLANEJADOS LTDA</t>
+  </si>
+  <si>
+    <t>13721798000293</t>
+  </si>
+  <si>
+    <t>INSTITUTO SAO MIGUEL ARCANJO</t>
+  </si>
+  <si>
+    <t>61816926000144</t>
+  </si>
+  <si>
+    <t>J. OSMAR MARQUES DE SOUZA</t>
+  </si>
+  <si>
+    <t>47991920000182</t>
+  </si>
+  <si>
+    <t>DIONE DA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>39591167000100</t>
+  </si>
+  <si>
+    <t>BRUNA NATALIA DO CARMO MAZZO PISSOLITO</t>
+  </si>
+  <si>
+    <t>55210134000129</t>
+  </si>
+  <si>
+    <t>ROSMERY SALCEDO APAZA</t>
+  </si>
+  <si>
+    <t>47505012000131</t>
+  </si>
+  <si>
+    <t>LUCIELE EVANGELISTA DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>62376167000109</t>
+  </si>
+  <si>
+    <t>GLOBAL TRADE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>RECADASTRO</t>
+  </si>
+  <si>
+    <t>49919722000133</t>
+  </si>
+  <si>
+    <t>49.919.722 DIEGO VIDAL DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>41568707000186</t>
+  </si>
+  <si>
+    <t>JUCIENE DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>41010770000100</t>
+  </si>
+  <si>
+    <t>DOUGLAS SANTANA VAZ DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>64860933000131</t>
+  </si>
+  <si>
+    <t>64.860.933 LUIZ GUSTAVO GONCALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>35901411000132</t>
+  </si>
+  <si>
+    <t>ALBERTO RIAL DE POLY</t>
+  </si>
+  <si>
+    <t>53101078000169</t>
+  </si>
+  <si>
+    <t>E A PEREIRA DE SOUZA SERVICOS</t>
+  </si>
+  <si>
+    <t>73850240000159</t>
+  </si>
+  <si>
+    <t>P C A PONTES CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>44456957000112</t>
+  </si>
+  <si>
+    <t>GGA ESFERAS DE VIDROS LTDA</t>
+  </si>
+  <si>
+    <t>63483572000199</t>
+  </si>
+  <si>
+    <t>F VALERIO LUCAS</t>
+  </si>
+  <si>
+    <t>56304711000295</t>
+  </si>
+  <si>
+    <t>M J LTDA</t>
+  </si>
+  <si>
+    <t>23348125000102</t>
+  </si>
+  <si>
+    <t>GABRIEL RODRIGUES DE MORAIS</t>
+  </si>
+  <si>
+    <t>43261885000195</t>
+  </si>
+  <si>
+    <t>43.261.885 MARILEIDE PEREIRA DAMACENA DA SILVA</t>
+  </si>
+  <si>
+    <t>65050309000131</t>
+  </si>
+  <si>
+    <t>JOSE CARLOS MAGALHAES PEREIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>13439959000170</t>
+  </si>
+  <si>
+    <t>AUTO TOUR TRANSPORTES E TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>57072165000196</t>
+  </si>
+  <si>
+    <t>57.072.165 ROBERIO SANTOS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>47151283000136</t>
+  </si>
+  <si>
+    <t>ELEDIR ALDINO RONCEN CONSTRUCAO</t>
+  </si>
+  <si>
+    <t>20831856000116</t>
+  </si>
+  <si>
+    <t>GUINCHO CACHOEIRA LTDA</t>
+  </si>
+  <si>
+    <t>53863140000150</t>
+  </si>
+  <si>
+    <t>53.863.140 ANA PAULA GOMES</t>
+  </si>
+  <si>
+    <t>21721112000101</t>
+  </si>
+  <si>
+    <t>OMAR ROCHA REDA</t>
+  </si>
+  <si>
+    <t>36916501000160</t>
+  </si>
+  <si>
+    <t>36.916.501 MARCELO FONSECA FIDELIS</t>
+  </si>
+  <si>
+    <t>66084499000170</t>
+  </si>
+  <si>
+    <t>J F DA SILVA JOSE SYUVA COCHOES</t>
+  </si>
+  <si>
+    <t>27727193000133</t>
+  </si>
+  <si>
+    <t>27.727.193 JOSE CARNEIRO DE AGUIAR FILHO</t>
+  </si>
+  <si>
+    <t>35106276000133</t>
+  </si>
+  <si>
+    <t>KLEYVERTON DANTAS DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>05017487000139</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO CULTURAL E COMUNITARIA ZAGAIA</t>
+  </si>
+  <si>
+    <t>23656624000167</t>
+  </si>
+  <si>
+    <t>VERA LUCIA DE SOUSA SILVA</t>
+  </si>
+  <si>
+    <t>34185102000140</t>
+  </si>
+  <si>
+    <t>ESLEY ROSA PEREIRA</t>
+  </si>
+  <si>
+    <t>20598867000106</t>
+  </si>
+  <si>
+    <t>ANA CRISTINA SILVA DE SOUSA</t>
+  </si>
+  <si>
+    <t>54831244000145</t>
+  </si>
+  <si>
+    <t>MARIO SERGIO STROPARO</t>
+  </si>
+  <si>
+    <t>Para garantir a seguranca e a validade do processo. Pedimos gentilmente que envie uma nova foto apenas com voce, conforme as orientacoes.&lt;br&gt;&lt;br&gt;Procuracao da empresa , assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado. Outorgante e a empresa (razao social) que concede os poderes</t>
+  </si>
+  <si>
+    <t>Procuracao da empresa , assinada via gov.br ou por meio de procuracao publica, em formato PDF. O documento deve conter, de forma expressa, os poderes para abrir e movimentar contas, alem de identificar corretamente o outorgante e o outorgado. Outorgante e a empresa (razao social) que concede os poderes</t>
+  </si>
+  <si>
+    <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2741,10 +3125,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2975,10 +3359,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="H18" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -5364,7 +5748,7 @@
         <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>403</v>
+        <v>18</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -7513,7 +7897,7 @@
         <v>8</v>
       </c>
       <c r="G193" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -7718,7 +8102,7 @@
         <v>8</v>
       </c>
       <c r="G201" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -7978,7 +8362,7 @@
         <v>7</v>
       </c>
       <c r="G211" t="s">
-        <v>403</v>
+        <v>18</v>
       </c>
       <c r="H211">
         <v>0</v>
@@ -8394,7 +8778,7 @@
         <v>404</v>
       </c>
       <c r="G227" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H227">
         <v>0</v>
@@ -8420,7 +8804,7 @@
         <v>7</v>
       </c>
       <c r="G228" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -8628,7 +9012,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -8838,6 +9222,9 @@
       <c r="G244" t="s">
         <v>18</v>
       </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
@@ -8861,6 +9248,9 @@
       <c r="G245" t="s">
         <v>18</v>
       </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
@@ -8884,6 +9274,9 @@
       <c r="G246" t="s">
         <v>18</v>
       </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
@@ -8905,7 +9298,10 @@
         <v>384</v>
       </c>
       <c r="G247" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
@@ -8930,6 +9326,9 @@
       <c r="G248" t="s">
         <v>21</v>
       </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
@@ -8953,6 +9352,9 @@
       <c r="G249" t="s">
         <v>18</v>
       </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
@@ -8999,6 +9401,9 @@
       <c r="G251" t="s">
         <v>18</v>
       </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
@@ -9022,6 +9427,9 @@
       <c r="G252" t="s">
         <v>18</v>
       </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
@@ -9045,6 +9453,9 @@
       <c r="G253" t="s">
         <v>18</v>
       </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
@@ -9068,6 +9479,9 @@
       <c r="G254" t="s">
         <v>18</v>
       </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
@@ -9091,6 +9505,9 @@
       <c r="G255" t="s">
         <v>18</v>
       </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
@@ -9114,8 +9531,11 @@
       <c r="G256" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>46120</v>
       </c>
@@ -9137,8 +9557,11 @@
       <c r="G257" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>46120</v>
       </c>
@@ -9160,8 +9583,11 @@
       <c r="G258" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>46120</v>
       </c>
@@ -9183,8 +9609,11 @@
       <c r="G259" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>46120</v>
       </c>
@@ -9206,8 +9635,11 @@
       <c r="G260" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>46120</v>
       </c>
@@ -9229,8 +9661,11 @@
       <c r="G261" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>46120</v>
       </c>
@@ -9250,10 +9685,10 @@
         <v>10</v>
       </c>
       <c r="G262" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>46120</v>
       </c>
@@ -9275,8 +9710,11 @@
       <c r="G263" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>46120</v>
       </c>
@@ -9296,10 +9734,13 @@
         <v>8</v>
       </c>
       <c r="G264" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>46120</v>
       </c>
@@ -9321,8 +9762,11 @@
       <c r="G265" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>46120</v>
       </c>
@@ -9344,8 +9788,11 @@
       <c r="G266" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>46120</v>
       </c>
@@ -9367,8 +9814,11 @@
       <c r="G267" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>46120</v>
       </c>
@@ -9390,8 +9840,11 @@
       <c r="G268" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>46120</v>
       </c>
@@ -9413,8 +9866,11 @@
       <c r="G269" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>46120</v>
       </c>
@@ -9434,10 +9890,13 @@
         <v>8</v>
       </c>
       <c r="G270" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H270" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>46120</v>
       </c>
@@ -9459,8 +9918,11 @@
       <c r="G271" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>46120</v>
       </c>
@@ -9482,8 +9944,11 @@
       <c r="G272" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>46120</v>
       </c>
@@ -9505,8 +9970,11 @@
       <c r="G273" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>46120</v>
       </c>
@@ -9528,8 +9996,11 @@
       <c r="G274" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>46120</v>
       </c>
@@ -9551,8 +10022,11 @@
       <c r="G275" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>46120</v>
       </c>
@@ -9574,8 +10048,11 @@
       <c r="G276" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>46120</v>
       </c>
@@ -9597,8 +10074,11 @@
       <c r="G277" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>46120</v>
       </c>
@@ -9620,8 +10100,11 @@
       <c r="G278" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>46120</v>
       </c>
@@ -9643,8 +10126,11 @@
       <c r="G279" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>46120</v>
       </c>
@@ -9666,8 +10152,11 @@
       <c r="G280" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>46120</v>
       </c>
@@ -9689,8 +10178,11 @@
       <c r="G281" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>46120</v>
       </c>
@@ -9712,8 +10204,11 @@
       <c r="G282" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>46120</v>
       </c>
@@ -9735,8 +10230,11 @@
       <c r="G283" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>46120</v>
       </c>
@@ -9758,8 +10256,11 @@
       <c r="G284" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>46120</v>
       </c>
@@ -9781,8 +10282,11 @@
       <c r="G285" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>46120</v>
       </c>
@@ -9804,8 +10308,11 @@
       <c r="G286" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>46120</v>
       </c>
@@ -9827,8 +10334,11 @@
       <c r="G287" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>46120</v>
       </c>
@@ -9850,8 +10360,11 @@
       <c r="G288" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>46120</v>
       </c>
@@ -9873,8 +10386,11 @@
       <c r="G289" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>46120</v>
       </c>
@@ -9896,8 +10412,11 @@
       <c r="G290" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>46120</v>
       </c>
@@ -9919,8 +10438,11 @@
       <c r="G291" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>46120</v>
       </c>
@@ -9942,8 +10464,11 @@
       <c r="G292" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>46120</v>
       </c>
@@ -9963,10 +10488,13 @@
         <v>8</v>
       </c>
       <c r="G293" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H293" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>46120</v>
       </c>
@@ -9988,8 +10516,11 @@
       <c r="G294" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>46120</v>
       </c>
@@ -10011,8 +10542,11 @@
       <c r="G295" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>46120</v>
       </c>
@@ -10034,8 +10568,11 @@
       <c r="G296" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>46120</v>
       </c>
@@ -10057,8 +10594,11 @@
       <c r="G297" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>46120</v>
       </c>
@@ -10080,8 +10620,11 @@
       <c r="G298" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>46120</v>
       </c>
@@ -10103,8 +10646,11 @@
       <c r="G299" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>46120</v>
       </c>
@@ -10126,8 +10672,11 @@
       <c r="G300" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>46120</v>
       </c>
@@ -10149,8 +10698,11 @@
       <c r="G301" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>46120</v>
       </c>
@@ -10172,8 +10724,11 @@
       <c r="G302" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>46120</v>
       </c>
@@ -10195,8 +10750,11 @@
       <c r="G303" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>46120</v>
       </c>
@@ -10218,8 +10776,11 @@
       <c r="G304" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>46120</v>
       </c>
@@ -10241,8 +10802,11 @@
       <c r="G305" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>46120</v>
       </c>
@@ -10264,8 +10828,11 @@
       <c r="G306" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>46120</v>
       </c>
@@ -10287,8 +10854,11 @@
       <c r="G307" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>46120</v>
       </c>
@@ -10310,8 +10880,11 @@
       <c r="G308" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>46120</v>
       </c>
@@ -10333,8 +10906,11 @@
       <c r="G309" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>46120</v>
       </c>
@@ -10356,8 +10932,11 @@
       <c r="G310" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>46120</v>
       </c>
@@ -10379,8 +10958,11 @@
       <c r="G311" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>46120</v>
       </c>
@@ -10402,8 +10984,11 @@
       <c r="G312" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>46120</v>
       </c>
@@ -10425,8 +11010,11 @@
       <c r="G313" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>46120</v>
       </c>
@@ -10448,8 +11036,11 @@
       <c r="G314" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>46120</v>
       </c>
@@ -10471,8 +11062,11 @@
       <c r="G315" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>46120</v>
       </c>
@@ -10494,8 +11088,11 @@
       <c r="G316" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>46120</v>
       </c>
@@ -10517,8 +11114,11 @@
       <c r="G317" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>46120</v>
       </c>
@@ -10540,8 +11140,11 @@
       <c r="G318" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>46120</v>
       </c>
@@ -10561,10 +11164,13 @@
         <v>8</v>
       </c>
       <c r="G319" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>46120</v>
       </c>
@@ -10586,8 +11192,11 @@
       <c r="G320" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>46120</v>
       </c>
@@ -10609,8 +11218,11 @@
       <c r="G321" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>46120</v>
       </c>
@@ -10632,8 +11244,11 @@
       <c r="G322" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>46120</v>
       </c>
@@ -10653,10 +11268,13 @@
         <v>8</v>
       </c>
       <c r="G323" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H323" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>46120</v>
       </c>
@@ -10676,7 +11294,1445 @@
         <v>8</v>
       </c>
       <c r="G324" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B325" t="s">
+        <v>696</v>
+      </c>
+      <c r="C325" t="s">
+        <v>697</v>
+      </c>
+      <c r="D325" t="s">
+        <v>12</v>
+      </c>
+      <c r="E325" t="s">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>384</v>
+      </c>
+      <c r="G325" t="s">
+        <v>18</v>
+      </c>
+      <c r="H325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B326" t="s">
+        <v>698</v>
+      </c>
+      <c r="C326" t="s">
+        <v>699</v>
+      </c>
+      <c r="D326" t="s">
+        <v>12</v>
+      </c>
+      <c r="E326" t="s">
+        <v>36</v>
+      </c>
+      <c r="F326" t="s">
+        <v>8</v>
+      </c>
+      <c r="G326" t="s">
+        <v>18</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B327" t="s">
+        <v>700</v>
+      </c>
+      <c r="C327" t="s">
+        <v>701</v>
+      </c>
+      <c r="D327" t="s">
+        <v>12</v>
+      </c>
+      <c r="E327" t="s">
+        <v>36</v>
+      </c>
+      <c r="F327" t="s">
+        <v>8</v>
+      </c>
+      <c r="G327" t="s">
+        <v>18</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B328" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328" t="s">
+        <v>703</v>
+      </c>
+      <c r="D328" t="s">
+        <v>27</v>
+      </c>
+      <c r="E328" t="s">
+        <v>37</v>
+      </c>
+      <c r="F328" t="s">
+        <v>242</v>
+      </c>
+      <c r="G328" t="s">
+        <v>18</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B329" t="s">
+        <v>704</v>
+      </c>
+      <c r="C329" t="s">
+        <v>705</v>
+      </c>
+      <c r="D329" t="s">
+        <v>22</v>
+      </c>
+      <c r="E329" t="s">
+        <v>38</v>
+      </c>
+      <c r="F329" t="s">
+        <v>7</v>
+      </c>
+      <c r="G329" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B330" t="s">
+        <v>706</v>
+      </c>
+      <c r="C330" t="s">
+        <v>707</v>
+      </c>
+      <c r="D330" t="s">
+        <v>30</v>
+      </c>
+      <c r="E330" t="s">
+        <v>38</v>
+      </c>
+      <c r="F330" t="s">
+        <v>7</v>
+      </c>
+      <c r="G330" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B331" t="s">
+        <v>708</v>
+      </c>
+      <c r="C331" t="s">
+        <v>709</v>
+      </c>
+      <c r="D331" t="s">
+        <v>14</v>
+      </c>
+      <c r="E331" t="s">
+        <v>36</v>
+      </c>
+      <c r="F331" t="s">
+        <v>8</v>
+      </c>
+      <c r="G331" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B332" t="s">
+        <v>710</v>
+      </c>
+      <c r="C332" t="s">
+        <v>711</v>
+      </c>
+      <c r="D332" t="s">
+        <v>30</v>
+      </c>
+      <c r="E332" t="s">
+        <v>38</v>
+      </c>
+      <c r="F332" t="s">
+        <v>7</v>
+      </c>
+      <c r="G332" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B333" t="s">
+        <v>712</v>
+      </c>
+      <c r="C333" t="s">
+        <v>713</v>
+      </c>
+      <c r="D333" t="s">
+        <v>16</v>
+      </c>
+      <c r="E333" t="s">
+        <v>36</v>
+      </c>
+      <c r="F333" t="s">
+        <v>8</v>
+      </c>
+      <c r="G333" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B334" t="s">
+        <v>714</v>
+      </c>
+      <c r="C334" t="s">
+        <v>715</v>
+      </c>
+      <c r="D334" t="s">
+        <v>23</v>
+      </c>
+      <c r="E334" t="s">
+        <v>36</v>
+      </c>
+      <c r="F334" t="s">
+        <v>8</v>
+      </c>
+      <c r="G334" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B335" t="s">
+        <v>716</v>
+      </c>
+      <c r="C335" t="s">
+        <v>717</v>
+      </c>
+      <c r="D335" t="s">
+        <v>11</v>
+      </c>
+      <c r="E335" t="s">
+        <v>36</v>
+      </c>
+      <c r="F335" t="s">
+        <v>8</v>
+      </c>
+      <c r="G335" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B336" t="s">
+        <v>718</v>
+      </c>
+      <c r="C336" t="s">
+        <v>719</v>
+      </c>
+      <c r="D336" t="s">
+        <v>39</v>
+      </c>
+      <c r="E336" t="s">
+        <v>38</v>
+      </c>
+      <c r="F336" t="s">
+        <v>7</v>
+      </c>
+      <c r="G336" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B337" t="s">
+        <v>720</v>
+      </c>
+      <c r="C337" t="s">
+        <v>721</v>
+      </c>
+      <c r="D337" t="s">
+        <v>28</v>
+      </c>
+      <c r="E337" t="s">
+        <v>36</v>
+      </c>
+      <c r="F337" t="s">
+        <v>8</v>
+      </c>
+      <c r="G337" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B338" t="s">
+        <v>722</v>
+      </c>
+      <c r="C338" t="s">
+        <v>723</v>
+      </c>
+      <c r="D338" t="s">
+        <v>15</v>
+      </c>
+      <c r="E338" t="s">
+        <v>36</v>
+      </c>
+      <c r="F338" t="s">
+        <v>8</v>
+      </c>
+      <c r="G338" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B339" t="s">
+        <v>724</v>
+      </c>
+      <c r="C339" t="s">
+        <v>725</v>
+      </c>
+      <c r="D339" t="s">
+        <v>14</v>
+      </c>
+      <c r="E339" t="s">
+        <v>36</v>
+      </c>
+      <c r="F339" t="s">
+        <v>8</v>
+      </c>
+      <c r="G339" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B340" t="s">
+        <v>726</v>
+      </c>
+      <c r="C340" t="s">
+        <v>727</v>
+      </c>
+      <c r="D340" t="s">
+        <v>28</v>
+      </c>
+      <c r="E340" t="s">
+        <v>36</v>
+      </c>
+      <c r="F340" t="s">
+        <v>8</v>
+      </c>
+      <c r="G340" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B341" t="s">
+        <v>728</v>
+      </c>
+      <c r="C341" t="s">
+        <v>729</v>
+      </c>
+      <c r="D341" t="s">
+        <v>11</v>
+      </c>
+      <c r="E341" t="s">
+        <v>36</v>
+      </c>
+      <c r="F341" t="s">
+        <v>8</v>
+      </c>
+      <c r="G341" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B342" t="s">
+        <v>730</v>
+      </c>
+      <c r="C342" t="s">
+        <v>731</v>
+      </c>
+      <c r="D342" t="s">
+        <v>23</v>
+      </c>
+      <c r="E342" t="s">
+        <v>36</v>
+      </c>
+      <c r="F342" t="s">
+        <v>8</v>
+      </c>
+      <c r="G342" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B343" t="s">
+        <v>732</v>
+      </c>
+      <c r="C343" t="s">
+        <v>733</v>
+      </c>
+      <c r="D343" t="s">
+        <v>9</v>
+      </c>
+      <c r="E343" t="s">
+        <v>38</v>
+      </c>
+      <c r="F343" t="s">
+        <v>7</v>
+      </c>
+      <c r="G343" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B344" t="s">
+        <v>734</v>
+      </c>
+      <c r="C344" t="s">
+        <v>735</v>
+      </c>
+      <c r="D344" t="s">
+        <v>19</v>
+      </c>
+      <c r="E344" t="s">
+        <v>36</v>
+      </c>
+      <c r="F344" t="s">
+        <v>384</v>
+      </c>
+      <c r="G344" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B345" t="s">
+        <v>736</v>
+      </c>
+      <c r="C345" t="s">
+        <v>737</v>
+      </c>
+      <c r="D345" t="s">
+        <v>15</v>
+      </c>
+      <c r="E345" t="s">
+        <v>36</v>
+      </c>
+      <c r="F345" t="s">
+        <v>8</v>
+      </c>
+      <c r="G345" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B346" t="s">
+        <v>738</v>
+      </c>
+      <c r="C346" t="s">
+        <v>739</v>
+      </c>
+      <c r="D346" t="s">
+        <v>28</v>
+      </c>
+      <c r="E346" t="s">
+        <v>36</v>
+      </c>
+      <c r="F346" t="s">
+        <v>8</v>
+      </c>
+      <c r="G346" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B347" t="s">
+        <v>740</v>
+      </c>
+      <c r="C347" t="s">
+        <v>741</v>
+      </c>
+      <c r="D347" t="s">
+        <v>24</v>
+      </c>
+      <c r="E347" t="s">
+        <v>38</v>
+      </c>
+      <c r="F347" t="s">
+        <v>7</v>
+      </c>
+      <c r="G347" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B348" t="s">
+        <v>742</v>
+      </c>
+      <c r="C348" t="s">
+        <v>743</v>
+      </c>
+      <c r="D348" t="s">
+        <v>11</v>
+      </c>
+      <c r="E348" t="s">
+        <v>36</v>
+      </c>
+      <c r="F348" t="s">
+        <v>8</v>
+      </c>
+      <c r="G348" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B349" t="s">
+        <v>744</v>
+      </c>
+      <c r="C349" t="s">
+        <v>745</v>
+      </c>
+      <c r="D349" t="s">
+        <v>9</v>
+      </c>
+      <c r="E349" t="s">
+        <v>38</v>
+      </c>
+      <c r="F349" t="s">
+        <v>7</v>
+      </c>
+      <c r="G349" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B350" t="s">
+        <v>746</v>
+      </c>
+      <c r="C350" t="s">
+        <v>747</v>
+      </c>
+      <c r="D350" t="s">
+        <v>12</v>
+      </c>
+      <c r="E350" t="s">
+        <v>36</v>
+      </c>
+      <c r="F350" t="s">
+        <v>7</v>
+      </c>
+      <c r="G350" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B351" t="s">
+        <v>748</v>
+      </c>
+      <c r="C351" t="s">
+        <v>749</v>
+      </c>
+      <c r="D351" t="s">
+        <v>19</v>
+      </c>
+      <c r="E351" t="s">
+        <v>36</v>
+      </c>
+      <c r="F351" t="s">
+        <v>384</v>
+      </c>
+      <c r="G351" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B352" t="s">
+        <v>750</v>
+      </c>
+      <c r="C352" t="s">
+        <v>751</v>
+      </c>
+      <c r="D352" t="s">
+        <v>40</v>
+      </c>
+      <c r="E352" t="s">
+        <v>38</v>
+      </c>
+      <c r="F352" t="s">
+        <v>10</v>
+      </c>
+      <c r="G352" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B353" t="s">
+        <v>752</v>
+      </c>
+      <c r="C353" t="s">
+        <v>753</v>
+      </c>
+      <c r="D353" t="s">
+        <v>39</v>
+      </c>
+      <c r="E353" t="s">
+        <v>38</v>
+      </c>
+      <c r="F353" t="s">
+        <v>7</v>
+      </c>
+      <c r="G353" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B354" t="s">
+        <v>754</v>
+      </c>
+      <c r="C354" t="s">
+        <v>755</v>
+      </c>
+      <c r="D354" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354" t="s">
+        <v>36</v>
+      </c>
+      <c r="F354" t="s">
+        <v>7</v>
+      </c>
+      <c r="G354" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B355" t="s">
+        <v>756</v>
+      </c>
+      <c r="C355" t="s">
+        <v>757</v>
+      </c>
+      <c r="D355" t="s">
+        <v>28</v>
+      </c>
+      <c r="E355" t="s">
+        <v>36</v>
+      </c>
+      <c r="F355" t="s">
+        <v>8</v>
+      </c>
+      <c r="G355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B356" t="s">
+        <v>758</v>
+      </c>
+      <c r="C356" t="s">
+        <v>759</v>
+      </c>
+      <c r="D356" t="s">
+        <v>30</v>
+      </c>
+      <c r="E356" t="s">
+        <v>38</v>
+      </c>
+      <c r="F356" t="s">
+        <v>7</v>
+      </c>
+      <c r="G356" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B357" t="s">
+        <v>760</v>
+      </c>
+      <c r="C357" t="s">
+        <v>761</v>
+      </c>
+      <c r="D357" t="s">
+        <v>30</v>
+      </c>
+      <c r="E357" t="s">
+        <v>38</v>
+      </c>
+      <c r="F357" t="s">
+        <v>7</v>
+      </c>
+      <c r="G357" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B358" t="s">
+        <v>762</v>
+      </c>
+      <c r="C358" t="s">
+        <v>763</v>
+      </c>
+      <c r="D358" t="s">
+        <v>39</v>
+      </c>
+      <c r="E358" t="s">
+        <v>38</v>
+      </c>
+      <c r="F358" t="s">
+        <v>764</v>
+      </c>
+      <c r="G358" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B359" t="s">
+        <v>765</v>
+      </c>
+      <c r="C359" t="s">
+        <v>766</v>
+      </c>
+      <c r="D359" t="s">
+        <v>12</v>
+      </c>
+      <c r="E359" t="s">
+        <v>36</v>
+      </c>
+      <c r="F359" t="s">
+        <v>8</v>
+      </c>
+      <c r="G359" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B360" t="s">
+        <v>767</v>
+      </c>
+      <c r="C360" t="s">
+        <v>768</v>
+      </c>
+      <c r="D360" t="s">
+        <v>16</v>
+      </c>
+      <c r="E360" t="s">
+        <v>36</v>
+      </c>
+      <c r="F360" t="s">
+        <v>7</v>
+      </c>
+      <c r="G360" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B361" t="s">
+        <v>769</v>
+      </c>
+      <c r="C361" t="s">
+        <v>770</v>
+      </c>
+      <c r="D361" t="s">
+        <v>15</v>
+      </c>
+      <c r="E361" t="s">
+        <v>36</v>
+      </c>
+      <c r="F361" t="s">
+        <v>764</v>
+      </c>
+      <c r="G361" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B362" t="s">
+        <v>771</v>
+      </c>
+      <c r="C362" t="s">
+        <v>772</v>
+      </c>
+      <c r="D362" t="s">
+        <v>22</v>
+      </c>
+      <c r="E362" t="s">
+        <v>38</v>
+      </c>
+      <c r="F362" t="s">
+        <v>8</v>
+      </c>
+      <c r="G362" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B363" t="s">
+        <v>773</v>
+      </c>
+      <c r="C363" t="s">
+        <v>774</v>
+      </c>
+      <c r="D363" t="s">
+        <v>14</v>
+      </c>
+      <c r="E363" t="s">
+        <v>36</v>
+      </c>
+      <c r="F363" t="s">
+        <v>8</v>
+      </c>
+      <c r="G363" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B364" t="s">
+        <v>775</v>
+      </c>
+      <c r="C364" t="s">
+        <v>776</v>
+      </c>
+      <c r="D364" t="s">
+        <v>15</v>
+      </c>
+      <c r="E364" t="s">
+        <v>36</v>
+      </c>
+      <c r="F364" t="s">
+        <v>8</v>
+      </c>
+      <c r="G364" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B365" t="s">
+        <v>777</v>
+      </c>
+      <c r="C365" t="s">
+        <v>778</v>
+      </c>
+      <c r="D365" t="s">
+        <v>24</v>
+      </c>
+      <c r="E365" t="s">
+        <v>38</v>
+      </c>
+      <c r="F365" t="s">
+        <v>764</v>
+      </c>
+      <c r="G365" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B366" t="s">
+        <v>779</v>
+      </c>
+      <c r="C366" t="s">
+        <v>780</v>
+      </c>
+      <c r="D366" t="s">
+        <v>22</v>
+      </c>
+      <c r="E366" t="s">
+        <v>38</v>
+      </c>
+      <c r="F366" t="s">
+        <v>8</v>
+      </c>
+      <c r="G366" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B367" t="s">
+        <v>781</v>
+      </c>
+      <c r="C367" t="s">
+        <v>782</v>
+      </c>
+      <c r="D367" t="s">
+        <v>14</v>
+      </c>
+      <c r="E367" t="s">
+        <v>36</v>
+      </c>
+      <c r="F367" t="s">
+        <v>8</v>
+      </c>
+      <c r="G367" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B368" t="s">
+        <v>783</v>
+      </c>
+      <c r="C368" t="s">
+        <v>784</v>
+      </c>
+      <c r="D368" t="s">
+        <v>23</v>
+      </c>
+      <c r="E368" t="s">
+        <v>36</v>
+      </c>
+      <c r="F368" t="s">
+        <v>8</v>
+      </c>
+      <c r="G368" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B369" t="s">
+        <v>785</v>
+      </c>
+      <c r="C369" t="s">
+        <v>786</v>
+      </c>
+      <c r="D369" t="s">
+        <v>11</v>
+      </c>
+      <c r="E369" t="s">
+        <v>36</v>
+      </c>
+      <c r="F369" t="s">
+        <v>8</v>
+      </c>
+      <c r="G369" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B370" t="s">
+        <v>787</v>
+      </c>
+      <c r="C370" t="s">
+        <v>788</v>
+      </c>
+      <c r="D370" t="s">
+        <v>22</v>
+      </c>
+      <c r="E370" t="s">
+        <v>38</v>
+      </c>
+      <c r="F370" t="s">
+        <v>8</v>
+      </c>
+      <c r="G370" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B371" t="s">
+        <v>789</v>
+      </c>
+      <c r="C371" t="s">
+        <v>790</v>
+      </c>
+      <c r="D371" t="s">
+        <v>11</v>
+      </c>
+      <c r="E371" t="s">
+        <v>36</v>
+      </c>
+      <c r="F371" t="s">
+        <v>8</v>
+      </c>
+      <c r="G371" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B372" t="s">
+        <v>791</v>
+      </c>
+      <c r="C372" t="s">
+        <v>792</v>
+      </c>
+      <c r="D372" t="s">
+        <v>25</v>
+      </c>
+      <c r="E372" t="s">
+        <v>38</v>
+      </c>
+      <c r="F372" t="s">
+        <v>10</v>
+      </c>
+      <c r="G372" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B373" t="s">
+        <v>793</v>
+      </c>
+      <c r="C373" t="s">
+        <v>794</v>
+      </c>
+      <c r="D373" t="s">
+        <v>14</v>
+      </c>
+      <c r="E373" t="s">
+        <v>36</v>
+      </c>
+      <c r="F373" t="s">
+        <v>8</v>
+      </c>
+      <c r="G373" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B374" t="s">
+        <v>795</v>
+      </c>
+      <c r="C374" t="s">
+        <v>796</v>
+      </c>
+      <c r="D374" t="s">
+        <v>24</v>
+      </c>
+      <c r="E374" t="s">
+        <v>38</v>
+      </c>
+      <c r="F374" t="s">
+        <v>8</v>
+      </c>
+      <c r="G374" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B375" t="s">
+        <v>797</v>
+      </c>
+      <c r="C375" t="s">
+        <v>798</v>
+      </c>
+      <c r="D375" t="s">
+        <v>28</v>
+      </c>
+      <c r="E375" t="s">
+        <v>36</v>
+      </c>
+      <c r="F375" t="s">
+        <v>8</v>
+      </c>
+      <c r="G375" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B376" t="s">
+        <v>799</v>
+      </c>
+      <c r="C376" t="s">
+        <v>800</v>
+      </c>
+      <c r="D376" t="s">
+        <v>16</v>
+      </c>
+      <c r="E376" t="s">
+        <v>36</v>
+      </c>
+      <c r="F376" t="s">
+        <v>8</v>
+      </c>
+      <c r="G376" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B377" t="s">
+        <v>801</v>
+      </c>
+      <c r="C377" t="s">
+        <v>802</v>
+      </c>
+      <c r="D377" t="s">
+        <v>16</v>
+      </c>
+      <c r="E377" t="s">
+        <v>36</v>
+      </c>
+      <c r="F377" t="s">
+        <v>8</v>
+      </c>
+      <c r="G377" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B378" t="s">
+        <v>803</v>
+      </c>
+      <c r="C378" t="s">
+        <v>804</v>
+      </c>
+      <c r="D378" t="s">
+        <v>16</v>
+      </c>
+      <c r="E378" t="s">
+        <v>36</v>
+      </c>
+      <c r="F378" t="s">
+        <v>8</v>
+      </c>
+      <c r="G378" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B379" t="s">
+        <v>805</v>
+      </c>
+      <c r="C379" t="s">
+        <v>806</v>
+      </c>
+      <c r="D379" t="s">
+        <v>23</v>
+      </c>
+      <c r="E379" t="s">
+        <v>36</v>
+      </c>
+      <c r="F379" t="s">
+        <v>8</v>
+      </c>
+      <c r="G379" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B380" t="s">
+        <v>807</v>
+      </c>
+      <c r="C380" t="s">
+        <v>808</v>
+      </c>
+      <c r="D380" t="s">
+        <v>30</v>
+      </c>
+      <c r="E380" t="s">
+        <v>38</v>
+      </c>
+      <c r="F380" t="s">
+        <v>8</v>
+      </c>
+      <c r="G380" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B381" t="s">
+        <v>809</v>
+      </c>
+      <c r="C381" t="s">
+        <v>810</v>
+      </c>
+      <c r="D381" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" t="s">
+        <v>36</v>
+      </c>
+      <c r="F381" t="s">
+        <v>8</v>
+      </c>
+      <c r="G381" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B382" t="s">
+        <v>811</v>
+      </c>
+      <c r="C382" t="s">
+        <v>812</v>
+      </c>
+      <c r="D382" t="s">
+        <v>22</v>
+      </c>
+      <c r="E382" t="s">
+        <v>38</v>
+      </c>
+      <c r="F382" t="s">
+        <v>8</v>
+      </c>
+      <c r="G382" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B383" t="s">
+        <v>813</v>
+      </c>
+      <c r="C383" t="s">
+        <v>814</v>
+      </c>
+      <c r="D383" t="s">
+        <v>15</v>
+      </c>
+      <c r="E383" t="s">
+        <v>36</v>
+      </c>
+      <c r="F383" t="s">
+        <v>8</v>
+      </c>
+      <c r="G383" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B384" t="s">
+        <v>815</v>
+      </c>
+      <c r="C384" t="s">
+        <v>816</v>
+      </c>
+      <c r="D384" t="s">
+        <v>261</v>
+      </c>
+      <c r="E384" t="s">
+        <v>36</v>
+      </c>
+      <c r="F384" t="s">
+        <v>8</v>
+      </c>
+      <c r="G384" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B385" t="s">
+        <v>817</v>
+      </c>
+      <c r="C385" t="s">
+        <v>818</v>
+      </c>
+      <c r="D385" t="s">
+        <v>28</v>
+      </c>
+      <c r="E385" t="s">
+        <v>36</v>
+      </c>
+      <c r="F385" t="s">
+        <v>8</v>
+      </c>
+      <c r="G385" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B386" t="s">
+        <v>819</v>
+      </c>
+      <c r="C386" t="s">
+        <v>820</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" t="s">
+        <v>36</v>
+      </c>
+      <c r="F386" t="s">
+        <v>8</v>
+      </c>
+      <c r="G386" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8F060-660E-46A1-807D-14851B6658A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D169B981-E939-4010-8C63-64CE50D5C822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="972">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -1646,9 +1646,6 @@
     <t>JOCELI V MARDEGAN</t>
   </si>
   <si>
-    <t>58.790.963 JOSE ADILSON DA SILVA</t>
-  </si>
-  <si>
     <t>33497465000159</t>
   </si>
   <si>
@@ -2511,6 +2508,453 @@
   </si>
   <si>
     <t>Ata de eleicao da diretoria atualizada e registrado no orgao competente&lt;br&gt;&lt;br&gt;Estatuto social atualizado e registrado no orgao competente</t>
+  </si>
+  <si>
+    <t>37697092000110</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAIQUEL CARDINAL DA SILVA</t>
+  </si>
+  <si>
+    <t>44883302000120</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VINICIUS PARREIRA SOUSA TEIXEIRA</t>
+  </si>
+  <si>
+    <t>41183564000194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDVALDO PAULO DOS REIS </t>
+  </si>
+  <si>
+    <t>58938379000165</t>
+  </si>
+  <si>
+    <t>ASW CONSTRUTORA E EMPREITEIRA DE MAO DE OBRA LTDA</t>
+  </si>
+  <si>
+    <t>24719459000108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMUEL FREITAS DA JUSTA </t>
+  </si>
+  <si>
+    <t>57778972000129</t>
+  </si>
+  <si>
+    <t>CAFE NA CAIXA LTDA</t>
+  </si>
+  <si>
+    <t>03239780000115</t>
+  </si>
+  <si>
+    <t>GABRIEL MELLO FROIS</t>
+  </si>
+  <si>
+    <t>62080968000122</t>
+  </si>
+  <si>
+    <t>CALLE COMERCIO E PRODUCOES LTDA</t>
+  </si>
+  <si>
+    <t>32810227000199</t>
+  </si>
+  <si>
+    <t>MARLON ROBERTO SANT ANA CARVALHO</t>
+  </si>
+  <si>
+    <t>57514726000160</t>
+  </si>
+  <si>
+    <t>KEVIN WILLIAM FIGUEIRA E SILVA</t>
+  </si>
+  <si>
+    <t>58746087000120</t>
+  </si>
+  <si>
+    <t>WANDERLEY LUIZ LABRE</t>
+  </si>
+  <si>
+    <t>56043196000156</t>
+  </si>
+  <si>
+    <t>A PINHEIRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>56026986000123</t>
+  </si>
+  <si>
+    <t>FERNANDO JUNIOR DA SILVA AMARAL</t>
+  </si>
+  <si>
+    <t>25013123000198</t>
+  </si>
+  <si>
+    <t>ELIO FLAMINI NETO</t>
+  </si>
+  <si>
+    <t>41629801000106</t>
+  </si>
+  <si>
+    <t>EDSON COSTA RIBEIRO JUNIOR</t>
+  </si>
+  <si>
+    <t>28851961000129</t>
+  </si>
+  <si>
+    <t>JANIELE PEREIRA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>69067411000109</t>
+  </si>
+  <si>
+    <t>TECBIKE COMERCIO DE BICICLETAS LTDA</t>
+  </si>
+  <si>
+    <t>21136173000101</t>
+  </si>
+  <si>
+    <t>JCC SANTIAGO TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>71180095000110</t>
+  </si>
+  <si>
+    <t>GARTEX - ENGENHARIA, ASSESSORIA E CONSULTORIA LTDA.</t>
+  </si>
+  <si>
+    <t>47060149000120</t>
+  </si>
+  <si>
+    <t>SANDRA DOS SANTOS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>27562641000196</t>
+  </si>
+  <si>
+    <t>27.562.641 MIGUEL ANTONIO BERNARDES DA SILVA</t>
+  </si>
+  <si>
+    <t>26174408000173</t>
+  </si>
+  <si>
+    <t>GABY BATATITAS LTDA</t>
+  </si>
+  <si>
+    <t>Mensageria</t>
+  </si>
+  <si>
+    <t>38014054000189</t>
+  </si>
+  <si>
+    <t>BRENO HENRIQUE DE MENESES COSTA</t>
+  </si>
+  <si>
+    <t>58450983000148</t>
+  </si>
+  <si>
+    <t>RENATO BORGES SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>32993828000184</t>
+  </si>
+  <si>
+    <t>EDINEIA MACHADO ROSA</t>
+  </si>
+  <si>
+    <t>66139231000199</t>
+  </si>
+  <si>
+    <t>RONALD MIGUEL FERREIRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>15825407000125</t>
+  </si>
+  <si>
+    <t>DIBOA PRODUCOES LTDA</t>
+  </si>
+  <si>
+    <t>51177001000147</t>
+  </si>
+  <si>
+    <t>BRYAN ABRAO NUNES</t>
+  </si>
+  <si>
+    <t>49593053000152</t>
+  </si>
+  <si>
+    <t>PIER REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>40402215000153</t>
+  </si>
+  <si>
+    <t>AZEVEDO BORGES SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>60133016000102</t>
+  </si>
+  <si>
+    <t>THED CASA DE RACAO LTDA</t>
+  </si>
+  <si>
+    <t>31305802000133</t>
+  </si>
+  <si>
+    <t>K2 EMPREENDIMENTOS COMERCIAIS LTDA.</t>
+  </si>
+  <si>
+    <t>19778694000110</t>
+  </si>
+  <si>
+    <t>UGUENEI SOARES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>58498562000197</t>
+  </si>
+  <si>
+    <t>S L ESTEVES INDUSTRIA E CONFECCOES LTDA</t>
+  </si>
+  <si>
+    <t>34508976000191</t>
+  </si>
+  <si>
+    <t>RB CANARIO DISTRIBUIDORA DE BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>36245147000199</t>
+  </si>
+  <si>
+    <t>F J OLIVEIRA SANTOS LTDA</t>
+  </si>
+  <si>
+    <t>22315955000251</t>
+  </si>
+  <si>
+    <t>Centro de Diagnosticos Laboclinica LTDA</t>
+  </si>
+  <si>
+    <t>28496417000106</t>
+  </si>
+  <si>
+    <t>SILVIO DE ALMEIDA SILVA</t>
+  </si>
+  <si>
+    <t>61661974000100</t>
+  </si>
+  <si>
+    <t>DDB ESTETICA LTDA</t>
+  </si>
+  <si>
+    <t>60447145000167</t>
+  </si>
+  <si>
+    <t>DIVINO SABOR GRILL RESTAURANTE LTDA</t>
+  </si>
+  <si>
+    <t>55108957000148</t>
+  </si>
+  <si>
+    <t>REPLAST REPRESENTACAO DE MATERIAL PLASTICO LTDA</t>
+  </si>
+  <si>
+    <t>44054090000179</t>
+  </si>
+  <si>
+    <t>FERNANDO CANEDO DA SILVA</t>
+  </si>
+  <si>
+    <t>54280392000119</t>
+  </si>
+  <si>
+    <t>DENTAL CENTER LTDA</t>
+  </si>
+  <si>
+    <t>48221298000196</t>
+  </si>
+  <si>
+    <t>DANILO HADDAD GARCIA REPRESENTACAO COMERCIAL</t>
+  </si>
+  <si>
+    <t>49967017000101</t>
+  </si>
+  <si>
+    <t>49.967.017 YVISEN LOHAN SANTANA SANTOS</t>
+  </si>
+  <si>
+    <t>29217521000187</t>
+  </si>
+  <si>
+    <t>CLAUDETE DA SILVA DE SOUSA GONCALVES</t>
+  </si>
+  <si>
+    <t>10334421000102</t>
+  </si>
+  <si>
+    <t>LEIVA TRANSPORTES E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>10647910000114</t>
+  </si>
+  <si>
+    <t>E. JUNIOR DESSI FARIA</t>
+  </si>
+  <si>
+    <t>21618436000119</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO ARAUJO DAS NEVES</t>
+  </si>
+  <si>
+    <t>50115032000100</t>
+  </si>
+  <si>
+    <t>PSICOLOGIA MAYARA ZAGO LTDA</t>
+  </si>
+  <si>
+    <t>08844727000167</t>
+  </si>
+  <si>
+    <t>MERCADO REDENTOR LTDA</t>
+  </si>
+  <si>
+    <t>30331252000164</t>
+  </si>
+  <si>
+    <t>30.331.252 MARCIO CARLOS MADEIRA</t>
+  </si>
+  <si>
+    <t>11206107000107</t>
+  </si>
+  <si>
+    <t>AROUCA HOLDING PATRIMONIAL E PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>34010949000194</t>
+  </si>
+  <si>
+    <t>RS SINALIZACAO VIARIA E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>46524698000145</t>
+  </si>
+  <si>
+    <t>HABITACAO ITAUBAL SPE LTDA</t>
+  </si>
+  <si>
+    <t>08839997000180</t>
+  </si>
+  <si>
+    <t>T F RIBEIRO SILVA LTDA</t>
+  </si>
+  <si>
+    <t>28927438000139</t>
+  </si>
+  <si>
+    <t>BRUNO HENRIQUE LAURENTINO BARBAROTO</t>
+  </si>
+  <si>
+    <t>50861994000109</t>
+  </si>
+  <si>
+    <t>50.861.994 BRUNA MARIA DE OLIVEIRA BEZERRA GAEDICKE</t>
+  </si>
+  <si>
+    <t>37097733000104</t>
+  </si>
+  <si>
+    <t>APARECIDA SOLANGE DE OLIVEIRA PONTES</t>
+  </si>
+  <si>
+    <t>60761372000162</t>
+  </si>
+  <si>
+    <t>VERA MARIA LIMA DE LIMA LTDA</t>
+  </si>
+  <si>
+    <t>27496475000177</t>
+  </si>
+  <si>
+    <t>MEIRE CARDOSO DE BRITO ROSA</t>
+  </si>
+  <si>
+    <t>21161123000184</t>
+  </si>
+  <si>
+    <t>CAETANO A. DE PADUA MOREIRA</t>
+  </si>
+  <si>
+    <t>32777775000164</t>
+  </si>
+  <si>
+    <t>32.777.775 FRANCISCO CANINDE DA SILVA</t>
+  </si>
+  <si>
+    <t>30537570000186</t>
+  </si>
+  <si>
+    <t>CENTRAO ESCOLA DE TRANSITO CUIABA LTDA</t>
+  </si>
+  <si>
+    <t>11248076000157</t>
+  </si>
+  <si>
+    <t>JACK'S COIFFEUR ACADEMIA DA BELEZA LTDA</t>
+  </si>
+  <si>
+    <t>48192177000163</t>
+  </si>
+  <si>
+    <t>ASX CONSULTORIA DE NEGOCIOS LTDA</t>
+  </si>
+  <si>
+    <t>58707196000139</t>
+  </si>
+  <si>
+    <t>58.707.196 ROZENILDO TEODOSIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>40169571000179</t>
+  </si>
+  <si>
+    <t>SAMPAIO TRANSPORTES E TURISMO LTDA</t>
+  </si>
+  <si>
+    <t>40440069000150</t>
+  </si>
+  <si>
+    <t>ALINE LUCIANO GONCALVES</t>
+  </si>
+  <si>
+    <t>32995781000198</t>
+  </si>
+  <si>
+    <t>WILLIAM DA SILVA MIRANDA WISA VEICULOS</t>
+  </si>
+  <si>
+    <t>21237720000145</t>
+  </si>
+  <si>
+    <t>PAULO CESAR PINHEIRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>52452586000129</t>
+  </si>
+  <si>
+    <t>ELLEN SERVICOS TERAPEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>58418817000164</t>
+  </si>
+  <si>
+    <t>LUANA PEREIRA GOMES</t>
+  </si>
+  <si>
+    <t>64693604000143</t>
+  </si>
+  <si>
+    <t>VASCONCELLOS TRADE REPRESENTACOES COMERCIAIS</t>
   </si>
 </sst>
 </file>
@@ -2883,7 +3327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H459"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -3024,7 +3468,7 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3099,10 +3543,10 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>518</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3128,7 +3572,7 @@
         <v>518</v>
       </c>
       <c r="H9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3362,7 +3806,7 @@
         <v>518</v>
       </c>
       <c r="H18" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -4714,7 +5158,7 @@
         <v>518</v>
       </c>
       <c r="H70" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -7770,7 +8214,7 @@
         <v>518</v>
       </c>
       <c r="H188" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -9257,22 +9701,22 @@
         <v>46120</v>
       </c>
       <c r="B246" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="C246" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D246" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E246" t="s">
         <v>36</v>
       </c>
       <c r="F246" t="s">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="G246" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -9283,19 +9727,19 @@
         <v>46120</v>
       </c>
       <c r="B247" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C247" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D247" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E247" t="s">
         <v>36</v>
       </c>
       <c r="F247" t="s">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="G247" t="s">
         <v>21</v>
@@ -9309,13 +9753,13 @@
         <v>46120</v>
       </c>
       <c r="B248" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C248" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D248" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E248" t="s">
         <v>36</v>
@@ -9324,7 +9768,7 @@
         <v>8</v>
       </c>
       <c r="G248" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -9335,25 +9779,22 @@
         <v>46120</v>
       </c>
       <c r="B249" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C249" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D249" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E249" t="s">
         <v>36</v>
       </c>
       <c r="F249" t="s">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="G249" t="s">
-        <v>18</v>
-      </c>
-      <c r="H249">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
@@ -9361,13 +9802,13 @@
         <v>46120</v>
       </c>
       <c r="B250" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C250" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D250" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E250" t="s">
         <v>36</v>
@@ -9376,7 +9817,10 @@
         <v>384</v>
       </c>
       <c r="G250" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
@@ -9384,19 +9828,19 @@
         <v>46120</v>
       </c>
       <c r="B251" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C251" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D251" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E251" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F251" t="s">
-        <v>384</v>
+        <v>7</v>
       </c>
       <c r="G251" t="s">
         <v>18</v>
@@ -9410,19 +9854,19 @@
         <v>46120</v>
       </c>
       <c r="B252" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C252" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D252" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E252" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F252" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G252" t="s">
         <v>18</v>
@@ -9436,13 +9880,13 @@
         <v>46120</v>
       </c>
       <c r="B253" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C253" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D253" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E253" t="s">
         <v>36</v>
@@ -9462,13 +9906,13 @@
         <v>46120</v>
       </c>
       <c r="B254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C254" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D254" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E254" t="s">
         <v>36</v>
@@ -9488,19 +9932,19 @@
         <v>46120</v>
       </c>
       <c r="B255" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C255" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D255" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E255" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F255" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G255" t="s">
         <v>18</v>
@@ -9514,19 +9958,19 @@
         <v>46120</v>
       </c>
       <c r="B256" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C256" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D256" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F256" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G256" t="s">
         <v>18</v>
@@ -9540,13 +9984,13 @@
         <v>46120</v>
       </c>
       <c r="B257" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C257" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D257" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E257" t="s">
         <v>36</v>
@@ -9555,7 +9999,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -9566,13 +10010,13 @@
         <v>46120</v>
       </c>
       <c r="B258" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C258" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D258" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E258" t="s">
         <v>36</v>
@@ -9592,19 +10036,19 @@
         <v>46120</v>
       </c>
       <c r="B259" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C259" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D259" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E259" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F259" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G259" t="s">
         <v>18</v>
@@ -9618,19 +10062,19 @@
         <v>46120</v>
       </c>
       <c r="B260" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C260" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D260" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E260" t="s">
         <v>38</v>
       </c>
       <c r="F260" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G260" t="s">
         <v>18</v>
@@ -9644,19 +10088,19 @@
         <v>46120</v>
       </c>
       <c r="B261" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C261" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D261" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E261" t="s">
         <v>38</v>
       </c>
       <c r="F261" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G261" t="s">
         <v>18</v>
@@ -9670,22 +10114,25 @@
         <v>46120</v>
       </c>
       <c r="B262" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C262" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D262" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F262" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G262" t="s">
         <v>18</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -9693,13 +10140,13 @@
         <v>46120</v>
       </c>
       <c r="B263" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C263" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D263" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E263" t="s">
         <v>36</v>
@@ -9719,19 +10166,19 @@
         <v>46120</v>
       </c>
       <c r="B264" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C264" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D264" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E264" t="s">
         <v>36</v>
       </c>
       <c r="F264" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G264" t="s">
         <v>18</v>
@@ -9745,19 +10192,19 @@
         <v>46120</v>
       </c>
       <c r="B265" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C265" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D265" t="s">
-        <v>16</v>
+        <v>261</v>
       </c>
       <c r="E265" t="s">
         <v>36</v>
       </c>
       <c r="F265" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G265" t="s">
         <v>18</v>
@@ -9771,13 +10218,13 @@
         <v>46120</v>
       </c>
       <c r="B266" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C266" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D266" t="s">
-        <v>261</v>
+        <v>11</v>
       </c>
       <c r="E266" t="s">
         <v>36</v>
@@ -9797,19 +10244,19 @@
         <v>46120</v>
       </c>
       <c r="B267" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C267" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D267" t="s">
-        <v>11</v>
+        <v>261</v>
       </c>
       <c r="E267" t="s">
         <v>36</v>
       </c>
       <c r="F267" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G267" t="s">
         <v>18</v>
@@ -9823,19 +10270,19 @@
         <v>46120</v>
       </c>
       <c r="B268" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C268" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D268" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
       <c r="E268" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F268" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G268" t="s">
         <v>18</v>
@@ -9849,25 +10296,25 @@
         <v>46120</v>
       </c>
       <c r="B269" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C269" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D269" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E269" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F269" t="s">
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>18</v>
-      </c>
-      <c r="H269">
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="H269" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -9875,13 +10322,13 @@
         <v>46120</v>
       </c>
       <c r="B270" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C270" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D270" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E270" t="s">
         <v>36</v>
@@ -9890,10 +10337,10 @@
         <v>8</v>
       </c>
       <c r="G270" t="s">
-        <v>518</v>
-      </c>
-      <c r="H270" t="s">
-        <v>823</v>
+        <v>18</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -9901,13 +10348,13 @@
         <v>46120</v>
       </c>
       <c r="B271" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C271" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D271" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E271" t="s">
         <v>36</v>
@@ -9916,7 +10363,7 @@
         <v>8</v>
       </c>
       <c r="G271" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -9927,13 +10374,13 @@
         <v>46120</v>
       </c>
       <c r="B272" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C272" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D272" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E272" t="s">
         <v>36</v>
@@ -9942,7 +10389,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -9953,19 +10400,19 @@
         <v>46120</v>
       </c>
       <c r="B273" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C273" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D273" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F273" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G273" t="s">
         <v>18</v>
@@ -9979,19 +10426,19 @@
         <v>46120</v>
       </c>
       <c r="B274" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C274" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D274" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E274" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F274" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G274" t="s">
         <v>18</v>
@@ -10005,13 +10452,13 @@
         <v>46120</v>
       </c>
       <c r="B275" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C275" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D275" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E275" t="s">
         <v>36</v>
@@ -10031,13 +10478,13 @@
         <v>46120</v>
       </c>
       <c r="B276" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C276" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D276" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E276" t="s">
         <v>36</v>
@@ -10057,13 +10504,13 @@
         <v>46120</v>
       </c>
       <c r="B277" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C277" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D277" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E277" t="s">
         <v>36</v>
@@ -10083,13 +10530,13 @@
         <v>46120</v>
       </c>
       <c r="B278" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C278" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D278" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E278" t="s">
         <v>36</v>
@@ -10109,10 +10556,10 @@
         <v>46120</v>
       </c>
       <c r="B279" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C279" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D279" t="s">
         <v>12</v>
@@ -10135,16 +10582,16 @@
         <v>46120</v>
       </c>
       <c r="B280" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C280" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D280" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E280" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F280" t="s">
         <v>8</v>
@@ -10161,13 +10608,13 @@
         <v>46120</v>
       </c>
       <c r="B281" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C281" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D281" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E281" t="s">
         <v>38</v>
@@ -10187,16 +10634,16 @@
         <v>46120</v>
       </c>
       <c r="B282" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C282" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D282" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E282" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F282" t="s">
         <v>8</v>
@@ -10213,13 +10660,13 @@
         <v>46120</v>
       </c>
       <c r="B283" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C283" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D283" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E283" t="s">
         <v>36</v>
@@ -10239,13 +10686,13 @@
         <v>46120</v>
       </c>
       <c r="B284" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C284" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D284" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E284" t="s">
         <v>36</v>
@@ -10254,7 +10701,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -10265,16 +10712,16 @@
         <v>46120</v>
       </c>
       <c r="B285" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C285" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D285" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E285" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F285" t="s">
         <v>8</v>
@@ -10291,22 +10738,22 @@
         <v>46120</v>
       </c>
       <c r="B286" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C286" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D286" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E286" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F286" t="s">
         <v>8</v>
       </c>
       <c r="G286" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H286">
         <v>0</v>
@@ -10317,13 +10764,13 @@
         <v>46120</v>
       </c>
       <c r="B287" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C287" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D287" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E287" t="s">
         <v>36</v>
@@ -10343,16 +10790,16 @@
         <v>46120</v>
       </c>
       <c r="B288" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C288" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D288" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E288" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F288" t="s">
         <v>8</v>
@@ -10369,16 +10816,16 @@
         <v>46120</v>
       </c>
       <c r="B289" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C289" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D289" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E289" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F289" t="s">
         <v>8</v>
@@ -10395,13 +10842,13 @@
         <v>46120</v>
       </c>
       <c r="B290" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C290" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D290" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E290" t="s">
         <v>36</v>
@@ -10421,13 +10868,13 @@
         <v>46120</v>
       </c>
       <c r="B291" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C291" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D291" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E291" t="s">
         <v>36</v>
@@ -10447,13 +10894,13 @@
         <v>46120</v>
       </c>
       <c r="B292" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C292" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D292" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E292" t="s">
         <v>36</v>
@@ -10462,10 +10909,10 @@
         <v>8</v>
       </c>
       <c r="G292" t="s">
-        <v>18</v>
-      </c>
-      <c r="H292">
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="H292" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -10473,25 +10920,25 @@
         <v>46120</v>
       </c>
       <c r="B293" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C293" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D293" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E293" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F293" t="s">
         <v>8</v>
       </c>
       <c r="G293" t="s">
-        <v>518</v>
-      </c>
-      <c r="H293" t="s">
-        <v>26</v>
+        <v>232</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
@@ -10499,22 +10946,22 @@
         <v>46120</v>
       </c>
       <c r="B294" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C294" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D294" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E294" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F294" t="s">
         <v>8</v>
       </c>
       <c r="G294" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -10525,10 +10972,10 @@
         <v>46120</v>
       </c>
       <c r="B295" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C295" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D295" t="s">
         <v>15</v>
@@ -10551,13 +10998,13 @@
         <v>46120</v>
       </c>
       <c r="B296" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C296" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D296" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E296" t="s">
         <v>36</v>
@@ -10577,13 +11024,13 @@
         <v>46120</v>
       </c>
       <c r="B297" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C297" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D297" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E297" t="s">
         <v>36</v>
@@ -10603,13 +11050,13 @@
         <v>46120</v>
       </c>
       <c r="B298" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C298" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D298" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E298" t="s">
         <v>36</v>
@@ -10629,13 +11076,13 @@
         <v>46120</v>
       </c>
       <c r="B299" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C299" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D299" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E299" t="s">
         <v>36</v>
@@ -10655,13 +11102,13 @@
         <v>46120</v>
       </c>
       <c r="B300" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C300" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D300" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E300" t="s">
         <v>36</v>
@@ -10681,13 +11128,13 @@
         <v>46120</v>
       </c>
       <c r="B301" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C301" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D301" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E301" t="s">
         <v>36</v>
@@ -10707,13 +11154,13 @@
         <v>46120</v>
       </c>
       <c r="B302" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C302" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D302" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E302" t="s">
         <v>36</v>
@@ -10722,7 +11169,7 @@
         <v>8</v>
       </c>
       <c r="G302" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -10733,10 +11180,10 @@
         <v>46120</v>
       </c>
       <c r="B303" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C303" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D303" t="s">
         <v>28</v>
@@ -10748,7 +11195,7 @@
         <v>8</v>
       </c>
       <c r="G303" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -10759,13 +11206,13 @@
         <v>46120</v>
       </c>
       <c r="B304" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C304" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D304" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="E304" t="s">
         <v>36</v>
@@ -10774,7 +11221,7 @@
         <v>8</v>
       </c>
       <c r="G304" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -10785,22 +11232,22 @@
         <v>46120</v>
       </c>
       <c r="B305" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C305" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D305" t="s">
-        <v>261</v>
+        <v>19</v>
       </c>
       <c r="E305" t="s">
         <v>36</v>
       </c>
       <c r="F305" t="s">
-        <v>8</v>
+        <v>404</v>
       </c>
       <c r="G305" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="H305">
         <v>0</v>
@@ -10811,10 +11258,10 @@
         <v>46120</v>
       </c>
       <c r="B306" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C306" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D306" t="s">
         <v>19</v>
@@ -10823,10 +11270,10 @@
         <v>36</v>
       </c>
       <c r="F306" t="s">
-        <v>404</v>
+        <v>8</v>
       </c>
       <c r="G306" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H306">
         <v>0</v>
@@ -10837,22 +11284,22 @@
         <v>46120</v>
       </c>
       <c r="B307" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C307" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D307" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E307" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F307" t="s">
         <v>8</v>
       </c>
       <c r="G307" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -10863,22 +11310,22 @@
         <v>46120</v>
       </c>
       <c r="B308" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C308" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D308" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E308" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F308" t="s">
         <v>8</v>
       </c>
       <c r="G308" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="H308">
         <v>0</v>
@@ -10889,13 +11336,13 @@
         <v>46120</v>
       </c>
       <c r="B309" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C309" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D309" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E309" t="s">
         <v>36</v>
@@ -10904,7 +11351,7 @@
         <v>8</v>
       </c>
       <c r="G309" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -10915,13 +11362,13 @@
         <v>46120</v>
       </c>
       <c r="B310" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C310" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D310" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E310" t="s">
         <v>36</v>
@@ -10930,7 +11377,7 @@
         <v>8</v>
       </c>
       <c r="G310" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H310">
         <v>0</v>
@@ -10941,13 +11388,13 @@
         <v>46120</v>
       </c>
       <c r="B311" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C311" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D311" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E311" t="s">
         <v>36</v>
@@ -10956,7 +11403,7 @@
         <v>8</v>
       </c>
       <c r="G311" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H311">
         <v>0</v>
@@ -10967,13 +11414,13 @@
         <v>46120</v>
       </c>
       <c r="B312" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C312" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D312" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E312" t="s">
         <v>36</v>
@@ -10993,13 +11440,13 @@
         <v>46120</v>
       </c>
       <c r="B313" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C313" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D313" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E313" t="s">
         <v>36</v>
@@ -11008,7 +11455,7 @@
         <v>8</v>
       </c>
       <c r="G313" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H313">
         <v>0</v>
@@ -11019,13 +11466,13 @@
         <v>46120</v>
       </c>
       <c r="B314" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C314" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D314" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E314" t="s">
         <v>36</v>
@@ -11034,7 +11481,7 @@
         <v>8</v>
       </c>
       <c r="G314" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -11045,22 +11492,22 @@
         <v>46120</v>
       </c>
       <c r="B315" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C315" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D315" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E315" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F315" t="s">
         <v>8</v>
       </c>
       <c r="G315" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -11071,22 +11518,22 @@
         <v>46120</v>
       </c>
       <c r="B316" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C316" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D316" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E316" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F316" t="s">
         <v>8</v>
       </c>
       <c r="G316" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -11097,16 +11544,16 @@
         <v>46120</v>
       </c>
       <c r="B317" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C317" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D317" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E317" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F317" t="s">
         <v>8</v>
@@ -11123,22 +11570,22 @@
         <v>46120</v>
       </c>
       <c r="B318" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C318" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D318" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E318" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F318" t="s">
         <v>8</v>
       </c>
       <c r="G318" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H318">
         <v>0</v>
@@ -11149,13 +11596,13 @@
         <v>46120</v>
       </c>
       <c r="B319" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C319" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D319" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E319" t="s">
         <v>36</v>
@@ -11164,7 +11611,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H319">
         <v>0</v>
@@ -11175,13 +11622,13 @@
         <v>46120</v>
       </c>
       <c r="B320" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C320" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D320" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E320" t="s">
         <v>36</v>
@@ -11201,13 +11648,13 @@
         <v>46120</v>
       </c>
       <c r="B321" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C321" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D321" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E321" t="s">
         <v>36</v>
@@ -11227,13 +11674,13 @@
         <v>46120</v>
       </c>
       <c r="B322" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C322" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D322" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>36</v>
@@ -11242,10 +11689,10 @@
         <v>8</v>
       </c>
       <c r="G322" t="s">
-        <v>18</v>
-      </c>
-      <c r="H322">
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="H322" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
@@ -11253,48 +11700,51 @@
         <v>46120</v>
       </c>
       <c r="B323" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C323" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D323" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E323" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F323" t="s">
         <v>8</v>
       </c>
       <c r="G323" t="s">
-        <v>518</v>
-      </c>
-      <c r="H323" t="s">
-        <v>695</v>
+        <v>18</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B324" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="C324" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="D324" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E324" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F324" t="s">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="G324" t="s">
         <v>18</v>
+      </c>
+      <c r="H324">
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
@@ -11302,10 +11752,10 @@
         <v>46121</v>
       </c>
       <c r="B325" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C325" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D325" t="s">
         <v>12</v>
@@ -11314,7 +11764,7 @@
         <v>36</v>
       </c>
       <c r="F325" t="s">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="G325" t="s">
         <v>18</v>
@@ -11328,10 +11778,10 @@
         <v>46121</v>
       </c>
       <c r="B326" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C326" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D326" t="s">
         <v>12</v>
@@ -11354,19 +11804,19 @@
         <v>46121</v>
       </c>
       <c r="B327" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C327" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D327" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E327" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="G327" t="s">
         <v>18</v>
@@ -11380,22 +11830,22 @@
         <v>46121</v>
       </c>
       <c r="B328" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C328" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D328" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E328" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F328" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="G328" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -11406,13 +11856,13 @@
         <v>46121</v>
       </c>
       <c r="B329" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C329" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D329" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E329" t="s">
         <v>38</v>
@@ -11421,7 +11871,10 @@
         <v>7</v>
       </c>
       <c r="G329" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H329">
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
@@ -11429,22 +11882,25 @@
         <v>46121</v>
       </c>
       <c r="B330" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C330" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D330" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E330" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F330" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G330" t="s">
         <v>21</v>
+      </c>
+      <c r="H330">
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
@@ -11452,22 +11908,25 @@
         <v>46121</v>
       </c>
       <c r="B331" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C331" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D331" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E331" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F331" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G331" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
@@ -11475,22 +11934,25 @@
         <v>46121</v>
       </c>
       <c r="B332" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C332" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D332" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E332" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F332" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G332" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -11498,13 +11960,13 @@
         <v>46121</v>
       </c>
       <c r="B333" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C333" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D333" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E333" t="s">
         <v>36</v>
@@ -11514,6 +11976,9 @@
       </c>
       <c r="G333" t="s">
         <v>18</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
@@ -11521,13 +11986,13 @@
         <v>46121</v>
       </c>
       <c r="B334" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C334" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D334" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E334" t="s">
         <v>36</v>
@@ -11537,6 +12002,9 @@
       </c>
       <c r="G334" t="s">
         <v>18</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
@@ -11544,22 +12012,25 @@
         <v>46121</v>
       </c>
       <c r="B335" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C335" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D335" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E335" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F335" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G335" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
@@ -11567,36 +12038,39 @@
         <v>46121</v>
       </c>
       <c r="B336" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C336" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D336" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E336" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F336" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G336" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>46121</v>
       </c>
       <c r="B337" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C337" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D337" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E337" t="s">
         <v>36</v>
@@ -11605,21 +12079,24 @@
         <v>8</v>
       </c>
       <c r="G337" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>46121</v>
       </c>
       <c r="B338" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C338" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D338" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E338" t="s">
         <v>36</v>
@@ -11630,19 +12107,22 @@
       <c r="G338" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>46121</v>
       </c>
       <c r="B339" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C339" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D339" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E339" t="s">
         <v>36</v>
@@ -11653,19 +12133,22 @@
       <c r="G339" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>46121</v>
       </c>
       <c r="B340" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C340" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D340" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E340" t="s">
         <v>36</v>
@@ -11676,19 +12159,22 @@
       <c r="G340" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>46121</v>
       </c>
       <c r="B341" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C341" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D341" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E341" t="s">
         <v>36</v>
@@ -11699,88 +12185,100 @@
       <c r="G341" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>46121</v>
       </c>
       <c r="B342" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C342" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D342" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E342" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F342" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G342" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>46121</v>
       </c>
       <c r="B343" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C343" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D343" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E343" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F343" t="s">
-        <v>7</v>
+        <v>384</v>
       </c>
       <c r="G343" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>46121</v>
       </c>
       <c r="B344" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C344" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D344" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E344" t="s">
         <v>36</v>
       </c>
       <c r="F344" t="s">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="G344" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>46121</v>
       </c>
       <c r="B345" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C345" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D345" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E345" t="s">
         <v>36</v>
@@ -11789,93 +12287,105 @@
         <v>8</v>
       </c>
       <c r="G345" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>46121</v>
       </c>
       <c r="B346" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C346" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D346" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E346" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F346" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G346" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>46121</v>
       </c>
       <c r="B347" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C347" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D347" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F347" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G347" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>46121</v>
       </c>
       <c r="B348" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C348" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D348" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E348" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F348" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G348" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>46121</v>
       </c>
       <c r="B349" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C349" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D349" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E349" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F349" t="s">
         <v>7</v>
@@ -11883,154 +12393,175 @@
       <c r="G349" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>46121</v>
       </c>
       <c r="B350" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C350" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D350" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E350" t="s">
         <v>36</v>
       </c>
       <c r="F350" t="s">
-        <v>7</v>
+        <v>384</v>
       </c>
       <c r="G350" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>46121</v>
       </c>
       <c r="B351" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C351" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D351" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E351" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F351" t="s">
-        <v>384</v>
+        <v>10</v>
       </c>
       <c r="G351" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H351" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>46121</v>
       </c>
       <c r="B352" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C352" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D352" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E352" t="s">
         <v>38</v>
       </c>
       <c r="F352" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G352" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>46121</v>
       </c>
       <c r="B353" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C353" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D353" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E353" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F353" t="s">
         <v>7</v>
       </c>
       <c r="G353" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>46121</v>
       </c>
       <c r="B354" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C354" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D354" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E354" t="s">
         <v>36</v>
       </c>
       <c r="F354" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G354" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>46121</v>
       </c>
       <c r="B355" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C355" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D355" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E355" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F355" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G355" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>46121</v>
       </c>
       <c r="B356" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C356" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D356" t="s">
         <v>30</v>
@@ -12044,137 +12575,155 @@
       <c r="G356" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>46121</v>
       </c>
       <c r="B357" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C357" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D357" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E357" t="s">
         <v>38</v>
       </c>
       <c r="F357" t="s">
-        <v>7</v>
+        <v>763</v>
       </c>
       <c r="G357" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>46121</v>
       </c>
       <c r="B358" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C358" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D358" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E358" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F358" t="s">
-        <v>764</v>
+        <v>8</v>
       </c>
       <c r="G358" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>46121</v>
       </c>
       <c r="B359" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C359" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D359" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E359" t="s">
         <v>36</v>
       </c>
       <c r="F359" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G359" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>46121</v>
       </c>
       <c r="B360" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C360" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D360" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E360" t="s">
         <v>36</v>
       </c>
       <c r="F360" t="s">
-        <v>7</v>
+        <v>763</v>
       </c>
       <c r="G360" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>46121</v>
       </c>
       <c r="B361" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C361" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D361" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E361" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F361" t="s">
-        <v>764</v>
+        <v>8</v>
       </c>
       <c r="G361" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>46121</v>
       </c>
       <c r="B362" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C362" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D362" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E362" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F362" t="s">
         <v>8</v>
@@ -12182,19 +12731,22 @@
       <c r="G362" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>46121</v>
       </c>
       <c r="B363" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C363" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D363" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E363" t="s">
         <v>36</v>
@@ -12205,68 +12757,77 @@
       <c r="G363" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>46121</v>
       </c>
       <c r="B364" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C364" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D364" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E364" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F364" t="s">
-        <v>8</v>
+        <v>763</v>
       </c>
       <c r="G364" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>46121</v>
       </c>
       <c r="B365" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C365" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D365" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E365" t="s">
         <v>38</v>
       </c>
       <c r="F365" t="s">
-        <v>764</v>
+        <v>8</v>
       </c>
       <c r="G365" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>46121</v>
       </c>
       <c r="B366" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C366" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D366" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E366" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F366" t="s">
         <v>8</v>
@@ -12274,19 +12835,22 @@
       <c r="G366" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>46121</v>
       </c>
       <c r="B367" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C367" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D367" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E367" t="s">
         <v>36</v>
@@ -12297,19 +12861,22 @@
       <c r="G367" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>46121</v>
       </c>
       <c r="B368" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C368" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D368" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E368" t="s">
         <v>36</v>
@@ -12320,114 +12887,129 @@
       <c r="G368" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>46121</v>
       </c>
       <c r="B369" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C369" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D369" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E369" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F369" t="s">
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>46121</v>
       </c>
       <c r="B370" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C370" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D370" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F370" t="s">
         <v>8</v>
       </c>
       <c r="G370" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>46121</v>
       </c>
       <c r="B371" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C371" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D371" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E371" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F371" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G371" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>46121</v>
       </c>
       <c r="B372" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C372" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D372" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E372" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F372" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G372" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>46121</v>
       </c>
       <c r="B373" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C373" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D373" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E373" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F373" t="s">
         <v>8</v>
@@ -12435,22 +13017,25 @@
       <c r="G373" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>46121</v>
       </c>
       <c r="B374" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C374" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D374" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E374" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F374" t="s">
         <v>8</v>
@@ -12458,19 +13043,22 @@
       <c r="G374" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>46121</v>
       </c>
       <c r="B375" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C375" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D375" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E375" t="s">
         <v>36</v>
@@ -12481,16 +13069,19 @@
       <c r="G375" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>46121</v>
       </c>
       <c r="B376" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C376" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D376" t="s">
         <v>16</v>
@@ -12504,16 +13095,19 @@
       <c r="G376" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>46121</v>
       </c>
       <c r="B377" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C377" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D377" t="s">
         <v>16</v>
@@ -12527,19 +13121,22 @@
       <c r="G377" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>46121</v>
       </c>
       <c r="B378" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C378" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D378" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E378" t="s">
         <v>36</v>
@@ -12550,111 +13147,126 @@
       <c r="G378" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>46121</v>
       </c>
       <c r="B379" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C379" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D379" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E379" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F379" t="s">
         <v>8</v>
       </c>
       <c r="G379" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>46121</v>
       </c>
       <c r="B380" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C380" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D380" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F380" t="s">
         <v>8</v>
       </c>
       <c r="G380" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>46121</v>
       </c>
       <c r="B381" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C381" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D381" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E381" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F381" t="s">
         <v>8</v>
       </c>
       <c r="G381" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>46121</v>
       </c>
       <c r="B382" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C382" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D382" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E382" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F382" t="s">
         <v>8</v>
       </c>
       <c r="G382" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>46121</v>
       </c>
       <c r="B383" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C383" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D383" t="s">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="E383" t="s">
         <v>36</v>
@@ -12663,21 +13275,24 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>46121</v>
       </c>
       <c r="B384" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C384" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D384" t="s">
-        <v>261</v>
+        <v>28</v>
       </c>
       <c r="E384" t="s">
         <v>36</v>
@@ -12686,53 +13301,1756 @@
         <v>8</v>
       </c>
       <c r="G384" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>46121</v>
       </c>
       <c r="B385" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C385" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D385" t="s">
+        <v>11</v>
+      </c>
+      <c r="E385" t="s">
+        <v>36</v>
+      </c>
+      <c r="F385" t="s">
+        <v>8</v>
+      </c>
+      <c r="G385" t="s">
+        <v>18</v>
+      </c>
+      <c r="H385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B386" t="s">
+        <v>823</v>
+      </c>
+      <c r="C386" t="s">
+        <v>824</v>
+      </c>
+      <c r="D386" t="s">
+        <v>27</v>
+      </c>
+      <c r="E386" t="s">
+        <v>37</v>
+      </c>
+      <c r="F386" t="s">
+        <v>242</v>
+      </c>
+      <c r="G386" t="s">
+        <v>18</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B387" t="s">
+        <v>825</v>
+      </c>
+      <c r="C387" t="s">
+        <v>826</v>
+      </c>
+      <c r="D387" t="s">
         <v>28</v>
       </c>
-      <c r="E385" t="s">
-        <v>36</v>
-      </c>
-      <c r="F385" t="s">
-        <v>8</v>
-      </c>
-      <c r="G385" t="s">
+      <c r="E387" t="s">
+        <v>36</v>
+      </c>
+      <c r="F387" t="s">
+        <v>8</v>
+      </c>
+      <c r="G387" t="s">
+        <v>18</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B388" t="s">
+        <v>827</v>
+      </c>
+      <c r="C388" t="s">
+        <v>828</v>
+      </c>
+      <c r="D388" t="s">
+        <v>24</v>
+      </c>
+      <c r="E388" t="s">
+        <v>38</v>
+      </c>
+      <c r="F388" t="s">
+        <v>7</v>
+      </c>
+      <c r="G388" t="s">
+        <v>18</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B389" t="s">
+        <v>829</v>
+      </c>
+      <c r="C389" t="s">
+        <v>830</v>
+      </c>
+      <c r="D389" t="s">
+        <v>24</v>
+      </c>
+      <c r="E389" t="s">
+        <v>38</v>
+      </c>
+      <c r="F389" t="s">
+        <v>7</v>
+      </c>
+      <c r="G389" t="s">
+        <v>18</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B390" t="s">
+        <v>831</v>
+      </c>
+      <c r="C390" t="s">
+        <v>832</v>
+      </c>
+      <c r="D390" t="s">
+        <v>11</v>
+      </c>
+      <c r="E390" t="s">
+        <v>36</v>
+      </c>
+      <c r="F390" t="s">
+        <v>8</v>
+      </c>
+      <c r="G390" t="s">
+        <v>18</v>
+      </c>
+      <c r="H390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B391" t="s">
+        <v>833</v>
+      </c>
+      <c r="C391" t="s">
+        <v>834</v>
+      </c>
+      <c r="D391" t="s">
+        <v>23</v>
+      </c>
+      <c r="E391" t="s">
+        <v>36</v>
+      </c>
+      <c r="F391" t="s">
+        <v>8</v>
+      </c>
+      <c r="G391" t="s">
+        <v>18</v>
+      </c>
+      <c r="H391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B392" t="s">
+        <v>835</v>
+      </c>
+      <c r="C392" t="s">
+        <v>836</v>
+      </c>
+      <c r="D392" t="s">
+        <v>27</v>
+      </c>
+      <c r="E392" t="s">
+        <v>37</v>
+      </c>
+      <c r="F392" t="s">
+        <v>242</v>
+      </c>
+      <c r="G392" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B393" t="s">
+        <v>837</v>
+      </c>
+      <c r="C393" t="s">
+        <v>838</v>
+      </c>
+      <c r="D393" t="s">
+        <v>27</v>
+      </c>
+      <c r="E393" t="s">
+        <v>37</v>
+      </c>
+      <c r="F393" t="s">
+        <v>242</v>
+      </c>
+      <c r="G393" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B394" t="s">
+        <v>839</v>
+      </c>
+      <c r="C394" t="s">
+        <v>840</v>
+      </c>
+      <c r="D394" t="s">
+        <v>27</v>
+      </c>
+      <c r="E394" t="s">
+        <v>37</v>
+      </c>
+      <c r="F394" t="s">
+        <v>242</v>
+      </c>
+      <c r="G394" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B395" t="s">
+        <v>841</v>
+      </c>
+      <c r="C395" t="s">
+        <v>842</v>
+      </c>
+      <c r="D395" t="s">
+        <v>27</v>
+      </c>
+      <c r="E395" t="s">
+        <v>37</v>
+      </c>
+      <c r="F395" t="s">
+        <v>242</v>
+      </c>
+      <c r="G395" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B396" t="s">
+        <v>843</v>
+      </c>
+      <c r="C396" t="s">
+        <v>844</v>
+      </c>
+      <c r="D396" t="s">
+        <v>27</v>
+      </c>
+      <c r="E396" t="s">
+        <v>37</v>
+      </c>
+      <c r="F396" t="s">
+        <v>242</v>
+      </c>
+      <c r="G396" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B397" t="s">
+        <v>845</v>
+      </c>
+      <c r="C397" t="s">
+        <v>846</v>
+      </c>
+      <c r="D397" t="s">
+        <v>6</v>
+      </c>
+      <c r="E397" t="s">
+        <v>36</v>
+      </c>
+      <c r="F397" t="s">
+        <v>8</v>
+      </c>
+      <c r="G397" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B398" t="s">
+        <v>847</v>
+      </c>
+      <c r="C398" t="s">
+        <v>848</v>
+      </c>
+      <c r="D398" t="s">
+        <v>22</v>
+      </c>
+      <c r="E398" t="s">
+        <v>38</v>
+      </c>
+      <c r="F398" t="s">
+        <v>7</v>
+      </c>
+      <c r="G398" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A386" s="1">
-        <v>46121</v>
-      </c>
-      <c r="B386" t="s">
-        <v>819</v>
-      </c>
-      <c r="C386" t="s">
-        <v>820</v>
-      </c>
-      <c r="D386" t="s">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B399" t="s">
+        <v>849</v>
+      </c>
+      <c r="C399" t="s">
+        <v>850</v>
+      </c>
+      <c r="D399" t="s">
+        <v>30</v>
+      </c>
+      <c r="E399" t="s">
+        <v>38</v>
+      </c>
+      <c r="F399" t="s">
+        <v>7</v>
+      </c>
+      <c r="G399" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B400" t="s">
+        <v>851</v>
+      </c>
+      <c r="C400" t="s">
+        <v>852</v>
+      </c>
+      <c r="D400" t="s">
+        <v>23</v>
+      </c>
+      <c r="E400" t="s">
+        <v>36</v>
+      </c>
+      <c r="F400" t="s">
+        <v>8</v>
+      </c>
+      <c r="G400" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B401" t="s">
+        <v>853</v>
+      </c>
+      <c r="C401" t="s">
+        <v>854</v>
+      </c>
+      <c r="D401" t="s">
+        <v>6</v>
+      </c>
+      <c r="E401" t="s">
+        <v>36</v>
+      </c>
+      <c r="F401" t="s">
+        <v>8</v>
+      </c>
+      <c r="G401" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B402" t="s">
+        <v>855</v>
+      </c>
+      <c r="C402" t="s">
+        <v>856</v>
+      </c>
+      <c r="D402" t="s">
+        <v>30</v>
+      </c>
+      <c r="E402" t="s">
+        <v>38</v>
+      </c>
+      <c r="F402" t="s">
+        <v>7</v>
+      </c>
+      <c r="G402" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B403" t="s">
+        <v>857</v>
+      </c>
+      <c r="C403" t="s">
+        <v>858</v>
+      </c>
+      <c r="D403" t="s">
+        <v>14</v>
+      </c>
+      <c r="E403" t="s">
+        <v>36</v>
+      </c>
+      <c r="F403" t="s">
+        <v>7</v>
+      </c>
+      <c r="G403" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B404" t="s">
+        <v>859</v>
+      </c>
+      <c r="C404" t="s">
+        <v>860</v>
+      </c>
+      <c r="D404" t="s">
+        <v>15</v>
+      </c>
+      <c r="E404" t="s">
+        <v>36</v>
+      </c>
+      <c r="F404" t="s">
+        <v>8</v>
+      </c>
+      <c r="G404" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B405" t="s">
+        <v>861</v>
+      </c>
+      <c r="C405" t="s">
+        <v>862</v>
+      </c>
+      <c r="D405" t="s">
+        <v>14</v>
+      </c>
+      <c r="E405" t="s">
+        <v>36</v>
+      </c>
+      <c r="F405" t="s">
+        <v>8</v>
+      </c>
+      <c r="G405" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B406" t="s">
+        <v>863</v>
+      </c>
+      <c r="C406" t="s">
+        <v>864</v>
+      </c>
+      <c r="D406" t="s">
+        <v>6</v>
+      </c>
+      <c r="E406" t="s">
+        <v>36</v>
+      </c>
+      <c r="F406" t="s">
+        <v>8</v>
+      </c>
+      <c r="G406" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B407" t="s">
+        <v>865</v>
+      </c>
+      <c r="C407" t="s">
+        <v>866</v>
+      </c>
+      <c r="D407" t="s">
+        <v>30</v>
+      </c>
+      <c r="E407" t="s">
+        <v>38</v>
+      </c>
+      <c r="F407" t="s">
+        <v>867</v>
+      </c>
+      <c r="G407" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B408" t="s">
+        <v>868</v>
+      </c>
+      <c r="C408" t="s">
+        <v>869</v>
+      </c>
+      <c r="D408" t="s">
+        <v>12</v>
+      </c>
+      <c r="E408" t="s">
+        <v>36</v>
+      </c>
+      <c r="F408" t="s">
+        <v>8</v>
+      </c>
+      <c r="G408" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B409" t="s">
+        <v>870</v>
+      </c>
+      <c r="C409" t="s">
+        <v>871</v>
+      </c>
+      <c r="D409" t="s">
+        <v>23</v>
+      </c>
+      <c r="E409" t="s">
+        <v>36</v>
+      </c>
+      <c r="F409" t="s">
+        <v>8</v>
+      </c>
+      <c r="G409" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B410" t="s">
+        <v>872</v>
+      </c>
+      <c r="C410" t="s">
+        <v>873</v>
+      </c>
+      <c r="D410" t="s">
+        <v>39</v>
+      </c>
+      <c r="E410" t="s">
+        <v>38</v>
+      </c>
+      <c r="F410" t="s">
+        <v>7</v>
+      </c>
+      <c r="G410" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B411" t="s">
+        <v>874</v>
+      </c>
+      <c r="C411" t="s">
+        <v>875</v>
+      </c>
+      <c r="D411" t="s">
+        <v>40</v>
+      </c>
+      <c r="E411" t="s">
+        <v>38</v>
+      </c>
+      <c r="F411" t="s">
+        <v>10</v>
+      </c>
+      <c r="G411" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B412" t="s">
+        <v>876</v>
+      </c>
+      <c r="C412" t="s">
+        <v>877</v>
+      </c>
+      <c r="D412" t="s">
+        <v>261</v>
+      </c>
+      <c r="E412" t="s">
+        <v>36</v>
+      </c>
+      <c r="F412" t="s">
+        <v>8</v>
+      </c>
+      <c r="G412" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B413" t="s">
+        <v>878</v>
+      </c>
+      <c r="C413" t="s">
+        <v>879</v>
+      </c>
+      <c r="D413" t="s">
+        <v>39</v>
+      </c>
+      <c r="E413" t="s">
+        <v>38</v>
+      </c>
+      <c r="F413" t="s">
+        <v>7</v>
+      </c>
+      <c r="G413" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B414" t="s">
+        <v>880</v>
+      </c>
+      <c r="C414" t="s">
+        <v>881</v>
+      </c>
+      <c r="D414" t="s">
         <v>11</v>
       </c>
-      <c r="E386" t="s">
-        <v>36</v>
-      </c>
-      <c r="F386" t="s">
-        <v>8</v>
-      </c>
-      <c r="G386" t="s">
-        <v>18</v>
+      <c r="E414" t="s">
+        <v>36</v>
+      </c>
+      <c r="F414" t="s">
+        <v>8</v>
+      </c>
+      <c r="G414" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B415" t="s">
+        <v>882</v>
+      </c>
+      <c r="C415" t="s">
+        <v>883</v>
+      </c>
+      <c r="D415" t="s">
+        <v>28</v>
+      </c>
+      <c r="E415" t="s">
+        <v>36</v>
+      </c>
+      <c r="F415" t="s">
+        <v>8</v>
+      </c>
+      <c r="G415" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B416" t="s">
+        <v>884</v>
+      </c>
+      <c r="C416" t="s">
+        <v>885</v>
+      </c>
+      <c r="D416" t="s">
+        <v>22</v>
+      </c>
+      <c r="E416" t="s">
+        <v>38</v>
+      </c>
+      <c r="F416" t="s">
+        <v>8</v>
+      </c>
+      <c r="G416" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B417" t="s">
+        <v>886</v>
+      </c>
+      <c r="C417" t="s">
+        <v>887</v>
+      </c>
+      <c r="D417" t="s">
+        <v>16</v>
+      </c>
+      <c r="E417" t="s">
+        <v>36</v>
+      </c>
+      <c r="F417" t="s">
+        <v>8</v>
+      </c>
+      <c r="G417" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B418" t="s">
+        <v>888</v>
+      </c>
+      <c r="C418" t="s">
+        <v>889</v>
+      </c>
+      <c r="D418" t="s">
+        <v>15</v>
+      </c>
+      <c r="E418" t="s">
+        <v>36</v>
+      </c>
+      <c r="F418" t="s">
+        <v>8</v>
+      </c>
+      <c r="G418" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B419" t="s">
+        <v>890</v>
+      </c>
+      <c r="C419" t="s">
+        <v>891</v>
+      </c>
+      <c r="D419" t="s">
+        <v>28</v>
+      </c>
+      <c r="E419" t="s">
+        <v>36</v>
+      </c>
+      <c r="F419" t="s">
+        <v>8</v>
+      </c>
+      <c r="G419" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B420" t="s">
+        <v>892</v>
+      </c>
+      <c r="C420" t="s">
+        <v>893</v>
+      </c>
+      <c r="D420" t="s">
+        <v>30</v>
+      </c>
+      <c r="E420" t="s">
+        <v>38</v>
+      </c>
+      <c r="F420" t="s">
+        <v>8</v>
+      </c>
+      <c r="G420" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B421" t="s">
+        <v>894</v>
+      </c>
+      <c r="C421" t="s">
+        <v>895</v>
+      </c>
+      <c r="D421" t="s">
+        <v>14</v>
+      </c>
+      <c r="E421" t="s">
+        <v>36</v>
+      </c>
+      <c r="F421" t="s">
+        <v>8</v>
+      </c>
+      <c r="G421" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B422" t="s">
+        <v>896</v>
+      </c>
+      <c r="C422" t="s">
+        <v>897</v>
+      </c>
+      <c r="D422" t="s">
+        <v>19</v>
+      </c>
+      <c r="E422" t="s">
+        <v>36</v>
+      </c>
+      <c r="F422" t="s">
+        <v>8</v>
+      </c>
+      <c r="G422" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B423" t="s">
+        <v>898</v>
+      </c>
+      <c r="C423" t="s">
+        <v>899</v>
+      </c>
+      <c r="D423" t="s">
+        <v>261</v>
+      </c>
+      <c r="E423" t="s">
+        <v>36</v>
+      </c>
+      <c r="F423" t="s">
+        <v>8</v>
+      </c>
+      <c r="G423" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B424" t="s">
+        <v>900</v>
+      </c>
+      <c r="C424" t="s">
+        <v>901</v>
+      </c>
+      <c r="D424" t="s">
+        <v>14</v>
+      </c>
+      <c r="E424" t="s">
+        <v>36</v>
+      </c>
+      <c r="F424" t="s">
+        <v>8</v>
+      </c>
+      <c r="G424" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B425" t="s">
+        <v>902</v>
+      </c>
+      <c r="C425" t="s">
+        <v>903</v>
+      </c>
+      <c r="D425" t="s">
+        <v>22</v>
+      </c>
+      <c r="E425" t="s">
+        <v>38</v>
+      </c>
+      <c r="F425" t="s">
+        <v>8</v>
+      </c>
+      <c r="G425" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B426" t="s">
+        <v>904</v>
+      </c>
+      <c r="C426" t="s">
+        <v>905</v>
+      </c>
+      <c r="D426" t="s">
+        <v>14</v>
+      </c>
+      <c r="E426" t="s">
+        <v>36</v>
+      </c>
+      <c r="F426" t="s">
+        <v>8</v>
+      </c>
+      <c r="G426" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B427" t="s">
+        <v>906</v>
+      </c>
+      <c r="C427" t="s">
+        <v>907</v>
+      </c>
+      <c r="D427" t="s">
+        <v>30</v>
+      </c>
+      <c r="E427" t="s">
+        <v>38</v>
+      </c>
+      <c r="F427" t="s">
+        <v>7</v>
+      </c>
+      <c r="G427" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B428" t="s">
+        <v>908</v>
+      </c>
+      <c r="C428" t="s">
+        <v>909</v>
+      </c>
+      <c r="D428" t="s">
+        <v>16</v>
+      </c>
+      <c r="E428" t="s">
+        <v>36</v>
+      </c>
+      <c r="F428" t="s">
+        <v>8</v>
+      </c>
+      <c r="G428" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B429" t="s">
+        <v>910</v>
+      </c>
+      <c r="C429" t="s">
+        <v>911</v>
+      </c>
+      <c r="D429" t="s">
+        <v>15</v>
+      </c>
+      <c r="E429" t="s">
+        <v>36</v>
+      </c>
+      <c r="F429" t="s">
+        <v>8</v>
+      </c>
+      <c r="G429" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B430" t="s">
+        <v>912</v>
+      </c>
+      <c r="C430" t="s">
+        <v>913</v>
+      </c>
+      <c r="D430" t="s">
+        <v>30</v>
+      </c>
+      <c r="E430" t="s">
+        <v>38</v>
+      </c>
+      <c r="F430" t="s">
+        <v>7</v>
+      </c>
+      <c r="G430" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B431" t="s">
+        <v>914</v>
+      </c>
+      <c r="C431" t="s">
+        <v>915</v>
+      </c>
+      <c r="D431" t="s">
+        <v>16</v>
+      </c>
+      <c r="E431" t="s">
+        <v>36</v>
+      </c>
+      <c r="F431" t="s">
+        <v>8</v>
+      </c>
+      <c r="G431" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B432" t="s">
+        <v>916</v>
+      </c>
+      <c r="C432" t="s">
+        <v>917</v>
+      </c>
+      <c r="D432" t="s">
+        <v>6</v>
+      </c>
+      <c r="E432" t="s">
+        <v>36</v>
+      </c>
+      <c r="F432" t="s">
+        <v>8</v>
+      </c>
+      <c r="G432" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B433" t="s">
+        <v>918</v>
+      </c>
+      <c r="C433" t="s">
+        <v>919</v>
+      </c>
+      <c r="D433" t="s">
+        <v>6</v>
+      </c>
+      <c r="E433" t="s">
+        <v>36</v>
+      </c>
+      <c r="F433" t="s">
+        <v>8</v>
+      </c>
+      <c r="G433" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A434" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B434" t="s">
+        <v>920</v>
+      </c>
+      <c r="C434" t="s">
+        <v>921</v>
+      </c>
+      <c r="D434" t="s">
+        <v>16</v>
+      </c>
+      <c r="E434" t="s">
+        <v>36</v>
+      </c>
+      <c r="F434" t="s">
+        <v>8</v>
+      </c>
+      <c r="G434" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A435" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B435" t="s">
+        <v>922</v>
+      </c>
+      <c r="C435" t="s">
+        <v>923</v>
+      </c>
+      <c r="D435" t="s">
+        <v>19</v>
+      </c>
+      <c r="E435" t="s">
+        <v>36</v>
+      </c>
+      <c r="F435" t="s">
+        <v>8</v>
+      </c>
+      <c r="G435" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A436" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B436" t="s">
+        <v>924</v>
+      </c>
+      <c r="C436" t="s">
+        <v>925</v>
+      </c>
+      <c r="D436" t="s">
+        <v>40</v>
+      </c>
+      <c r="E436" t="s">
+        <v>38</v>
+      </c>
+      <c r="F436" t="s">
+        <v>7</v>
+      </c>
+      <c r="G436" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A437" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B437" t="s">
+        <v>926</v>
+      </c>
+      <c r="C437" t="s">
+        <v>927</v>
+      </c>
+      <c r="D437" t="s">
+        <v>25</v>
+      </c>
+      <c r="E437" t="s">
+        <v>38</v>
+      </c>
+      <c r="F437" t="s">
+        <v>7</v>
+      </c>
+      <c r="G437" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A438" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B438" t="s">
+        <v>928</v>
+      </c>
+      <c r="C438" t="s">
+        <v>929</v>
+      </c>
+      <c r="D438" t="s">
+        <v>11</v>
+      </c>
+      <c r="E438" t="s">
+        <v>36</v>
+      </c>
+      <c r="F438" t="s">
+        <v>8</v>
+      </c>
+      <c r="G438" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A439" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B439" t="s">
+        <v>930</v>
+      </c>
+      <c r="C439" t="s">
+        <v>931</v>
+      </c>
+      <c r="D439" t="s">
+        <v>15</v>
+      </c>
+      <c r="E439" t="s">
+        <v>36</v>
+      </c>
+      <c r="F439" t="s">
+        <v>8</v>
+      </c>
+      <c r="G439" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A440" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B440" t="s">
+        <v>932</v>
+      </c>
+      <c r="C440" t="s">
+        <v>933</v>
+      </c>
+      <c r="D440" t="s">
+        <v>30</v>
+      </c>
+      <c r="E440" t="s">
+        <v>38</v>
+      </c>
+      <c r="F440" t="s">
+        <v>8</v>
+      </c>
+      <c r="G440" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A441" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B441" t="s">
+        <v>934</v>
+      </c>
+      <c r="C441" t="s">
+        <v>935</v>
+      </c>
+      <c r="D441" t="s">
+        <v>14</v>
+      </c>
+      <c r="E441" t="s">
+        <v>36</v>
+      </c>
+      <c r="F441" t="s">
+        <v>8</v>
+      </c>
+      <c r="G441" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A442" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B442" t="s">
+        <v>936</v>
+      </c>
+      <c r="C442" t="s">
+        <v>937</v>
+      </c>
+      <c r="D442" t="s">
+        <v>6</v>
+      </c>
+      <c r="E442" t="s">
+        <v>36</v>
+      </c>
+      <c r="F442" t="s">
+        <v>8</v>
+      </c>
+      <c r="G442" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A443" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B443" t="s">
+        <v>938</v>
+      </c>
+      <c r="C443" t="s">
+        <v>939</v>
+      </c>
+      <c r="D443" t="s">
+        <v>28</v>
+      </c>
+      <c r="E443" t="s">
+        <v>36</v>
+      </c>
+      <c r="F443" t="s">
+        <v>8</v>
+      </c>
+      <c r="G443" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A444" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B444" t="s">
+        <v>940</v>
+      </c>
+      <c r="C444" t="s">
+        <v>941</v>
+      </c>
+      <c r="D444" t="s">
+        <v>19</v>
+      </c>
+      <c r="E444" t="s">
+        <v>36</v>
+      </c>
+      <c r="F444" t="s">
+        <v>8</v>
+      </c>
+      <c r="G444" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A445" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B445" t="s">
+        <v>942</v>
+      </c>
+      <c r="C445" t="s">
+        <v>943</v>
+      </c>
+      <c r="D445" t="s">
+        <v>40</v>
+      </c>
+      <c r="E445" t="s">
+        <v>38</v>
+      </c>
+      <c r="F445" t="s">
+        <v>7</v>
+      </c>
+      <c r="G445" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A446" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B446" t="s">
+        <v>944</v>
+      </c>
+      <c r="C446" t="s">
+        <v>945</v>
+      </c>
+      <c r="D446" t="s">
+        <v>24</v>
+      </c>
+      <c r="E446" t="s">
+        <v>38</v>
+      </c>
+      <c r="F446" t="s">
+        <v>7</v>
+      </c>
+      <c r="G446" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A447" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B447" t="s">
+        <v>946</v>
+      </c>
+      <c r="C447" t="s">
+        <v>947</v>
+      </c>
+      <c r="D447" t="s">
+        <v>14</v>
+      </c>
+      <c r="E447" t="s">
+        <v>36</v>
+      </c>
+      <c r="F447" t="s">
+        <v>8</v>
+      </c>
+      <c r="G447" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A448" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B448" t="s">
+        <v>948</v>
+      </c>
+      <c r="C448" t="s">
+        <v>949</v>
+      </c>
+      <c r="D448" t="s">
+        <v>22</v>
+      </c>
+      <c r="E448" t="s">
+        <v>38</v>
+      </c>
+      <c r="F448" t="s">
+        <v>7</v>
+      </c>
+      <c r="G448" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B449" t="s">
+        <v>950</v>
+      </c>
+      <c r="C449" t="s">
+        <v>951</v>
+      </c>
+      <c r="D449" t="s">
+        <v>15</v>
+      </c>
+      <c r="E449" t="s">
+        <v>36</v>
+      </c>
+      <c r="F449" t="s">
+        <v>8</v>
+      </c>
+      <c r="G449" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B450" t="s">
+        <v>952</v>
+      </c>
+      <c r="C450" t="s">
+        <v>953</v>
+      </c>
+      <c r="D450" t="s">
+        <v>15</v>
+      </c>
+      <c r="E450" t="s">
+        <v>36</v>
+      </c>
+      <c r="F450" t="s">
+        <v>8</v>
+      </c>
+      <c r="G450" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B451" t="s">
+        <v>954</v>
+      </c>
+      <c r="C451" t="s">
+        <v>955</v>
+      </c>
+      <c r="D451" t="s">
+        <v>14</v>
+      </c>
+      <c r="E451" t="s">
+        <v>36</v>
+      </c>
+      <c r="F451" t="s">
+        <v>8</v>
+      </c>
+      <c r="G451" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B452" t="s">
+        <v>956</v>
+      </c>
+      <c r="C452" t="s">
+        <v>957</v>
+      </c>
+      <c r="D452" t="s">
+        <v>25</v>
+      </c>
+      <c r="E452" t="s">
+        <v>38</v>
+      </c>
+      <c r="F452" t="s">
+        <v>7</v>
+      </c>
+      <c r="G452" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B453" t="s">
+        <v>958</v>
+      </c>
+      <c r="C453" t="s">
+        <v>959</v>
+      </c>
+      <c r="D453" t="s">
+        <v>28</v>
+      </c>
+      <c r="E453" t="s">
+        <v>36</v>
+      </c>
+      <c r="F453" t="s">
+        <v>8</v>
+      </c>
+      <c r="G453" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B454" t="s">
+        <v>960</v>
+      </c>
+      <c r="C454" t="s">
+        <v>961</v>
+      </c>
+      <c r="D454" t="s">
+        <v>12</v>
+      </c>
+      <c r="E454" t="s">
+        <v>36</v>
+      </c>
+      <c r="F454" t="s">
+        <v>8</v>
+      </c>
+      <c r="G454" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B455" t="s">
+        <v>962</v>
+      </c>
+      <c r="C455" t="s">
+        <v>963</v>
+      </c>
+      <c r="D455" t="s">
+        <v>14</v>
+      </c>
+      <c r="E455" t="s">
+        <v>36</v>
+      </c>
+      <c r="F455" t="s">
+        <v>8</v>
+      </c>
+      <c r="G455" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B456" t="s">
+        <v>964</v>
+      </c>
+      <c r="C456" t="s">
+        <v>965</v>
+      </c>
+      <c r="D456" t="s">
+        <v>19</v>
+      </c>
+      <c r="E456" t="s">
+        <v>36</v>
+      </c>
+      <c r="F456" t="s">
+        <v>8</v>
+      </c>
+      <c r="G456" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B457" t="s">
+        <v>966</v>
+      </c>
+      <c r="C457" t="s">
+        <v>967</v>
+      </c>
+      <c r="D457" t="s">
+        <v>19</v>
+      </c>
+      <c r="E457" t="s">
+        <v>36</v>
+      </c>
+      <c r="F457" t="s">
+        <v>8</v>
+      </c>
+      <c r="G457" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B458" t="s">
+        <v>968</v>
+      </c>
+      <c r="C458" t="s">
+        <v>969</v>
+      </c>
+      <c r="D458" t="s">
+        <v>14</v>
+      </c>
+      <c r="E458" t="s">
+        <v>36</v>
+      </c>
+      <c r="F458" t="s">
+        <v>8</v>
+      </c>
+      <c r="G458" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B459" t="s">
+        <v>970</v>
+      </c>
+      <c r="C459" t="s">
+        <v>971</v>
+      </c>
+      <c r="D459" t="s">
+        <v>25</v>
+      </c>
+      <c r="E459" t="s">
+        <v>38</v>
+      </c>
+      <c r="F459" t="s">
+        <v>8</v>
+      </c>
+      <c r="G459" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/first-atlas/producao_2026-04.xlsx
+++ b/first-atlas/producao_2026-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\augustoalmeida\Augusto\bots_comissionamento\bot_atlas\first-atlas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D169B981-E939-4010-8C63-64CE50D5C822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CB8779-A867-4E81-8AE4-48E92D20F753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{F5572131-3C84-4D9C-B555-72DCC3B1940B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3760" uniqueCount="1301">
   <si>
     <t>DATA_BASE</t>
   </si>
@@ -2114,9 +2114,6 @@
     <t>LGO SERVICOS LTDA</t>
   </si>
   <si>
-    <t>Envie uma procuracao com o prazo vigente, pois a enviada foi emitida a mais de tres anos.</t>
-  </si>
-  <si>
     <t>Ata de eleicao da empresa CENTRO RECREATIVO ESP UNIAO AMIGOS DE VILA PROSPERIDADE, atualizado e registrada no orgao competente. Esse documento formaliza a eleicao e/ou nomeacao dos representantes legais e administradores, informando cargos, prazos de mandato e poderes de representacao, comprovando quem esta autorizado a agir em nome da entidade.&lt;br&gt;&lt;br&gt;Estatuto social da empresa CENTRO RECREATIVO ESP UNIAO AMIGOS DE VILA PROSPERIDADE, atualizado e registrado no orgao competente. Esse documento estabelece as regras de funcionamento da empresa, descrevendo sua finalidade, estrutura administrativa, orgaos de gestao e forma de representacao legal, comprovando sua existencia e regularidade.</t>
   </si>
   <si>
@@ -2955,6 +2952,996 @@
   </si>
   <si>
     <t>VASCONCELLOS TRADE REPRESENTACOES COMERCIAIS</t>
+  </si>
+  <si>
+    <t>59593448000109</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JOCIELE APARECIDA IANZ DE SOUZA MACHADO</t>
+  </si>
+  <si>
+    <t>62812428000196</t>
+  </si>
+  <si>
+    <t>VALDECI CAETANO DE LIMA</t>
+  </si>
+  <si>
+    <t>22772841000150</t>
+  </si>
+  <si>
+    <t>KEAH ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>34617934000199</t>
+  </si>
+  <si>
+    <t>34.617.934 IZABEL BEATRIZ RODRIGUES DE MOURA</t>
+  </si>
+  <si>
+    <t>24103164000102</t>
+  </si>
+  <si>
+    <t>GIOVANNA VIDAL PAGOT</t>
+  </si>
+  <si>
+    <t>35200719000150</t>
+  </si>
+  <si>
+    <t>GEORGE SIEDLER</t>
+  </si>
+  <si>
+    <t>34137750000121</t>
+  </si>
+  <si>
+    <t>34.137.750 JOSIAS DOS SANTOS BARBOSA</t>
+  </si>
+  <si>
+    <t>32851573000115</t>
+  </si>
+  <si>
+    <t>J P CRUZ LEANDRO PRIMAVERA MIX</t>
+  </si>
+  <si>
+    <t>66094766000190</t>
+  </si>
+  <si>
+    <t>MILENA MOURA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>26963557000111</t>
+  </si>
+  <si>
+    <t>JORGE LUIZ ANTONIO</t>
+  </si>
+  <si>
+    <t>48019622000198</t>
+  </si>
+  <si>
+    <t>48.019.622 DOUGLAS DA SILVA GAIA</t>
+  </si>
+  <si>
+    <t>66057111000142</t>
+  </si>
+  <si>
+    <t>NAJARA NASCIMENTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>64521382000181</t>
+  </si>
+  <si>
+    <t>P. FELIPE MAGALHAES DE ALMEIDA E CIA LTDA</t>
+  </si>
+  <si>
+    <t>59762889000197</t>
+  </si>
+  <si>
+    <t>TALISSON S GOMES</t>
+  </si>
+  <si>
+    <t>27316925000100</t>
+  </si>
+  <si>
+    <t>LEONIS COELHO BARBOSA</t>
+  </si>
+  <si>
+    <t>12247513000180</t>
+  </si>
+  <si>
+    <t>ESQUELMIR COCCI FILHO</t>
+  </si>
+  <si>
+    <t>64749478000100</t>
+  </si>
+  <si>
+    <t>IVANDO DE ARAUJO SILVA</t>
+  </si>
+  <si>
+    <t>54152093000107</t>
+  </si>
+  <si>
+    <t>GUILHERME LIMA DA SILVA</t>
+  </si>
+  <si>
+    <t>57567500000127</t>
+  </si>
+  <si>
+    <t>INSTITUTO YARA ROOSEVELT BEZERRA DE MENEZES SERVICOS DE FISIOTERAPIA LTDA</t>
+  </si>
+  <si>
+    <t>43566814000109</t>
+  </si>
+  <si>
+    <t>ERIC JUNIO FURLAN LTDA</t>
+  </si>
+  <si>
+    <t>26427056000110</t>
+  </si>
+  <si>
+    <t>JOBSON MARTINS MONCORVO</t>
+  </si>
+  <si>
+    <t>28048859000190</t>
+  </si>
+  <si>
+    <t>28.048.859 ISMAEL LEONI SOARES</t>
+  </si>
+  <si>
+    <t>26940339000161</t>
+  </si>
+  <si>
+    <t>EPOC EDUCACAO POR PRINCIPIOS LTDA</t>
+  </si>
+  <si>
+    <t>34396272000174</t>
+  </si>
+  <si>
+    <t>34.396.272 SIMONE CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>28054646000170</t>
+  </si>
+  <si>
+    <t>FABIO CAMPIN PEREIRA TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>10936371000214</t>
+  </si>
+  <si>
+    <t>R ALVES LIMA</t>
+  </si>
+  <si>
+    <t>49201657000106</t>
+  </si>
+  <si>
+    <t>DULCE CARE SAUDE E ACOLHIMENTO LTDA</t>
+  </si>
+  <si>
+    <t>64006804000180</t>
+  </si>
+  <si>
+    <t>CAICK PEREIRA LACERDA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>63983468000163</t>
+  </si>
+  <si>
+    <t>TRANSCHAVES LTDA</t>
+  </si>
+  <si>
+    <t>64185336000159</t>
+  </si>
+  <si>
+    <t>SP PSICOPEDAGOGIA LTDA</t>
+  </si>
+  <si>
+    <t>35175870000186</t>
+  </si>
+  <si>
+    <t>MANUTENCAO E SERVICOS DE PINTURA MUNIZ LTDA</t>
+  </si>
+  <si>
+    <t>22831521000123</t>
+  </si>
+  <si>
+    <t>ANDERSON VIEIRA DANTAS</t>
+  </si>
+  <si>
+    <t>64340365000148</t>
+  </si>
+  <si>
+    <t>G F DA SILVA MANUTENCAO</t>
+  </si>
+  <si>
+    <t>62518937000100</t>
+  </si>
+  <si>
+    <t>ALMIR GALVAO MACEDO COUTO</t>
+  </si>
+  <si>
+    <t>59145158000283</t>
+  </si>
+  <si>
+    <t>WJ BIJUTERIAS LTDA</t>
+  </si>
+  <si>
+    <t>64861146000104</t>
+  </si>
+  <si>
+    <t>AOS REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>48108689000107</t>
+  </si>
+  <si>
+    <t>MARCIA GONCALVES DA SILVA QUITES</t>
+  </si>
+  <si>
+    <t>45418252000173</t>
+  </si>
+  <si>
+    <t>JHONATAN PEREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>60152319000164</t>
+  </si>
+  <si>
+    <t>J N CLEMENTINO SILVA MANUTENCOES</t>
+  </si>
+  <si>
+    <t>63545880000100</t>
+  </si>
+  <si>
+    <t>VOLNEI EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>65112272000129</t>
+  </si>
+  <si>
+    <t>J.F CONSTRUCOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>59780433000150</t>
+  </si>
+  <si>
+    <t>BASICO PARA CONSTRUCAO JAMARI LTDA</t>
+  </si>
+  <si>
+    <t>17119352000163</t>
+  </si>
+  <si>
+    <t>ROSEANE SILVA GOIS</t>
+  </si>
+  <si>
+    <t>18552648000136</t>
+  </si>
+  <si>
+    <t>MAGDA PEREIRA LOPES</t>
+  </si>
+  <si>
+    <t>10795053000108</t>
+  </si>
+  <si>
+    <t>L. R. MIGUEL JUNIOR LTDA</t>
+  </si>
+  <si>
+    <t>62791224000116</t>
+  </si>
+  <si>
+    <t>GALVAO RESTAURANTE E LANCHONETE LTDA</t>
+  </si>
+  <si>
+    <t>53809673000234</t>
+  </si>
+  <si>
+    <t>SBX CONSULTING ASSESSORIA EMPRESARIAL LTDA</t>
+  </si>
+  <si>
+    <t>20072554000101</t>
+  </si>
+  <si>
+    <t>NFD DISTRIBUIDORA DE BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>40516020000134</t>
+  </si>
+  <si>
+    <t>RFG REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>14473989000165</t>
+  </si>
+  <si>
+    <t>14.473.989 MARIA CLAUDECI DOS SANTOS</t>
+  </si>
+  <si>
+    <t>37640004000144</t>
+  </si>
+  <si>
+    <t>VALDECIR LAGUNA</t>
+  </si>
+  <si>
+    <t>57875168000168</t>
+  </si>
+  <si>
+    <t>ESPACO BARN LOGNE LTDA</t>
+  </si>
+  <si>
+    <t>46950274000142</t>
+  </si>
+  <si>
+    <t>DATSON MARTINS NASCIMENTO</t>
+  </si>
+  <si>
+    <t>60910580000186</t>
+  </si>
+  <si>
+    <t>ALVARO FERNANDO DA SILVA REGO LTDA</t>
+  </si>
+  <si>
+    <t>20299961000156</t>
+  </si>
+  <si>
+    <t>EUDES EDUARDO DA COSTA</t>
+  </si>
+  <si>
+    <t>63351391000290</t>
+  </si>
+  <si>
+    <t>L V B2B DISTRIBUIDORA TRADING GLOBAL IMPORTACAO E EXPORTACAO DE MOVEIS COLCHOES E ELETRONICOS LTDA</t>
+  </si>
+  <si>
+    <t>64158937000172</t>
+  </si>
+  <si>
+    <t>MASTERGRIG SOLUCOES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>41339638000139</t>
+  </si>
+  <si>
+    <t>41.339.638 RAFAEL AMORIM CERQUEIRA</t>
+  </si>
+  <si>
+    <t>54151292000192</t>
+  </si>
+  <si>
+    <t>CASTRO CARPINTARIA LTDA</t>
+  </si>
+  <si>
+    <t>41656230000190</t>
+  </si>
+  <si>
+    <t>MUNICO MARTINS</t>
+  </si>
+  <si>
+    <t>24783445000153</t>
+  </si>
+  <si>
+    <t>ABNADAB DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>64379270000138</t>
+  </si>
+  <si>
+    <t>ASSIS TRANSPORTES E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>26786965000145</t>
+  </si>
+  <si>
+    <t>MARANATA TERRAPLANAGEM E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>41190616000150</t>
+  </si>
+  <si>
+    <t>EMAE ENGTEC MANUTENCAO E ACESSORIOS E EQUIPAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>30724721000105</t>
+  </si>
+  <si>
+    <t>MIREILA ALVES PEREIRA</t>
+  </si>
+  <si>
+    <t>21326503000121</t>
+  </si>
+  <si>
+    <t>21.326.503 MARCONE NUNES CELESTRINO</t>
+  </si>
+  <si>
+    <t>47750309000162</t>
+  </si>
+  <si>
+    <t>EVOKE MOTORES COMERCIO DE PECAS MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t>49661113000127</t>
+  </si>
+  <si>
+    <t>JAIME ALEX CORCETE</t>
+  </si>
+  <si>
+    <t>31834029000100</t>
+  </si>
+  <si>
+    <t>31.834.029 WILTON SOARES ASCENCIO JUNIOR</t>
+  </si>
+  <si>
+    <t>33888390000137</t>
+  </si>
+  <si>
+    <t>E L RIBEIRO DOMINGOS COMERCIO VAREJISTA</t>
+  </si>
+  <si>
+    <t>26527404000121</t>
+  </si>
+  <si>
+    <t>28539747000131</t>
+  </si>
+  <si>
+    <t>CELSO RICARDO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>41240937000111</t>
+  </si>
+  <si>
+    <t>G M DE OLIVEIRA MAQUINAS E COMERCIO</t>
+  </si>
+  <si>
+    <t>57171965000164</t>
+  </si>
+  <si>
+    <t>E A D SANTOS</t>
+  </si>
+  <si>
+    <t>56190395000197</t>
+  </si>
+  <si>
+    <t>MAURO SERGIO FERNANDES DE ARAUJO LTDA</t>
+  </si>
+  <si>
+    <t>42674577000129</t>
+  </si>
+  <si>
+    <t>VALDINEI PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>63915945000153</t>
+  </si>
+  <si>
+    <t>BALBINO SERVICOS COMBINADOS LTDA</t>
+  </si>
+  <si>
+    <t>60840614000103</t>
+  </si>
+  <si>
+    <t>BIRA PLACAS LTDA</t>
+  </si>
+  <si>
+    <t>40055889000129</t>
+  </si>
+  <si>
+    <t>TEOTONHO SANTANA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>46365669000188</t>
+  </si>
+  <si>
+    <t>DEIWID GUINCHO LTDA</t>
+  </si>
+  <si>
+    <t>23580203000108</t>
+  </si>
+  <si>
+    <t>WILLIAM AUGUSTO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>58335486000107</t>
+  </si>
+  <si>
+    <t>EDSON FERREIRA DE PAIVA REPRESENTACAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>25912888000160</t>
+  </si>
+  <si>
+    <t>MAYCON GEOVANY ALVES SOARES</t>
+  </si>
+  <si>
+    <t>59415405000133</t>
+  </si>
+  <si>
+    <t>MANFREDO DE OLIVEIRA PINHEIRO</t>
+  </si>
+  <si>
+    <t>55102544000156</t>
+  </si>
+  <si>
+    <t>55.102.544 CARLOS VINICIUS MENDES SODRE</t>
+  </si>
+  <si>
+    <t>35678616000109</t>
+  </si>
+  <si>
+    <t>WILLIAM A F SINOTTI SERVICOS ADMINISTRATIVOS</t>
+  </si>
+  <si>
+    <t>27924108000127</t>
+  </si>
+  <si>
+    <t>27.924.108 LUCAS FISCHER MAGALHAES</t>
+  </si>
+  <si>
+    <t>45135273000181</t>
+  </si>
+  <si>
+    <t>45.135.273 MIRIAN LUCIA GARCIA MARTELINI</t>
+  </si>
+  <si>
+    <t>62178331000173</t>
+  </si>
+  <si>
+    <t>62.178.331 RAFAEL SZPAK MONTEIRO</t>
+  </si>
+  <si>
+    <t>63113357000104</t>
+  </si>
+  <si>
+    <t>PADARIA E CAFETERIA KIOSKO LUZ SANA LTDA</t>
+  </si>
+  <si>
+    <t>53206609000188</t>
+  </si>
+  <si>
+    <t>B.L. CAMARGO</t>
+  </si>
+  <si>
+    <t>32860704000120</t>
+  </si>
+  <si>
+    <t>ANTONIA G. B. CAMPELO - METALURGICA</t>
+  </si>
+  <si>
+    <t>48709907000150</t>
+  </si>
+  <si>
+    <t>MVM COMERCIO DE EQUIPAMENTOS INDUSTRIAIS LTDA</t>
+  </si>
+  <si>
+    <t>58666757000107</t>
+  </si>
+  <si>
+    <t>CHARLES DE SOUZA REPRESENTACAO COMERCIAL</t>
+  </si>
+  <si>
+    <t>24930638000190</t>
+  </si>
+  <si>
+    <t>EXITTUS ASSESSORIA EM RECURSOS HUMANOS LTDA</t>
+  </si>
+  <si>
+    <t>62556003000163</t>
+  </si>
+  <si>
+    <t>AZZAS AGROPECUARIA GOIAS LTDA</t>
+  </si>
+  <si>
+    <t>19427679000128</t>
+  </si>
+  <si>
+    <t>MAXXIVET SERVICOS EMPRESARIAIS LTDA</t>
+  </si>
+  <si>
+    <t>19686300000366</t>
+  </si>
+  <si>
+    <t>ARTUR DE OLIVEIRA PINTO</t>
+  </si>
+  <si>
+    <t>62429494000181</t>
+  </si>
+  <si>
+    <t>MATHEUS CRUZ EYEWEAR LTDA</t>
+  </si>
+  <si>
+    <t>31156336000171</t>
+  </si>
+  <si>
+    <t>ALESSANDRO BARBOSA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>35531921000165</t>
+  </si>
+  <si>
+    <t>CARLOS LEONEL LISBOA DA SILVA</t>
+  </si>
+  <si>
+    <t>39490431000119</t>
+  </si>
+  <si>
+    <t>MARMORARIA 3R JEOVA JIREH LTDA</t>
+  </si>
+  <si>
+    <t>30729259000139</t>
+  </si>
+  <si>
+    <t>R MOREIRAS MARTINEZ</t>
+  </si>
+  <si>
+    <t>44665976000159</t>
+  </si>
+  <si>
+    <t>GLEIDSON JOHN NASCIMENTO AZEVEDO</t>
+  </si>
+  <si>
+    <t>46373892000177</t>
+  </si>
+  <si>
+    <t>ERICK WILLIAN CARVALHO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>31395860000286</t>
+  </si>
+  <si>
+    <t>P. J. P. DOS SANTOS LTDA</t>
+  </si>
+  <si>
+    <t>24079404000180</t>
+  </si>
+  <si>
+    <t>QUEILA CILENE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>56017133000125</t>
+  </si>
+  <si>
+    <t>KATIUSCIA MARTINS TAROUCO</t>
+  </si>
+  <si>
+    <t>62220663000179</t>
+  </si>
+  <si>
+    <t>EFICAZ INSTALACOES ELETRICAS LTDA</t>
+  </si>
+  <si>
+    <t>58096723000116</t>
+  </si>
+  <si>
+    <t>W C DE OLIVEIRA SERVICOS DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>61875444000165</t>
+  </si>
+  <si>
+    <t>GOODS SALGADOS LTDA</t>
+  </si>
+  <si>
+    <t>28354766000193</t>
+  </si>
+  <si>
+    <t>RENATO MIRANDA TOLENTINO</t>
+  </si>
+  <si>
+    <t>33100931000110</t>
+  </si>
+  <si>
+    <t>33.100.931 EDUARDO PEREIRA ROCHA</t>
+  </si>
+  <si>
+    <t>52349331000135</t>
+  </si>
+  <si>
+    <t>LEIDIANE GOMES POLZIN BASTREGHI SERVICOS ADMINISTRATIVOS LTDA</t>
+  </si>
+  <si>
+    <t>64593267000112</t>
+  </si>
+  <si>
+    <t>ILDEFONSO CARLOS MACHADO JUNIOR CORRETAGEM DE IMOVEIS</t>
+  </si>
+  <si>
+    <t>59087005000146</t>
+  </si>
+  <si>
+    <t>ALEX SANDRO PEREIRA VIANA</t>
+  </si>
+  <si>
+    <t>48049128000176</t>
+  </si>
+  <si>
+    <t>VINICIUS SILVA DE ARAGAO</t>
+  </si>
+  <si>
+    <t>26037243000198</t>
+  </si>
+  <si>
+    <t>MARCELO LEAL XAVIER LTDA</t>
+  </si>
+  <si>
+    <t>57561778000197</t>
+  </si>
+  <si>
+    <t>TAGUA PARQUE VEICULOS LTDA</t>
+  </si>
+  <si>
+    <t>10333871000261</t>
+  </si>
+  <si>
+    <t>MINERACAO CAMPO ALEGRE LTDA</t>
+  </si>
+  <si>
+    <t>33742506000125</t>
+  </si>
+  <si>
+    <t>VOAR CENTRO DE INTEGRACAO E CUIDADOS ESTETICOS LTDA</t>
+  </si>
+  <si>
+    <t>29565996000164</t>
+  </si>
+  <si>
+    <t>ZAAPPY TELECOMUNICACOES LTDA</t>
+  </si>
+  <si>
+    <t>43740009000141</t>
+  </si>
+  <si>
+    <t>JOSE FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>22274720000188</t>
+  </si>
+  <si>
+    <t>ROSELI ALVES BATINGA</t>
+  </si>
+  <si>
+    <t>48704676000192</t>
+  </si>
+  <si>
+    <t>FELIPE RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>46699865000199</t>
+  </si>
+  <si>
+    <t>VIVIANE PEIXOTO DA SILVA PAGANI</t>
+  </si>
+  <si>
+    <t>51127534000114</t>
+  </si>
+  <si>
+    <t>LAURA PALANCA JULIANI</t>
+  </si>
+  <si>
+    <t>54050370000162</t>
+  </si>
+  <si>
+    <t>AL-MIX ENGENHARIA E CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>52241840000140</t>
+  </si>
+  <si>
+    <t>FLASH SERVICOS DE TELECOMUNICACOES E INFORMATICA LTDA</t>
+  </si>
+  <si>
+    <t>48464600000137</t>
+  </si>
+  <si>
+    <t>GILLI PAISAGISMO LTDA</t>
+  </si>
+  <si>
+    <t>45060355000104</t>
+  </si>
+  <si>
+    <t>MS FORTE TRANSPORTE E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>20218687000143</t>
+  </si>
+  <si>
+    <t>LEANDRO DE MORAIS MACHADO ALOJAMENTO</t>
+  </si>
+  <si>
+    <t>40281166000148</t>
+  </si>
+  <si>
+    <t>ARRY TRANSPORTE LTDA</t>
+  </si>
+  <si>
+    <t>61526583000183</t>
+  </si>
+  <si>
+    <t>QUIRINO TINTAS LTDA</t>
+  </si>
+  <si>
+    <t>07155692000196</t>
+  </si>
+  <si>
+    <t>L FERREIRA METALURGICA</t>
+  </si>
+  <si>
+    <t>22849337000100</t>
+  </si>
+  <si>
+    <t>CLEITON ROBERTO BARBOSA DIAS</t>
+  </si>
+  <si>
+    <t>37465552000185</t>
+  </si>
+  <si>
+    <t>IVO DIAS DE FREITAS</t>
+  </si>
+  <si>
+    <t>19842945000189</t>
+  </si>
+  <si>
+    <t>GAMARRA ESPORTES E LAZER LTDA</t>
+  </si>
+  <si>
+    <t>47218072000173</t>
+  </si>
+  <si>
+    <t>GERSON EMMANUEL RODRIGUES DOS SANTOS LTDA</t>
+  </si>
+  <si>
+    <t>34752175000177</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA TRANSLAUBE LTDA</t>
+  </si>
+  <si>
+    <t>27629926000105</t>
+  </si>
+  <si>
+    <t>GM CONSULTORIO MEDICO E LABORATORIO LTDA</t>
+  </si>
+  <si>
+    <t>10775735000140</t>
+  </si>
+  <si>
+    <t>V. E. A. SIQUEIRA REPRESENTACOES COMERCIAIS</t>
+  </si>
+  <si>
+    <t>21793606000100</t>
+  </si>
+  <si>
+    <t>MARIA VILANI ARAUJO DA SILVA</t>
+  </si>
+  <si>
+    <t>17147450000104</t>
+  </si>
+  <si>
+    <t>LEONARDO SILVA SOUSA</t>
+  </si>
+  <si>
+    <t>18290226000130</t>
+  </si>
+  <si>
+    <t>DIONATAN WEBER DA ROCHA</t>
+  </si>
+  <si>
+    <t>57722657000180</t>
+  </si>
+  <si>
+    <t>VB REPRESENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>23741927000188</t>
+  </si>
+  <si>
+    <t>A. LUIZ CEDRAZ SILVA</t>
+  </si>
+  <si>
+    <t>34639632000111</t>
+  </si>
+  <si>
+    <t>PAULO SERGIO F SOUZA</t>
+  </si>
+  <si>
+    <t>62298855000106</t>
+  </si>
+  <si>
+    <t>ARQUIVAL PROJETOS LTDA</t>
+  </si>
+  <si>
+    <t>29989726000261</t>
+  </si>
+  <si>
+    <t>FABIO DAROS SERVICO DE HOSPEDAGEM LTDA</t>
+  </si>
+  <si>
+    <t>03472716000180</t>
+  </si>
+  <si>
+    <t>AMARELINHO INDUSTRIA E COMERCIO DE DOCES LTDA</t>
+  </si>
+  <si>
+    <t>53676314000175</t>
+  </si>
+  <si>
+    <t>53.676.314 ELENALDO DOS SANTOS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>32563161000180</t>
+  </si>
+  <si>
+    <t>RODRIGO AMADEU LORENCAO - SITIO SANTA ANGELA</t>
+  </si>
+  <si>
+    <t>61814595000103</t>
+  </si>
+  <si>
+    <t>F J OLIVEIRA REPRESENTACOES COMERCIAIS LTDA</t>
+  </si>
+  <si>
+    <t>59164065000115</t>
+  </si>
+  <si>
+    <t>NET FIBRA LTDA</t>
+  </si>
+  <si>
+    <t>04472920000163</t>
+  </si>
+  <si>
+    <t>BIG TOLDOS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>64288713000185</t>
+  </si>
+  <si>
+    <t>CONSTRUTORA E PRESTADORA DE SERVICO VIEIRA LTDA</t>
+  </si>
+  <si>
+    <t>23108063000161</t>
+  </si>
+  <si>
+    <t>ALINE MELLO - SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
+    <t>59207865000176</t>
+  </si>
+  <si>
+    <t>INSTITUTO AMAURY JUNIOR</t>
+  </si>
+  <si>
+    <t>46713659000196</t>
+  </si>
+  <si>
+    <t>WEIGERT E ROSSI TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>51789866000164</t>
+  </si>
+  <si>
+    <t>G THOMAZ CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>BONFIM EXPRESS LTDA</t>
+  </si>
+  <si>
+    <t>AVENIDA COMERCIO DE METAIS LTDA</t>
+  </si>
+  <si>
+    <t>PIT STOP CONVENIENCIA LTDA</t>
+  </si>
+  <si>
+    <t>NOSSA PIPA CONFEITARIA LTDA</t>
+  </si>
+  <si>
+    <t>A procuracao precisa delegar poderes perante o Banco C6 ou perante qualquer instituicao financeira.</t>
+  </si>
+  <si>
+    <t>38135571000297</t>
+  </si>
+  <si>
+    <t>30039899000117</t>
+  </si>
+  <si>
+    <t>62240077000196</t>
+  </si>
+  <si>
+    <t>29568546000125</t>
   </si>
 </sst>
 </file>
@@ -3327,7 +4314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A45A88-3D17-4433-986A-11075963C36F}">
-  <dimension ref="A1:H459"/>
+  <dimension ref="A1:H624"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -3413,7 +4400,7 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
-        <v>232</v>
+        <v>403</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3465,10 +4452,10 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>518</v>
       </c>
       <c r="H5" t="s">
-        <v>691</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3546,7 +4533,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3572,7 +4559,7 @@
         <v>518</v>
       </c>
       <c r="H9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3806,7 +4793,7 @@
         <v>518</v>
       </c>
       <c r="H18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -5158,7 +6145,7 @@
         <v>518</v>
       </c>
       <c r="H70" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -8214,7 +9201,7 @@
         <v>518</v>
       </c>
       <c r="H188" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -9248,7 +10235,7 @@
         <v>7</v>
       </c>
       <c r="G228" t="s">
-        <v>232</v>
+        <v>403</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -10311,10 +11298,10 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>518</v>
+        <v>20</v>
       </c>
       <c r="H269" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
@@ -11692,7 +12679,7 @@
         <v>518</v>
       </c>
       <c r="H322" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
@@ -11726,10 +12713,10 @@
         <v>46121</v>
       </c>
       <c r="B324" t="s">
+        <v>694</v>
+      </c>
+      <c r="C324" t="s">
         <v>695</v>
-      </c>
-      <c r="C324" t="s">
-        <v>696</v>
       </c>
       <c r="D324" t="s">
         <v>12</v>
@@ -11752,10 +12739,10 @@
         <v>46121</v>
       </c>
       <c r="B325" t="s">
+        <v>696</v>
+      </c>
+      <c r="C325" t="s">
         <v>697</v>
-      </c>
-      <c r="C325" t="s">
-        <v>698</v>
       </c>
       <c r="D325" t="s">
         <v>12</v>
@@ -11778,10 +12765,10 @@
         <v>46121</v>
       </c>
       <c r="B326" t="s">
+        <v>698</v>
+      </c>
+      <c r="C326" t="s">
         <v>699</v>
-      </c>
-      <c r="C326" t="s">
-        <v>700</v>
       </c>
       <c r="D326" t="s">
         <v>12</v>
@@ -11804,10 +12791,10 @@
         <v>46121</v>
       </c>
       <c r="B327" t="s">
+        <v>700</v>
+      </c>
+      <c r="C327" t="s">
         <v>701</v>
-      </c>
-      <c r="C327" t="s">
-        <v>702</v>
       </c>
       <c r="D327" t="s">
         <v>27</v>
@@ -11830,10 +12817,10 @@
         <v>46121</v>
       </c>
       <c r="B328" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328" t="s">
         <v>703</v>
-      </c>
-      <c r="C328" t="s">
-        <v>704</v>
       </c>
       <c r="D328" t="s">
         <v>22</v>
@@ -11845,7 +12832,7 @@
         <v>7</v>
       </c>
       <c r="G328" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -11856,10 +12843,10 @@
         <v>46121</v>
       </c>
       <c r="B329" t="s">
+        <v>704</v>
+      </c>
+      <c r="C329" t="s">
         <v>705</v>
-      </c>
-      <c r="C329" t="s">
-        <v>706</v>
       </c>
       <c r="D329" t="s">
         <v>30</v>
@@ -11882,10 +12869,10 @@
         <v>46121</v>
       </c>
       <c r="B330" t="s">
+        <v>706</v>
+      </c>
+      <c r="C330" t="s">
         <v>707</v>
-      </c>
-      <c r="C330" t="s">
-        <v>708</v>
       </c>
       <c r="D330" t="s">
         <v>14</v>
@@ -11908,10 +12895,10 @@
         <v>46121</v>
       </c>
       <c r="B331" t="s">
+        <v>708</v>
+      </c>
+      <c r="C331" t="s">
         <v>709</v>
-      </c>
-      <c r="C331" t="s">
-        <v>710</v>
       </c>
       <c r="D331" t="s">
         <v>30</v>
@@ -11934,10 +12921,10 @@
         <v>46121</v>
       </c>
       <c r="B332" t="s">
+        <v>710</v>
+      </c>
+      <c r="C332" t="s">
         <v>711</v>
-      </c>
-      <c r="C332" t="s">
-        <v>712</v>
       </c>
       <c r="D332" t="s">
         <v>16</v>
@@ -11960,10 +12947,10 @@
         <v>46121</v>
       </c>
       <c r="B333" t="s">
+        <v>712</v>
+      </c>
+      <c r="C333" t="s">
         <v>713</v>
-      </c>
-      <c r="C333" t="s">
-        <v>714</v>
       </c>
       <c r="D333" t="s">
         <v>23</v>
@@ -11986,10 +12973,10 @@
         <v>46121</v>
       </c>
       <c r="B334" t="s">
+        <v>714</v>
+      </c>
+      <c r="C334" t="s">
         <v>715</v>
-      </c>
-      <c r="C334" t="s">
-        <v>716</v>
       </c>
       <c r="D334" t="s">
         <v>11</v>
@@ -12012,10 +12999,10 @@
         <v>46121</v>
       </c>
       <c r="B335" t="s">
+        <v>716</v>
+      </c>
+      <c r="C335" t="s">
         <v>717</v>
-      </c>
-      <c r="C335" t="s">
-        <v>718</v>
       </c>
       <c r="D335" t="s">
         <v>39</v>
@@ -12038,10 +13025,10 @@
         <v>46121</v>
       </c>
       <c r="B336" t="s">
+        <v>718</v>
+      </c>
+      <c r="C336" t="s">
         <v>719</v>
-      </c>
-      <c r="C336" t="s">
-        <v>720</v>
       </c>
       <c r="D336" t="s">
         <v>28</v>
@@ -12064,10 +13051,10 @@
         <v>46121</v>
       </c>
       <c r="B337" t="s">
+        <v>720</v>
+      </c>
+      <c r="C337" t="s">
         <v>721</v>
-      </c>
-      <c r="C337" t="s">
-        <v>722</v>
       </c>
       <c r="D337" t="s">
         <v>15</v>
@@ -12090,10 +13077,10 @@
         <v>46121</v>
       </c>
       <c r="B338" t="s">
+        <v>722</v>
+      </c>
+      <c r="C338" t="s">
         <v>723</v>
-      </c>
-      <c r="C338" t="s">
-        <v>724</v>
       </c>
       <c r="D338" t="s">
         <v>14</v>
@@ -12116,10 +13103,10 @@
         <v>46121</v>
       </c>
       <c r="B339" t="s">
+        <v>724</v>
+      </c>
+      <c r="C339" t="s">
         <v>725</v>
-      </c>
-      <c r="C339" t="s">
-        <v>726</v>
       </c>
       <c r="D339" t="s">
         <v>28</v>
@@ -12142,10 +13129,10 @@
         <v>46121</v>
       </c>
       <c r="B340" t="s">
+        <v>726</v>
+      </c>
+      <c r="C340" t="s">
         <v>727</v>
-      </c>
-      <c r="C340" t="s">
-        <v>728</v>
       </c>
       <c r="D340" t="s">
         <v>11</v>
@@ -12168,10 +13155,10 @@
         <v>46121</v>
       </c>
       <c r="B341" t="s">
+        <v>728</v>
+      </c>
+      <c r="C341" t="s">
         <v>729</v>
-      </c>
-      <c r="C341" t="s">
-        <v>730</v>
       </c>
       <c r="D341" t="s">
         <v>23</v>
@@ -12194,10 +13181,10 @@
         <v>46121</v>
       </c>
       <c r="B342" t="s">
+        <v>730</v>
+      </c>
+      <c r="C342" t="s">
         <v>731</v>
-      </c>
-      <c r="C342" t="s">
-        <v>732</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
@@ -12220,10 +13207,10 @@
         <v>46121</v>
       </c>
       <c r="B343" t="s">
+        <v>732</v>
+      </c>
+      <c r="C343" t="s">
         <v>733</v>
-      </c>
-      <c r="C343" t="s">
-        <v>734</v>
       </c>
       <c r="D343" t="s">
         <v>19</v>
@@ -12246,10 +13233,10 @@
         <v>46121</v>
       </c>
       <c r="B344" t="s">
+        <v>734</v>
+      </c>
+      <c r="C344" t="s">
         <v>735</v>
-      </c>
-      <c r="C344" t="s">
-        <v>736</v>
       </c>
       <c r="D344" t="s">
         <v>15</v>
@@ -12272,10 +13259,10 @@
         <v>46121</v>
       </c>
       <c r="B345" t="s">
+        <v>736</v>
+      </c>
+      <c r="C345" t="s">
         <v>737</v>
-      </c>
-      <c r="C345" t="s">
-        <v>738</v>
       </c>
       <c r="D345" t="s">
         <v>28</v>
@@ -12298,10 +13285,10 @@
         <v>46121</v>
       </c>
       <c r="B346" t="s">
+        <v>738</v>
+      </c>
+      <c r="C346" t="s">
         <v>739</v>
-      </c>
-      <c r="C346" t="s">
-        <v>740</v>
       </c>
       <c r="D346" t="s">
         <v>24</v>
@@ -12324,10 +13311,10 @@
         <v>46121</v>
       </c>
       <c r="B347" t="s">
+        <v>740</v>
+      </c>
+      <c r="C347" t="s">
         <v>741</v>
-      </c>
-      <c r="C347" t="s">
-        <v>742</v>
       </c>
       <c r="D347" t="s">
         <v>11</v>
@@ -12350,10 +13337,10 @@
         <v>46121</v>
       </c>
       <c r="B348" t="s">
+        <v>742</v>
+      </c>
+      <c r="C348" t="s">
         <v>743</v>
-      </c>
-      <c r="C348" t="s">
-        <v>744</v>
       </c>
       <c r="D348" t="s">
         <v>9</v>
@@ -12376,10 +13363,10 @@
         <v>46121</v>
       </c>
       <c r="B349" t="s">
+        <v>744</v>
+      </c>
+      <c r="C349" t="s">
         <v>745</v>
-      </c>
-      <c r="C349" t="s">
-        <v>746</v>
       </c>
       <c r="D349" t="s">
         <v>12</v>
@@ -12402,10 +13389,10 @@
         <v>46121</v>
       </c>
       <c r="B350" t="s">
+        <v>746</v>
+      </c>
+      <c r="C350" t="s">
         <v>747</v>
-      </c>
-      <c r="C350" t="s">
-        <v>748</v>
       </c>
       <c r="D350" t="s">
         <v>19</v>
@@ -12428,10 +13415,10 @@
         <v>46121</v>
       </c>
       <c r="B351" t="s">
+        <v>748</v>
+      </c>
+      <c r="C351" t="s">
         <v>749</v>
-      </c>
-      <c r="C351" t="s">
-        <v>750</v>
       </c>
       <c r="D351" t="s">
         <v>40</v>
@@ -12446,7 +13433,7 @@
         <v>20</v>
       </c>
       <c r="H351" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
@@ -12454,10 +13441,10 @@
         <v>46121</v>
       </c>
       <c r="B352" t="s">
+        <v>750</v>
+      </c>
+      <c r="C352" t="s">
         <v>751</v>
-      </c>
-      <c r="C352" t="s">
-        <v>752</v>
       </c>
       <c r="D352" t="s">
         <v>39</v>
@@ -12480,10 +13467,10 @@
         <v>46121</v>
       </c>
       <c r="B353" t="s">
+        <v>752</v>
+      </c>
+      <c r="C353" t="s">
         <v>753</v>
-      </c>
-      <c r="C353" t="s">
-        <v>754</v>
       </c>
       <c r="D353" t="s">
         <v>6</v>
@@ -12506,10 +13493,10 @@
         <v>46121</v>
       </c>
       <c r="B354" t="s">
+        <v>754</v>
+      </c>
+      <c r="C354" t="s">
         <v>755</v>
-      </c>
-      <c r="C354" t="s">
-        <v>756</v>
       </c>
       <c r="D354" t="s">
         <v>28</v>
@@ -12532,10 +13519,10 @@
         <v>46121</v>
       </c>
       <c r="B355" t="s">
+        <v>756</v>
+      </c>
+      <c r="C355" t="s">
         <v>757</v>
-      </c>
-      <c r="C355" t="s">
-        <v>758</v>
       </c>
       <c r="D355" t="s">
         <v>30</v>
@@ -12558,10 +13545,10 @@
         <v>46121</v>
       </c>
       <c r="B356" t="s">
+        <v>758</v>
+      </c>
+      <c r="C356" t="s">
         <v>759</v>
-      </c>
-      <c r="C356" t="s">
-        <v>760</v>
       </c>
       <c r="D356" t="s">
         <v>30</v>
@@ -12584,22 +13571,22 @@
         <v>46121</v>
       </c>
       <c r="B357" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C357" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D357" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E357" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F357" t="s">
-        <v>763</v>
+        <v>8</v>
       </c>
       <c r="G357" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -12610,22 +13597,22 @@
         <v>46121</v>
       </c>
       <c r="B358" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C358" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D358" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E358" t="s">
         <v>36</v>
       </c>
       <c r="F358" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G358" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -12636,19 +13623,19 @@
         <v>46121</v>
       </c>
       <c r="B359" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C359" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D359" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>36</v>
       </c>
       <c r="F359" t="s">
-        <v>7</v>
+        <v>762</v>
       </c>
       <c r="G359" t="s">
         <v>21</v>
@@ -12662,22 +13649,22 @@
         <v>46121</v>
       </c>
       <c r="B360" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C360" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D360" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E360" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F360" t="s">
-        <v>763</v>
+        <v>8</v>
       </c>
       <c r="G360" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H360">
         <v>0</v>
@@ -12688,16 +13675,16 @@
         <v>46121</v>
       </c>
       <c r="B361" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C361" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D361" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E361" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F361" t="s">
         <v>8</v>
@@ -12714,13 +13701,13 @@
         <v>46121</v>
       </c>
       <c r="B362" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C362" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D362" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E362" t="s">
         <v>36</v>
@@ -12740,22 +13727,22 @@
         <v>46121</v>
       </c>
       <c r="B363" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C363" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D363" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E363" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F363" t="s">
-        <v>8</v>
+        <v>762</v>
       </c>
       <c r="G363" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -12766,22 +13753,22 @@
         <v>46121</v>
       </c>
       <c r="B364" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C364" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D364" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E364" t="s">
         <v>38</v>
       </c>
       <c r="F364" t="s">
-        <v>763</v>
+        <v>8</v>
       </c>
       <c r="G364" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H364">
         <v>0</v>
@@ -12792,16 +13779,16 @@
         <v>46121</v>
       </c>
       <c r="B365" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C365" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D365" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E365" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F365" t="s">
         <v>8</v>
@@ -12818,13 +13805,13 @@
         <v>46121</v>
       </c>
       <c r="B366" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C366" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D366" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E366" t="s">
         <v>36</v>
@@ -12844,13 +13831,13 @@
         <v>46121</v>
       </c>
       <c r="B367" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C367" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D367" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E367" t="s">
         <v>36</v>
@@ -12870,22 +13857,22 @@
         <v>46121</v>
       </c>
       <c r="B368" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C368" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D368" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E368" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F368" t="s">
         <v>8</v>
       </c>
       <c r="G368" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -12896,22 +13883,22 @@
         <v>46121</v>
       </c>
       <c r="B369" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C369" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D369" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F369" t="s">
         <v>8</v>
       </c>
       <c r="G369" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -12922,22 +13909,22 @@
         <v>46121</v>
       </c>
       <c r="B370" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C370" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D370" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E370" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F370" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G370" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -12948,19 +13935,19 @@
         <v>46121</v>
       </c>
       <c r="B371" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C371" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D371" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E371" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F371" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G371" t="s">
         <v>21</v>
@@ -12974,22 +13961,22 @@
         <v>46121</v>
       </c>
       <c r="B372" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C372" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D372" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E372" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F372" t="s">
         <v>8</v>
       </c>
       <c r="G372" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -13000,16 +13987,16 @@
         <v>46121</v>
       </c>
       <c r="B373" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C373" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D373" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E373" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F373" t="s">
         <v>8</v>
@@ -13026,13 +14013,13 @@
         <v>46121</v>
       </c>
       <c r="B374" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C374" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D374" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E374" t="s">
         <v>36</v>
@@ -13052,10 +14039,10 @@
         <v>46121</v>
       </c>
       <c r="B375" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C375" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D375" t="s">
         <v>16</v>
@@ -13078,10 +14065,10 @@
         <v>46121</v>
       </c>
       <c r="B376" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C376" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D376" t="s">
         <v>16</v>
@@ -13104,13 +14091,13 @@
         <v>46121</v>
       </c>
       <c r="B377" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C377" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D377" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E377" t="s">
         <v>36</v>
@@ -13130,13 +14117,13 @@
         <v>46121</v>
       </c>
       <c r="B378" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C378" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D378" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E378" t="s">
         <v>36</v>
@@ -13156,13 +14143,13 @@
         <v>46121</v>
       </c>
       <c r="B379" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C379" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D379" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E379" t="s">
         <v>38</v>
@@ -13171,7 +14158,7 @@
         <v>8</v>
       </c>
       <c r="G379" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -13182,13 +14169,13 @@
         <v>46121</v>
       </c>
       <c r="B380" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C380" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D380" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E380" t="s">
         <v>36</v>
@@ -13208,16 +14195,16 @@
         <v>46121</v>
       </c>
       <c r="B381" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C381" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D381" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="E381" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F381" t="s">
         <v>8</v>
@@ -13234,13 +14221,13 @@
         <v>46121</v>
       </c>
       <c r="B382" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C382" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D382" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E382" t="s">
         <v>36</v>
@@ -13249,7 +14236,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H382">
         <v>0</v>
@@ -13260,13 +14247,13 @@
         <v>46121</v>
       </c>
       <c r="B383" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C383" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D383" t="s">
-        <v>261</v>
+        <v>11</v>
       </c>
       <c r="E383" t="s">
         <v>36</v>
@@ -13275,7 +14262,7 @@
         <v>8</v>
       </c>
       <c r="G383" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H383">
         <v>0</v>
@@ -13283,25 +14270,25 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B384" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="C384" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D384" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E384" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F384" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="G384" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H384">
         <v>0</v>
@@ -13309,16 +14296,16 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B385" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C385" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="D385" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E385" t="s">
         <v>36</v>
@@ -13338,19 +14325,19 @@
         <v>46122</v>
       </c>
       <c r="B386" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C386" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D386" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E386" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F386" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="G386" t="s">
         <v>18</v>
@@ -13364,19 +14351,19 @@
         <v>46122</v>
       </c>
       <c r="B387" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C387" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D387" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E387" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F387" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G387" t="s">
         <v>18</v>
@@ -13390,19 +14377,19 @@
         <v>46122</v>
       </c>
       <c r="B388" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C388" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D388" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F388" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G388" t="s">
         <v>18</v>
@@ -13416,19 +14403,19 @@
         <v>46122</v>
       </c>
       <c r="B389" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C389" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D389" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E389" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F389" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G389" t="s">
         <v>18</v>
@@ -13442,19 +14429,19 @@
         <v>46122</v>
       </c>
       <c r="B390" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C390" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D390" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E390" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F390" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="G390" t="s">
         <v>18</v>
@@ -13468,19 +14455,19 @@
         <v>46122</v>
       </c>
       <c r="B391" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C391" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D391" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E391" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F391" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="G391" t="s">
         <v>18</v>
@@ -13494,10 +14481,10 @@
         <v>46122</v>
       </c>
       <c r="B392" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C392" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D392" t="s">
         <v>27</v>
@@ -13510,6 +14497,9 @@
       </c>
       <c r="G392" t="s">
         <v>18</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
@@ -13517,10 +14507,10 @@
         <v>46122</v>
       </c>
       <c r="B393" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C393" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D393" t="s">
         <v>27</v>
@@ -13533,6 +14523,9 @@
       </c>
       <c r="G393" t="s">
         <v>18</v>
+      </c>
+      <c r="H393">
+        <v>0</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
@@ -13540,10 +14533,10 @@
         <v>46122</v>
       </c>
       <c r="B394" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C394" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D394" t="s">
         <v>27</v>
@@ -13556,6 +14549,9 @@
       </c>
       <c r="G394" t="s">
         <v>18</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -13563,22 +14559,25 @@
         <v>46122</v>
       </c>
       <c r="B395" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C395" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D395" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E395" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F395" t="s">
-        <v>242</v>
+        <v>8</v>
       </c>
       <c r="G395" t="s">
         <v>18</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
@@ -13586,22 +14585,25 @@
         <v>46122</v>
       </c>
       <c r="B396" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C396" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D396" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E396" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F396" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="G396" t="s">
-        <v>18</v>
+        <v>232</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
@@ -13609,22 +14611,25 @@
         <v>46122</v>
       </c>
       <c r="B397" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C397" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D397" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E397" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F397" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G397" t="s">
-        <v>18</v>
+        <v>232</v>
+      </c>
+      <c r="H397">
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
@@ -13632,22 +14637,25 @@
         <v>46122</v>
       </c>
       <c r="B398" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C398" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D398" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E398" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F398" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G398" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
@@ -13655,22 +14663,25 @@
         <v>46122</v>
       </c>
       <c r="B399" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C399" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D399" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E399" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F399" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G399" t="s">
         <v>18</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
@@ -13678,79 +14689,88 @@
         <v>46122</v>
       </c>
       <c r="B400" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C400" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D400" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E400" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F400" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G400" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>46122</v>
       </c>
       <c r="B401" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C401" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D401" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E401" t="s">
         <v>36</v>
       </c>
       <c r="F401" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G401" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>46122</v>
       </c>
       <c r="B402" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C402" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D402" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E402" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F402" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G402" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>46122</v>
       </c>
       <c r="B403" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C403" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D403" t="s">
         <v>14</v>
@@ -13759,24 +14779,27 @@
         <v>36</v>
       </c>
       <c r="F403" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G403" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>46122</v>
       </c>
       <c r="B404" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C404" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D404" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E404" t="s">
         <v>36</v>
@@ -13787,42 +14810,48 @@
       <c r="G404" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>46122</v>
       </c>
       <c r="B405" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C405" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D405" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E405" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F405" t="s">
-        <v>8</v>
+        <v>866</v>
       </c>
       <c r="G405" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>46122</v>
       </c>
       <c r="B406" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C406" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D406" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E406" t="s">
         <v>36</v>
@@ -13833,134 +14862,152 @@
       <c r="G406" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>46122</v>
       </c>
       <c r="B407" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C407" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D407" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E407" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F407" t="s">
-        <v>867</v>
+        <v>8</v>
       </c>
       <c r="G407" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>46122</v>
       </c>
       <c r="B408" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C408" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D408" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E408" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F408" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G408" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>46122</v>
       </c>
       <c r="B409" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C409" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D409" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E409" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F409" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G409" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>46122</v>
       </c>
       <c r="B410" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C410" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D410" t="s">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c r="E410" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F410" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G410" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>46122</v>
       </c>
       <c r="B411" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C411" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D411" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E411" t="s">
         <v>38</v>
       </c>
       <c r="F411" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G411" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="H411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>46122</v>
       </c>
       <c r="B412" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C412" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D412" t="s">
-        <v>261</v>
+        <v>11</v>
       </c>
       <c r="E412" t="s">
         <v>36</v>
@@ -13971,45 +15018,51 @@
       <c r="G412" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>46122</v>
       </c>
       <c r="B413" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C413" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D413" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E413" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F413" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G413" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>46122</v>
       </c>
       <c r="B414" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C414" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D414" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E414" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F414" t="s">
         <v>8</v>
@@ -14017,19 +15070,22 @@
       <c r="G414" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>46122</v>
       </c>
       <c r="B415" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C415" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D415" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E415" t="s">
         <v>36</v>
@@ -14040,22 +15096,25 @@
       <c r="G415" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>46122</v>
       </c>
       <c r="B416" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C416" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D416" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E416" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F416" t="s">
         <v>8</v>
@@ -14063,19 +15122,22 @@
       <c r="G416" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>46122</v>
       </c>
       <c r="B417" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C417" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D417" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E417" t="s">
         <v>36</v>
@@ -14086,42 +15148,48 @@
       <c r="G417" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>46122</v>
       </c>
       <c r="B418" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C418" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D418" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E418" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F418" t="s">
         <v>8</v>
       </c>
       <c r="G418" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>46122</v>
       </c>
       <c r="B419" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C419" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D419" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E419" t="s">
         <v>36</v>
@@ -14132,22 +15200,25 @@
       <c r="G419" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>46122</v>
       </c>
       <c r="B420" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C420" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D420" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E420" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F420" t="s">
         <v>8</v>
@@ -14155,19 +15226,22 @@
       <c r="G420" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>46122</v>
       </c>
       <c r="B421" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C421" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D421" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="E421" t="s">
         <v>36</v>
@@ -14178,19 +15252,22 @@
       <c r="G421" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>46122</v>
       </c>
       <c r="B422" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C422" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D422" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E422" t="s">
         <v>36</v>
@@ -14199,24 +15276,27 @@
         <v>8</v>
       </c>
       <c r="G422" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>46122</v>
       </c>
       <c r="B423" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C423" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D423" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="E423" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F423" t="s">
         <v>8</v>
@@ -14224,16 +15304,19 @@
       <c r="G423" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>46122</v>
       </c>
       <c r="B424" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C424" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D424" t="s">
         <v>14</v>
@@ -14245,44 +15328,50 @@
         <v>8</v>
       </c>
       <c r="G424" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H424" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>46122</v>
       </c>
       <c r="B425" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C425" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D425" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E425" t="s">
         <v>38</v>
       </c>
       <c r="F425" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G425" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="H425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>46122</v>
       </c>
       <c r="B426" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C426" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D426" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E426" t="s">
         <v>36</v>
@@ -14291,67 +15380,76 @@
         <v>8</v>
       </c>
       <c r="G426" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>46122</v>
       </c>
       <c r="B427" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C427" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D427" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E427" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F427" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G427" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>46122</v>
       </c>
       <c r="B428" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C428" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D428" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E428" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F428" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G428" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>46122</v>
       </c>
       <c r="B429" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C429" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D429" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E429" t="s">
         <v>36</v>
@@ -14360,44 +15458,50 @@
         <v>8</v>
       </c>
       <c r="G429" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>46122</v>
       </c>
       <c r="B430" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C430" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D430" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E430" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F430" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G430" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>46122</v>
       </c>
       <c r="B431" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C431" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D431" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E431" t="s">
         <v>36</v>
@@ -14408,19 +15512,22 @@
       <c r="G431" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <v>46122</v>
       </c>
       <c r="B432" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C432" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D432" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E432" t="s">
         <v>36</v>
@@ -14431,19 +15538,22 @@
       <c r="G432" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <v>46122</v>
       </c>
       <c r="B433" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C433" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D433" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E433" t="s">
         <v>36</v>
@@ -14454,134 +15564,152 @@
       <c r="G433" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <v>46122</v>
       </c>
       <c r="B434" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C434" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D434" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E434" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F434" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G434" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <v>46122</v>
       </c>
       <c r="B435" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C435" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D435" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E435" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F435" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G435" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>46122</v>
       </c>
       <c r="B436" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C436" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D436" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F436" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G436" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H436" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>46122</v>
       </c>
       <c r="B437" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C437" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D437" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E437" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F437" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G437" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>46122</v>
       </c>
       <c r="B438" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C438" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D438" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E438" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F438" t="s">
         <v>8</v>
       </c>
       <c r="G438" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="H438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>46122</v>
       </c>
       <c r="B439" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C439" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D439" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E439" t="s">
         <v>36</v>
@@ -14590,44 +15718,50 @@
         <v>8</v>
       </c>
       <c r="G439" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>46122</v>
       </c>
       <c r="B440" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C440" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D440" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E440" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F440" t="s">
         <v>8</v>
       </c>
       <c r="G440" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>46122</v>
       </c>
       <c r="B441" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C441" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D441" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E441" t="s">
         <v>36</v>
@@ -14636,21 +15770,24 @@
         <v>8</v>
       </c>
       <c r="G441" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>46122</v>
       </c>
       <c r="B442" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C442" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E442" t="s">
         <v>36</v>
@@ -14661,88 +15798,100 @@
       <c r="G442" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>46122</v>
       </c>
       <c r="B443" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C443" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D443" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E443" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F443" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G443" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>46122</v>
       </c>
       <c r="B444" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C444" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D444" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E444" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F444" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G444" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <v>46122</v>
       </c>
       <c r="B445" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C445" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D445" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E445" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F445" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G445" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>46122</v>
       </c>
       <c r="B446" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C446" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D446" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E446" t="s">
         <v>38</v>
@@ -14753,19 +15902,22 @@
       <c r="G446" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>46122</v>
       </c>
       <c r="B447" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C447" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D447" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E447" t="s">
         <v>36</v>
@@ -14776,42 +15928,48 @@
       <c r="G447" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>46122</v>
       </c>
       <c r="B448" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C448" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D448" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E448" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F448" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G448" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>46122</v>
       </c>
       <c r="B449" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C449" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D449" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E449" t="s">
         <v>36</v>
@@ -14820,44 +15978,50 @@
         <v>8</v>
       </c>
       <c r="G449" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="H449" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>46122</v>
       </c>
       <c r="B450" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C450" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D450" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E450" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F450" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G450" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>46122</v>
       </c>
       <c r="B451" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C451" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D451" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E451" t="s">
         <v>36</v>
@@ -14866,44 +16030,50 @@
         <v>8</v>
       </c>
       <c r="G451" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="H451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>46122</v>
       </c>
       <c r="B452" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C452" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D452" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E452" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F452" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G452" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>46122</v>
       </c>
       <c r="B453" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C453" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D453" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E453" t="s">
         <v>36</v>
@@ -14912,21 +16082,24 @@
         <v>8</v>
       </c>
       <c r="G453" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="H453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>46122</v>
       </c>
       <c r="B454" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C454" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D454" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E454" t="s">
         <v>36</v>
@@ -14937,19 +16110,22 @@
       <c r="G454" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>46122</v>
       </c>
       <c r="B455" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C455" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D455" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E455" t="s">
         <v>36</v>
@@ -14958,21 +16134,21 @@
         <v>8</v>
       </c>
       <c r="G455" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>46122</v>
       </c>
       <c r="B456" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C456" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D456" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E456" t="s">
         <v>36</v>
@@ -14981,75 +16157,4098 @@
         <v>8</v>
       </c>
       <c r="G456" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="H456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>46122</v>
       </c>
       <c r="B457" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C457" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D457" t="s">
+        <v>25</v>
+      </c>
+      <c r="E457" t="s">
+        <v>38</v>
+      </c>
+      <c r="F457" t="s">
+        <v>8</v>
+      </c>
+      <c r="G457" t="s">
+        <v>20</v>
+      </c>
+      <c r="H457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B458" t="s">
+        <v>971</v>
+      </c>
+      <c r="C458" t="s">
+        <v>972</v>
+      </c>
+      <c r="D458" t="s">
+        <v>23</v>
+      </c>
+      <c r="E458" t="s">
+        <v>36</v>
+      </c>
+      <c r="F458" t="s">
+        <v>8</v>
+      </c>
+      <c r="G458" t="s">
+        <v>18</v>
+      </c>
+      <c r="H458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B459" t="s">
+        <v>973</v>
+      </c>
+      <c r="C459" t="s">
+        <v>974</v>
+      </c>
+      <c r="D459" t="s">
+        <v>15</v>
+      </c>
+      <c r="E459" t="s">
+        <v>36</v>
+      </c>
+      <c r="F459" t="s">
+        <v>8</v>
+      </c>
+      <c r="G459" t="s">
+        <v>18</v>
+      </c>
+      <c r="H459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B460" t="s">
+        <v>975</v>
+      </c>
+      <c r="C460" t="s">
+        <v>976</v>
+      </c>
+      <c r="D460" t="s">
+        <v>11</v>
+      </c>
+      <c r="E460" t="s">
+        <v>36</v>
+      </c>
+      <c r="F460" t="s">
+        <v>8</v>
+      </c>
+      <c r="G460" t="s">
+        <v>18</v>
+      </c>
+      <c r="H460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A461" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B461" t="s">
+        <v>977</v>
+      </c>
+      <c r="C461" t="s">
+        <v>978</v>
+      </c>
+      <c r="D461" t="s">
+        <v>16</v>
+      </c>
+      <c r="E461" t="s">
+        <v>36</v>
+      </c>
+      <c r="F461" t="s">
+        <v>8</v>
+      </c>
+      <c r="G461" t="s">
+        <v>18</v>
+      </c>
+      <c r="H461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A462" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B462" t="s">
+        <v>979</v>
+      </c>
+      <c r="C462" t="s">
+        <v>980</v>
+      </c>
+      <c r="D462" t="s">
+        <v>11</v>
+      </c>
+      <c r="E462" t="s">
+        <v>36</v>
+      </c>
+      <c r="F462" t="s">
+        <v>8</v>
+      </c>
+      <c r="G462" t="s">
+        <v>18</v>
+      </c>
+      <c r="H462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A463" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B463" t="s">
+        <v>981</v>
+      </c>
+      <c r="C463" t="s">
+        <v>982</v>
+      </c>
+      <c r="D463" t="s">
+        <v>16</v>
+      </c>
+      <c r="E463" t="s">
+        <v>36</v>
+      </c>
+      <c r="F463" t="s">
+        <v>8</v>
+      </c>
+      <c r="G463" t="s">
+        <v>18</v>
+      </c>
+      <c r="H463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A464" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B464" t="s">
+        <v>983</v>
+      </c>
+      <c r="C464" t="s">
+        <v>984</v>
+      </c>
+      <c r="D464" t="s">
+        <v>16</v>
+      </c>
+      <c r="E464" t="s">
+        <v>36</v>
+      </c>
+      <c r="F464" t="s">
+        <v>8</v>
+      </c>
+      <c r="G464" t="s">
+        <v>18</v>
+      </c>
+      <c r="H464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A465" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B465" t="s">
+        <v>985</v>
+      </c>
+      <c r="C465" t="s">
+        <v>986</v>
+      </c>
+      <c r="D465" t="s">
+        <v>12</v>
+      </c>
+      <c r="E465" t="s">
+        <v>36</v>
+      </c>
+      <c r="F465" t="s">
+        <v>8</v>
+      </c>
+      <c r="G465" t="s">
+        <v>18</v>
+      </c>
+      <c r="H465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A466" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B466" t="s">
+        <v>987</v>
+      </c>
+      <c r="C466" t="s">
+        <v>988</v>
+      </c>
+      <c r="D466" t="s">
+        <v>12</v>
+      </c>
+      <c r="E466" t="s">
+        <v>36</v>
+      </c>
+      <c r="F466" t="s">
+        <v>384</v>
+      </c>
+      <c r="G466" t="s">
+        <v>18</v>
+      </c>
+      <c r="H466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A467" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B467" t="s">
+        <v>989</v>
+      </c>
+      <c r="C467" t="s">
+        <v>990</v>
+      </c>
+      <c r="D467" t="s">
+        <v>12</v>
+      </c>
+      <c r="E467" t="s">
+        <v>36</v>
+      </c>
+      <c r="F467" t="s">
+        <v>8</v>
+      </c>
+      <c r="G467" t="s">
+        <v>18</v>
+      </c>
+      <c r="H467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A468" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B468" t="s">
+        <v>991</v>
+      </c>
+      <c r="C468" t="s">
+        <v>992</v>
+      </c>
+      <c r="D468" t="s">
+        <v>11</v>
+      </c>
+      <c r="E468" t="s">
+        <v>36</v>
+      </c>
+      <c r="F468" t="s">
+        <v>8</v>
+      </c>
+      <c r="G468" t="s">
+        <v>18</v>
+      </c>
+      <c r="H468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A469" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B469" t="s">
+        <v>993</v>
+      </c>
+      <c r="C469" t="s">
+        <v>994</v>
+      </c>
+      <c r="D469" t="s">
+        <v>24</v>
+      </c>
+      <c r="E469" t="s">
+        <v>38</v>
+      </c>
+      <c r="F469" t="s">
+        <v>7</v>
+      </c>
+      <c r="G469" t="s">
+        <v>18</v>
+      </c>
+      <c r="H469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A470" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B470" t="s">
+        <v>995</v>
+      </c>
+      <c r="C470" t="s">
+        <v>996</v>
+      </c>
+      <c r="D470" t="s">
+        <v>30</v>
+      </c>
+      <c r="E470" t="s">
+        <v>38</v>
+      </c>
+      <c r="F470" t="s">
+        <v>7</v>
+      </c>
+      <c r="G470" t="s">
+        <v>20</v>
+      </c>
+      <c r="H470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A471" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B471" t="s">
+        <v>997</v>
+      </c>
+      <c r="C471" t="s">
+        <v>998</v>
+      </c>
+      <c r="D471" t="s">
+        <v>11</v>
+      </c>
+      <c r="E471" t="s">
+        <v>36</v>
+      </c>
+      <c r="F471" t="s">
+        <v>8</v>
+      </c>
+      <c r="G471" t="s">
+        <v>18</v>
+      </c>
+      <c r="H471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A472" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B472" t="s">
+        <v>999</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D472" t="s">
+        <v>9</v>
+      </c>
+      <c r="E472" t="s">
+        <v>38</v>
+      </c>
+      <c r="F472" t="s">
+        <v>7</v>
+      </c>
+      <c r="G472" t="s">
+        <v>18</v>
+      </c>
+      <c r="H472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A473" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C473" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D473" t="s">
+        <v>28</v>
+      </c>
+      <c r="E473" t="s">
+        <v>36</v>
+      </c>
+      <c r="F473" t="s">
+        <v>8</v>
+      </c>
+      <c r="G473" t="s">
+        <v>18</v>
+      </c>
+      <c r="H473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A474" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D474" t="s">
+        <v>22</v>
+      </c>
+      <c r="E474" t="s">
+        <v>38</v>
+      </c>
+      <c r="F474" t="s">
+        <v>8</v>
+      </c>
+      <c r="G474" t="s">
+        <v>18</v>
+      </c>
+      <c r="H474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A475" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B475" t="s">
+        <v>760</v>
+      </c>
+      <c r="C475" t="s">
+        <v>761</v>
+      </c>
+      <c r="D475" t="s">
+        <v>30</v>
+      </c>
+      <c r="E475" t="s">
+        <v>38</v>
+      </c>
+      <c r="F475" t="s">
+        <v>7</v>
+      </c>
+      <c r="G475" t="s">
+        <v>20</v>
+      </c>
+      <c r="H475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A476" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D476" t="s">
+        <v>261</v>
+      </c>
+      <c r="E476" t="s">
+        <v>36</v>
+      </c>
+      <c r="F476" t="s">
+        <v>7</v>
+      </c>
+      <c r="G476" t="s">
+        <v>18</v>
+      </c>
+      <c r="H476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A477" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D477" t="s">
+        <v>9</v>
+      </c>
+      <c r="E477" t="s">
+        <v>38</v>
+      </c>
+      <c r="F477" t="s">
+        <v>7</v>
+      </c>
+      <c r="G477" t="s">
+        <v>18</v>
+      </c>
+      <c r="H477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A478" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D478" t="s">
+        <v>23</v>
+      </c>
+      <c r="E478" t="s">
+        <v>36</v>
+      </c>
+      <c r="F478" t="s">
+        <v>8</v>
+      </c>
+      <c r="G478" t="s">
+        <v>18</v>
+      </c>
+      <c r="H478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A479" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D479" t="s">
+        <v>30</v>
+      </c>
+      <c r="E479" t="s">
+        <v>38</v>
+      </c>
+      <c r="F479" t="s">
+        <v>7</v>
+      </c>
+      <c r="G479" t="s">
+        <v>18</v>
+      </c>
+      <c r="H479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A480" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D480" t="s">
+        <v>11</v>
+      </c>
+      <c r="E480" t="s">
+        <v>36</v>
+      </c>
+      <c r="F480" t="s">
+        <v>8</v>
+      </c>
+      <c r="G480" t="s">
+        <v>18</v>
+      </c>
+      <c r="H480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A481" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D481" t="s">
+        <v>6</v>
+      </c>
+      <c r="E481" t="s">
+        <v>36</v>
+      </c>
+      <c r="F481" t="s">
+        <v>8</v>
+      </c>
+      <c r="G481" t="s">
+        <v>18</v>
+      </c>
+      <c r="H481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A482" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D482" t="s">
+        <v>16</v>
+      </c>
+      <c r="E482" t="s">
+        <v>36</v>
+      </c>
+      <c r="F482" t="s">
+        <v>8</v>
+      </c>
+      <c r="G482" t="s">
+        <v>18</v>
+      </c>
+      <c r="H482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A483" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D483" t="s">
+        <v>16</v>
+      </c>
+      <c r="E483" t="s">
+        <v>36</v>
+      </c>
+      <c r="F483" t="s">
+        <v>8</v>
+      </c>
+      <c r="G483" t="s">
+        <v>21</v>
+      </c>
+      <c r="H483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A484" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D484" t="s">
+        <v>9</v>
+      </c>
+      <c r="E484" t="s">
+        <v>38</v>
+      </c>
+      <c r="F484" t="s">
+        <v>7</v>
+      </c>
+      <c r="G484" t="s">
+        <v>20</v>
+      </c>
+      <c r="H484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A485" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D485" t="s">
+        <v>23</v>
+      </c>
+      <c r="E485" t="s">
+        <v>36</v>
+      </c>
+      <c r="F485" t="s">
+        <v>8</v>
+      </c>
+      <c r="G485" t="s">
+        <v>518</v>
+      </c>
+      <c r="H485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A486" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D486" t="s">
+        <v>16</v>
+      </c>
+      <c r="E486" t="s">
+        <v>36</v>
+      </c>
+      <c r="F486" t="s">
+        <v>8</v>
+      </c>
+      <c r="G486" t="s">
+        <v>21</v>
+      </c>
+      <c r="H486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A487" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D487" t="s">
+        <v>23</v>
+      </c>
+      <c r="E487" t="s">
+        <v>36</v>
+      </c>
+      <c r="F487" t="s">
+        <v>8</v>
+      </c>
+      <c r="G487" t="s">
+        <v>18</v>
+      </c>
+      <c r="H487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A488" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D488" t="s">
+        <v>28</v>
+      </c>
+      <c r="E488" t="s">
+        <v>36</v>
+      </c>
+      <c r="F488" t="s">
+        <v>8</v>
+      </c>
+      <c r="G488" t="s">
+        <v>18</v>
+      </c>
+      <c r="H488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A489" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C489" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D489" t="s">
+        <v>39</v>
+      </c>
+      <c r="E489" t="s">
+        <v>38</v>
+      </c>
+      <c r="F489" t="s">
+        <v>7</v>
+      </c>
+      <c r="G489" t="s">
+        <v>18</v>
+      </c>
+      <c r="H489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A490" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D490" t="s">
+        <v>16</v>
+      </c>
+      <c r="E490" t="s">
+        <v>36</v>
+      </c>
+      <c r="F490" t="s">
+        <v>8</v>
+      </c>
+      <c r="G490" t="s">
+        <v>18</v>
+      </c>
+      <c r="H490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A491" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D491" t="s">
+        <v>6</v>
+      </c>
+      <c r="E491" t="s">
+        <v>36</v>
+      </c>
+      <c r="F491" t="s">
+        <v>8</v>
+      </c>
+      <c r="G491" t="s">
+        <v>18</v>
+      </c>
+      <c r="H491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A492" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D492" t="s">
+        <v>22</v>
+      </c>
+      <c r="E492" t="s">
+        <v>38</v>
+      </c>
+      <c r="F492" t="s">
+        <v>8</v>
+      </c>
+      <c r="G492" t="s">
+        <v>20</v>
+      </c>
+      <c r="H492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A493" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C493" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D493" t="s">
+        <v>28</v>
+      </c>
+      <c r="E493" t="s">
+        <v>36</v>
+      </c>
+      <c r="F493" t="s">
+        <v>8</v>
+      </c>
+      <c r="G493" t="s">
+        <v>18</v>
+      </c>
+      <c r="H493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A494" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D494" t="s">
+        <v>23</v>
+      </c>
+      <c r="E494" t="s">
+        <v>36</v>
+      </c>
+      <c r="F494" t="s">
+        <v>8</v>
+      </c>
+      <c r="G494" t="s">
+        <v>21</v>
+      </c>
+      <c r="H494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A495" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D495" t="s">
+        <v>16</v>
+      </c>
+      <c r="E495" t="s">
+        <v>36</v>
+      </c>
+      <c r="F495" t="s">
+        <v>8</v>
+      </c>
+      <c r="G495" t="s">
+        <v>18</v>
+      </c>
+      <c r="H495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A496" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C496" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D496" t="s">
+        <v>9</v>
+      </c>
+      <c r="E496" t="s">
+        <v>38</v>
+      </c>
+      <c r="F496" t="s">
+        <v>7</v>
+      </c>
+      <c r="G496" t="s">
+        <v>18</v>
+      </c>
+      <c r="H496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A497" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D497" t="s">
+        <v>24</v>
+      </c>
+      <c r="E497" t="s">
+        <v>38</v>
+      </c>
+      <c r="F497" t="s">
+        <v>7</v>
+      </c>
+      <c r="G497" t="s">
+        <v>20</v>
+      </c>
+      <c r="H497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D498" t="s">
+        <v>12</v>
+      </c>
+      <c r="E498" t="s">
+        <v>36</v>
+      </c>
+      <c r="F498" t="s">
+        <v>8</v>
+      </c>
+      <c r="G498" t="s">
+        <v>518</v>
+      </c>
+      <c r="H498" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D499" t="s">
+        <v>9</v>
+      </c>
+      <c r="E499" t="s">
+        <v>38</v>
+      </c>
+      <c r="F499" t="s">
+        <v>7</v>
+      </c>
+      <c r="G499" t="s">
+        <v>18</v>
+      </c>
+      <c r="H499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D500" t="s">
+        <v>9</v>
+      </c>
+      <c r="E500" t="s">
+        <v>38</v>
+      </c>
+      <c r="F500" t="s">
+        <v>866</v>
+      </c>
+      <c r="G500" t="s">
+        <v>18</v>
+      </c>
+      <c r="H500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D501" t="s">
+        <v>14</v>
+      </c>
+      <c r="E501" t="s">
+        <v>36</v>
+      </c>
+      <c r="F501" t="s">
+        <v>8</v>
+      </c>
+      <c r="G501" t="s">
+        <v>20</v>
+      </c>
+      <c r="H501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D502" t="s">
+        <v>14</v>
+      </c>
+      <c r="E502" t="s">
+        <v>36</v>
+      </c>
+      <c r="F502" t="s">
+        <v>8</v>
+      </c>
+      <c r="G502" t="s">
+        <v>18</v>
+      </c>
+      <c r="H502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D503" t="s">
+        <v>11</v>
+      </c>
+      <c r="E503" t="s">
+        <v>36</v>
+      </c>
+      <c r="F503" t="s">
+        <v>8</v>
+      </c>
+      <c r="G503" t="s">
+        <v>18</v>
+      </c>
+      <c r="H503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D504" t="s">
+        <v>14</v>
+      </c>
+      <c r="E504" t="s">
+        <v>36</v>
+      </c>
+      <c r="F504" t="s">
+        <v>8</v>
+      </c>
+      <c r="G504" t="s">
+        <v>21</v>
+      </c>
+      <c r="H504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D505" t="s">
         <v>19</v>
       </c>
-      <c r="E457" t="s">
-        <v>36</v>
-      </c>
-      <c r="F457" t="s">
-        <v>8</v>
-      </c>
-      <c r="G457" t="s">
+      <c r="E505" t="s">
+        <v>36</v>
+      </c>
+      <c r="F505" t="s">
+        <v>8</v>
+      </c>
+      <c r="G505" t="s">
+        <v>18</v>
+      </c>
+      <c r="H505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D506" t="s">
+        <v>14</v>
+      </c>
+      <c r="E506" t="s">
+        <v>36</v>
+      </c>
+      <c r="F506" t="s">
+        <v>7</v>
+      </c>
+      <c r="G506" t="s">
+        <v>18</v>
+      </c>
+      <c r="H506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D507" t="s">
+        <v>11</v>
+      </c>
+      <c r="E507" t="s">
+        <v>36</v>
+      </c>
+      <c r="F507" t="s">
+        <v>8</v>
+      </c>
+      <c r="G507" t="s">
+        <v>18</v>
+      </c>
+      <c r="H507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D508" t="s">
+        <v>6</v>
+      </c>
+      <c r="E508" t="s">
+        <v>36</v>
+      </c>
+      <c r="F508" t="s">
+        <v>8</v>
+      </c>
+      <c r="G508" t="s">
+        <v>18</v>
+      </c>
+      <c r="H508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D509" t="s">
+        <v>15</v>
+      </c>
+      <c r="E509" t="s">
+        <v>36</v>
+      </c>
+      <c r="F509" t="s">
+        <v>8</v>
+      </c>
+      <c r="G509" t="s">
+        <v>18</v>
+      </c>
+      <c r="H509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D510" t="s">
+        <v>30</v>
+      </c>
+      <c r="E510" t="s">
+        <v>38</v>
+      </c>
+      <c r="F510" t="s">
+        <v>7</v>
+      </c>
+      <c r="G510" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D511" t="s">
+        <v>28</v>
+      </c>
+      <c r="E511" t="s">
+        <v>36</v>
+      </c>
+      <c r="F511" t="s">
+        <v>8</v>
+      </c>
+      <c r="G511" t="s">
+        <v>18</v>
+      </c>
+      <c r="H511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D512" t="s">
+        <v>16</v>
+      </c>
+      <c r="E512" t="s">
+        <v>36</v>
+      </c>
+      <c r="F512" t="s">
+        <v>8</v>
+      </c>
+      <c r="G512" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A458" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B458" t="s">
-        <v>968</v>
-      </c>
-      <c r="C458" t="s">
-        <v>969</v>
-      </c>
-      <c r="D458" t="s">
+      <c r="H512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D513" t="s">
+        <v>23</v>
+      </c>
+      <c r="E513" t="s">
+        <v>36</v>
+      </c>
+      <c r="F513" t="s">
+        <v>8</v>
+      </c>
+      <c r="G513" t="s">
+        <v>18</v>
+      </c>
+      <c r="H513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D514" t="s">
+        <v>6</v>
+      </c>
+      <c r="E514" t="s">
+        <v>36</v>
+      </c>
+      <c r="F514" t="s">
+        <v>8</v>
+      </c>
+      <c r="G514" t="s">
+        <v>18</v>
+      </c>
+      <c r="H514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D515" t="s">
+        <v>11</v>
+      </c>
+      <c r="E515" t="s">
+        <v>36</v>
+      </c>
+      <c r="F515" t="s">
+        <v>8</v>
+      </c>
+      <c r="G515" t="s">
+        <v>21</v>
+      </c>
+      <c r="H515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C516" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D516" t="s">
+        <v>28</v>
+      </c>
+      <c r="E516" t="s">
+        <v>36</v>
+      </c>
+      <c r="F516" t="s">
+        <v>8</v>
+      </c>
+      <c r="G516" t="s">
+        <v>18</v>
+      </c>
+      <c r="H516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C517" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D517" t="s">
+        <v>25</v>
+      </c>
+      <c r="E517" t="s">
+        <v>38</v>
+      </c>
+      <c r="F517" t="s">
+        <v>7</v>
+      </c>
+      <c r="G517" t="s">
+        <v>18</v>
+      </c>
+      <c r="H517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A518" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D518" t="s">
+        <v>19</v>
+      </c>
+      <c r="E518" t="s">
+        <v>36</v>
+      </c>
+      <c r="F518" t="s">
+        <v>8</v>
+      </c>
+      <c r="G518" t="s">
+        <v>18</v>
+      </c>
+      <c r="H518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A519" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D519" t="s">
+        <v>16</v>
+      </c>
+      <c r="E519" t="s">
+        <v>36</v>
+      </c>
+      <c r="F519" t="s">
+        <v>8</v>
+      </c>
+      <c r="G519" t="s">
+        <v>18</v>
+      </c>
+      <c r="H519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A520" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D520" t="s">
+        <v>15</v>
+      </c>
+      <c r="E520" t="s">
+        <v>36</v>
+      </c>
+      <c r="F520" t="s">
+        <v>8</v>
+      </c>
+      <c r="G520" t="s">
+        <v>18</v>
+      </c>
+      <c r="H520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A521" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D521" t="s">
         <v>14</v>
       </c>
-      <c r="E458" t="s">
-        <v>36</v>
-      </c>
-      <c r="F458" t="s">
-        <v>8</v>
-      </c>
-      <c r="G458" t="s">
+      <c r="E521" t="s">
+        <v>36</v>
+      </c>
+      <c r="F521" t="s">
+        <v>8</v>
+      </c>
+      <c r="G521" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A459" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B459" t="s">
-        <v>970</v>
-      </c>
-      <c r="C459" t="s">
-        <v>971</v>
-      </c>
-      <c r="D459" t="s">
+      <c r="H521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A522" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D522" t="s">
+        <v>23</v>
+      </c>
+      <c r="E522" t="s">
+        <v>36</v>
+      </c>
+      <c r="F522" t="s">
+        <v>8</v>
+      </c>
+      <c r="G522" t="s">
+        <v>21</v>
+      </c>
+      <c r="H522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A523" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C523" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D523" t="s">
+        <v>14</v>
+      </c>
+      <c r="E523" t="s">
+        <v>36</v>
+      </c>
+      <c r="F523" t="s">
+        <v>8</v>
+      </c>
+      <c r="G523" t="s">
+        <v>18</v>
+      </c>
+      <c r="H523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A524" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D524" t="s">
+        <v>15</v>
+      </c>
+      <c r="E524" t="s">
+        <v>36</v>
+      </c>
+      <c r="F524" t="s">
+        <v>8</v>
+      </c>
+      <c r="G524" t="s">
+        <v>21</v>
+      </c>
+      <c r="H524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A525" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D525" t="s">
+        <v>6</v>
+      </c>
+      <c r="E525" t="s">
+        <v>36</v>
+      </c>
+      <c r="F525" t="s">
+        <v>8</v>
+      </c>
+      <c r="G525" t="s">
+        <v>18</v>
+      </c>
+      <c r="H525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A526" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D526" t="s">
+        <v>12</v>
+      </c>
+      <c r="E526" t="s">
+        <v>36</v>
+      </c>
+      <c r="F526" t="s">
+        <v>8</v>
+      </c>
+      <c r="G526" t="s">
+        <v>18</v>
+      </c>
+      <c r="H526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A527" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D527" t="s">
+        <v>14</v>
+      </c>
+      <c r="E527" t="s">
+        <v>36</v>
+      </c>
+      <c r="F527" t="s">
+        <v>8</v>
+      </c>
+      <c r="G527" t="s">
+        <v>18</v>
+      </c>
+      <c r="H527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A528" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D528" t="s">
+        <v>11</v>
+      </c>
+      <c r="E528" t="s">
+        <v>36</v>
+      </c>
+      <c r="F528" t="s">
+        <v>8</v>
+      </c>
+      <c r="G528" t="s">
+        <v>18</v>
+      </c>
+      <c r="H528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A529" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D529" t="s">
+        <v>14</v>
+      </c>
+      <c r="E529" t="s">
+        <v>36</v>
+      </c>
+      <c r="F529" t="s">
+        <v>8</v>
+      </c>
+      <c r="G529" t="s">
+        <v>18</v>
+      </c>
+      <c r="H529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A530" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D530" t="s">
+        <v>14</v>
+      </c>
+      <c r="E530" t="s">
+        <v>36</v>
+      </c>
+      <c r="F530" t="s">
+        <v>8</v>
+      </c>
+      <c r="G530" t="s">
+        <v>20</v>
+      </c>
+      <c r="H530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A531" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D531" t="s">
+        <v>19</v>
+      </c>
+      <c r="E531" t="s">
+        <v>36</v>
+      </c>
+      <c r="F531" t="s">
+        <v>8</v>
+      </c>
+      <c r="G531" t="s">
+        <v>18</v>
+      </c>
+      <c r="H531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A532" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D532" t="s">
+        <v>9</v>
+      </c>
+      <c r="E532" t="s">
+        <v>38</v>
+      </c>
+      <c r="F532" t="s">
+        <v>7</v>
+      </c>
+      <c r="G532" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A533" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C533" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D533" t="s">
+        <v>16</v>
+      </c>
+      <c r="E533" t="s">
+        <v>36</v>
+      </c>
+      <c r="F533" t="s">
+        <v>8</v>
+      </c>
+      <c r="G533" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A534" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D534" t="s">
+        <v>16</v>
+      </c>
+      <c r="E534" t="s">
+        <v>36</v>
+      </c>
+      <c r="F534" t="s">
+        <v>8</v>
+      </c>
+      <c r="G534" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A535" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C535" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D535" t="s">
+        <v>11</v>
+      </c>
+      <c r="E535" t="s">
+        <v>36</v>
+      </c>
+      <c r="F535" t="s">
+        <v>8</v>
+      </c>
+      <c r="G535" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A536" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C536" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D536" t="s">
+        <v>23</v>
+      </c>
+      <c r="E536" t="s">
+        <v>36</v>
+      </c>
+      <c r="F536" t="s">
+        <v>8</v>
+      </c>
+      <c r="G536" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A537" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D537" t="s">
+        <v>24</v>
+      </c>
+      <c r="E537" t="s">
+        <v>38</v>
+      </c>
+      <c r="F537" t="s">
+        <v>7</v>
+      </c>
+      <c r="G537" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A538" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D538" t="s">
+        <v>12</v>
+      </c>
+      <c r="E538" t="s">
+        <v>36</v>
+      </c>
+      <c r="F538" t="s">
+        <v>8</v>
+      </c>
+      <c r="G538" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A539" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D539" t="s">
+        <v>6</v>
+      </c>
+      <c r="E539" t="s">
+        <v>36</v>
+      </c>
+      <c r="F539" t="s">
+        <v>8</v>
+      </c>
+      <c r="G539" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A540" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D540" t="s">
+        <v>14</v>
+      </c>
+      <c r="E540" t="s">
+        <v>36</v>
+      </c>
+      <c r="F540" t="s">
+        <v>8</v>
+      </c>
+      <c r="G540" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A541" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C541" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D541" t="s">
+        <v>6</v>
+      </c>
+      <c r="E541" t="s">
+        <v>36</v>
+      </c>
+      <c r="F541" t="s">
+        <v>8</v>
+      </c>
+      <c r="G541" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A542" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D542" t="s">
+        <v>19</v>
+      </c>
+      <c r="E542" t="s">
+        <v>36</v>
+      </c>
+      <c r="F542" t="s">
+        <v>8</v>
+      </c>
+      <c r="G542" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A543" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D543" t="s">
+        <v>261</v>
+      </c>
+      <c r="E543" t="s">
+        <v>36</v>
+      </c>
+      <c r="F543" t="s">
+        <v>7</v>
+      </c>
+      <c r="G543" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A544" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C544" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D544" t="s">
+        <v>28</v>
+      </c>
+      <c r="E544" t="s">
+        <v>36</v>
+      </c>
+      <c r="F544" t="s">
+        <v>384</v>
+      </c>
+      <c r="G544" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A545" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D545" t="s">
+        <v>30</v>
+      </c>
+      <c r="E545" t="s">
+        <v>38</v>
+      </c>
+      <c r="F545" t="s">
+        <v>7</v>
+      </c>
+      <c r="G545" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A546" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C546" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D546" t="s">
+        <v>11</v>
+      </c>
+      <c r="E546" t="s">
+        <v>36</v>
+      </c>
+      <c r="F546" t="s">
+        <v>8</v>
+      </c>
+      <c r="G546" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A547" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D547" t="s">
+        <v>15</v>
+      </c>
+      <c r="E547" t="s">
+        <v>36</v>
+      </c>
+      <c r="F547" t="s">
+        <v>8</v>
+      </c>
+      <c r="G547" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A548" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C548" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D548" t="s">
+        <v>11</v>
+      </c>
+      <c r="E548" t="s">
+        <v>36</v>
+      </c>
+      <c r="F548" t="s">
+        <v>8</v>
+      </c>
+      <c r="G548" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A549" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C549" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D549" t="s">
+        <v>24</v>
+      </c>
+      <c r="E549" t="s">
+        <v>38</v>
+      </c>
+      <c r="F549" t="s">
+        <v>7</v>
+      </c>
+      <c r="G549" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A550" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C550" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D550" t="s">
+        <v>9</v>
+      </c>
+      <c r="E550" t="s">
+        <v>38</v>
+      </c>
+      <c r="F550" t="s">
+        <v>7</v>
+      </c>
+      <c r="G550" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A551" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C551" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D551" t="s">
+        <v>6</v>
+      </c>
+      <c r="E551" t="s">
+        <v>36</v>
+      </c>
+      <c r="F551" t="s">
+        <v>8</v>
+      </c>
+      <c r="G551" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A552" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D552" t="s">
+        <v>40</v>
+      </c>
+      <c r="E552" t="s">
+        <v>38</v>
+      </c>
+      <c r="F552" t="s">
+        <v>7</v>
+      </c>
+      <c r="G552" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A553" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D553" t="s">
+        <v>39</v>
+      </c>
+      <c r="E553" t="s">
+        <v>38</v>
+      </c>
+      <c r="F553" t="s">
+        <v>7</v>
+      </c>
+      <c r="G553" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A554" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C554" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D554" t="s">
+        <v>12</v>
+      </c>
+      <c r="E554" t="s">
+        <v>36</v>
+      </c>
+      <c r="F554" t="s">
+        <v>8</v>
+      </c>
+      <c r="G554" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A555" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D555" t="s">
+        <v>30</v>
+      </c>
+      <c r="E555" t="s">
+        <v>38</v>
+      </c>
+      <c r="F555" t="s">
+        <v>7</v>
+      </c>
+      <c r="G555" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A556" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D556" t="s">
+        <v>11</v>
+      </c>
+      <c r="E556" t="s">
+        <v>36</v>
+      </c>
+      <c r="F556" t="s">
+        <v>8</v>
+      </c>
+      <c r="G556" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A557" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C557" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D557" t="s">
+        <v>6</v>
+      </c>
+      <c r="E557" t="s">
+        <v>36</v>
+      </c>
+      <c r="F557" t="s">
+        <v>8</v>
+      </c>
+      <c r="G557" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A558" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C558" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D558" t="s">
+        <v>23</v>
+      </c>
+      <c r="E558" t="s">
+        <v>36</v>
+      </c>
+      <c r="F558" t="s">
+        <v>8</v>
+      </c>
+      <c r="G558" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A559" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D559" t="s">
+        <v>22</v>
+      </c>
+      <c r="E559" t="s">
+        <v>38</v>
+      </c>
+      <c r="F559" t="s">
+        <v>8</v>
+      </c>
+      <c r="G559" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A560" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D560" t="s">
+        <v>16</v>
+      </c>
+      <c r="E560" t="s">
+        <v>36</v>
+      </c>
+      <c r="F560" t="s">
+        <v>8</v>
+      </c>
+      <c r="G560" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A561" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D561" t="s">
+        <v>12</v>
+      </c>
+      <c r="E561" t="s">
+        <v>36</v>
+      </c>
+      <c r="F561" t="s">
+        <v>8</v>
+      </c>
+      <c r="G561" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A562" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D562" t="s">
+        <v>6</v>
+      </c>
+      <c r="E562" t="s">
+        <v>36</v>
+      </c>
+      <c r="F562" t="s">
+        <v>8</v>
+      </c>
+      <c r="G562" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A563" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C563" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D563" t="s">
+        <v>40</v>
+      </c>
+      <c r="E563" t="s">
+        <v>38</v>
+      </c>
+      <c r="F563" t="s">
+        <v>7</v>
+      </c>
+      <c r="G563" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A564" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D564" t="s">
+        <v>28</v>
+      </c>
+      <c r="E564" t="s">
+        <v>36</v>
+      </c>
+      <c r="F564" t="s">
+        <v>8</v>
+      </c>
+      <c r="G564" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A565" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C565" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D565" t="s">
+        <v>39</v>
+      </c>
+      <c r="E565" t="s">
+        <v>38</v>
+      </c>
+      <c r="F565" t="s">
+        <v>7</v>
+      </c>
+      <c r="G565" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A566" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C566" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D566" t="s">
+        <v>40</v>
+      </c>
+      <c r="E566" t="s">
+        <v>38</v>
+      </c>
+      <c r="F566" t="s">
+        <v>7</v>
+      </c>
+      <c r="G566" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A567" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D567" t="s">
+        <v>16</v>
+      </c>
+      <c r="E567" t="s">
+        <v>36</v>
+      </c>
+      <c r="F567" t="s">
+        <v>8</v>
+      </c>
+      <c r="G567" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A568" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D568" t="s">
+        <v>6</v>
+      </c>
+      <c r="E568" t="s">
+        <v>36</v>
+      </c>
+      <c r="F568" t="s">
+        <v>8</v>
+      </c>
+      <c r="G568" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A569" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C569" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D569" t="s">
+        <v>22</v>
+      </c>
+      <c r="E569" t="s">
+        <v>38</v>
+      </c>
+      <c r="F569" t="s">
+        <v>8</v>
+      </c>
+      <c r="G569" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A570" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C570" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D570" t="s">
+        <v>12</v>
+      </c>
+      <c r="E570" t="s">
+        <v>36</v>
+      </c>
+      <c r="F570" t="s">
+        <v>8</v>
+      </c>
+      <c r="G570" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A571" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C571" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D571" t="s">
+        <v>23</v>
+      </c>
+      <c r="E571" t="s">
+        <v>36</v>
+      </c>
+      <c r="F571" t="s">
+        <v>8</v>
+      </c>
+      <c r="G571" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A572" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C572" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D572" t="s">
+        <v>16</v>
+      </c>
+      <c r="E572" t="s">
+        <v>36</v>
+      </c>
+      <c r="F572" t="s">
+        <v>8</v>
+      </c>
+      <c r="G572" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A573" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C573" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D573" t="s">
+        <v>30</v>
+      </c>
+      <c r="E573" t="s">
+        <v>38</v>
+      </c>
+      <c r="F573" t="s">
+        <v>7</v>
+      </c>
+      <c r="G573" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A574" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C574" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D574" t="s">
+        <v>28</v>
+      </c>
+      <c r="E574" t="s">
+        <v>36</v>
+      </c>
+      <c r="F574" t="s">
+        <v>8</v>
+      </c>
+      <c r="G574" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A575" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C575" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D575" t="s">
+        <v>39</v>
+      </c>
+      <c r="E575" t="s">
+        <v>38</v>
+      </c>
+      <c r="F575" t="s">
+        <v>7</v>
+      </c>
+      <c r="G575" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A576" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C576" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D576" t="s">
+        <v>19</v>
+      </c>
+      <c r="E576" t="s">
+        <v>36</v>
+      </c>
+      <c r="F576" t="s">
+        <v>8</v>
+      </c>
+      <c r="G576" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A577" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C577" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D577" t="s">
+        <v>15</v>
+      </c>
+      <c r="E577" t="s">
+        <v>36</v>
+      </c>
+      <c r="F577" t="s">
+        <v>8</v>
+      </c>
+      <c r="G577" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A578" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C578" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D578" t="s">
+        <v>14</v>
+      </c>
+      <c r="E578" t="s">
+        <v>36</v>
+      </c>
+      <c r="F578" t="s">
+        <v>8</v>
+      </c>
+      <c r="G578" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A579" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C579" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D579" t="s">
+        <v>14</v>
+      </c>
+      <c r="E579" t="s">
+        <v>36</v>
+      </c>
+      <c r="F579" t="s">
+        <v>8</v>
+      </c>
+      <c r="G579" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A580" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C580" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D580" t="s">
+        <v>19</v>
+      </c>
+      <c r="E580" t="s">
+        <v>36</v>
+      </c>
+      <c r="F580" t="s">
+        <v>8</v>
+      </c>
+      <c r="G580" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A581" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C581" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D581" t="s">
+        <v>40</v>
+      </c>
+      <c r="E581" t="s">
+        <v>38</v>
+      </c>
+      <c r="F581" t="s">
+        <v>7</v>
+      </c>
+      <c r="G581" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A582" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C582" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D582" t="s">
+        <v>39</v>
+      </c>
+      <c r="E582" t="s">
+        <v>38</v>
+      </c>
+      <c r="F582" t="s">
+        <v>7</v>
+      </c>
+      <c r="G582" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A583" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C583" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D583" t="s">
+        <v>11</v>
+      </c>
+      <c r="E583" t="s">
+        <v>36</v>
+      </c>
+      <c r="F583" t="s">
+        <v>8</v>
+      </c>
+      <c r="G583" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A584" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C584" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D584" t="s">
+        <v>28</v>
+      </c>
+      <c r="E584" t="s">
+        <v>36</v>
+      </c>
+      <c r="F584" t="s">
+        <v>8</v>
+      </c>
+      <c r="G584" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A585" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C585" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D585" t="s">
+        <v>14</v>
+      </c>
+      <c r="E585" t="s">
+        <v>36</v>
+      </c>
+      <c r="F585" t="s">
+        <v>8</v>
+      </c>
+      <c r="G585" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A586" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C586" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D586" t="s">
+        <v>16</v>
+      </c>
+      <c r="E586" t="s">
+        <v>36</v>
+      </c>
+      <c r="F586" t="s">
+        <v>8</v>
+      </c>
+      <c r="G586" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A587" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C587" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D587" t="s">
+        <v>6</v>
+      </c>
+      <c r="E587" t="s">
+        <v>36</v>
+      </c>
+      <c r="F587" t="s">
+        <v>8</v>
+      </c>
+      <c r="G587" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A588" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C588" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D588" t="s">
+        <v>16</v>
+      </c>
+      <c r="E588" t="s">
+        <v>36</v>
+      </c>
+      <c r="F588" t="s">
+        <v>8</v>
+      </c>
+      <c r="G588" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A589" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C589" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D589" t="s">
+        <v>23</v>
+      </c>
+      <c r="E589" t="s">
+        <v>36</v>
+      </c>
+      <c r="F589" t="s">
+        <v>8</v>
+      </c>
+      <c r="G589" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A590" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C590" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D590" t="s">
+        <v>11</v>
+      </c>
+      <c r="E590" t="s">
+        <v>36</v>
+      </c>
+      <c r="F590" t="s">
+        <v>8</v>
+      </c>
+      <c r="G590" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A591" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B591" t="s">
+        <v>805</v>
+      </c>
+      <c r="C591" t="s">
+        <v>806</v>
+      </c>
+      <c r="D591" t="s">
+        <v>22</v>
+      </c>
+      <c r="E591" t="s">
+        <v>38</v>
+      </c>
+      <c r="F591" t="s">
+        <v>8</v>
+      </c>
+      <c r="G591" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A592" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C592" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D592" t="s">
+        <v>23</v>
+      </c>
+      <c r="E592" t="s">
+        <v>36</v>
+      </c>
+      <c r="F592" t="s">
+        <v>8</v>
+      </c>
+      <c r="G592" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A593" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C593" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D593" t="s">
+        <v>16</v>
+      </c>
+      <c r="E593" t="s">
+        <v>36</v>
+      </c>
+      <c r="F593" t="s">
+        <v>8</v>
+      </c>
+      <c r="G593" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A594" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C594" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D594" t="s">
+        <v>15</v>
+      </c>
+      <c r="E594" t="s">
+        <v>36</v>
+      </c>
+      <c r="F594" t="s">
+        <v>8</v>
+      </c>
+      <c r="G594" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A595" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C595" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D595" t="s">
+        <v>14</v>
+      </c>
+      <c r="E595" t="s">
+        <v>36</v>
+      </c>
+      <c r="F595" t="s">
+        <v>8</v>
+      </c>
+      <c r="G595" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A596" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C596" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D596" t="s">
         <v>25</v>
       </c>
-      <c r="E459" t="s">
+      <c r="E596" t="s">
         <v>38</v>
       </c>
-      <c r="F459" t="s">
-        <v>8</v>
-      </c>
-      <c r="G459" t="s">
+      <c r="F596" t="s">
+        <v>7</v>
+      </c>
+      <c r="G596" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A597" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C597" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D597" t="s">
+        <v>14</v>
+      </c>
+      <c r="E597" t="s">
+        <v>36</v>
+      </c>
+      <c r="F597" t="s">
+        <v>8</v>
+      </c>
+      <c r="G597" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A598" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D598" t="s">
+        <v>22</v>
+      </c>
+      <c r="E598" t="s">
+        <v>38</v>
+      </c>
+      <c r="F598" t="s">
+        <v>8</v>
+      </c>
+      <c r="G598" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A599" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D599" t="s">
+        <v>6</v>
+      </c>
+      <c r="E599" t="s">
+        <v>36</v>
+      </c>
+      <c r="F599" t="s">
+        <v>8</v>
+      </c>
+      <c r="G599" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A600" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C600" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D600" t="s">
+        <v>19</v>
+      </c>
+      <c r="E600" t="s">
+        <v>36</v>
+      </c>
+      <c r="F600" t="s">
+        <v>8</v>
+      </c>
+      <c r="G600" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A601" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C601" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D601" t="s">
+        <v>14</v>
+      </c>
+      <c r="E601" t="s">
+        <v>36</v>
+      </c>
+      <c r="F601" t="s">
+        <v>8</v>
+      </c>
+      <c r="G601" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A602" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D602" t="s">
+        <v>15</v>
+      </c>
+      <c r="E602" t="s">
+        <v>36</v>
+      </c>
+      <c r="F602" t="s">
+        <v>8</v>
+      </c>
+      <c r="G602" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A603" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D603" t="s">
+        <v>11</v>
+      </c>
+      <c r="E603" t="s">
+        <v>36</v>
+      </c>
+      <c r="F603" t="s">
+        <v>8</v>
+      </c>
+      <c r="G603" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A604" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D604" t="s">
+        <v>15</v>
+      </c>
+      <c r="E604" t="s">
+        <v>36</v>
+      </c>
+      <c r="F604" t="s">
+        <v>8</v>
+      </c>
+      <c r="G604" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A605" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C605" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D605" t="s">
+        <v>19</v>
+      </c>
+      <c r="E605" t="s">
+        <v>36</v>
+      </c>
+      <c r="F605" t="s">
+        <v>8</v>
+      </c>
+      <c r="G605" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A606" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C606" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D606" t="s">
+        <v>23</v>
+      </c>
+      <c r="E606" t="s">
+        <v>36</v>
+      </c>
+      <c r="F606" t="s">
+        <v>8</v>
+      </c>
+      <c r="G606" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A607" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D607" t="s">
+        <v>14</v>
+      </c>
+      <c r="E607" t="s">
+        <v>36</v>
+      </c>
+      <c r="F607" t="s">
+        <v>8</v>
+      </c>
+      <c r="G607" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A608" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D608" t="s">
+        <v>12</v>
+      </c>
+      <c r="E608" t="s">
+        <v>36</v>
+      </c>
+      <c r="F608" t="s">
+        <v>8</v>
+      </c>
+      <c r="G608" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A609" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D609" t="s">
+        <v>28</v>
+      </c>
+      <c r="E609" t="s">
+        <v>36</v>
+      </c>
+      <c r="F609" t="s">
+        <v>8</v>
+      </c>
+      <c r="G609" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A610" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D610" t="s">
+        <v>23</v>
+      </c>
+      <c r="E610" t="s">
+        <v>36</v>
+      </c>
+      <c r="F610" t="s">
+        <v>8</v>
+      </c>
+      <c r="G610" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A611" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C611" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D611" t="s">
+        <v>16</v>
+      </c>
+      <c r="E611" t="s">
+        <v>36</v>
+      </c>
+      <c r="F611" t="s">
+        <v>8</v>
+      </c>
+      <c r="G611" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A612" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C612" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D612" t="s">
+        <v>22</v>
+      </c>
+      <c r="E612" t="s">
+        <v>38</v>
+      </c>
+      <c r="F612" t="s">
+        <v>8</v>
+      </c>
+      <c r="G612" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A613" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C613" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D613" t="s">
+        <v>16</v>
+      </c>
+      <c r="E613" t="s">
+        <v>36</v>
+      </c>
+      <c r="F613" t="s">
+        <v>8</v>
+      </c>
+      <c r="G613" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A614" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D614" t="s">
+        <v>19</v>
+      </c>
+      <c r="E614" t="s">
+        <v>36</v>
+      </c>
+      <c r="F614" t="s">
+        <v>8</v>
+      </c>
+      <c r="G614" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A615" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D615" t="s">
+        <v>30</v>
+      </c>
+      <c r="E615" t="s">
+        <v>38</v>
+      </c>
+      <c r="F615" t="s">
+        <v>8</v>
+      </c>
+      <c r="G615" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A616" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C616" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D616" t="s">
+        <v>19</v>
+      </c>
+      <c r="E616" t="s">
+        <v>36</v>
+      </c>
+      <c r="F616" t="s">
+        <v>8</v>
+      </c>
+      <c r="G616" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A617" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C617" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D617" t="s">
+        <v>19</v>
+      </c>
+      <c r="E617" t="s">
+        <v>36</v>
+      </c>
+      <c r="F617" t="s">
+        <v>8</v>
+      </c>
+      <c r="G617" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A618" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C618" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D618" t="s">
+        <v>12</v>
+      </c>
+      <c r="E618" t="s">
+        <v>36</v>
+      </c>
+      <c r="F618" t="s">
+        <v>8</v>
+      </c>
+      <c r="G618" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A619" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D619" t="s">
+        <v>12</v>
+      </c>
+      <c r="E619" t="s">
+        <v>36</v>
+      </c>
+      <c r="F619" t="s">
+        <v>8</v>
+      </c>
+      <c r="G619" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A620" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C620" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D620" t="s">
+        <v>6</v>
+      </c>
+      <c r="E620" t="s">
+        <v>36</v>
+      </c>
+      <c r="F620" t="s">
+        <v>8</v>
+      </c>
+      <c r="G620" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A621" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D621" t="s">
+        <v>30</v>
+      </c>
+      <c r="E621" t="s">
+        <v>38</v>
+      </c>
+      <c r="F621" t="s">
+        <v>8</v>
+      </c>
+      <c r="G621" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A622" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D622" t="s">
+        <v>25</v>
+      </c>
+      <c r="E622" t="s">
+        <v>38</v>
+      </c>
+      <c r="F622" t="s">
+        <v>8</v>
+      </c>
+      <c r="G622" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A623" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D623" t="s">
+        <v>19</v>
+      </c>
+      <c r="E623" t="s">
+        <v>36</v>
+      </c>
+      <c r="F623" t="s">
+        <v>8</v>
+      </c>
+      <c r="G623" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A624" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D624" t="s">
+        <v>12</v>
+      </c>
+      <c r="E624" t="s">
+        <v>36</v>
+      </c>
+      <c r="F624" t="s">
+        <v>8</v>
+      </c>
+      <c r="G624" t="s">
         <v>20</v>
       </c>
     </row>
